--- a/docs/Backlog Proyecto Titulo.xlsx
+++ b/docs/Backlog Proyecto Titulo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1407" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="573">
   <si>
     <t>Etapa</t>
   </si>
@@ -59,9 +59,15 @@
     <t>Esfuerzo estimado (h)</t>
   </si>
   <si>
+    <t>Etapa 2</t>
+  </si>
+  <si>
     <t>Esfuerzo real (h)</t>
   </si>
   <si>
+    <t>Diseño técnico, arquitectura, protocolo e implementación inicial</t>
+  </si>
+  <si>
     <t>Criterios de aceptación / entregables</t>
   </si>
   <si>
@@ -71,15 +77,9 @@
     <t>EP-01</t>
   </si>
   <si>
-    <t>Etapa 2</t>
-  </si>
-  <si>
     <t>Épica</t>
   </si>
   <si>
-    <t>Diseño técnico, arquitectura, protocolo e implementación inicial</t>
-  </si>
-  <si>
     <t>Etapa 1: Definición, investigación y análisis de requerimientos</t>
   </si>
   <si>
@@ -89,15 +89,15 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Etapa 3</t>
+  </si>
+  <si>
+    <t>Implementación observabilidad, pruebas piloto y validación preliminar</t>
+  </si>
+  <si>
     <t>Problema, estado del arte, objetivos, requerimientos y alternativas definidos y respaldados.</t>
   </si>
   <si>
-    <t>Etapa 3</t>
-  </si>
-  <si>
-    <t>Implementación observabilidad, pruebas piloto y validación preliminar</t>
-  </si>
-  <si>
     <t>Realizado</t>
   </si>
   <si>
@@ -107,16 +107,31 @@
     <t>Historia</t>
   </si>
   <si>
+    <t>Investigación bibliográfica y estado del arte</t>
+  </si>
+  <si>
+    <t>OG, OE1, OE2, OE4</t>
+  </si>
+  <si>
     <t>Etapa 4</t>
   </si>
   <si>
     <t>Campaña definitiva, análisis, informe final y defensa</t>
   </si>
   <si>
-    <t>Investigación bibliográfica y estado del arte</t>
-  </si>
-  <si>
-    <t>OG, OE1, OE2, OE4</t>
+    <t>Conjunto de fuentes académicas y técnicas organizado en BibTeX y utilizado en el informe.</t>
+  </si>
+  <si>
+    <t>T-01.1</t>
+  </si>
+  <si>
+    <t>Tarea</t>
+  </si>
+  <si>
+    <t>Investigar comparaciones de distribuciones ligeras de Kubernetes</t>
+  </si>
+  <si>
+    <t>OE1, OE2</t>
   </si>
   <si>
     <t>Indicador</t>
@@ -128,27 +143,12 @@
     <t>Total de horas estimadas (tareas)</t>
   </si>
   <si>
-    <t>Conjunto de fuentes académicas y técnicas organizado en BibTeX y utilizado en el informe.</t>
+    <t>Fichas bibliográficas sobre K3s, MicroK8s y métricas de CPU, memoria, throughput y latencia.</t>
   </si>
   <si>
     <t>Total de horas reales (tareas)</t>
   </si>
   <si>
-    <t>T-01.1</t>
-  </si>
-  <si>
-    <t>Tarea</t>
-  </si>
-  <si>
-    <t>Investigar comparaciones de distribuciones ligeras de Kubernetes</t>
-  </si>
-  <si>
-    <t>OE1, OE2</t>
-  </si>
-  <si>
-    <t>Fichas bibliográficas sobre K3s, MicroK8s y métricas de CPU, memoria, throughput y latencia.</t>
-  </si>
-  <si>
     <t>T-01.2</t>
   </si>
   <si>
@@ -1010,63 +1010,63 @@
     <t>Aplicación idéntica desplegada y accesible mediante el mecanismo definido.</t>
   </si>
   <si>
+    <t>T-18.1</t>
+  </si>
+  <si>
+    <t>Desplegar aplicación de referencia en K3s y MicroK8s</t>
+  </si>
+  <si>
+    <t>Aplicación responde correctamente en ambos clústeres.</t>
+  </si>
+  <si>
+    <t>T-18.2</t>
+  </si>
+  <si>
+    <t>Configurar acceso a la aplicación y endpoints de prueba</t>
+  </si>
+  <si>
+    <t>Endpoints equivalentes y comprobados.</t>
+  </si>
+  <si>
+    <t>T-18.3</t>
+  </si>
+  <si>
+    <t>Desarrollar scripts k6 para escenarios de carga</t>
+  </si>
+  <si>
+    <t>Scripts parametrizados para idle, carga media y carga alta.</t>
+  </si>
+  <si>
+    <t>T-18.4</t>
+  </si>
+  <si>
+    <t>Configurar exportación y organización de resultados k6</t>
+  </si>
+  <si>
+    <t>Resultados guardados por escenario y repetición.</t>
+  </si>
+  <si>
+    <t>T-18.5</t>
+  </si>
+  <si>
+    <t>Habilitar Service LoadBalancer con kube-vip (192.168.100.150) en ambas distribuciones</t>
+  </si>
+  <si>
+    <t>Service de la aplicación de referencia con IP .150 accesible desde el host en K3s y MicroK8s.</t>
+  </si>
+  <si>
+    <t>HU-19</t>
+  </si>
+  <si>
+    <t>Implementación de pruebas de resiliencia</t>
+  </si>
+  <si>
+    <t>Fallo controlado y recuperación medibles sin pérdida intencional de quórum.</t>
+  </si>
+  <si>
     <t>Pendiente</t>
   </si>
   <si>
-    <t>T-18.1</t>
-  </si>
-  <si>
-    <t>Desplegar aplicación de referencia en K3s y MicroK8s</t>
-  </si>
-  <si>
-    <t>Aplicación responde correctamente en ambos clústeres.</t>
-  </si>
-  <si>
-    <t>T-18.2</t>
-  </si>
-  <si>
-    <t>Configurar acceso a la aplicación y endpoints de prueba</t>
-  </si>
-  <si>
-    <t>Endpoints equivalentes y comprobados.</t>
-  </si>
-  <si>
-    <t>T-18.3</t>
-  </si>
-  <si>
-    <t>Desarrollar scripts k6 para escenarios de carga</t>
-  </si>
-  <si>
-    <t>Scripts parametrizados para idle, carga media y carga alta.</t>
-  </si>
-  <si>
-    <t>T-18.4</t>
-  </si>
-  <si>
-    <t>Configurar exportación y organización de resultados k6</t>
-  </si>
-  <si>
-    <t>Resultados guardados por escenario y repetición.</t>
-  </si>
-  <si>
-    <t>T-18.5</t>
-  </si>
-  <si>
-    <t>Habilitar Service LoadBalancer con kube-vip (192.168.100.150) en ambas distribuciones</t>
-  </si>
-  <si>
-    <t>Service de la aplicación de referencia con IP .150 accesible desde el host en K3s y MicroK8s.</t>
-  </si>
-  <si>
-    <t>HU-19</t>
-  </si>
-  <si>
-    <t>Implementación de pruebas de resiliencia</t>
-  </si>
-  <si>
-    <t>Fallo controlado y recuperación medibles sin pérdida intencional de quórum.</t>
-  </si>
-  <si>
     <t>T-19.1</t>
   </si>
   <si>
@@ -1103,10 +1103,19 @@
     <t>Ubicación del pod definida; valores efectivos de detección y tolerancia registrados por distribución y diferencias documentadas.</t>
   </si>
   <si>
+    <t>T-19.5</t>
+  </si>
+  <si>
+    <t>Tratar el titular de la VIP y revalidar su migración con kube-vip v1.2.4</t>
+  </si>
+  <si>
+    <t>Estrategia sobre el titular de la VIP decidida y documentada; migración de la VIP revalidada con kube-vip v1.2.4 en ambas distribuciones.</t>
+  </si>
+  <si>
     <t>HU-32</t>
   </si>
   <si>
-    <t>Orquestación de ejecuciones experimentales</t>
+    <t>Implementar orquestador de ejecuciones con metadatos de ventana y ubicación</t>
   </si>
   <si>
     <t>Cada ejecución queda registrada con distribución, escenario, repetición y ventana temporal, y deja datos aptos para el análisis.</t>
@@ -1115,7 +1124,7 @@
     <t>T-32.1</t>
   </si>
   <si>
-    <t>Implementar orquestador de ejecuciones (metadatos de ventana, external_labels, snapshot de Prometheus y estabilización)</t>
+    <t>Implementar orquestador de ejecuciones (metadatos de ventana y de ubicación: nodo de la VIP del plano de control, nodo de la VIP del servicio y nodo del pod; etiqueta distribution; snapshot de Prometheus y estabilización)</t>
   </si>
   <si>
     <t>Script versionado que ejecuta una repetición completa y guarda metadatos, resultados de k6 y snapshot de Prometheus.</t>
@@ -1229,6 +1238,15 @@
     <t>Serie de tiempos de despliegue por distribución, cronometrada sin carga de k6.</t>
   </si>
   <si>
+    <t>T-20.7</t>
+  </si>
+  <si>
+    <t>Caracterizar reposo del host y fijar política de servicios</t>
+  </si>
+  <si>
+    <t>Consumo en reposo del host caracterizado con y sin sesión gráfica; política de servicios del host definida y documentada antes de T-20.1.</t>
+  </si>
+  <si>
     <t>HU-21</t>
   </si>
   <si>
@@ -1272,6 +1290,15 @@
   </si>
   <si>
     <t>Número de repeticiones por combinación confirmado o ajustado según la variabilidad observada en el piloto.</t>
+  </si>
+  <si>
+    <t>T-21.5</t>
+  </si>
+  <si>
+    <t>Aislar CPU de servicios del host y de QEMU (opcional)</t>
+  </si>
+  <si>
+    <t>Aislamiento de CPU aplicado y documentado, o descartado con justificación; efecto sobre la variabilidad registrado.</t>
   </si>
   <si>
     <t>HU-22</t>
@@ -1741,11 +1768,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1818,19 +1845,19 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1842,38 +1869,38 @@
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1888,19 +1915,19 @@
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1912,16 +1939,16 @@
     <xf borderId="1" fillId="0" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -2050,7 +2077,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J173" displayName="Backlog" name="Backlog" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J176" displayName="Backlog" name="Backlog" id="1">
   <tableColumns count="10">
     <tableColumn name="ID" id="1"/>
     <tableColumn name="Tipo" id="2"/>
@@ -2269,7 +2296,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="2" width="12.0"/>
-    <col customWidth="1" min="3" max="3" width="96.13"/>
+    <col customWidth="1" min="3" max="3" width="149.38"/>
     <col customWidth="1" min="4" max="4" width="21.5"/>
     <col customWidth="1" min="5" max="5" width="12.88"/>
     <col customWidth="1" min="6" max="6" width="20.88"/>
@@ -2278,32 +2305,32 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="H1" s="6" t="s">
         <v>16</v>
       </c>
+      <c r="H1" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="I1" s="10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J1" s="10" t="s">
         <v>0</v>
@@ -2311,10 +2338,10 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>22</v>
@@ -2325,16 +2352,16 @@
       <c r="E2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="15">
         <f t="shared" ref="F2:G2" si="1">F3+F8+F12+F16+F22</f>
         <v>74</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="15">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>28</v>
@@ -2351,24 +2378,24 @@
         <v>30</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="15">
         <f t="shared" ref="F3:G3" si="2">SUM(F4:F7)</f>
         <v>19</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="15">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>28</v>
@@ -2378,130 +2405,130 @@
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="21" t="s">
+      <c r="A4" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="G4" s="21">
+        <v>8.0</v>
+      </c>
+      <c r="H4" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="23">
-        <v>6.0</v>
-      </c>
-      <c r="G4" s="23">
-        <v>8.0</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="20" t="s">
+      <c r="J4" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="23">
+      <c r="D5" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="21">
         <v>5.0</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="21">
         <v>5.0</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="H5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="20" t="s">
+      <c r="J5" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="20" t="s">
+      <c r="B6" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="23">
+      <c r="E6" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="21">
         <v>5.0</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="21">
         <v>4.0</v>
       </c>
-      <c r="H6" s="20" t="s">
+      <c r="H6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="20" t="s">
+      <c r="J6" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="20" t="s">
+      <c r="B7" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="21">
         <v>3.0</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="21">
         <v>3.0</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="I7" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="20" t="s">
+      <c r="J7" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2521,11 +2548,11 @@
       <c r="E8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="15">
         <f t="shared" ref="F8:G8" si="3">SUM(F9:F11)</f>
         <v>12</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
@@ -2554,98 +2581,98 @@
       <c r="X8" s="24"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="20" t="s">
+      <c r="B9" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="23">
+      <c r="E9" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="21">
         <v>5.0</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="21">
         <v>5.0</v>
       </c>
-      <c r="H9" s="20" t="s">
+      <c r="H9" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="20" t="s">
+      <c r="J9" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="20" t="s">
+      <c r="B10" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="23">
+      <c r="E10" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="21">
         <v>3.0</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="21">
         <v>3.0</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="20" t="s">
+      <c r="B11" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="23">
+      <c r="E11" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="21">
         <v>4.0</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="21">
         <v>4.0</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="H11" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J11" s="20" t="s">
+      <c r="J11" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2665,11 +2692,11 @@
       <c r="E12" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="15">
         <f t="shared" ref="F12:G12" si="4">SUM(F13:F15)</f>
         <v>11</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="15">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
@@ -2698,98 +2725,98 @@
       <c r="X12" s="24"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="20" t="s">
+      <c r="B13" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="23">
+      <c r="E13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="21">
         <v>4.0</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="21">
         <v>4.0</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J13" s="20" t="s">
+      <c r="J13" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="20" t="s">
+      <c r="B14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="23">
+      <c r="E14" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="21">
         <v>3.0</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="21">
         <v>3.0</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="22" t="s">
+      <c r="I14" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J14" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="B15" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="23">
+      <c r="E15" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="21">
         <v>4.0</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="21">
         <v>4.0</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="22" t="s">
+      <c r="I15" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="20" t="s">
+      <c r="J15" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2809,11 +2836,11 @@
       <c r="E16" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="15">
         <f t="shared" ref="F16:G16" si="5">SUM(F17:F21)</f>
         <v>17</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
@@ -2842,162 +2869,162 @@
       <c r="X16" s="24"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="20" t="s">
+      <c r="B17" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="23">
+      <c r="E17" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="21">
         <v>3.0</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="21">
         <v>3.0</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="22" t="s">
+      <c r="I17" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="20" t="s">
+      <c r="J17" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="20" t="s">
+      <c r="B18" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E18" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="23">
+      <c r="E18" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="21">
         <v>3.0</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="21">
         <v>3.0</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="22" t="s">
+      <c r="I18" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J18" s="20" t="s">
+      <c r="J18" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="20" t="s">
+      <c r="B19" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="23">
+      <c r="E19" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="21">
         <v>4.0</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="21">
         <v>3.0</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="22" t="s">
+      <c r="I19" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="20" t="s">
+      <c r="J19" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="23">
+      <c r="E20" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="21">
         <v>5.0</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="21">
         <v>4.0</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="H20" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="22" t="s">
+      <c r="I20" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J20" s="20" t="s">
+      <c r="J20" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="20" t="s">
+      <c r="B21" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="23">
+      <c r="E21" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="21">
         <v>2.0</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="21">
         <v>2.0</v>
       </c>
-      <c r="H21" s="20" t="s">
+      <c r="H21" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="I21" s="22" t="s">
+      <c r="I21" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J21" s="20" t="s">
+      <c r="J21" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3012,16 +3039,16 @@
         <v>106</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="15">
         <f t="shared" ref="F22:G22" si="6">SUM(F23:F27)</f>
         <v>15</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
@@ -3050,162 +3077,162 @@
       <c r="X22" s="24"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="20" t="s">
+      <c r="B23" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="21">
         <v>3.0</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="21">
         <v>3.0</v>
       </c>
-      <c r="H23" s="20" t="s">
+      <c r="H23" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="22" t="s">
+      <c r="I23" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J23" s="20" t="s">
+      <c r="J23" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="20" t="s">
+      <c r="A24" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" s="20" t="s">
+      <c r="B24" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="23">
+      <c r="E24" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="21">
         <v>3.0</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="21">
         <v>3.0</v>
       </c>
-      <c r="H24" s="20" t="s">
+      <c r="H24" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="I24" s="22" t="s">
+      <c r="I24" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J24" s="20" t="s">
+      <c r="J24" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C25" s="20" t="s">
+      <c r="B25" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="23">
+      <c r="E25" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="21">
         <v>3.0</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="21">
         <v>3.0</v>
       </c>
-      <c r="H25" s="20" t="s">
+      <c r="H25" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="I25" s="22" t="s">
+      <c r="I25" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J25" s="20" t="s">
+      <c r="J25" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="20" t="s">
+      <c r="A26" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="23">
+      <c r="E26" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="21">
         <v>3.0</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="21">
         <v>3.0</v>
       </c>
-      <c r="H26" s="20" t="s">
+      <c r="H26" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I26" s="22" t="s">
+      <c r="I26" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J26" s="20" t="s">
+      <c r="J26" s="16" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="20" t="s">
+      <c r="B27" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="21">
         <v>3.0</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="20">
         <v>3.0</v>
       </c>
-      <c r="H27" s="20" t="s">
+      <c r="H27" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="I27" s="22" t="s">
+      <c r="I27" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J27" s="20" t="s">
+      <c r="J27" s="16" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3214,7 +3241,7 @@
         <v>124</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>125</v>
@@ -3225,11 +3252,11 @@
       <c r="E28" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="15">
         <f t="shared" ref="F28:G28" si="7">F29+F34+F40+F46</f>
         <v>40</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="15">
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
@@ -3240,7 +3267,7 @@
         <v>28</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
@@ -3273,11 +3300,11 @@
       <c r="E29" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F29" s="15">
         <f t="shared" ref="F29:G29" si="8">SUM(F30:F33)</f>
         <v>10</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
@@ -3288,7 +3315,7 @@
         <v>28</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
@@ -3306,131 +3333,131 @@
       <c r="X29" s="24"/>
     </row>
     <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="20" t="s">
+      <c r="B30" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="21" t="s">
+      <c r="D30" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="23">
+      <c r="E30" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="21">
         <v>2.0</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="21">
         <v>2.0</v>
       </c>
-      <c r="H30" s="20" t="s">
+      <c r="H30" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="I30" s="22" t="s">
+      <c r="I30" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="20" t="s">
-        <v>19</v>
+      <c r="J30" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="20" t="s">
+      <c r="A31" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="20" t="s">
+      <c r="B31" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E31" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="23">
+      <c r="E31" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="21">
         <v>3.0</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="21">
         <v>3.0</v>
       </c>
-      <c r="H31" s="20" t="s">
+      <c r="H31" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="I31" s="22" t="s">
+      <c r="I31" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J31" s="20" t="s">
-        <v>19</v>
+      <c r="J31" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="20" t="s">
+      <c r="A32" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="20" t="s">
+      <c r="B32" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="23">
+      <c r="E32" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="21">
         <v>3.0</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="21">
         <v>3.0</v>
       </c>
-      <c r="H32" s="20" t="s">
+      <c r="H32" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="I32" s="22" t="s">
+      <c r="I32" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J32" s="20" t="s">
-        <v>19</v>
+      <c r="J32" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="20" t="s">
+      <c r="B33" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="D33" s="21" t="s">
+      <c r="D33" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="21">
         <v>2.0</v>
       </c>
       <c r="G33" s="25">
         <v>2.0</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="H33" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="I33" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J33" s="20" t="s">
-        <v>19</v>
+      <c r="J33" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
@@ -3464,7 +3491,7 @@
         <v>28</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K34" s="24"/>
       <c r="L34" s="24"/>
@@ -3482,163 +3509,163 @@
       <c r="X34" s="24"/>
     </row>
     <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="B35" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C35" s="20" t="s">
+      <c r="B35" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="D35" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="23">
+      <c r="E35" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="21">
         <v>3.0</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="21">
         <v>2.0</v>
       </c>
-      <c r="H35" s="20" t="s">
+      <c r="H35" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="I35" s="22" t="s">
+      <c r="I35" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J35" s="20" t="s">
-        <v>19</v>
+      <c r="J35" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="20" t="s">
+      <c r="A36" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="20" t="s">
+      <c r="B36" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="23">
+      <c r="E36" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="21">
         <v>3.0</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="21">
         <v>2.0</v>
       </c>
-      <c r="H36" s="20" t="s">
+      <c r="H36" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="I36" s="22" t="s">
+      <c r="I36" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J36" s="20" t="s">
-        <v>19</v>
+      <c r="J36" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="20" t="s">
+      <c r="A37" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="23">
+      <c r="E37" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="21">
         <v>3.0</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="21">
         <v>2.0</v>
       </c>
-      <c r="H37" s="20" t="s">
+      <c r="H37" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="I37" s="22" t="s">
+      <c r="I37" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J37" s="20" t="s">
-        <v>19</v>
+      <c r="J37" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="20" t="s">
+      <c r="B38" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="23">
+      <c r="E38" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="21">
         <v>3.0</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="21">
         <v>2.0</v>
       </c>
-      <c r="H38" s="20" t="s">
+      <c r="H38" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="I38" s="22" t="s">
+      <c r="I38" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J38" s="20" t="s">
-        <v>19</v>
+      <c r="J38" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="20" t="s">
+      <c r="A39" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="20" t="s">
+      <c r="B39" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="23">
+      <c r="E39" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="21">
         <v>3.0</v>
       </c>
       <c r="G39" s="25">
         <v>2.0</v>
       </c>
-      <c r="H39" s="20" t="s">
+      <c r="H39" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="I39" s="22" t="s">
+      <c r="I39" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J39" s="20" t="s">
-        <v>19</v>
+      <c r="J39" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
@@ -3672,7 +3699,7 @@
         <v>28</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K40" s="24"/>
       <c r="L40" s="24"/>
@@ -3690,163 +3717,163 @@
       <c r="X40" s="24"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="20" t="s">
+      <c r="A41" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="20" t="s">
+      <c r="B41" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D41" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" s="23">
+      <c r="E41" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="21">
         <v>2.0</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="21">
         <v>2.0</v>
       </c>
-      <c r="H41" s="20" t="s">
+      <c r="H41" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="I41" s="22" t="s">
+      <c r="I41" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J41" s="20" t="s">
-        <v>19</v>
+      <c r="J41" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="20" t="s">
+      <c r="A42" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B42" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="20" t="s">
+      <c r="B42" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="23">
+      <c r="E42" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="21">
         <v>2.0</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="21">
         <v>1.0</v>
       </c>
-      <c r="H42" s="20" t="s">
+      <c r="H42" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="I42" s="22" t="s">
+      <c r="I42" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J42" s="20" t="s">
-        <v>19</v>
+      <c r="J42" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="20" t="s">
+      <c r="A43" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="B43" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="20" t="s">
+      <c r="B43" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E43" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F43" s="23">
+      <c r="E43" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="21">
         <v>2.0</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="21">
         <v>2.0</v>
       </c>
-      <c r="H43" s="20" t="s">
+      <c r="H43" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="I43" s="22" t="s">
+      <c r="I43" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J43" s="20" t="s">
-        <v>19</v>
+      <c r="J43" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="20" t="s">
+      <c r="A44" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="B44" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="20" t="s">
+      <c r="B44" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D44" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E44" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="23">
+      <c r="E44" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="21">
         <v>2.0</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="21">
         <v>2.0</v>
       </c>
-      <c r="H44" s="20" t="s">
+      <c r="H44" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="I44" s="22" t="s">
+      <c r="I44" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J44" s="20" t="s">
-        <v>19</v>
+      <c r="J44" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="20" t="s">
+      <c r="A45" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="20" t="s">
+      <c r="B45" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="E45" s="22" t="s">
+      <c r="E45" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="21">
         <v>1.0</v>
       </c>
       <c r="G45" s="25">
         <v>1.0</v>
       </c>
-      <c r="H45" s="20" t="s">
+      <c r="H45" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="I45" s="22" t="s">
+      <c r="I45" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J45" s="20" t="s">
-        <v>19</v>
+      <c r="J45" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
@@ -3880,7 +3907,7 @@
         <v>28</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K46" s="24"/>
       <c r="L46" s="24"/>
@@ -3898,99 +3925,99 @@
       <c r="X46" s="24"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B47" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="20" t="s">
+      <c r="B47" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D47" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E47" s="22" t="s">
+      <c r="D47" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E47" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="21">
         <v>2.0</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="21">
         <v>2.0</v>
       </c>
-      <c r="H47" s="20" t="s">
+      <c r="H47" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="I47" s="22" t="s">
+      <c r="I47" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J47" s="20" t="s">
-        <v>19</v>
+      <c r="J47" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="20" t="s">
+      <c r="B48" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="22" t="s">
+      <c r="E48" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="21">
         <v>1.0</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="21">
         <v>1.0</v>
       </c>
-      <c r="H48" s="20" t="s">
+      <c r="H48" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="I48" s="22" t="s">
+      <c r="I48" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J48" s="20" t="s">
-        <v>19</v>
+      <c r="J48" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="20" t="s">
+      <c r="A49" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B49" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="20" t="s">
+      <c r="B49" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="22" t="s">
+      <c r="E49" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F49" s="23">
+      <c r="F49" s="21">
         <v>3.0</v>
       </c>
       <c r="G49" s="25">
         <v>2.0</v>
       </c>
-      <c r="H49" s="20" t="s">
+      <c r="H49" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="I49" s="22" t="s">
+      <c r="I49" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J49" s="20" t="s">
-        <v>19</v>
+      <c r="J49" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
@@ -3998,7 +4025,7 @@
         <v>193</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>194</v>
@@ -4009,11 +4036,11 @@
       <c r="E50" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F50" s="14">
+      <c r="F50" s="15">
         <f t="shared" ref="F50:G50" si="12">F51</f>
         <v>2</v>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="15">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
@@ -4024,7 +4051,7 @@
         <v>28</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K50" s="24"/>
       <c r="L50" s="24"/>
@@ -4072,7 +4099,7 @@
         <v>28</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K51" s="24"/>
       <c r="L51" s="24"/>
@@ -4090,67 +4117,67 @@
       <c r="X51" s="24"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="20" t="s">
+      <c r="A52" s="16" t="s">
         <v>200</v>
       </c>
-      <c r="B52" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C52" s="20" t="s">
+      <c r="B52" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F52" s="23">
+      <c r="E52" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="21">
         <v>1.0</v>
       </c>
-      <c r="G52" s="23">
+      <c r="G52" s="21">
         <v>1.0</v>
       </c>
-      <c r="H52" s="20" t="s">
+      <c r="H52" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="I52" s="22" t="s">
+      <c r="I52" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J52" s="20" t="s">
-        <v>19</v>
+      <c r="J52" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="20" t="s">
+      <c r="A53" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="B53" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="20" t="s">
+      <c r="B53" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="16" t="s">
         <v>204</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="D53" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="E53" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F53" s="23">
+      <c r="E53" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" s="21">
         <v>1.0</v>
       </c>
       <c r="G53" s="25">
         <v>1.0</v>
       </c>
-      <c r="H53" s="20" t="s">
+      <c r="H53" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="I53" s="22" t="s">
+      <c r="I53" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J53" s="20" t="s">
-        <v>19</v>
+      <c r="J53" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -4158,7 +4185,7 @@
         <v>206</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>207</v>
@@ -4169,11 +4196,11 @@
       <c r="E54" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="14">
+      <c r="F54" s="15">
         <f t="shared" ref="F54:G54" si="14">F55+F61+F66+F71+F80</f>
         <v>32</v>
       </c>
-      <c r="G54" s="14">
+      <c r="G54" s="15">
         <f t="shared" si="14"/>
         <v>42</v>
       </c>
@@ -4184,7 +4211,7 @@
         <v>28</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K54" s="24"/>
       <c r="L54" s="24"/>
@@ -4232,7 +4259,7 @@
         <v>28</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K55" s="24"/>
       <c r="L55" s="24"/>
@@ -4250,163 +4277,163 @@
       <c r="X55" s="24"/>
     </row>
     <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="20" t="s">
+      <c r="A56" s="16" t="s">
         <v>212</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" s="20" t="s">
+      <c r="B56" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="D56" s="21" t="s">
+      <c r="D56" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E56" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F56" s="23">
+      <c r="E56" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="21">
         <v>1.0</v>
       </c>
-      <c r="G56" s="23">
+      <c r="G56" s="21">
         <v>1.0</v>
       </c>
-      <c r="H56" s="20" t="s">
+      <c r="H56" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="I56" s="22" t="s">
+      <c r="I56" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J56" s="20" t="s">
-        <v>19</v>
+      <c r="J56" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="20" t="s">
+      <c r="A57" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="B57" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C57" s="20" t="s">
+      <c r="B57" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="16" t="s">
         <v>216</v>
       </c>
-      <c r="D57" s="21" t="s">
+      <c r="D57" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E57" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F57" s="23">
+      <c r="E57" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" s="21">
         <v>1.0</v>
       </c>
-      <c r="G57" s="23">
+      <c r="G57" s="21">
         <v>1.0</v>
       </c>
-      <c r="H57" s="20" t="s">
+      <c r="H57" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="I57" s="22" t="s">
+      <c r="I57" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J57" s="20" t="s">
-        <v>19</v>
+      <c r="J57" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="20" t="s">
+      <c r="A58" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="B58" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C58" s="20" t="s">
+      <c r="B58" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="D58" s="21" t="s">
+      <c r="D58" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E58" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="23">
+      <c r="E58" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" s="21">
         <v>1.0</v>
       </c>
-      <c r="G58" s="23">
+      <c r="G58" s="21">
         <v>1.0</v>
       </c>
-      <c r="H58" s="20" t="s">
+      <c r="H58" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="I58" s="22" t="s">
+      <c r="I58" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J58" s="20" t="s">
-        <v>19</v>
+      <c r="J58" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="20" t="s">
+      <c r="A59" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="B59" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C59" s="20" t="s">
+      <c r="B59" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="D59" s="21" t="s">
+      <c r="D59" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E59" s="22" t="s">
+      <c r="E59" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="23">
+      <c r="F59" s="21">
         <v>1.0</v>
       </c>
       <c r="G59" s="25">
         <v>1.0</v>
       </c>
-      <c r="H59" s="20" t="s">
+      <c r="H59" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="I59" s="22" t="s">
+      <c r="I59" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J59" s="20" t="s">
-        <v>19</v>
+      <c r="J59" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="20" t="s">
+      <c r="A60" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="B60" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C60" s="20" t="s">
+      <c r="B60" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="D60" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E60" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" s="23">
+      <c r="D60" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="21">
         <v>1.0</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="21">
         <v>1.0</v>
       </c>
-      <c r="H60" s="20" t="s">
+      <c r="H60" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="I60" s="22" t="s">
+      <c r="I60" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J60" s="20" t="s">
-        <v>19</v>
+      <c r="J60" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
@@ -4440,7 +4467,7 @@
         <v>28</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K61" s="24"/>
       <c r="L61" s="24"/>
@@ -4458,131 +4485,131 @@
       <c r="X61" s="24"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="20" t="s">
+      <c r="A62" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="B62" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C62" s="20" t="s">
+      <c r="B62" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="D62" s="21" t="s">
+      <c r="D62" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" s="23">
+      <c r="E62" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="21">
         <v>2.0</v>
       </c>
-      <c r="G62" s="23">
+      <c r="G62" s="21">
         <v>2.0</v>
       </c>
-      <c r="H62" s="20" t="s">
+      <c r="H62" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="I62" s="22" t="s">
+      <c r="I62" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J62" s="20" t="s">
-        <v>19</v>
+      <c r="J62" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="B63" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C63" s="20" t="s">
+      <c r="B63" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="D63" s="21" t="s">
+      <c r="D63" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E63" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F63" s="23">
+      <c r="E63" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" s="21">
         <v>1.0</v>
       </c>
       <c r="G63" s="25">
         <v>1.0</v>
       </c>
-      <c r="H63" s="20" t="s">
+      <c r="H63" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="I63" s="22" t="s">
+      <c r="I63" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J63" s="20" t="s">
-        <v>19</v>
+      <c r="J63" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="16" t="s">
         <v>236</v>
       </c>
-      <c r="B64" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C64" s="20" t="s">
+      <c r="B64" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="D64" s="21" t="s">
+      <c r="D64" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F64" s="23">
+      <c r="E64" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" s="21">
         <v>2.0</v>
       </c>
-      <c r="G64" s="23">
+      <c r="G64" s="21">
         <v>2.0</v>
       </c>
-      <c r="H64" s="20" t="s">
+      <c r="H64" s="16" t="s">
         <v>238</v>
       </c>
-      <c r="I64" s="22" t="s">
+      <c r="I64" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J64" s="20" t="s">
-        <v>19</v>
+      <c r="J64" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" s="20" t="s">
+      <c r="A65" s="16" t="s">
         <v>239</v>
       </c>
-      <c r="B65" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C65" s="20" t="s">
+      <c r="B65" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="D65" s="21" t="s">
+      <c r="D65" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F65" s="23">
+      <c r="F65" s="21">
         <v>2.0</v>
       </c>
-      <c r="G65" s="23">
+      <c r="G65" s="21">
         <v>2.0</v>
       </c>
-      <c r="H65" s="20" t="s">
+      <c r="H65" s="16" t="s">
         <v>241</v>
       </c>
-      <c r="I65" s="22" t="s">
+      <c r="I65" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J65" s="20" t="s">
-        <v>19</v>
+      <c r="J65" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
@@ -4616,7 +4643,7 @@
         <v>28</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K66" s="24"/>
       <c r="L66" s="24"/>
@@ -4634,131 +4661,131 @@
       <c r="X66" s="24"/>
     </row>
     <row r="67" ht="22.5" customHeight="1">
-      <c r="A67" s="20" t="s">
+      <c r="A67" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="B67" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C67" s="20" t="s">
+      <c r="B67" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C67" s="16" t="s">
         <v>246</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E67" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" s="23">
+      <c r="E67" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="21">
         <v>2.0</v>
       </c>
       <c r="G67" s="25">
         <v>2.0</v>
       </c>
-      <c r="H67" s="20" t="s">
+      <c r="H67" s="16" t="s">
         <v>247</v>
       </c>
-      <c r="I67" s="22" t="s">
+      <c r="I67" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J67" s="20" t="s">
-        <v>19</v>
+      <c r="J67" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="20" t="s">
+      <c r="A68" s="16" t="s">
         <v>248</v>
       </c>
-      <c r="B68" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C68" s="20" t="s">
+      <c r="B68" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C68" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D68" s="21" t="s">
+      <c r="D68" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E68" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F68" s="23">
+      <c r="E68" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="21">
         <v>1.0</v>
       </c>
-      <c r="G68" s="23">
+      <c r="G68" s="21">
         <v>1.0</v>
       </c>
-      <c r="H68" s="20" t="s">
+      <c r="H68" s="16" t="s">
         <v>250</v>
       </c>
-      <c r="I68" s="22" t="s">
+      <c r="I68" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J68" s="20" t="s">
-        <v>19</v>
+      <c r="J68" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="20" t="s">
+      <c r="A69" s="16" t="s">
         <v>251</v>
       </c>
-      <c r="B69" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C69" s="20" t="s">
+      <c r="B69" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C69" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="D69" s="21" t="s">
+      <c r="D69" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E69" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F69" s="23">
+      <c r="E69" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" s="21">
         <v>1.0</v>
       </c>
-      <c r="G69" s="23">
+      <c r="G69" s="21">
         <v>1.0</v>
       </c>
-      <c r="H69" s="20" t="s">
+      <c r="H69" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="I69" s="22" t="s">
+      <c r="I69" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J69" s="20" t="s">
-        <v>19</v>
+      <c r="J69" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="20" t="s">
+      <c r="A70" s="16" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C70" s="20" t="s">
+      <c r="B70" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="D70" s="21" t="s">
+      <c r="D70" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E70" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F70" s="23">
+      <c r="E70" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F70" s="21">
         <v>2.0</v>
       </c>
-      <c r="G70" s="23">
+      <c r="G70" s="21">
         <v>2.0</v>
       </c>
-      <c r="H70" s="20" t="s">
+      <c r="H70" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="I70" s="22" t="s">
+      <c r="I70" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J70" s="20" t="s">
-        <v>19</v>
+      <c r="J70" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -4777,11 +4804,11 @@
       <c r="E71" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F71" s="14">
+      <c r="F71" s="15">
         <f t="shared" ref="F71:G71" si="18">SUM(F72:F79)</f>
         <v>10</v>
       </c>
-      <c r="G71" s="14">
+      <c r="G71" s="15">
         <f t="shared" si="18"/>
         <v>14</v>
       </c>
@@ -4792,7 +4819,7 @@
         <v>28</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
@@ -4810,259 +4837,259 @@
       <c r="X71" s="24"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="B72" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C72" s="20" t="s">
+      <c r="B72" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" s="16" t="s">
         <v>261</v>
       </c>
-      <c r="D72" s="21" t="s">
+      <c r="D72" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" s="23">
+      <c r="E72" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="21">
         <v>2.0</v>
       </c>
-      <c r="G72" s="23">
+      <c r="G72" s="21">
         <v>2.0</v>
       </c>
-      <c r="H72" s="20" t="s">
+      <c r="H72" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="I72" s="22" t="s">
+      <c r="I72" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J72" s="20" t="s">
-        <v>19</v>
+      <c r="J72" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="B73" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C73" s="20" t="s">
+      <c r="B73" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="21" t="s">
+      <c r="D73" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E73" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F73" s="23">
+      <c r="E73" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="21">
         <v>2.0</v>
       </c>
-      <c r="G73" s="23">
+      <c r="G73" s="21">
         <v>5.0</v>
       </c>
-      <c r="H73" s="20" t="s">
+      <c r="H73" s="16" t="s">
         <v>265</v>
       </c>
-      <c r="I73" s="22" t="s">
+      <c r="I73" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J73" s="20" t="s">
-        <v>19</v>
+      <c r="J73" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="B74" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C74" s="20" t="s">
+      <c r="B74" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C74" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="D74" s="21" t="s">
+      <c r="D74" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E74" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F74" s="23">
+      <c r="E74" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="21">
         <v>1.0</v>
       </c>
       <c r="G74" s="25">
         <v>1.0</v>
       </c>
-      <c r="H74" s="20" t="s">
+      <c r="H74" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="I74" s="22" t="s">
+      <c r="I74" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J74" s="20" t="s">
-        <v>19</v>
+      <c r="J74" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="20" t="s">
+      <c r="A75" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="B75" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="20" t="s">
+      <c r="B75" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C75" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="D75" s="21" t="s">
+      <c r="D75" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E75" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F75" s="23">
+      <c r="E75" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="21">
         <v>1.0</v>
       </c>
       <c r="G75" s="25">
         <v>1.0</v>
       </c>
-      <c r="H75" s="20" t="s">
+      <c r="H75" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="I75" s="22" t="s">
+      <c r="I75" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J75" s="20" t="s">
-        <v>19</v>
+      <c r="J75" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="20" t="s">
+      <c r="A76" s="16" t="s">
         <v>271</v>
       </c>
-      <c r="B76" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C76" s="20" t="s">
+      <c r="B76" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="D76" s="21" t="s">
+      <c r="D76" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E76" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F76" s="23">
+      <c r="E76" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="21">
         <v>1.0</v>
       </c>
-      <c r="G76" s="23">
+      <c r="G76" s="21">
         <v>1.0</v>
       </c>
-      <c r="H76" s="20" t="s">
+      <c r="H76" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="I76" s="22" t="s">
+      <c r="I76" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J76" s="20" t="s">
-        <v>19</v>
+      <c r="J76" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="20" t="s">
+      <c r="A77" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="B77" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C77" s="20" t="s">
+      <c r="B77" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C77" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="D77" s="21" t="s">
+      <c r="D77" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E77" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F77" s="23">
+      <c r="E77" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="21">
         <v>1.0</v>
       </c>
-      <c r="G77" s="23">
+      <c r="G77" s="21">
         <v>1.0</v>
       </c>
-      <c r="H77" s="20" t="s">
+      <c r="H77" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="I77" s="22" t="s">
+      <c r="I77" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J77" s="20" t="s">
-        <v>19</v>
+      <c r="J77" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="20" t="s">
+      <c r="A78" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="B78" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C78" s="20" t="s">
+      <c r="B78" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C78" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="D78" s="21" t="s">
+      <c r="D78" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E78" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F78" s="23">
+      <c r="E78" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="21">
         <v>1.0</v>
       </c>
-      <c r="G78" s="23">
+      <c r="G78" s="21">
         <v>1.0</v>
       </c>
-      <c r="H78" s="20" t="s">
+      <c r="H78" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="I78" s="22" t="s">
+      <c r="I78" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J78" s="20" t="s">
-        <v>19</v>
+      <c r="J78" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="20" t="s">
+      <c r="A79" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="B79" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C79" s="20" t="s">
+      <c r="B79" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="D79" s="21" t="s">
+      <c r="D79" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E79" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F79" s="23">
+      <c r="E79" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="21">
         <v>1.0</v>
       </c>
-      <c r="G79" s="23">
+      <c r="G79" s="21">
         <v>2.0</v>
       </c>
-      <c r="H79" s="20" t="s">
+      <c r="H79" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="I79" s="22" t="s">
+      <c r="I79" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J79" s="20" t="s">
-        <v>19</v>
+      <c r="J79" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
@@ -5081,11 +5108,11 @@
       <c r="E80" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F80" s="14">
+      <c r="F80" s="15">
         <f t="shared" ref="F80:G80" si="19">SUM(F81:F83)</f>
         <v>4</v>
       </c>
-      <c r="G80" s="14">
+      <c r="G80" s="15">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
@@ -5096,7 +5123,7 @@
         <v>28</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K80" s="24"/>
       <c r="L80" s="24"/>
@@ -5114,99 +5141,99 @@
       <c r="X80" s="24"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="20" t="s">
+      <c r="A81" s="16" t="s">
         <v>283</v>
       </c>
-      <c r="B81" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C81" s="20" t="s">
+      <c r="B81" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C81" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="D81" s="21" t="s">
+      <c r="D81" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E81" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F81" s="23">
+      <c r="E81" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="21">
         <v>2.0</v>
       </c>
-      <c r="G81" s="23">
+      <c r="G81" s="21">
         <v>8.0</v>
       </c>
-      <c r="H81" s="20" t="s">
+      <c r="H81" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="I81" s="22" t="s">
+      <c r="I81" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J81" s="20" t="s">
-        <v>19</v>
+      <c r="J81" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="20" t="s">
+      <c r="A82" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="B82" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C82" s="20" t="s">
+      <c r="B82" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="D82" s="21" t="s">
+      <c r="D82" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E82" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F82" s="23">
+      <c r="E82" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" s="21">
         <v>1.0</v>
       </c>
-      <c r="G82" s="23">
+      <c r="G82" s="21">
         <v>1.0</v>
       </c>
-      <c r="H82" s="20" t="s">
+      <c r="H82" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="I82" s="22" t="s">
+      <c r="I82" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J82" s="20" t="s">
-        <v>19</v>
+      <c r="J82" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="20" t="s">
+      <c r="A83" s="16" t="s">
         <v>289</v>
       </c>
-      <c r="B83" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C83" s="20" t="s">
+      <c r="B83" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83" s="16" t="s">
         <v>290</v>
       </c>
-      <c r="D83" s="21" t="s">
+      <c r="D83" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E83" s="22" t="s">
+      <c r="E83" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F83" s="23">
+      <c r="F83" s="21">
         <v>1.0</v>
       </c>
-      <c r="G83" s="23">
+      <c r="G83" s="21">
         <v>1.0</v>
       </c>
-      <c r="H83" s="20" t="s">
+      <c r="H83" s="16" t="s">
         <v>291</v>
       </c>
-      <c r="I83" s="22" t="s">
+      <c r="I83" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J83" s="20" t="s">
-        <v>19</v>
+      <c r="J83" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -5214,7 +5241,7 @@
         <v>292</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>293</v>
@@ -5226,11 +5253,11 @@
         <v>24</v>
       </c>
       <c r="F84" s="27">
-        <v>45.0</v>
+        <v>47.0</v>
       </c>
       <c r="G84" s="26">
-        <f>G85+G90+G96+G102+G107</f>
-        <v>12</v>
+        <f>G85+G90+G96+G102+G108</f>
+        <v>20</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>294</v>
@@ -5239,7 +5266,7 @@
         <v>295</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K84" s="24"/>
       <c r="L84" s="24"/>
@@ -5272,11 +5299,11 @@
       <c r="E85" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F85" s="14">
+      <c r="F85" s="15">
         <f t="shared" ref="F85:G85" si="20">SUM(F86:F89)</f>
         <v>5</v>
       </c>
-      <c r="G85" s="14">
+      <c r="G85" s="15">
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
@@ -5287,7 +5314,7 @@
         <v>28</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K85" s="24"/>
       <c r="L85" s="24"/>
@@ -5305,22 +5332,22 @@
       <c r="X85" s="24"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="20" t="s">
+      <c r="A86" s="16" t="s">
         <v>299</v>
       </c>
-      <c r="B86" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C86" s="20" t="s">
+      <c r="B86" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="D86" s="21" t="s">
+      <c r="D86" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E86" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="23">
+      <c r="E86" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" s="21">
         <v>1.0</v>
       </c>
       <c r="G86" s="30">
@@ -5332,27 +5359,27 @@
       <c r="I86" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J86" s="20" t="s">
-        <v>26</v>
+      <c r="J86" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="20" t="s">
+      <c r="A87" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="B87" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C87" s="20" t="s">
+      <c r="B87" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C87" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="D87" s="21" t="s">
+      <c r="D87" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F87" s="23">
+      <c r="E87" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" s="21">
         <v>1.0</v>
       </c>
       <c r="G87" s="30">
@@ -5364,27 +5391,27 @@
       <c r="I87" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J87" s="20" t="s">
-        <v>26</v>
+      <c r="J87" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="20" t="s">
+      <c r="A88" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="B88" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C88" s="20" t="s">
+      <c r="B88" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="D88" s="21" t="s">
+      <c r="D88" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E88" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F88" s="23">
+      <c r="E88" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="21">
         <v>2.0</v>
       </c>
       <c r="G88" s="30">
@@ -5396,27 +5423,27 @@
       <c r="I88" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J88" s="20" t="s">
-        <v>26</v>
+      <c r="J88" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="20" t="s">
+      <c r="A89" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="B89" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C89" s="20" t="s">
+      <c r="B89" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C89" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="D89" s="21" t="s">
+      <c r="D89" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E89" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F89" s="23">
+      <c r="E89" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F89" s="21">
         <v>1.0</v>
       </c>
       <c r="G89" s="30">
@@ -5428,8 +5455,8 @@
       <c r="I89" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J89" s="20" t="s">
-        <v>26</v>
+      <c r="J89" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
@@ -5448,11 +5475,11 @@
       <c r="E90" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F90" s="14">
+      <c r="F90" s="15">
         <f t="shared" ref="F90:G90" si="21">SUM(F91:F95)</f>
         <v>11</v>
       </c>
-      <c r="G90" s="14">
+      <c r="G90" s="15">
         <f t="shared" si="21"/>
         <v>7</v>
       </c>
@@ -5463,7 +5490,7 @@
         <v>28</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K90" s="24"/>
       <c r="L90" s="24"/>
@@ -5481,131 +5508,131 @@
       <c r="X90" s="24"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="20" t="s">
+      <c r="A91" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="B91" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C91" s="20" t="s">
+      <c r="B91" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="D91" s="21" t="s">
+      <c r="D91" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E91" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" s="23">
+      <c r="E91" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="21">
         <v>2.0</v>
       </c>
       <c r="G91" s="30">
         <v>1.0</v>
       </c>
-      <c r="H91" s="20" t="s">
+      <c r="H91" s="16" t="s">
         <v>316</v>
       </c>
       <c r="I91" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J91" s="20" t="s">
-        <v>26</v>
+      <c r="J91" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="20" t="s">
+      <c r="A92" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="B92" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C92" s="20" t="s">
+      <c r="B92" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C92" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="D92" s="21" t="s">
+      <c r="D92" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E92" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F92" s="23">
+      <c r="E92" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="21">
         <v>3.0</v>
       </c>
       <c r="G92" s="30">
         <v>2.0</v>
       </c>
-      <c r="H92" s="20" t="s">
+      <c r="H92" s="16" t="s">
         <v>319</v>
       </c>
       <c r="I92" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J92" s="20" t="s">
-        <v>26</v>
+      <c r="J92" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="20" t="s">
+      <c r="A93" s="16" t="s">
         <v>320</v>
       </c>
-      <c r="B93" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C93" s="20" t="s">
+      <c r="B93" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C93" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="D93" s="21" t="s">
+      <c r="D93" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E93" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F93" s="23">
+      <c r="E93" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="21">
         <v>2.0</v>
       </c>
       <c r="G93" s="30">
         <v>1.0</v>
       </c>
-      <c r="H93" s="20" t="s">
+      <c r="H93" s="16" t="s">
         <v>322</v>
       </c>
       <c r="I93" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J93" s="20" t="s">
-        <v>26</v>
+      <c r="J93" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="20" t="s">
+      <c r="A94" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="B94" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C94" s="20" t="s">
+      <c r="B94" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C94" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="D94" s="21" t="s">
+      <c r="D94" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E94" s="22" t="s">
+      <c r="E94" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F94" s="23">
+      <c r="F94" s="21">
         <v>2.0</v>
       </c>
       <c r="G94" s="33">
         <v>1.0</v>
       </c>
-      <c r="H94" s="20" t="s">
+      <c r="H94" s="16" t="s">
         <v>325</v>
       </c>
       <c r="I94" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J94" s="20" t="s">
-        <v>26</v>
+      <c r="J94" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
@@ -5613,7 +5640,7 @@
         <v>326</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C95" s="31" t="s">
         <v>327</v>
@@ -5637,7 +5664,7 @@
         <v>28</v>
       </c>
       <c r="J95" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
@@ -5656,22 +5683,22 @@
       <c r="E96" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F96" s="14">
+      <c r="F96" s="15">
         <f t="shared" ref="F96:G96" si="22">SUM(F97:F101)</f>
         <v>8</v>
       </c>
-      <c r="G96" s="14">
+      <c r="G96" s="15">
         <f t="shared" si="22"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H96" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="I96" s="13" t="s">
-        <v>332</v>
+      <c r="I96" s="28" t="s">
+        <v>28</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K96" s="24"/>
       <c r="L96" s="24"/>
@@ -5689,134 +5716,142 @@
       <c r="X96" s="24"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="20" t="s">
+      <c r="A97" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="B97" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C97" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="B97" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C97" s="20" t="s">
+      <c r="D97" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E97" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G97" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="H97" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="D97" s="21" t="s">
+      <c r="I97" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J97" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="B98" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="D98" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E97" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="G97" s="23"/>
-      <c r="H97" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="I97" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J97" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="B98" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C98" s="20" t="s">
+      <c r="E98" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="G98" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="H98" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="D98" s="21" t="s">
+      <c r="I98" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J98" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="B99" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="D99" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E98" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F98" s="23">
-        <v>2.0</v>
-      </c>
-      <c r="G98" s="23"/>
-      <c r="H98" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="I98" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J98" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="B99" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C99" s="20" t="s">
+      <c r="E99" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="G99" s="30">
+        <v>1.0</v>
+      </c>
+      <c r="H99" s="16" t="s">
         <v>340</v>
       </c>
-      <c r="D99" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E99" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F99" s="23">
+      <c r="I99" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J99" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C100" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E100" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="21">
         <v>1.0</v>
       </c>
-      <c r="G99" s="23"/>
-      <c r="H99" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="I99" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J99" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="B100" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C100" s="20" t="s">
+      <c r="G100" s="30">
+        <v>1.0</v>
+      </c>
+      <c r="H100" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="D100" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E100" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F100" s="23">
-        <v>1.0</v>
-      </c>
-      <c r="G100" s="23"/>
-      <c r="H100" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="I100" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J100" s="20" t="s">
-        <v>26</v>
+      <c r="I100" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="B101" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C101" s="31" t="s">
         <v>345</v>
-      </c>
-      <c r="B101" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C101" s="31" t="s">
-        <v>346</v>
       </c>
       <c r="D101" s="34" t="s">
         <v>50</v>
@@ -5827,26 +5862,28 @@
       <c r="F101" s="30">
         <v>1.0</v>
       </c>
-      <c r="G101" s="23"/>
+      <c r="G101" s="30">
+        <v>2.0</v>
+      </c>
       <c r="H101" s="31" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I101" s="32" t="s">
-        <v>332</v>
+        <v>28</v>
       </c>
       <c r="J101" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D102" s="12" t="s">
         <v>99</v>
@@ -5854,22 +5891,21 @@
       <c r="E102" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F102" s="14">
-        <f t="shared" ref="F102:G102" si="23">SUM(F103:F106)</f>
-        <v>10</v>
-      </c>
-      <c r="G102" s="14">
-        <f t="shared" si="23"/>
+      <c r="F102" s="27">
+        <v>12.0</v>
+      </c>
+      <c r="G102" s="15">
+        <f>SUM(G103:G106)</f>
         <v>0</v>
       </c>
       <c r="H102" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="I102" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="I102" s="13" t="s">
-        <v>332</v>
-      </c>
       <c r="J102" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K102" s="24"/>
       <c r="L102" s="24"/>
@@ -5887,93 +5923,93 @@
       <c r="X102" s="24"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="20" t="s">
+      <c r="A103" s="16" t="s">
         <v>351</v>
       </c>
-      <c r="B103" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C103" s="20" t="s">
+      <c r="B103" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C103" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="D103" s="21" t="s">
+      <c r="D103" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E103" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F103" s="23">
+      <c r="E103" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" s="21">
         <v>2.0</v>
       </c>
-      <c r="G103" s="23"/>
-      <c r="H103" s="20" t="s">
+      <c r="G103" s="21"/>
+      <c r="H103" s="16" t="s">
         <v>353</v>
       </c>
-      <c r="I103" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J103" s="20" t="s">
-        <v>26</v>
+      <c r="I103" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J103" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="20" t="s">
+      <c r="A104" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="B104" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C104" s="20" t="s">
+      <c r="B104" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" s="16" t="s">
         <v>355</v>
       </c>
-      <c r="D104" s="21" t="s">
+      <c r="D104" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E104" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F104" s="23">
+      <c r="E104" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F104" s="21">
         <v>3.0</v>
       </c>
-      <c r="G104" s="23"/>
-      <c r="H104" s="20" t="s">
+      <c r="G104" s="21"/>
+      <c r="H104" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="I104" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J104" s="20" t="s">
-        <v>26</v>
+      <c r="I104" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J104" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="20" t="s">
+      <c r="A105" s="16" t="s">
         <v>357</v>
       </c>
-      <c r="B105" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C105" s="20" t="s">
+      <c r="B105" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="D105" s="21" t="s">
+      <c r="D105" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E105" s="22" t="s">
+      <c r="E105" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F105" s="23">
+      <c r="F105" s="21">
         <v>3.0</v>
       </c>
-      <c r="G105" s="23"/>
-      <c r="H105" s="20" t="s">
+      <c r="G105" s="21"/>
+      <c r="H105" s="16" t="s">
         <v>359</v>
       </c>
-      <c r="I105" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J105" s="20" t="s">
-        <v>26</v>
+      <c r="I105" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J105" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -5981,7 +6017,7 @@
         <v>360</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C106" s="31" t="s">
         <v>361</v>
@@ -5995,141 +6031,141 @@
       <c r="F106" s="30">
         <v>2.0</v>
       </c>
-      <c r="G106" s="23"/>
+      <c r="G106" s="21"/>
       <c r="H106" s="31" t="s">
         <v>362</v>
       </c>
       <c r="I106" s="32" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J106" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="11" t="s">
+      <c r="A107" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C107" s="31" t="s">
+        <v>364</v>
+      </c>
+      <c r="D107" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E107" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F107" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="G107" s="21"/>
+      <c r="H107" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="I107" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J107" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="A108" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="B108" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C107" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="D107" s="35" t="s">
+      <c r="C108" s="29" t="s">
+        <v>367</v>
+      </c>
+      <c r="D108" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="E107" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F107" s="26">
-        <f t="shared" ref="F107:G107" si="24">SUM(F108)</f>
+      <c r="E108" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F108" s="26">
+        <f t="shared" ref="F108:G108" si="23">SUM(F109)</f>
         <v>6</v>
       </c>
-      <c r="G107" s="14">
-        <f t="shared" si="24"/>
+      <c r="G108" s="15">
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="H107" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="I107" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J107" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="B108" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C108" s="31" t="s">
-        <v>367</v>
-      </c>
-      <c r="D108" s="34" t="s">
+      <c r="H108" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="I108" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J108" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="A109" s="31" t="s">
+        <v>369</v>
+      </c>
+      <c r="B109" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C109" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="D109" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="E108" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="F108" s="30">
+      <c r="E109" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F109" s="30">
         <v>6.0</v>
       </c>
-      <c r="G108" s="23"/>
-      <c r="H108" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="I108" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="J108" s="31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="29" t="s">
-        <v>369</v>
-      </c>
-      <c r="B109" s="29" t="s">
+      <c r="G109" s="21"/>
+      <c r="H109" s="31" t="s">
+        <v>371</v>
+      </c>
+      <c r="I109" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J109" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="29" t="s">
+        <v>372</v>
+      </c>
+      <c r="B110" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C109" s="29" t="s">
-        <v>370</v>
-      </c>
-      <c r="D109" s="36" t="s">
+      <c r="C110" s="29" t="s">
+        <v>373</v>
+      </c>
+      <c r="D110" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="E109" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="F109" s="27">
+      <c r="E110" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="F110" s="27">
         <v>5.0</v>
       </c>
-      <c r="G109" s="37">
+      <c r="G110" s="37">
         <v>0.0</v>
       </c>
-      <c r="H109" s="29" t="s">
-        <v>371</v>
-      </c>
-      <c r="I109" s="28" t="s">
-        <v>332</v>
-      </c>
-      <c r="J109" s="29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="B110" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C110" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="D110" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="E110" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="F110" s="30">
-        <v>2.0</v>
-      </c>
-      <c r="G110" s="23"/>
-      <c r="H110" s="31" t="s">
+      <c r="H110" s="29" t="s">
         <v>374</v>
       </c>
-      <c r="I110" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="J110" s="31" t="s">
-        <v>26</v>
+      <c r="I110" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="J110" s="29" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
@@ -6137,7 +6173,7 @@
         <v>375</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C111" s="31" t="s">
         <v>376</v>
@@ -6151,15 +6187,15 @@
       <c r="F111" s="30">
         <v>2.0</v>
       </c>
-      <c r="G111" s="23"/>
+      <c r="G111" s="21"/>
       <c r="H111" s="31" t="s">
         <v>377</v>
       </c>
       <c r="I111" s="32" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J111" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
@@ -6167,7 +6203,7 @@
         <v>378</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C112" s="31" t="s">
         <v>379</v>
@@ -6179,98 +6215,80 @@
         <v>24</v>
       </c>
       <c r="F112" s="30">
-        <v>1.0</v>
-      </c>
-      <c r="G112" s="23"/>
+        <v>2.0</v>
+      </c>
+      <c r="G112" s="21"/>
       <c r="H112" s="31" t="s">
         <v>380</v>
       </c>
       <c r="I112" s="32" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J112" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="11" t="s">
+      <c r="A113" s="31" t="s">
         <v>381</v>
       </c>
-      <c r="B113" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C113" s="11" t="s">
+      <c r="B113" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C113" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="D113" s="12" t="s">
+      <c r="D113" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="E113" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F113" s="27">
-        <v>65.0</v>
-      </c>
-      <c r="G113" s="14">
-        <f>G114+G121+G126+G131+G137</f>
-        <v>0</v>
-      </c>
-      <c r="H113" s="11" t="s">
+      <c r="E113" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F113" s="30">
+        <v>1.0</v>
+      </c>
+      <c r="G113" s="21"/>
+      <c r="H113" s="31" t="s">
         <v>383</v>
       </c>
-      <c r="I113" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J113" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K113" s="24"/>
-      <c r="L113" s="24"/>
-      <c r="M113" s="24"/>
-      <c r="N113" s="24"/>
-      <c r="O113" s="24"/>
-      <c r="P113" s="24"/>
-      <c r="Q113" s="24"/>
-      <c r="R113" s="24"/>
-      <c r="S113" s="24"/>
-      <c r="T113" s="24"/>
-      <c r="U113" s="24"/>
-      <c r="V113" s="24"/>
-      <c r="W113" s="24"/>
-      <c r="X113" s="24"/>
+      <c r="I113" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J113" s="31" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="11" t="s">
         <v>384</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>385</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="F114" s="26">
-        <f t="shared" ref="F114:G114" si="25">SUM(F115:F120)</f>
-        <v>21</v>
-      </c>
-      <c r="G114" s="26">
-        <f t="shared" si="25"/>
+      <c r="F114" s="27">
+        <v>70.0</v>
+      </c>
+      <c r="G114" s="15">
+        <f>G115+G123+G129+G134+G140</f>
         <v>0</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>386</v>
       </c>
       <c r="I114" s="13" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J114" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K114" s="24"/>
       <c r="L114" s="24"/>
@@ -6288,153 +6306,170 @@
       <c r="X114" s="24"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="20" t="s">
+      <c r="A115" s="11" t="s">
         <v>387</v>
       </c>
-      <c r="B115" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C115" s="20" t="s">
+      <c r="B115" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C115" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="D115" s="21" t="s">
+      <c r="D115" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E115" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F115" s="23">
+      <c r="E115" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F115" s="27">
+        <v>24.0</v>
+      </c>
+      <c r="G115" s="26">
+        <f>SUM(G116:G121)</f>
+        <v>0</v>
+      </c>
+      <c r="H115" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="I115" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J115" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K115" s="24"/>
+      <c r="L115" s="24"/>
+      <c r="M115" s="24"/>
+      <c r="N115" s="24"/>
+      <c r="O115" s="24"/>
+      <c r="P115" s="24"/>
+      <c r="Q115" s="24"/>
+      <c r="R115" s="24"/>
+      <c r="S115" s="24"/>
+      <c r="T115" s="24"/>
+      <c r="U115" s="24"/>
+      <c r="V115" s="24"/>
+      <c r="W115" s="24"/>
+      <c r="X115" s="24"/>
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
+      <c r="A116" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="B116" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C116" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="D116" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F116" s="21">
         <v>3.0</v>
       </c>
-      <c r="G115" s="23"/>
-      <c r="H115" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="I115" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J115" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="B116" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C116" s="20" t="s">
-        <v>391</v>
-      </c>
-      <c r="D116" s="21" t="s">
+      <c r="G116" s="21"/>
+      <c r="H116" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="I116" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J116" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="B117" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C117" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="D117" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E116" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F116" s="23">
+      <c r="E117" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F117" s="21">
         <v>6.0</v>
       </c>
-      <c r="G116" s="23"/>
-      <c r="H116" s="20" t="s">
-        <v>392</v>
-      </c>
-      <c r="I116" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J116" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="B117" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C117" s="20" t="s">
-        <v>394</v>
-      </c>
-      <c r="D117" s="21" t="s">
+      <c r="G117" s="21"/>
+      <c r="H117" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="I117" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J117" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="B118" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C118" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="D118" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E117" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F117" s="23">
+      <c r="E118" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F118" s="21">
         <v>1.0</v>
       </c>
-      <c r="G117" s="25"/>
-      <c r="H117" s="20" t="s">
-        <v>395</v>
-      </c>
-      <c r="I117" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J117" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="B118" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C118" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="D118" s="21" t="s">
+      <c r="G118" s="25"/>
+      <c r="H118" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="I118" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J118" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="B119" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C119" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="D119" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E118" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F118" s="23">
+      <c r="E119" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F119" s="21">
         <v>3.0</v>
       </c>
-      <c r="G118" s="23"/>
-      <c r="H118" s="31" t="s">
-        <v>398</v>
-      </c>
-      <c r="I118" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J118" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="31" t="s">
-        <v>399</v>
-      </c>
-      <c r="B119" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C119" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="D119" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E119" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" s="30">
-        <v>5.0</v>
-      </c>
-      <c r="G119" s="23"/>
+      <c r="G119" s="21"/>
       <c r="H119" s="31" t="s">
         <v>401</v>
       </c>
-      <c r="I119" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="J119" s="31" t="s">
-        <v>26</v>
+      <c r="I119" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J119" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -6442,626 +6477,621 @@
         <v>402</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C120" s="31" t="s">
         <v>403</v>
       </c>
       <c r="D120" s="34" t="s">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="E120" s="32" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="F120" s="30">
-        <v>3.0</v>
-      </c>
-      <c r="G120" s="23"/>
+        <v>5.0</v>
+      </c>
+      <c r="G120" s="21"/>
       <c r="H120" s="31" t="s">
         <v>404</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J120" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="11" t="s">
+      <c r="A121" s="31" t="s">
         <v>405</v>
       </c>
-      <c r="B121" s="11" t="s">
+      <c r="B121" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C121" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="D121" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E121" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F121" s="30">
+        <v>3.0</v>
+      </c>
+      <c r="G121" s="21"/>
+      <c r="H121" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="I121" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J121" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
+      <c r="A122" s="31" t="s">
+        <v>408</v>
+      </c>
+      <c r="B122" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C122" s="31" t="s">
+        <v>409</v>
+      </c>
+      <c r="D122" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E122" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F122" s="30">
+        <v>3.0</v>
+      </c>
+      <c r="G122" s="21"/>
+      <c r="H122" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="I122" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J122" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
+      <c r="A123" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="B123" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C121" s="11" t="s">
-        <v>406</v>
-      </c>
-      <c r="D121" s="12" t="s">
+      <c r="C123" s="11" t="s">
+        <v>412</v>
+      </c>
+      <c r="D123" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E121" s="13" t="s">
+      <c r="E123" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="F121" s="26">
-        <f t="shared" ref="F121:G121" si="26">SUM(F122:F125)</f>
-        <v>16</v>
-      </c>
-      <c r="G121" s="26">
-        <f t="shared" si="26"/>
+      <c r="F123" s="27">
+        <v>18.0</v>
+      </c>
+      <c r="G123" s="26">
+        <f>SUM(G124:G127)</f>
         <v>0</v>
       </c>
-      <c r="H121" s="11" t="s">
-        <v>407</v>
-      </c>
-      <c r="I121" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J121" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K121" s="24"/>
-      <c r="L121" s="24"/>
-      <c r="M121" s="24"/>
-      <c r="N121" s="24"/>
-      <c r="O121" s="24"/>
-      <c r="P121" s="24"/>
-      <c r="Q121" s="24"/>
-      <c r="R121" s="24"/>
-      <c r="S121" s="24"/>
-      <c r="T121" s="24"/>
-      <c r="U121" s="24"/>
-      <c r="V121" s="24"/>
-      <c r="W121" s="24"/>
-      <c r="X121" s="24"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="20" t="s">
-        <v>408</v>
-      </c>
-      <c r="B122" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C122" s="20" t="s">
-        <v>409</v>
-      </c>
-      <c r="D122" s="21" t="s">
+      <c r="H123" s="11" t="s">
+        <v>413</v>
+      </c>
+      <c r="I123" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J123" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K123" s="24"/>
+      <c r="L123" s="24"/>
+      <c r="M123" s="24"/>
+      <c r="N123" s="24"/>
+      <c r="O123" s="24"/>
+      <c r="P123" s="24"/>
+      <c r="Q123" s="24"/>
+      <c r="R123" s="24"/>
+      <c r="S123" s="24"/>
+      <c r="T123" s="24"/>
+      <c r="U123" s="24"/>
+      <c r="V123" s="24"/>
+      <c r="W123" s="24"/>
+      <c r="X123" s="24"/>
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
+      <c r="A124" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="B124" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C124" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="D124" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E122" s="22" t="s">
+      <c r="E124" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F122" s="23">
+      <c r="F124" s="21">
         <v>2.0</v>
       </c>
-      <c r="G122" s="23"/>
-      <c r="H122" s="20" t="s">
-        <v>410</v>
-      </c>
-      <c r="I122" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J122" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="20" t="s">
-        <v>411</v>
-      </c>
-      <c r="B123" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C123" s="20" t="s">
-        <v>412</v>
-      </c>
-      <c r="D123" s="21" t="s">
+      <c r="G124" s="21"/>
+      <c r="H124" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="I124" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J124" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="B125" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C125" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="D125" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E123" s="22" t="s">
+      <c r="E125" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F123" s="23">
+      <c r="F125" s="21">
         <v>2.0</v>
       </c>
-      <c r="G123" s="23"/>
-      <c r="H123" s="20" t="s">
-        <v>413</v>
-      </c>
-      <c r="I123" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J123" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="20" t="s">
-        <v>414</v>
-      </c>
-      <c r="B124" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C124" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="D124" s="21" t="s">
+      <c r="G125" s="21"/>
+      <c r="H125" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="I125" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J125" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="B126" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C126" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="D126" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E124" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F124" s="23">
+      <c r="E126" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F126" s="21">
         <v>10.0</v>
       </c>
-      <c r="G124" s="25"/>
-      <c r="H124" s="20" t="s">
-        <v>416</v>
-      </c>
-      <c r="I124" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J124" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="B125" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C125" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="D125" s="34" t="s">
+      <c r="G126" s="25"/>
+      <c r="H126" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="I126" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J126" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
+      <c r="A127" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="B127" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C127" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="D127" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="E125" s="32" t="s">
+      <c r="E127" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="F125" s="30">
+      <c r="F127" s="30">
         <v>2.0</v>
       </c>
-      <c r="G125" s="25"/>
-      <c r="H125" s="31" t="s">
-        <v>419</v>
-      </c>
-      <c r="I125" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="J125" s="31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="11" t="s">
-        <v>420</v>
-      </c>
-      <c r="B126" s="11" t="s">
+      <c r="G127" s="25"/>
+      <c r="H127" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="I127" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J127" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
+      <c r="A128" s="31" t="s">
+        <v>426</v>
+      </c>
+      <c r="B128" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C128" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="D128" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E128" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F128" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="G128" s="25"/>
+      <c r="H128" s="31" t="s">
+        <v>428</v>
+      </c>
+      <c r="I128" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J128" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
+      <c r="A129" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="B129" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C126" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="D126" s="12" t="s">
+      <c r="C129" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="D129" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E126" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F126" s="14">
-        <f t="shared" ref="F126:G126" si="27">SUM(F127:F130)</f>
+      <c r="E129" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F129" s="15">
+        <f t="shared" ref="F129:G129" si="24">SUM(F130:F133)</f>
         <v>12</v>
       </c>
-      <c r="G126" s="14">
-        <f t="shared" si="27"/>
+      <c r="G129" s="15">
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H126" s="11" t="s">
-        <v>422</v>
-      </c>
-      <c r="I126" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J126" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K126" s="24"/>
-      <c r="L126" s="24"/>
-      <c r="M126" s="24"/>
-      <c r="N126" s="24"/>
-      <c r="O126" s="24"/>
-      <c r="P126" s="24"/>
-      <c r="Q126" s="24"/>
-      <c r="R126" s="24"/>
-      <c r="S126" s="24"/>
-      <c r="T126" s="24"/>
-      <c r="U126" s="24"/>
-      <c r="V126" s="24"/>
-      <c r="W126" s="24"/>
-      <c r="X126" s="24"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="B127" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C127" s="20" t="s">
-        <v>424</v>
-      </c>
-      <c r="D127" s="21" t="s">
+      <c r="H129" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="I129" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J129" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K129" s="24"/>
+      <c r="L129" s="24"/>
+      <c r="M129" s="24"/>
+      <c r="N129" s="24"/>
+      <c r="O129" s="24"/>
+      <c r="P129" s="24"/>
+      <c r="Q129" s="24"/>
+      <c r="R129" s="24"/>
+      <c r="S129" s="24"/>
+      <c r="T129" s="24"/>
+      <c r="U129" s="24"/>
+      <c r="V129" s="24"/>
+      <c r="W129" s="24"/>
+      <c r="X129" s="24"/>
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
+      <c r="A130" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="B130" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C130" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="D130" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E127" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F127" s="23">
+      <c r="E130" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F130" s="21">
         <v>3.0</v>
       </c>
-      <c r="G127" s="23"/>
-      <c r="H127" s="20" t="s">
-        <v>425</v>
-      </c>
-      <c r="I127" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J127" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="20" t="s">
-        <v>426</v>
-      </c>
-      <c r="B128" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C128" s="20" t="s">
-        <v>427</v>
-      </c>
-      <c r="D128" s="21" t="s">
+      <c r="G130" s="21"/>
+      <c r="H130" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="I130" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J130" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
+      <c r="A131" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="B131" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C131" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="D131" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E128" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F128" s="23">
+      <c r="E131" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F131" s="21">
         <v>3.0</v>
       </c>
-      <c r="G128" s="23"/>
-      <c r="H128" s="20" t="s">
-        <v>428</v>
-      </c>
-      <c r="I128" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J128" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="20" t="s">
-        <v>429</v>
-      </c>
-      <c r="B129" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C129" s="20" t="s">
-        <v>430</v>
-      </c>
-      <c r="D129" s="21" t="s">
+      <c r="G131" s="21"/>
+      <c r="H131" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="I131" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J131" s="16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
+      <c r="A132" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="B132" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C132" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="D132" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E129" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F129" s="23">
+      <c r="E132" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F132" s="21">
         <v>3.0</v>
       </c>
-      <c r="G129" s="23"/>
-      <c r="H129" s="20" t="s">
-        <v>431</v>
-      </c>
-      <c r="I129" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J129" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="31" t="s">
-        <v>432</v>
-      </c>
-      <c r="B130" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C130" s="31" t="s">
-        <v>433</v>
-      </c>
-      <c r="D130" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="E130" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="F130" s="30">
-        <v>3.0</v>
-      </c>
-      <c r="G130" s="23"/>
-      <c r="H130" s="31" t="s">
-        <v>434</v>
-      </c>
-      <c r="I130" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="J130" s="31" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="11" t="s">
-        <v>435</v>
-      </c>
-      <c r="B131" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C131" s="11" t="s">
-        <v>436</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E131" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F131" s="27">
-        <v>12.0</v>
-      </c>
-      <c r="G131" s="14">
-        <f>SUM(G132:G135)</f>
-        <v>0</v>
-      </c>
-      <c r="H131" s="11" t="s">
-        <v>437</v>
-      </c>
-      <c r="I131" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J131" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K131" s="24"/>
-      <c r="L131" s="24"/>
-      <c r="M131" s="24"/>
-      <c r="N131" s="24"/>
-      <c r="O131" s="24"/>
-      <c r="P131" s="24"/>
-      <c r="Q131" s="24"/>
-      <c r="R131" s="24"/>
-      <c r="S131" s="24"/>
-      <c r="T131" s="24"/>
-      <c r="U131" s="24"/>
-      <c r="V131" s="24"/>
-      <c r="W131" s="24"/>
-      <c r="X131" s="24"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="20" t="s">
-        <v>438</v>
-      </c>
-      <c r="B132" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C132" s="20" t="s">
-        <v>439</v>
-      </c>
-      <c r="D132" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="E132" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="F132" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="G132" s="23"/>
-      <c r="H132" s="20" t="s">
+      <c r="G132" s="21"/>
+      <c r="H132" s="16" t="s">
         <v>440</v>
       </c>
-      <c r="I132" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J132" s="20" t="s">
-        <v>26</v>
+      <c r="I132" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J132" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="20" t="s">
+      <c r="A133" s="31" t="s">
         <v>441</v>
       </c>
-      <c r="B133" s="20" t="s">
-        <v>41</v>
+      <c r="B133" s="31" t="s">
+        <v>37</v>
       </c>
       <c r="C133" s="31" t="s">
         <v>442</v>
       </c>
-      <c r="D133" s="21" t="s">
+      <c r="D133" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="E133" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="F133" s="30">
+        <v>3.0</v>
+      </c>
+      <c r="G133" s="21"/>
+      <c r="H133" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="I133" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J133" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
+      <c r="A134" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>445</v>
+      </c>
+      <c r="D134" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E134" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F134" s="27">
+        <v>12.0</v>
+      </c>
+      <c r="G134" s="15">
+        <f>SUM(G135:G138)</f>
+        <v>0</v>
+      </c>
+      <c r="H134" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="I134" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J134" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K134" s="24"/>
+      <c r="L134" s="24"/>
+      <c r="M134" s="24"/>
+      <c r="N134" s="24"/>
+      <c r="O134" s="24"/>
+      <c r="P134" s="24"/>
+      <c r="Q134" s="24"/>
+      <c r="R134" s="24"/>
+      <c r="S134" s="24"/>
+      <c r="T134" s="24"/>
+      <c r="U134" s="24"/>
+      <c r="V134" s="24"/>
+      <c r="W134" s="24"/>
+      <c r="X134" s="24"/>
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
+      <c r="A135" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="B135" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="D135" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="E133" s="22" t="s">
+      <c r="E135" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F133" s="23">
+      <c r="F135" s="21">
         <v>3.0</v>
       </c>
-      <c r="G133" s="23"/>
-      <c r="H133" s="20" t="s">
-        <v>443</v>
-      </c>
-      <c r="I133" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J133" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="20" t="s">
-        <v>444</v>
-      </c>
-      <c r="B134" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C134" s="20" t="s">
-        <v>445</v>
-      </c>
-      <c r="D134" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E134" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="F134" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="G134" s="23"/>
-      <c r="H134" s="20" t="s">
-        <v>446</v>
-      </c>
-      <c r="I134" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J134" s="20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="20" t="s">
-        <v>447</v>
-      </c>
-      <c r="B135" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C135" s="20" t="s">
-        <v>448</v>
-      </c>
-      <c r="D135" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E135" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="F135" s="23">
-        <v>2.0</v>
-      </c>
-      <c r="G135" s="25"/>
-      <c r="H135" s="20" t="s">
+      <c r="G135" s="21"/>
+      <c r="H135" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="I135" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J135" s="20" t="s">
-        <v>26</v>
+      <c r="I135" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J135" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="31" t="s">
+      <c r="A136" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="B136" s="31" t="s">
-        <v>41</v>
+      <c r="B136" s="16" t="s">
+        <v>37</v>
       </c>
       <c r="C136" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="D136" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="E136" s="32" t="s">
+      <c r="D136" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="E136" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F136" s="30">
-        <v>1.0</v>
-      </c>
-      <c r="G136" s="25"/>
-      <c r="H136" s="31" t="s">
+      <c r="F136" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G136" s="21"/>
+      <c r="H136" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="I136" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="J136" s="31" t="s">
-        <v>26</v>
+      <c r="I136" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J136" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="11" t="s">
+      <c r="A137" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="B137" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C137" s="11" t="s">
+      <c r="B137" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C137" s="16" t="s">
         <v>454</v>
       </c>
-      <c r="D137" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="E137" s="13" t="s">
+      <c r="D137" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E137" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F137" s="26">
-        <f t="shared" ref="F137:G137" si="28">SUM(F138:F139)</f>
-        <v>4</v>
-      </c>
-      <c r="G137" s="14">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="H137" s="11" t="s">
+      <c r="F137" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G137" s="21"/>
+      <c r="H137" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="I137" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="J137" s="11" t="s">
-        <v>26</v>
+      <c r="I137" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J137" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="31" t="s">
+      <c r="A138" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="B138" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="C138" s="31" t="s">
+      <c r="B138" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C138" s="16" t="s">
         <v>457</v>
       </c>
-      <c r="D138" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="E138" s="32" t="s">
+      <c r="D138" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E138" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F138" s="30">
+      <c r="F138" s="21">
         <v>2.0</v>
       </c>
       <c r="G138" s="25"/>
-      <c r="H138" s="31" t="s">
+      <c r="H138" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="I138" s="32" t="s">
-        <v>295</v>
-      </c>
-      <c r="J138" s="31" t="s">
-        <v>26</v>
+      <c r="I138" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J138" s="16" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -7069,29 +7099,29 @@
         <v>459</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C139" s="31" t="s">
         <v>460</v>
       </c>
       <c r="D139" s="34" t="s">
-        <v>59</v>
+        <v>99</v>
       </c>
       <c r="E139" s="32" t="s">
         <v>110</v>
       </c>
       <c r="F139" s="30">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G139" s="25"/>
       <c r="H139" s="31" t="s">
         <v>461</v>
       </c>
       <c r="I139" s="32" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J139" s="31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -7099,629 +7129,615 @@
         <v>462</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C140" s="11" t="s">
         <v>463</v>
       </c>
-      <c r="D140" s="12" t="s">
+      <c r="D140" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="E140" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F140" s="26">
+        <f t="shared" ref="F140:G140" si="25">SUM(F141:F142)</f>
+        <v>4</v>
+      </c>
+      <c r="G140" s="15">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="H140" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="I140" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="J140" s="11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
+      <c r="A141" s="31" t="s">
+        <v>465</v>
+      </c>
+      <c r="B141" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C141" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="D141" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E141" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F141" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="G141" s="25"/>
+      <c r="H141" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="I141" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="J141" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
+      <c r="A142" s="31" t="s">
+        <v>468</v>
+      </c>
+      <c r="B142" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C142" s="31" t="s">
+        <v>469</v>
+      </c>
+      <c r="D142" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="E142" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="F142" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="G142" s="25"/>
+      <c r="H142" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="I142" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="J142" s="31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="11" t="s">
+        <v>471</v>
+      </c>
+      <c r="B143" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C143" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="D143" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E140" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F140" s="26">
-        <f t="shared" ref="F140:G140" si="29">F141+F145+F149+F155</f>
+      <c r="E143" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F143" s="26">
+        <f t="shared" ref="F143:G143" si="26">F144+F148+F152+F158</f>
         <v>62</v>
       </c>
-      <c r="G140" s="26">
+      <c r="G143" s="26">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+      <c r="H143" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="I143" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J143" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K143" s="24"/>
+      <c r="L143" s="24"/>
+      <c r="M143" s="24"/>
+      <c r="N143" s="24"/>
+      <c r="O143" s="24"/>
+      <c r="P143" s="24"/>
+      <c r="Q143" s="24"/>
+      <c r="R143" s="24"/>
+      <c r="S143" s="24"/>
+      <c r="T143" s="24"/>
+      <c r="U143" s="24"/>
+      <c r="V143" s="24"/>
+      <c r="W143" s="24"/>
+      <c r="X143" s="24"/>
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
+      <c r="A144" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C144" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E144" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F144" s="26">
+        <f t="shared" ref="F144:G144" si="27">SUM(F145:F147)</f>
+        <v>25</v>
+      </c>
+      <c r="G144" s="26">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="H144" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="I144" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J144" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K144" s="24"/>
+      <c r="L144" s="24"/>
+      <c r="M144" s="24"/>
+      <c r="N144" s="24"/>
+      <c r="O144" s="24"/>
+      <c r="P144" s="24"/>
+      <c r="Q144" s="24"/>
+      <c r="R144" s="24"/>
+      <c r="S144" s="24"/>
+      <c r="T144" s="24"/>
+      <c r="U144" s="24"/>
+      <c r="V144" s="24"/>
+      <c r="W144" s="24"/>
+      <c r="X144" s="24"/>
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
+      <c r="A145" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="B145" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C145" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E145" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F145" s="21">
+        <v>10.0</v>
+      </c>
+      <c r="G145" s="21"/>
+      <c r="H145" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="I145" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J145" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
+      <c r="A146" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="B146" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C146" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E146" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F146" s="21">
+        <v>10.0</v>
+      </c>
+      <c r="G146" s="21"/>
+      <c r="H146" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="I146" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J146" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
+      <c r="A147" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="B147" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C147" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="D147" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E147" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F147" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="G147" s="21"/>
+      <c r="H147" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="I147" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J147" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
+      <c r="A148" s="11" t="s">
+        <v>485</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>486</v>
+      </c>
+      <c r="D148" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E148" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F148" s="15">
+        <f t="shared" ref="F148:G148" si="28">SUM(F149:F151)</f>
+        <v>12</v>
+      </c>
+      <c r="G148" s="15">
+        <f t="shared" si="28"/>
+        <v>0</v>
+      </c>
+      <c r="H148" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="I148" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J148" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K148" s="24"/>
+      <c r="L148" s="24"/>
+      <c r="M148" s="24"/>
+      <c r="N148" s="24"/>
+      <c r="O148" s="24"/>
+      <c r="P148" s="24"/>
+      <c r="Q148" s="24"/>
+      <c r="R148" s="24"/>
+      <c r="S148" s="24"/>
+      <c r="T148" s="24"/>
+      <c r="U148" s="24"/>
+      <c r="V148" s="24"/>
+      <c r="W148" s="24"/>
+      <c r="X148" s="24"/>
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
+      <c r="A149" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="B149" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="D149" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E149" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F149" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G149" s="21"/>
+      <c r="H149" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="I149" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J149" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="16" t="s">
+        <v>491</v>
+      </c>
+      <c r="B150" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C150" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="D150" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E150" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F150" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G150" s="21"/>
+      <c r="H150" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="I150" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J150" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="B151" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C151" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="D151" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E151" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F151" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G151" s="25"/>
+      <c r="H151" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="I151" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J151" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="D152" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E152" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F152" s="15">
+        <f t="shared" ref="F152:G152" si="29">SUM(F153:F157)</f>
+        <v>19</v>
+      </c>
+      <c r="G152" s="15">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H140" s="11" t="s">
-        <v>464</v>
-      </c>
-      <c r="I140" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J140" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K140" s="24"/>
-      <c r="L140" s="24"/>
-      <c r="M140" s="24"/>
-      <c r="N140" s="24"/>
-      <c r="O140" s="24"/>
-      <c r="P140" s="24"/>
-      <c r="Q140" s="24"/>
-      <c r="R140" s="24"/>
-      <c r="S140" s="24"/>
-      <c r="T140" s="24"/>
-      <c r="U140" s="24"/>
-      <c r="V140" s="24"/>
-      <c r="W140" s="24"/>
-      <c r="X140" s="24"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="11" t="s">
-        <v>465</v>
-      </c>
-      <c r="B141" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C141" s="11" t="s">
-        <v>466</v>
-      </c>
-      <c r="D141" s="12" t="s">
+      <c r="H152" s="11" t="s">
+        <v>498</v>
+      </c>
+      <c r="I152" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J152" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K152" s="24"/>
+      <c r="L152" s="24"/>
+      <c r="M152" s="24"/>
+      <c r="N152" s="24"/>
+      <c r="O152" s="24"/>
+      <c r="P152" s="24"/>
+      <c r="Q152" s="24"/>
+      <c r="R152" s="24"/>
+      <c r="S152" s="24"/>
+      <c r="T152" s="24"/>
+      <c r="U152" s="24"/>
+      <c r="V152" s="24"/>
+      <c r="W152" s="24"/>
+      <c r="X152" s="24"/>
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="B153" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C153" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="D153" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E153" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F153" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G153" s="21"/>
+      <c r="H153" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="I153" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J153" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="B154" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C154" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="D154" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E141" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F141" s="26">
-        <f t="shared" ref="F141:G141" si="30">SUM(F142:F144)</f>
-        <v>25</v>
-      </c>
-      <c r="G141" s="26">
-        <f t="shared" si="30"/>
-        <v>0</v>
-      </c>
-      <c r="H141" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="I141" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J141" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K141" s="24"/>
-      <c r="L141" s="24"/>
-      <c r="M141" s="24"/>
-      <c r="N141" s="24"/>
-      <c r="O141" s="24"/>
-      <c r="P141" s="24"/>
-      <c r="Q141" s="24"/>
-      <c r="R141" s="24"/>
-      <c r="S141" s="24"/>
-      <c r="T141" s="24"/>
-      <c r="U141" s="24"/>
-      <c r="V141" s="24"/>
-      <c r="W141" s="24"/>
-      <c r="X141" s="24"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="20" t="s">
-        <v>468</v>
-      </c>
-      <c r="B142" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C142" s="20" t="s">
-        <v>469</v>
-      </c>
-      <c r="D142" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E142" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F142" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="G142" s="23"/>
-      <c r="H142" s="20" t="s">
-        <v>470</v>
-      </c>
-      <c r="I142" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J142" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="20" t="s">
-        <v>471</v>
-      </c>
-      <c r="B143" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C143" s="20" t="s">
-        <v>472</v>
-      </c>
-      <c r="D143" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E143" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F143" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="G143" s="23"/>
-      <c r="H143" s="20" t="s">
-        <v>470</v>
-      </c>
-      <c r="I143" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J143" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="20" t="s">
-        <v>473</v>
-      </c>
-      <c r="B144" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C144" s="20" t="s">
-        <v>474</v>
-      </c>
-      <c r="D144" s="21" t="s">
+      <c r="E154" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F154" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G154" s="21"/>
+      <c r="H154" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="I154" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J154" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="B155" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C155" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="D155" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E144" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F144" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="G144" s="23"/>
-      <c r="H144" s="20" t="s">
-        <v>475</v>
-      </c>
-      <c r="I144" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J144" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="11" t="s">
-        <v>476</v>
-      </c>
-      <c r="B145" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C145" s="11" t="s">
-        <v>477</v>
-      </c>
-      <c r="D145" s="12" t="s">
+      <c r="E155" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F155" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G155" s="21"/>
+      <c r="H155" s="16" t="s">
+        <v>507</v>
+      </c>
+      <c r="I155" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J155" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="B156" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C156" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="D156" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="E156" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F156" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G156" s="25"/>
+      <c r="H156" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="I156" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J156" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="B157" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C157" s="16" t="s">
+        <v>512</v>
+      </c>
+      <c r="D157" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="E145" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F145" s="14">
-        <f t="shared" ref="F145:G145" si="31">SUM(F146:F148)</f>
-        <v>12</v>
-      </c>
-      <c r="G145" s="14">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H145" s="11" t="s">
-        <v>478</v>
-      </c>
-      <c r="I145" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J145" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K145" s="24"/>
-      <c r="L145" s="24"/>
-      <c r="M145" s="24"/>
-      <c r="N145" s="24"/>
-      <c r="O145" s="24"/>
-      <c r="P145" s="24"/>
-      <c r="Q145" s="24"/>
-      <c r="R145" s="24"/>
-      <c r="S145" s="24"/>
-      <c r="T145" s="24"/>
-      <c r="U145" s="24"/>
-      <c r="V145" s="24"/>
-      <c r="W145" s="24"/>
-      <c r="X145" s="24"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="20" t="s">
-        <v>479</v>
-      </c>
-      <c r="B146" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C146" s="20" t="s">
-        <v>480</v>
-      </c>
-      <c r="D146" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E146" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F146" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G146" s="23"/>
-      <c r="H146" s="20" t="s">
-        <v>481</v>
-      </c>
-      <c r="I146" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J146" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="20" t="s">
-        <v>482</v>
-      </c>
-      <c r="B147" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C147" s="20" t="s">
-        <v>483</v>
-      </c>
-      <c r="D147" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E147" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F147" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G147" s="23"/>
-      <c r="H147" s="20" t="s">
-        <v>481</v>
-      </c>
-      <c r="I147" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J147" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="20" t="s">
-        <v>484</v>
-      </c>
-      <c r="B148" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C148" s="20" t="s">
-        <v>485</v>
-      </c>
-      <c r="D148" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="E148" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F148" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G148" s="25"/>
-      <c r="H148" s="20" t="s">
-        <v>486</v>
-      </c>
-      <c r="I148" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J148" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="B149" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C149" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="D149" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E149" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F149" s="14">
-        <f t="shared" ref="F149:G149" si="32">SUM(F150:F154)</f>
-        <v>19</v>
-      </c>
-      <c r="G149" s="14">
-        <f t="shared" si="32"/>
-        <v>0</v>
-      </c>
-      <c r="H149" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="I149" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J149" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
-      <c r="R149" s="24"/>
-      <c r="S149" s="24"/>
-      <c r="T149" s="24"/>
-      <c r="U149" s="24"/>
-      <c r="V149" s="24"/>
-      <c r="W149" s="24"/>
-      <c r="X149" s="24"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="20" t="s">
-        <v>490</v>
-      </c>
-      <c r="B150" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C150" s="20" t="s">
-        <v>491</v>
-      </c>
-      <c r="D150" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E150" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F150" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G150" s="23"/>
-      <c r="H150" s="20" t="s">
-        <v>492</v>
-      </c>
-      <c r="I150" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J150" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="20" t="s">
-        <v>493</v>
-      </c>
-      <c r="B151" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C151" s="20" t="s">
-        <v>494</v>
-      </c>
-      <c r="D151" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E151" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F151" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G151" s="23"/>
-      <c r="H151" s="20" t="s">
-        <v>495</v>
-      </c>
-      <c r="I151" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J151" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="20" t="s">
-        <v>496</v>
-      </c>
-      <c r="B152" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C152" s="20" t="s">
-        <v>497</v>
-      </c>
-      <c r="D152" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E152" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F152" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G152" s="23"/>
-      <c r="H152" s="20" t="s">
-        <v>498</v>
-      </c>
-      <c r="I152" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J152" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="20" t="s">
-        <v>499</v>
-      </c>
-      <c r="B153" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C153" s="20" t="s">
-        <v>500</v>
-      </c>
-      <c r="D153" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="E153" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F153" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G153" s="25"/>
-      <c r="H153" s="20" t="s">
-        <v>501</v>
-      </c>
-      <c r="I153" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J153" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="20" t="s">
-        <v>502</v>
-      </c>
-      <c r="B154" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C154" s="20" t="s">
-        <v>503</v>
-      </c>
-      <c r="D154" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E154" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F154" s="23">
+      <c r="E157" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F157" s="21">
         <v>3.0</v>
       </c>
-      <c r="G154" s="23"/>
-      <c r="H154" s="20" t="s">
-        <v>504</v>
-      </c>
-      <c r="I154" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J154" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="11" t="s">
-        <v>505</v>
-      </c>
-      <c r="B155" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C155" s="11" t="s">
-        <v>506</v>
-      </c>
-      <c r="D155" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E155" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F155" s="26">
-        <f t="shared" ref="F155:G155" si="33">SUM(F156:F157)</f>
-        <v>6</v>
-      </c>
-      <c r="G155" s="26">
-        <f t="shared" si="33"/>
-        <v>0</v>
-      </c>
-      <c r="H155" s="11" t="s">
-        <v>507</v>
-      </c>
-      <c r="I155" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J155" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K155" s="24"/>
-      <c r="L155" s="24"/>
-      <c r="M155" s="24"/>
-      <c r="N155" s="24"/>
-      <c r="O155" s="24"/>
-      <c r="P155" s="24"/>
-      <c r="Q155" s="24"/>
-      <c r="R155" s="24"/>
-      <c r="S155" s="24"/>
-      <c r="T155" s="24"/>
-      <c r="U155" s="24"/>
-      <c r="V155" s="24"/>
-      <c r="W155" s="24"/>
-      <c r="X155" s="24"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="20" t="s">
-        <v>508</v>
-      </c>
-      <c r="B156" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C156" s="20" t="s">
-        <v>509</v>
-      </c>
-      <c r="D156" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E156" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F156" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="G156" s="25"/>
-      <c r="H156" s="20" t="s">
-        <v>510</v>
-      </c>
-      <c r="I156" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J156" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="20" t="s">
-        <v>511</v>
-      </c>
-      <c r="B157" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C157" s="20" t="s">
-        <v>512</v>
-      </c>
-      <c r="D157" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E157" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F157" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="G157" s="23"/>
-      <c r="H157" s="20" t="s">
+      <c r="G157" s="21"/>
+      <c r="H157" s="16" t="s">
         <v>513</v>
       </c>
-      <c r="I157" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J157" s="20" t="s">
-        <v>31</v>
+      <c r="I157" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J157" s="16" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
@@ -7729,33 +7745,33 @@
         <v>514</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C158" s="11" t="s">
         <v>515</v>
       </c>
       <c r="D158" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E158" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F158" s="26">
+        <f t="shared" ref="F158:G158" si="30">SUM(F159:F160)</f>
+        <v>6</v>
+      </c>
+      <c r="G158" s="26">
+        <f t="shared" si="30"/>
+        <v>0</v>
+      </c>
+      <c r="H158" s="11" t="s">
         <v>516</v>
       </c>
-      <c r="E158" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F158" s="26">
-        <f t="shared" ref="F158:G158" si="34">F159+F163+F166+F169</f>
-        <v>60</v>
-      </c>
-      <c r="G158" s="26">
-        <f t="shared" si="34"/>
-        <v>0</v>
-      </c>
-      <c r="H158" s="11" t="s">
-        <v>517</v>
-      </c>
       <c r="I158" s="13" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="J158" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K158" s="24"/>
       <c r="L158" s="24"/>
@@ -7773,527 +7789,626 @@
       <c r="X158" s="24"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="11" t="s">
+      <c r="A159" s="16" t="s">
+        <v>517</v>
+      </c>
+      <c r="B159" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C159" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B159" s="11" t="s">
+      <c r="D159" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E159" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F159" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G159" s="25"/>
+      <c r="H159" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="I159" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J159" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="B160" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C160" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="D160" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E160" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F160" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G160" s="21"/>
+      <c r="H160" s="16" t="s">
+        <v>522</v>
+      </c>
+      <c r="I160" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J160" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="B161" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C161" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="D161" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="E161" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F161" s="26">
+        <f t="shared" ref="F161:G161" si="31">F162+F166+F169+F172</f>
+        <v>60</v>
+      </c>
+      <c r="G161" s="26">
+        <f t="shared" si="31"/>
+        <v>0</v>
+      </c>
+      <c r="H161" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="I161" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J161" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K161" s="24"/>
+      <c r="L161" s="24"/>
+      <c r="M161" s="24"/>
+      <c r="N161" s="24"/>
+      <c r="O161" s="24"/>
+      <c r="P161" s="24"/>
+      <c r="Q161" s="24"/>
+      <c r="R161" s="24"/>
+      <c r="S161" s="24"/>
+      <c r="T161" s="24"/>
+      <c r="U161" s="24"/>
+      <c r="V161" s="24"/>
+      <c r="W161" s="24"/>
+      <c r="X161" s="24"/>
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="B162" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C159" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="D159" s="12" t="s">
+      <c r="C162" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="D162" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E159" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F159" s="14">
-        <f t="shared" ref="F159:G159" si="35">SUM(F160:F162)</f>
+      <c r="E162" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F162" s="15">
+        <f t="shared" ref="F162:G162" si="32">SUM(F163:F165)</f>
         <v>12</v>
       </c>
-      <c r="G159" s="14">
+      <c r="G162" s="15">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H162" s="11" t="s">
+        <v>529</v>
+      </c>
+      <c r="I162" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J162" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K162" s="24"/>
+      <c r="L162" s="24"/>
+      <c r="M162" s="24"/>
+      <c r="N162" s="24"/>
+      <c r="O162" s="24"/>
+      <c r="P162" s="24"/>
+      <c r="Q162" s="24"/>
+      <c r="R162" s="24"/>
+      <c r="S162" s="24"/>
+      <c r="T162" s="24"/>
+      <c r="U162" s="24"/>
+      <c r="V162" s="24"/>
+      <c r="W162" s="24"/>
+      <c r="X162" s="24"/>
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
+      <c r="A163" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="B163" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C163" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="D163" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E163" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F163" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G163" s="21"/>
+      <c r="H163" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="I163" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J163" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
+      <c r="A164" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="B164" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C164" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="D164" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E164" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F164" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G164" s="21"/>
+      <c r="H164" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="I164" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J164" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="B165" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C165" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="D165" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="E165" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F165" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G165" s="21"/>
+      <c r="H165" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="I165" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J165" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="11" t="s">
+        <v>539</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C166" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="D166" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E166" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F166" s="26">
+        <f t="shared" ref="F166:G166" si="33">SUM(F167:F168)</f>
+        <v>8</v>
+      </c>
+      <c r="G166" s="26">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+      <c r="H166" s="11" t="s">
+        <v>541</v>
+      </c>
+      <c r="I166" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J166" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K166" s="24"/>
+      <c r="L166" s="24"/>
+      <c r="M166" s="24"/>
+      <c r="N166" s="24"/>
+      <c r="O166" s="24"/>
+      <c r="P166" s="24"/>
+      <c r="Q166" s="24"/>
+      <c r="R166" s="24"/>
+      <c r="S166" s="24"/>
+      <c r="T166" s="24"/>
+      <c r="U166" s="24"/>
+      <c r="V166" s="24"/>
+      <c r="W166" s="24"/>
+      <c r="X166" s="24"/>
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="B167" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C167" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="D167" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E167" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F167" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="G167" s="38"/>
+      <c r="H167" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="I167" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J167" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="B168" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C168" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="D168" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="E168" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F168" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G168" s="38"/>
+      <c r="H168" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="I168" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J168" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="B169" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C169" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="D169" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="E169" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F169" s="21">
+        <f t="shared" ref="F169:G169" si="34">SUM(F170:F171)</f>
+        <v>8</v>
+      </c>
+      <c r="G169" s="38">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="H169" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="I169" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J169" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="B170" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="D170" s="18" t="s">
+        <v>195</v>
+      </c>
+      <c r="E170" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F170" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G170" s="38"/>
+      <c r="H170" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="I170" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J170" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="B171" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C171" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="D171" s="18" t="s">
+        <v>556</v>
+      </c>
+      <c r="E171" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F171" s="21">
+        <v>4.0</v>
+      </c>
+      <c r="G171" s="38"/>
+      <c r="H171" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="I171" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J171" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="11" t="s">
+        <v>558</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C172" s="11" t="s">
+        <v>559</v>
+      </c>
+      <c r="D172" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E172" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F172" s="26">
+        <f t="shared" ref="F172:G172" si="35">SUM(F173:F176)</f>
+        <v>32</v>
+      </c>
+      <c r="G172" s="39">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="H159" s="11" t="s">
-        <v>520</v>
-      </c>
-      <c r="I159" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J159" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K159" s="24"/>
-      <c r="L159" s="24"/>
-      <c r="M159" s="24"/>
-      <c r="N159" s="24"/>
-      <c r="O159" s="24"/>
-      <c r="P159" s="24"/>
-      <c r="Q159" s="24"/>
-      <c r="R159" s="24"/>
-      <c r="S159" s="24"/>
-      <c r="T159" s="24"/>
-      <c r="U159" s="24"/>
-      <c r="V159" s="24"/>
-      <c r="W159" s="24"/>
-      <c r="X159" s="24"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="20" t="s">
-        <v>521</v>
-      </c>
-      <c r="B160" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C160" s="20" t="s">
-        <v>522</v>
-      </c>
-      <c r="D160" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E160" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F160" s="23">
+      <c r="H172" s="11" t="s">
+        <v>560</v>
+      </c>
+      <c r="I172" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="J172" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K172" s="24"/>
+      <c r="L172" s="24"/>
+      <c r="M172" s="24"/>
+      <c r="N172" s="24"/>
+      <c r="O172" s="24"/>
+      <c r="P172" s="24"/>
+      <c r="Q172" s="24"/>
+      <c r="R172" s="24"/>
+      <c r="S172" s="24"/>
+      <c r="T172" s="24"/>
+      <c r="U172" s="24"/>
+      <c r="V172" s="24"/>
+      <c r="W172" s="24"/>
+      <c r="X172" s="24"/>
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="B173" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C173" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="D173" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E173" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F173" s="21">
+        <v>3.0</v>
+      </c>
+      <c r="G173" s="38"/>
+      <c r="H173" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="I173" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J173" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="B174" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C174" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="D174" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E174" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F174" s="21">
         <v>4.0</v>
       </c>
-      <c r="G160" s="23"/>
-      <c r="H160" s="20" t="s">
-        <v>523</v>
-      </c>
-      <c r="I160" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J160" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="20" t="s">
-        <v>524</v>
-      </c>
-      <c r="B161" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C161" s="20" t="s">
-        <v>525</v>
-      </c>
-      <c r="D161" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E161" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F161" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G161" s="23"/>
-      <c r="H161" s="20" t="s">
-        <v>526</v>
-      </c>
-      <c r="I161" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J161" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="20" t="s">
-        <v>527</v>
-      </c>
-      <c r="B162" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C162" s="20" t="s">
-        <v>528</v>
-      </c>
-      <c r="D162" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E162" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F162" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G162" s="23"/>
-      <c r="H162" s="20" t="s">
-        <v>529</v>
-      </c>
-      <c r="I162" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J162" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="11" t="s">
-        <v>530</v>
-      </c>
-      <c r="B163" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C163" s="11" t="s">
-        <v>531</v>
-      </c>
-      <c r="D163" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E163" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F163" s="26">
-        <f t="shared" ref="F163:G163" si="36">SUM(F164:F165)</f>
-        <v>8</v>
-      </c>
-      <c r="G163" s="26">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="H163" s="11" t="s">
-        <v>532</v>
-      </c>
-      <c r="I163" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J163" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K163" s="24"/>
-      <c r="L163" s="24"/>
-      <c r="M163" s="24"/>
-      <c r="N163" s="24"/>
-      <c r="O163" s="24"/>
-      <c r="P163" s="24"/>
-      <c r="Q163" s="24"/>
-      <c r="R163" s="24"/>
-      <c r="S163" s="24"/>
-      <c r="T163" s="24"/>
-      <c r="U163" s="24"/>
-      <c r="V163" s="24"/>
-      <c r="W163" s="24"/>
-      <c r="X163" s="24"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="20" t="s">
-        <v>533</v>
-      </c>
-      <c r="B164" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C164" s="20" t="s">
-        <v>534</v>
-      </c>
-      <c r="D164" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E164" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="F164" s="23">
+      <c r="G174" s="38"/>
+      <c r="H174" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="I174" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J174" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="B175" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C175" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D175" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="E175" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F175" s="21">
         <v>5.0</v>
       </c>
-      <c r="G164" s="38"/>
-      <c r="H164" s="20" t="s">
-        <v>535</v>
-      </c>
-      <c r="I164" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J164" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="20" t="s">
-        <v>536</v>
-      </c>
-      <c r="B165" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C165" s="20" t="s">
-        <v>537</v>
-      </c>
-      <c r="D165" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E165" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="F165" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="G165" s="38"/>
-      <c r="H165" s="20" t="s">
-        <v>538</v>
-      </c>
-      <c r="I165" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J165" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="20" t="s">
-        <v>539</v>
-      </c>
-      <c r="B166" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C166" s="20" t="s">
-        <v>540</v>
-      </c>
-      <c r="D166" s="21" t="s">
-        <v>516</v>
-      </c>
-      <c r="E166" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F166" s="23">
-        <f t="shared" ref="F166:G166" si="37">SUM(F167:F168)</f>
-        <v>8</v>
-      </c>
-      <c r="G166" s="38">
-        <f t="shared" si="37"/>
-        <v>0</v>
-      </c>
-      <c r="H166" s="20" t="s">
-        <v>541</v>
-      </c>
-      <c r="I166" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J166" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="20" t="s">
-        <v>542</v>
-      </c>
-      <c r="B167" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C167" s="20" t="s">
-        <v>543</v>
-      </c>
-      <c r="D167" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E167" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F167" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G167" s="38"/>
-      <c r="H167" s="20" t="s">
-        <v>544</v>
-      </c>
-      <c r="I167" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J167" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="20" t="s">
-        <v>545</v>
-      </c>
-      <c r="B168" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C168" s="20" t="s">
-        <v>546</v>
-      </c>
-      <c r="D168" s="21" t="s">
-        <v>547</v>
-      </c>
-      <c r="E168" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="F168" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G168" s="38"/>
-      <c r="H168" s="20" t="s">
-        <v>548</v>
-      </c>
-      <c r="I168" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J168" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="11" t="s">
-        <v>549</v>
-      </c>
-      <c r="B169" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C169" s="11" t="s">
-        <v>550</v>
-      </c>
-      <c r="D169" s="12" t="s">
+      <c r="G175" s="38"/>
+      <c r="H175" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="I175" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J175" s="16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="B176" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C176" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="D176" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E169" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F169" s="26">
-        <f t="shared" ref="F169:G169" si="38">SUM(F170:F173)</f>
-        <v>32</v>
-      </c>
-      <c r="G169" s="39">
-        <f t="shared" si="38"/>
-        <v>0</v>
-      </c>
-      <c r="H169" s="11" t="s">
-        <v>551</v>
-      </c>
-      <c r="I169" s="13" t="s">
-        <v>332</v>
-      </c>
-      <c r="J169" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="K169" s="24"/>
-      <c r="L169" s="24"/>
-      <c r="M169" s="24"/>
-      <c r="N169" s="24"/>
-      <c r="O169" s="24"/>
-      <c r="P169" s="24"/>
-      <c r="Q169" s="24"/>
-      <c r="R169" s="24"/>
-      <c r="S169" s="24"/>
-      <c r="T169" s="24"/>
-      <c r="U169" s="24"/>
-      <c r="V169" s="24"/>
-      <c r="W169" s="24"/>
-      <c r="X169" s="24"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="20" t="s">
-        <v>552</v>
-      </c>
-      <c r="B170" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C170" s="20" t="s">
-        <v>553</v>
-      </c>
-      <c r="D170" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E170" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="F170" s="23">
-        <v>3.0</v>
-      </c>
-      <c r="G170" s="38"/>
-      <c r="H170" s="20" t="s">
-        <v>554</v>
-      </c>
-      <c r="I170" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J170" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="20" t="s">
-        <v>555</v>
-      </c>
-      <c r="B171" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C171" s="20" t="s">
-        <v>556</v>
-      </c>
-      <c r="D171" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E171" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F171" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G171" s="38"/>
-      <c r="H171" s="20" t="s">
-        <v>557</v>
-      </c>
-      <c r="I171" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J171" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="20" t="s">
-        <v>558</v>
-      </c>
-      <c r="B172" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C172" s="20" t="s">
-        <v>559</v>
-      </c>
-      <c r="D172" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E172" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F172" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="G172" s="38"/>
-      <c r="H172" s="20" t="s">
-        <v>560</v>
-      </c>
-      <c r="I172" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J172" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="20" t="s">
-        <v>561</v>
-      </c>
-      <c r="B173" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C173" s="20" t="s">
-        <v>562</v>
-      </c>
-      <c r="D173" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E173" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F173" s="23">
+      <c r="E176" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F176" s="21">
         <v>20.0</v>
       </c>
-      <c r="G173" s="38"/>
-      <c r="H173" s="20" t="s">
-        <v>563</v>
-      </c>
-      <c r="I173" s="22" t="s">
-        <v>332</v>
-      </c>
-      <c r="J173" s="20" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="I174" s="40"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="C175" s="41"/>
-      <c r="I175" s="40"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="I176" s="40"/>
+      <c r="G176" s="38"/>
+      <c r="H176" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="I176" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J176" s="16" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="I177" s="40"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
+      <c r="C178" s="41"/>
       <c r="I178" s="40"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -10777,9 +10892,15 @@
     <row r="1005" ht="15.75" customHeight="1">
       <c r="I1005" s="40"/>
     </row>
-    <row r="1006" ht="15.75" customHeight="1"/>
-    <row r="1007" ht="15.75" customHeight="1"/>
-    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1">
+      <c r="I1006" s="40"/>
+    </row>
+    <row r="1007" ht="15.75" customHeight="1">
+      <c r="I1007" s="40"/>
+    </row>
+    <row r="1008" ht="15.75" customHeight="1">
+      <c r="I1008" s="40"/>
+    </row>
     <row r="1009" ht="15.75" customHeight="1"/>
     <row r="1010" ht="15.75" customHeight="1"/>
     <row r="1011" ht="15.75" customHeight="1"/>
@@ -10789,33 +10910,36 @@
     <row r="1015" ht="15.75" customHeight="1"/>
     <row r="1016" ht="15.75" customHeight="1"/>
     <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="I2:I1005">
+  <conditionalFormatting sqref="I2:I1008">
     <cfRule type="cellIs" dxfId="5" priority="1" stopIfTrue="1" operator="equal">
       <formula>"Realizado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I1005">
+  <conditionalFormatting sqref="I2:I1008">
     <cfRule type="cellIs" dxfId="6" priority="2" stopIfTrue="1" operator="equal">
       <formula>"En progreso"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I1005">
+  <conditionalFormatting sqref="I2:I1008">
     <cfRule type="cellIs" dxfId="7" priority="3" stopIfTrue="1" operator="equal">
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I1005">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I1008">
       <formula1>"Pendiente,En progreso,Realizado"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="B2:B67">
       <formula1>"Épica,Historia,Tarea"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F173">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F176">
       <formula1>AND(ISNUMBER(F2),(NOT(OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" sqref="D2:D173">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" sqref="D2:D176">
       <formula1>"OE1,OE2,OE3,OG,OE4,OE2, OE3,OE1, OE2, OE3,OG, OE1, OE2, OE3,OG, OE1, OE2, OE3, OE4,OE1, OE2,OG, OE1, OE2, OE4,OG, OE2, OE3, OE4,OE1, OE2, OE3, OE4,OG, OE3, OE4,OG, OE3, OE4,OG, OE3"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="E2:E67">
@@ -10882,158 +11006,158 @@
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>74</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>73</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>20</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A2,Backlog!I:I,"Realizado")</f>
         <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B3" s="4">
         <v>46297.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D3" s="3">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>74</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>77</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>43</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A3,Backlog!I:I,"Realizado")</f>
         <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="14">
+        <v>46325.0</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B4" s="15">
-        <v>46325.0</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="D4" s="3">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
-        <v>110</v>
-      </c>
-      <c r="E4" s="8">
+        <v>117</v>
+      </c>
+      <c r="E4" s="7">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
-        <v>12</v>
-      </c>
-      <c r="F4" s="8">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
-        <v>43</v>
-      </c>
-      <c r="G4" s="8">
+        <v>46</v>
+      </c>
+      <c r="G4" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A4,Backlog!I:I,"Realizado")</f>
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B5" s="4">
         <v>46360.0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="7">
+        <v>34</v>
+      </c>
+      <c r="D5" s="6">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
         <v>122</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
         <v>24</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A5,Backlog!I:I,"Realizado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
+        <v>41</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="18">
+      <c r="A8" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="22">
         <f>SUM(D2:D5)</f>
-        <v>380</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
+        <v>387</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="18">
+      <c r="A9" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="22">
         <f>SUM(E2:E5)</f>
-        <v>162</v>
-      </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <f>SUM(F2:F5)</f>
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <f>SUM(G2:G5)</f>
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/docs/Backlog Proyecto Titulo.xlsx
+++ b/docs/Backlog Proyecto Titulo.xlsx
@@ -41,9 +41,15 @@
     <t>Problema, investigación, objetivos y requerimientos</t>
   </si>
   <si>
+    <t>Etapa 2</t>
+  </si>
+  <si>
     <t>ID</t>
   </si>
   <si>
+    <t>Diseño técnico, arquitectura, protocolo e implementación inicial</t>
+  </si>
+  <si>
     <t>Tipo</t>
   </si>
   <si>
@@ -56,16 +62,16 @@
     <t>Prioridad</t>
   </si>
   <si>
+    <t>Etapa 3</t>
+  </si>
+  <si>
     <t>Esfuerzo estimado (h)</t>
   </si>
   <si>
-    <t>Etapa 2</t>
-  </si>
-  <si>
     <t>Esfuerzo real (h)</t>
   </si>
   <si>
-    <t>Diseño técnico, arquitectura, protocolo e implementación inicial</t>
+    <t>Implementación observabilidad, pruebas piloto y validación preliminar</t>
   </si>
   <si>
     <t>Criterios de aceptación / entregables</t>
@@ -77,6 +83,12 @@
     <t>EP-01</t>
   </si>
   <si>
+    <t>Etapa 4</t>
+  </si>
+  <si>
+    <t>Campaña definitiva, análisis, informe final y defensa</t>
+  </si>
+  <si>
     <t>Épica</t>
   </si>
   <si>
@@ -89,10 +101,16 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Etapa 3</t>
-  </si>
-  <si>
-    <t>Implementación observabilidad, pruebas piloto y validación preliminar</t>
+    <t>Indicador</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
+    <t>Total de horas estimadas (tareas)</t>
+  </si>
+  <si>
+    <t>Total de horas reales (tareas)</t>
   </si>
   <si>
     <t>Problema, estado del arte, objetivos, requerimientos y alternativas definidos y respaldados.</t>
@@ -113,12 +131,6 @@
     <t>OG, OE1, OE2, OE4</t>
   </si>
   <si>
-    <t>Etapa 4</t>
-  </si>
-  <si>
-    <t>Campaña definitiva, análisis, informe final y defensa</t>
-  </si>
-  <si>
     <t>Conjunto de fuentes académicas y técnicas organizado en BibTeX y utilizado en el informe.</t>
   </si>
   <si>
@@ -134,21 +146,9 @@
     <t>OE1, OE2</t>
   </si>
   <si>
-    <t>Indicador</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Total de horas estimadas (tareas)</t>
-  </si>
-  <si>
     <t>Fichas bibliográficas sobre K3s, MicroK8s y métricas de CPU, memoria, throughput y latencia.</t>
   </si>
   <si>
-    <t>Total de horas reales (tareas)</t>
-  </si>
-  <si>
     <t>T-01.2</t>
   </si>
   <si>
@@ -1064,18 +1064,18 @@
     <t>Fallo controlado y recuperación medibles sin pérdida intencional de quórum.</t>
   </si>
   <si>
+    <t>T-19.1</t>
+  </si>
+  <si>
+    <t>Implementar procedimiento/script de fallo controlado de un nodo</t>
+  </si>
+  <si>
+    <t>Fallo reproducible sobre un único nodo.</t>
+  </si>
+  <si>
     <t>Pendiente</t>
   </si>
   <si>
-    <t>T-19.1</t>
-  </si>
-  <si>
-    <t>Implementar procedimiento/script de fallo controlado de un nodo</t>
-  </si>
-  <si>
-    <t>Fallo reproducible sobre un único nodo.</t>
-  </si>
-  <si>
     <t>T-19.2</t>
   </si>
   <si>
@@ -1091,42 +1091,42 @@
     <t>Integrar solicitudes afectadas con resultados k6</t>
   </si>
   <si>
-    <t>Cantidad de solicitudes afectadas asociada al intervalo de fallo.</t>
+    <t>Cantidad de solicitudes afectadas asociada al intervalo de fallo. Si la tasa de carga es provisional (T-20.5 pendiente), las corridas se marcan como verificación y no como piloto.</t>
   </si>
   <si>
     <t>T-19.4</t>
   </si>
   <si>
-    <t>Fijar ubicación del pod de NGINX durante el fallo y verificar parámetros efectivos de detección y tolerancia en cada distribución</t>
-  </si>
-  <si>
-    <t>Ubicación del pod definida; valores efectivos de detección y tolerancia registrados por distribución y diferencias documentadas.</t>
+    <t>Fijar ubicación del pod de NGINX durante el fallo y verificar parámetros de detección y tolerancia</t>
+  </si>
+  <si>
+    <t>Regla de ubicación implementada: al inyectar el fallo el pod no está en el nodo titular de la VIP (se mueve si coincide); valores efectivos de detección y tolerancia registrados por distribución y diferencias documentadas.</t>
   </si>
   <si>
     <t>T-19.5</t>
   </si>
   <si>
-    <t>Tratar el titular de la VIP y revalidar su migración con kube-vip v1.2.4</t>
-  </si>
-  <si>
-    <t>Estrategia sobre el titular de la VIP decidida y documentada; migración de la VIP revalidada con kube-vip v1.2.4 en ambas distribuciones.</t>
+    <t>Revalidar la migración de la VIP con kube-vip v1.2.4</t>
+  </si>
+  <si>
+    <t>Migración de la VIP revalidada con kube-vip v1.2.4 en K3s y MicroK8s; titular de la VIP registrado en cada corrida, sin control del arranque.</t>
   </si>
   <si>
     <t>HU-32</t>
   </si>
   <si>
+    <t>Orquestación de ejecuciones experimentales</t>
+  </si>
+  <si>
+    <t>Cada ejecución queda registrada con distribución, escenario, repetición y ventana temporal, y deja datos aptos para el análisis.</t>
+  </si>
+  <si>
+    <t>T-32.1</t>
+  </si>
+  <si>
     <t>Implementar orquestador de ejecuciones con metadatos de ventana y ubicación</t>
   </si>
   <si>
-    <t>Cada ejecución queda registrada con distribución, escenario, repetición y ventana temporal, y deja datos aptos para el análisis.</t>
-  </si>
-  <si>
-    <t>T-32.1</t>
-  </si>
-  <si>
-    <t>Implementar orquestador de ejecuciones (metadatos de ventana y de ubicación: nodo de la VIP del plano de control, nodo de la VIP del servicio y nodo del pod; etiqueta distribution; snapshot de Prometheus y estabilización)</t>
-  </si>
-  <si>
     <t>Script versionado que ejecuta una repetición completa y guarda metadatos, resultados de k6 y snapshot de Prometheus.</t>
   </si>
   <si>
@@ -1244,7 +1244,7 @@
     <t>Caracterizar reposo del host y fijar política de servicios</t>
   </si>
   <si>
-    <t>Consumo en reposo del host caracterizado con y sin sesión gráfica; política de servicios del host definida y documentada antes de T-20.1.</t>
+    <t>Consumo en reposo del host caracterizado con y sin sesión gráfica; política de servicios y de fuentes externas de chrony definida; criterio de reloj convergido antes de lanzar k6 y tratamiento de ufw documentados, antes de T-20.1.</t>
   </si>
   <si>
     <t>HU-21</t>
@@ -1854,6 +1854,9 @@
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1869,28 +1872,13 @@
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1898,6 +1886,18 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -2306,263 +2306,263 @@
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
       <c r="A1" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="15">
+      <c r="B2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="17">
         <f t="shared" ref="F2:G2" si="1">F3+F8+F12+F16+F22</f>
         <v>74</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="17">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" s="11" t="s">
+      <c r="H2" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="15">
+      <c r="A3" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="17">
         <f t="shared" ref="F3:G3" si="2">SUM(F4:F7)</f>
         <v>19</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="17">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="H3" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="11" t="s">
+      <c r="H3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="23">
+        <v>6.0</v>
+      </c>
+      <c r="G4" s="23">
+        <v>8.0</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="G5" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="G6" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="G7" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="21">
-        <v>6.0</v>
-      </c>
-      <c r="G4" s="21">
-        <v>8.0</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="21">
-        <v>5.0</v>
-      </c>
-      <c r="G5" s="21">
-        <v>5.0</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="21">
-        <v>5.0</v>
-      </c>
-      <c r="G6" s="21">
-        <v>4.0</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="21">
-        <v>3.0</v>
-      </c>
-      <c r="G7" s="21">
-        <v>3.0</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="15">
+      <c r="E8" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="17">
         <f t="shared" ref="F8:G8" si="3">SUM(F9:F11)</f>
         <v>12</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="17">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
-      <c r="H8" s="11" t="s">
+      <c r="H8" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="11" t="s">
+      <c r="I8" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="12" t="s">
         <v>7</v>
       </c>
       <c r="K8" s="24"/>
@@ -2581,132 +2581,132 @@
       <c r="X8" s="24"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="21">
+      <c r="E9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="23">
         <v>5.0</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="23">
         <v>5.0</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="16" t="s">
+      <c r="I9" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="21">
+      <c r="E10" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F10" s="23">
         <v>3.0</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="23">
         <v>3.0</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="16" t="s">
+      <c r="I10" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="21">
+      <c r="E11" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="23">
         <v>4.0</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="23">
         <v>4.0</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="16" t="s">
+      <c r="I11" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="B12" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="15">
+      <c r="D12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="17">
         <f t="shared" ref="F12:G12" si="4">SUM(F13:F15)</f>
         <v>11</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="17">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="11" t="s">
+      <c r="I12" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>7</v>
       </c>
       <c r="K12" s="24"/>
@@ -2725,132 +2725,132 @@
       <c r="X12" s="24"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="21">
+      <c r="D13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13" s="23">
         <v>4.0</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="23">
         <v>4.0</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I13" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="16" t="s">
+      <c r="I13" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="21">
+      <c r="E14" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="23">
         <v>3.0</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="23">
         <v>3.0</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="16" t="s">
+      <c r="I14" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="21">
+      <c r="D15" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="23">
         <v>4.0</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="23">
         <v>4.0</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="16" t="s">
+      <c r="I15" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="E16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="17">
         <f t="shared" ref="F16:G16" si="5">SUM(F17:F21)</f>
         <v>17</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="17">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="I16" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="11" t="s">
+      <c r="I16" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="12" t="s">
         <v>7</v>
       </c>
       <c r="K16" s="24"/>
@@ -2869,196 +2869,196 @@
       <c r="X16" s="24"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="16" t="s">
+      <c r="B17" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="21">
+      <c r="E17" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="23">
         <v>3.0</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="23">
         <v>3.0</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="16" t="s">
+      <c r="I17" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="21">
+      <c r="E18" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="23">
         <v>3.0</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="23">
         <v>3.0</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="16" t="s">
+      <c r="I18" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="B19" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="21">
+      <c r="E19" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="23">
         <v>4.0</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G19" s="23">
         <v>3.0</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="16" t="s">
+      <c r="I19" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="21">
+      <c r="E20" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="23">
         <v>5.0</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="23">
         <v>4.0</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="16" t="s">
+      <c r="I20" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J20" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="B21" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="21">
+      <c r="E21" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="23">
         <v>2.0</v>
       </c>
-      <c r="G21" s="21">
+      <c r="G21" s="23">
         <v>2.0</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="I21" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="16" t="s">
+      <c r="I21" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="B22" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="15">
+      <c r="D22" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="17">
         <f t="shared" ref="F22:G22" si="6">SUM(F23:F27)</f>
         <v>15</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="17">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
-      <c r="H22" s="11" t="s">
+      <c r="H22" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="I22" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="11" t="s">
+      <c r="I22" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J22" s="12" t="s">
         <v>7</v>
       </c>
       <c r="K22" s="24"/>
@@ -3077,197 +3077,197 @@
       <c r="X22" s="24"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="B23" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="21">
+      <c r="F23" s="23">
         <v>3.0</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="23">
         <v>3.0</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="16" t="s">
+      <c r="I23" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J23" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="21">
+      <c r="E24" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="23">
         <v>3.0</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="23">
         <v>3.0</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="H24" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="I24" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24" s="16" t="s">
+      <c r="I24" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J24" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="B25" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="21">
+      <c r="E25" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F25" s="23">
         <v>3.0</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="23">
         <v>3.0</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="I25" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="16" t="s">
+      <c r="I25" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J25" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="B26" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="21">
+      <c r="E26" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="23">
         <v>3.0</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="23">
         <v>3.0</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="I26" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="16" t="s">
+      <c r="I26" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J26" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="B27" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="21">
+      <c r="F27" s="23">
         <v>3.0</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="22">
         <v>3.0</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="I27" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="16" t="s">
+      <c r="I27" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J27" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="11" t="s">
+      <c r="B28" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F28" s="15">
+      <c r="E28" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F28" s="17">
         <f t="shared" ref="F28:G28" si="7">F29+F34+F40+F46</f>
         <v>40</v>
       </c>
-      <c r="G28" s="15">
+      <c r="G28" s="17">
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
-      <c r="H28" s="11" t="s">
+      <c r="H28" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="I28" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>15</v>
+      <c r="I28" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
@@ -3285,37 +3285,37 @@
       <c r="X28" s="24"/>
     </row>
     <row r="29" ht="22.5" customHeight="1">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="11" t="s">
+      <c r="B29" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="15">
+      <c r="E29" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F29" s="17">
         <f t="shared" ref="F29:G29" si="8">SUM(F30:F33)</f>
         <v>10</v>
       </c>
-      <c r="G29" s="15">
+      <c r="G29" s="17">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
-      <c r="H29" s="11" t="s">
+      <c r="H29" s="12" t="s">
         <v>130</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J29" s="11" t="s">
-        <v>15</v>
+      <c r="I29" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
@@ -3333,148 +3333,148 @@
       <c r="X29" s="24"/>
     </row>
     <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="B30" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="21">
+      <c r="E30" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="23">
         <v>2.0</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="23">
         <v>2.0</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="I30" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>15</v>
+      <c r="I30" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="B31" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E31" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="21">
+      <c r="E31" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="23">
         <v>3.0</v>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="23">
         <v>3.0</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I31" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>15</v>
+      <c r="I31" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="B32" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="21">
+      <c r="E32" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32" s="23">
         <v>3.0</v>
       </c>
-      <c r="G32" s="21">
+      <c r="G32" s="23">
         <v>3.0</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="I32" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>15</v>
+      <c r="I32" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="16" t="s">
+      <c r="B33" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D33" s="18" t="s">
+      <c r="D33" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="21">
+      <c r="F33" s="23">
         <v>2.0</v>
       </c>
       <c r="G33" s="25">
         <v>2.0</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I33" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J33" s="16" t="s">
-        <v>15</v>
+      <c r="I33" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C34" s="11" t="s">
+      <c r="B34" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="13" t="s">
-        <v>24</v>
+      <c r="E34" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F34" s="26">
         <f t="shared" ref="F34:G34" si="9">SUM(F35:F39)</f>
@@ -3484,14 +3484,14 @@
         <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="H34" s="11" t="s">
+      <c r="H34" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="I34" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J34" s="11" t="s">
-        <v>15</v>
+      <c r="I34" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K34" s="24"/>
       <c r="L34" s="24"/>
@@ -3509,180 +3509,180 @@
       <c r="X34" s="24"/>
     </row>
     <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="16" t="s">
+      <c r="B35" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="21">
+      <c r="E35" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35" s="23">
         <v>3.0</v>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="23">
         <v>2.0</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="I35" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J35" s="16" t="s">
-        <v>15</v>
+      <c r="I35" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="B36" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="21">
+      <c r="E36" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F36" s="23">
         <v>3.0</v>
       </c>
-      <c r="G36" s="21">
+      <c r="G36" s="23">
         <v>2.0</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="I36" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="16" t="s">
-        <v>15</v>
+      <c r="I36" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="16" t="s">
+      <c r="B37" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="21">
+      <c r="E37" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F37" s="23">
         <v>3.0</v>
       </c>
-      <c r="G37" s="21">
+      <c r="G37" s="23">
         <v>2.0</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="I37" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J37" s="16" t="s">
-        <v>15</v>
+      <c r="I37" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38" s="16" t="s">
+      <c r="B38" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="21">
+      <c r="E38" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F38" s="23">
         <v>3.0</v>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="23">
         <v>2.0</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="H38" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="I38" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>15</v>
+      <c r="I38" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="B39" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="21">
+      <c r="E39" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F39" s="23">
         <v>3.0</v>
       </c>
       <c r="G39" s="25">
         <v>2.0</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="I39" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J39" s="16" t="s">
-        <v>15</v>
+      <c r="I39" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B40" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C40" s="11" t="s">
+      <c r="B40" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E40" s="13" t="s">
-        <v>24</v>
+      <c r="E40" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F40" s="26">
         <f t="shared" ref="F40:G40" si="10">SUM(F41:F45)</f>
@@ -3692,14 +3692,14 @@
         <f t="shared" si="10"/>
         <v>8</v>
       </c>
-      <c r="H40" s="11" t="s">
+      <c r="H40" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I40" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J40" s="11" t="s">
-        <v>15</v>
+      <c r="I40" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K40" s="24"/>
       <c r="L40" s="24"/>
@@ -3717,179 +3717,179 @@
       <c r="X40" s="24"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B41" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" s="21">
+      <c r="E41" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="23">
         <v>2.0</v>
       </c>
-      <c r="G41" s="21">
+      <c r="G41" s="23">
         <v>2.0</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="H41" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="I41" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J41" s="16" t="s">
-        <v>15</v>
+      <c r="I41" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="16" t="s">
+      <c r="B42" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="21">
+      <c r="E42" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="23">
         <v>2.0</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="23">
         <v>1.0</v>
       </c>
-      <c r="H42" s="16" t="s">
+      <c r="H42" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="I42" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J42" s="16" t="s">
-        <v>15</v>
+      <c r="I42" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="B43" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E43" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F43" s="21">
+      <c r="E43" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43" s="23">
         <v>2.0</v>
       </c>
-      <c r="G43" s="21">
+      <c r="G43" s="23">
         <v>2.0</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="H43" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="I43" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J43" s="16" t="s">
-        <v>15</v>
+      <c r="I43" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="B44" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="16" t="s">
+      <c r="B44" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E44" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="21">
+      <c r="E44" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44" s="23">
         <v>2.0</v>
       </c>
-      <c r="G44" s="21">
+      <c r="G44" s="23">
         <v>2.0</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="H44" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="I44" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="16" t="s">
-        <v>15</v>
+      <c r="I44" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C45" s="16" t="s">
+      <c r="B45" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="23">
         <v>1.0</v>
       </c>
       <c r="G45" s="25">
         <v>1.0</v>
       </c>
-      <c r="H45" s="16" t="s">
+      <c r="H45" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="I45" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J45" s="16" t="s">
-        <v>15</v>
+      <c r="I45" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="B46" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C46" s="11" t="s">
+      <c r="B46" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="14" t="s">
         <v>110</v>
       </c>
       <c r="F46" s="26">
@@ -3900,14 +3900,14 @@
         <f t="shared" si="11"/>
         <v>5</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="I46" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J46" s="11" t="s">
-        <v>15</v>
+      <c r="I46" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J46" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K46" s="24"/>
       <c r="L46" s="24"/>
@@ -3925,133 +3925,133 @@
       <c r="X46" s="24"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C47" s="16" t="s">
+      <c r="B47" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D47" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="20" t="s">
+      <c r="D47" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F47" s="21">
+      <c r="F47" s="23">
         <v>2.0</v>
       </c>
-      <c r="G47" s="21">
+      <c r="G47" s="23">
         <v>2.0</v>
       </c>
-      <c r="H47" s="16" t="s">
+      <c r="H47" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="I47" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J47" s="16" t="s">
-        <v>15</v>
+      <c r="I47" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C48" s="16" t="s">
+      <c r="B48" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F48" s="21">
+      <c r="F48" s="23">
         <v>1.0</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="23">
         <v>1.0</v>
       </c>
-      <c r="H48" s="16" t="s">
+      <c r="H48" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="I48" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J48" s="16" t="s">
-        <v>15</v>
+      <c r="I48" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" s="16" t="s">
+      <c r="B49" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F49" s="21">
+      <c r="F49" s="23">
         <v>3.0</v>
       </c>
       <c r="G49" s="25">
         <v>2.0</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="H49" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="I49" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J49" s="16" t="s">
-        <v>15</v>
+      <c r="I49" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B50" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="11" t="s">
+      <c r="B50" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="E50" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F50" s="15">
+      <c r="E50" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" s="17">
         <f t="shared" ref="F50:G50" si="12">F51</f>
         <v>2</v>
       </c>
-      <c r="G50" s="15">
+      <c r="G50" s="17">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="I50" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J50" s="11" t="s">
-        <v>15</v>
+      <c r="I50" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K50" s="24"/>
       <c r="L50" s="24"/>
@@ -4069,20 +4069,20 @@
       <c r="X50" s="24"/>
     </row>
     <row r="51" ht="22.5" customHeight="1">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="B51" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" s="11" t="s">
+      <c r="B51" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>198</v>
       </c>
-      <c r="D51" s="12" t="s">
+      <c r="D51" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="E51" s="13" t="s">
-        <v>24</v>
+      <c r="E51" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F51" s="26">
         <f t="shared" ref="F51:G51" si="13">SUM(F52:F53)</f>
@@ -4092,14 +4092,14 @@
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="I51" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J51" s="11" t="s">
-        <v>15</v>
+      <c r="I51" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J51" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K51" s="24"/>
       <c r="L51" s="24"/>
@@ -4117,101 +4117,101 @@
       <c r="X51" s="24"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B52" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" s="16" t="s">
+      <c r="B52" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F52" s="21">
+      <c r="E52" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="23">
         <v>1.0</v>
       </c>
-      <c r="G52" s="21">
+      <c r="G52" s="23">
         <v>1.0</v>
       </c>
-      <c r="H52" s="16" t="s">
+      <c r="H52" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="I52" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J52" s="16" t="s">
-        <v>15</v>
+      <c r="I52" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="B53" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C53" s="16" t="s">
+      <c r="B53" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E53" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F53" s="21">
+      <c r="E53" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="23">
         <v>1.0</v>
       </c>
       <c r="G53" s="25">
         <v>1.0</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="I53" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J53" s="16" t="s">
-        <v>15</v>
+      <c r="I53" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J53" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="B54" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C54" s="11" t="s">
+      <c r="B54" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="12" t="s">
         <v>207</v>
       </c>
-      <c r="D54" s="12" t="s">
+      <c r="D54" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E54" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F54" s="15">
+      <c r="E54" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" s="17">
         <f t="shared" ref="F54:G54" si="14">F55+F61+F66+F71+F80</f>
         <v>32</v>
       </c>
-      <c r="G54" s="15">
+      <c r="G54" s="17">
         <f t="shared" si="14"/>
         <v>42</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="I54" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J54" s="11" t="s">
-        <v>15</v>
+      <c r="I54" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J54" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K54" s="24"/>
       <c r="L54" s="24"/>
@@ -4229,20 +4229,20 @@
       <c r="X54" s="24"/>
     </row>
     <row r="55" ht="22.5" customHeight="1">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B55" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C55" s="11" t="s">
+      <c r="B55" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="D55" s="12" t="s">
+      <c r="D55" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E55" s="13" t="s">
-        <v>24</v>
+      <c r="E55" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F55" s="26">
         <f t="shared" ref="F55:G55" si="15">SUM(F56:F60)</f>
@@ -4252,14 +4252,14 @@
         <f t="shared" si="15"/>
         <v>5</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="I55" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J55" s="11" t="s">
-        <v>15</v>
+      <c r="I55" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J55" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K55" s="24"/>
       <c r="L55" s="24"/>
@@ -4277,180 +4277,180 @@
       <c r="X55" s="24"/>
     </row>
     <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B56" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C56" s="16" t="s">
+      <c r="B56" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E56" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F56" s="21">
+      <c r="E56" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56" s="23">
         <v>1.0</v>
       </c>
-      <c r="G56" s="21">
+      <c r="G56" s="23">
         <v>1.0</v>
       </c>
-      <c r="H56" s="16" t="s">
+      <c r="H56" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="I56" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J56" s="16" t="s">
-        <v>15</v>
+      <c r="I56" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="B57" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C57" s="16" t="s">
+      <c r="B57" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E57" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F57" s="21">
+      <c r="E57" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F57" s="23">
         <v>1.0</v>
       </c>
-      <c r="G57" s="21">
+      <c r="G57" s="23">
         <v>1.0</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H57" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="I57" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J57" s="16" t="s">
-        <v>15</v>
+      <c r="I57" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J57" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="B58" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C58" s="16" t="s">
+      <c r="B58" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E58" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="21">
+      <c r="E58" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="23">
         <v>1.0</v>
       </c>
-      <c r="G58" s="21">
+      <c r="G58" s="23">
         <v>1.0</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="H58" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="I58" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J58" s="16" t="s">
-        <v>15</v>
+      <c r="I58" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J58" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="B59" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C59" s="16" t="s">
+      <c r="B59" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="21">
+      <c r="F59" s="23">
         <v>1.0</v>
       </c>
       <c r="G59" s="25">
         <v>1.0</v>
       </c>
-      <c r="H59" s="16" t="s">
+      <c r="H59" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="I59" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J59" s="16" t="s">
-        <v>15</v>
+      <c r="I59" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J59" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="16" t="s">
+      <c r="B60" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="D60" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" s="21">
+      <c r="D60" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F60" s="23">
         <v>1.0</v>
       </c>
-      <c r="G60" s="21">
+      <c r="G60" s="23">
         <v>1.0</v>
       </c>
-      <c r="H60" s="16" t="s">
+      <c r="H60" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="I60" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J60" s="16" t="s">
-        <v>15</v>
+      <c r="I60" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J60" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="B61" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C61" s="11" t="s">
+      <c r="B61" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="D61" s="12" t="s">
+      <c r="D61" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E61" s="13" t="s">
-        <v>24</v>
+      <c r="E61" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F61" s="26">
         <f t="shared" ref="F61:G61" si="16">SUM(F62:F65)</f>
@@ -4460,14 +4460,14 @@
         <f t="shared" si="16"/>
         <v>7</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="12" t="s">
         <v>229</v>
       </c>
-      <c r="I61" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J61" s="11" t="s">
-        <v>15</v>
+      <c r="I61" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J61" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K61" s="24"/>
       <c r="L61" s="24"/>
@@ -4485,148 +4485,148 @@
       <c r="X61" s="24"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="B62" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C62" s="16" t="s">
+      <c r="B62" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="D62" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" s="21">
+      <c r="E62" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" s="23">
         <v>2.0</v>
       </c>
-      <c r="G62" s="21">
+      <c r="G62" s="23">
         <v>2.0</v>
       </c>
-      <c r="H62" s="16" t="s">
+      <c r="H62" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="I62" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J62" s="16" t="s">
-        <v>15</v>
+      <c r="I62" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J62" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="B63" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C63" s="16" t="s">
+      <c r="B63" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E63" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F63" s="21">
+      <c r="E63" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" s="23">
         <v>1.0</v>
       </c>
       <c r="G63" s="25">
         <v>1.0</v>
       </c>
-      <c r="H63" s="16" t="s">
+      <c r="H63" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="I63" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J63" s="16" t="s">
-        <v>15</v>
+      <c r="I63" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J63" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C64" s="16" t="s">
+      <c r="B64" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F64" s="21">
+      <c r="E64" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" s="23">
         <v>2.0</v>
       </c>
-      <c r="G64" s="21">
+      <c r="G64" s="23">
         <v>2.0</v>
       </c>
-      <c r="H64" s="16" t="s">
+      <c r="H64" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="I64" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J64" s="16" t="s">
-        <v>15</v>
+      <c r="I64" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J64" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B65" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65" s="16" t="s">
+      <c r="B65" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F65" s="21">
+      <c r="F65" s="23">
         <v>2.0</v>
       </c>
-      <c r="G65" s="21">
+      <c r="G65" s="23">
         <v>2.0</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="H65" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="I65" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J65" s="16" t="s">
-        <v>15</v>
+      <c r="I65" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J65" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C66" s="11" t="s">
+      <c r="B66" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C66" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D66" s="12" t="s">
+      <c r="D66" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E66" s="13" t="s">
-        <v>24</v>
+      <c r="E66" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F66" s="26">
         <f t="shared" ref="F66:G66" si="17">SUM(F67:F70)</f>
@@ -4636,14 +4636,14 @@
         <f t="shared" si="17"/>
         <v>6</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="I66" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J66" s="11" t="s">
-        <v>15</v>
+      <c r="I66" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J66" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K66" s="24"/>
       <c r="L66" s="24"/>
@@ -4661,165 +4661,165 @@
       <c r="X66" s="24"/>
     </row>
     <row r="67" ht="22.5" customHeight="1">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="B67" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C67" s="16" t="s">
+      <c r="B67" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E67" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" s="21">
+      <c r="E67" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67" s="23">
         <v>2.0</v>
       </c>
       <c r="G67" s="25">
         <v>2.0</v>
       </c>
-      <c r="H67" s="16" t="s">
+      <c r="H67" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="I67" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J67" s="16" t="s">
-        <v>15</v>
+      <c r="I67" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J67" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" s="16" t="s">
+      <c r="B68" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E68" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F68" s="21">
+      <c r="E68" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F68" s="23">
         <v>1.0</v>
       </c>
-      <c r="G68" s="21">
+      <c r="G68" s="23">
         <v>1.0</v>
       </c>
-      <c r="H68" s="16" t="s">
+      <c r="H68" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="I68" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J68" s="16" t="s">
-        <v>15</v>
+      <c r="I68" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J68" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C69" s="16" t="s">
+      <c r="B69" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="D69" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E69" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F69" s="21">
+      <c r="E69" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69" s="23">
         <v>1.0</v>
       </c>
-      <c r="G69" s="21">
+      <c r="G69" s="23">
         <v>1.0</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="H69" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="I69" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J69" s="16" t="s">
-        <v>15</v>
+      <c r="I69" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J69" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C70" s="16" t="s">
+      <c r="B70" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E70" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F70" s="21">
+      <c r="E70" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F70" s="23">
         <v>2.0</v>
       </c>
-      <c r="G70" s="21">
+      <c r="G70" s="23">
         <v>2.0</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="H70" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="I70" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J70" s="16" t="s">
-        <v>15</v>
+      <c r="I70" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J70" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="B71" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C71" s="11" t="s">
+      <c r="B71" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C71" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E71" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F71" s="15">
+      <c r="E71" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F71" s="17">
         <f t="shared" ref="F71:G71" si="18">SUM(F72:F79)</f>
         <v>10</v>
       </c>
-      <c r="G71" s="15">
+      <c r="G71" s="17">
         <f t="shared" si="18"/>
         <v>14</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="I71" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>15</v>
+      <c r="I71" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
@@ -4837,293 +4837,293 @@
       <c r="X71" s="24"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="B72" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C72" s="16" t="s">
+      <c r="B72" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D72" s="18" t="s">
+      <c r="D72" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" s="21">
+      <c r="E72" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" s="23">
         <v>2.0</v>
       </c>
-      <c r="G72" s="21">
+      <c r="G72" s="23">
         <v>2.0</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="H72" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="I72" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J72" s="16" t="s">
-        <v>15</v>
+      <c r="I72" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J72" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="B73" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C73" s="16" t="s">
+      <c r="B73" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="D73" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E73" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F73" s="21">
+      <c r="E73" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73" s="23">
         <v>2.0</v>
       </c>
-      <c r="G73" s="21">
+      <c r="G73" s="23">
         <v>5.0</v>
       </c>
-      <c r="H73" s="16" t="s">
+      <c r="H73" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="I73" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J73" s="16" t="s">
-        <v>15</v>
+      <c r="I73" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J73" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="B74" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C74" s="16" t="s">
+      <c r="B74" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="D74" s="18" t="s">
+      <c r="D74" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E74" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F74" s="21">
+      <c r="E74" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" s="23">
         <v>1.0</v>
       </c>
       <c r="G74" s="25">
         <v>1.0</v>
       </c>
-      <c r="H74" s="16" t="s">
+      <c r="H74" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I74" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J74" s="16" t="s">
-        <v>15</v>
+      <c r="I74" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J74" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="B75" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C75" s="16" t="s">
+      <c r="B75" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="D75" s="18" t="s">
+      <c r="D75" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E75" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F75" s="21">
+      <c r="E75" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="23">
         <v>1.0</v>
       </c>
       <c r="G75" s="25">
         <v>1.0</v>
       </c>
-      <c r="H75" s="16" t="s">
+      <c r="H75" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I75" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>15</v>
+      <c r="I75" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J75" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="B76" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C76" s="16" t="s">
+      <c r="B76" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D76" s="18" t="s">
+      <c r="D76" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E76" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F76" s="21">
+      <c r="E76" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F76" s="23">
         <v>1.0</v>
       </c>
-      <c r="G76" s="21">
+      <c r="G76" s="23">
         <v>1.0</v>
       </c>
-      <c r="H76" s="16" t="s">
+      <c r="H76" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I76" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J76" s="16" t="s">
-        <v>15</v>
+      <c r="I76" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J76" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C77" s="16" t="s">
+      <c r="B77" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C77" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="D77" s="18" t="s">
+      <c r="D77" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E77" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F77" s="21">
+      <c r="E77" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F77" s="23">
         <v>1.0</v>
       </c>
-      <c r="G77" s="21">
+      <c r="G77" s="23">
         <v>1.0</v>
       </c>
-      <c r="H77" s="16" t="s">
+      <c r="H77" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I77" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J77" s="16" t="s">
-        <v>15</v>
+      <c r="I77" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J77" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="B78" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C78" s="16" t="s">
+      <c r="B78" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="D78" s="18" t="s">
+      <c r="D78" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E78" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F78" s="21">
+      <c r="E78" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F78" s="23">
         <v>1.0</v>
       </c>
-      <c r="G78" s="21">
+      <c r="G78" s="23">
         <v>1.0</v>
       </c>
-      <c r="H78" s="16" t="s">
+      <c r="H78" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I78" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J78" s="16" t="s">
-        <v>15</v>
+      <c r="I78" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J78" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="B79" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C79" s="16" t="s">
+      <c r="B79" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="D79" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E79" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F79" s="21">
+      <c r="E79" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" s="23">
         <v>1.0</v>
       </c>
-      <c r="G79" s="21">
+      <c r="G79" s="23">
         <v>2.0</v>
       </c>
-      <c r="H79" s="16" t="s">
+      <c r="H79" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="I79" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J79" s="16" t="s">
-        <v>15</v>
+      <c r="I79" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J79" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="12" t="s">
         <v>280</v>
       </c>
-      <c r="B80" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C80" s="11" t="s">
+      <c r="B80" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C80" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="D80" s="12" t="s">
+      <c r="D80" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E80" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F80" s="15">
+      <c r="E80" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80" s="17">
         <f t="shared" ref="F80:G80" si="19">SUM(F81:F83)</f>
         <v>4</v>
       </c>
-      <c r="G80" s="15">
+      <c r="G80" s="17">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="I80" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>15</v>
+      <c r="I80" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J80" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="K80" s="24"/>
       <c r="L80" s="24"/>
@@ -5141,116 +5141,116 @@
       <c r="X80" s="24"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="B81" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C81" s="16" t="s">
+      <c r="B81" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="D81" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E81" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F81" s="21">
+      <c r="E81" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81" s="23">
         <v>2.0</v>
       </c>
-      <c r="G81" s="21">
+      <c r="G81" s="23">
         <v>8.0</v>
       </c>
-      <c r="H81" s="16" t="s">
+      <c r="H81" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="I81" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J81" s="16" t="s">
-        <v>15</v>
+      <c r="I81" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J81" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="B82" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C82" s="16" t="s">
+      <c r="B82" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C82" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="D82" s="18" t="s">
+      <c r="D82" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E82" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F82" s="21">
+      <c r="E82" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82" s="23">
         <v>1.0</v>
       </c>
-      <c r="G82" s="21">
+      <c r="G82" s="23">
         <v>1.0</v>
       </c>
-      <c r="H82" s="16" t="s">
+      <c r="H82" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="I82" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J82" s="16" t="s">
-        <v>15</v>
+      <c r="I82" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J82" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="B83" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C83" s="16" t="s">
+      <c r="B83" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C83" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="D83" s="18" t="s">
+      <c r="D83" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E83" s="20" t="s">
+      <c r="E83" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F83" s="21">
+      <c r="F83" s="23">
         <v>1.0</v>
       </c>
-      <c r="G83" s="21">
+      <c r="G83" s="23">
         <v>1.0</v>
       </c>
-      <c r="H83" s="16" t="s">
+      <c r="H83" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="I83" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J83" s="16" t="s">
-        <v>15</v>
+      <c r="I83" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="J83" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="B84" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C84" s="11" t="s">
+      <c r="B84" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="D84" s="12" t="s">
+      <c r="D84" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E84" s="13" t="s">
-        <v>24</v>
+      <c r="E84" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F84" s="27">
         <v>47.0</v>
@@ -5259,14 +5259,14 @@
         <f>G85+G90+G96+G102+G108</f>
         <v>20</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" s="12" t="s">
         <v>294</v>
       </c>
       <c r="I84" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="J84" s="11" t="s">
-        <v>25</v>
+      <c r="J84" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K84" s="24"/>
       <c r="L84" s="24"/>
@@ -5284,26 +5284,26 @@
       <c r="X84" s="24"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="B85" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C85" s="11" t="s">
+      <c r="B85" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" s="12" t="s">
         <v>297</v>
       </c>
-      <c r="D85" s="12" t="s">
+      <c r="D85" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E85" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F85" s="15">
+      <c r="E85" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F85" s="17">
         <f t="shared" ref="F85:G85" si="20">SUM(F86:F89)</f>
         <v>5</v>
       </c>
-      <c r="G85" s="15">
+      <c r="G85" s="17">
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
@@ -5311,10 +5311,10 @@
         <v>298</v>
       </c>
       <c r="I85" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J85" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K85" s="24"/>
       <c r="L85" s="24"/>
@@ -5332,22 +5332,22 @@
       <c r="X85" s="24"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="16" t="s">
+      <c r="A86" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="B86" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C86" s="16" t="s">
+      <c r="B86" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="D86" s="18" t="s">
+      <c r="D86" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E86" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="21">
+      <c r="E86" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F86" s="23">
         <v>1.0</v>
       </c>
       <c r="G86" s="30">
@@ -5357,29 +5357,29 @@
         <v>301</v>
       </c>
       <c r="I86" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J86" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J86" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="16" t="s">
+      <c r="A87" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="B87" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C87" s="16" t="s">
+      <c r="B87" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C87" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="D87" s="18" t="s">
+      <c r="D87" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F87" s="21">
+      <c r="E87" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F87" s="23">
         <v>1.0</v>
       </c>
       <c r="G87" s="30">
@@ -5389,29 +5389,29 @@
         <v>304</v>
       </c>
       <c r="I87" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J87" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J87" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="16" t="s">
+      <c r="A88" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="B88" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C88" s="16" t="s">
+      <c r="B88" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C88" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="D88" s="18" t="s">
+      <c r="D88" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E88" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F88" s="21">
+      <c r="E88" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F88" s="23">
         <v>2.0</v>
       </c>
       <c r="G88" s="30">
@@ -5421,29 +5421,29 @@
         <v>307</v>
       </c>
       <c r="I88" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J88" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J88" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="16" t="s">
+      <c r="A89" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="B89" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C89" s="16" t="s">
+      <c r="B89" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C89" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="D89" s="18" t="s">
+      <c r="D89" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E89" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F89" s="21">
+      <c r="E89" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F89" s="23">
         <v>1.0</v>
       </c>
       <c r="G89" s="30">
@@ -5453,44 +5453,44 @@
         <v>310</v>
       </c>
       <c r="I89" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J89" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J89" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="B90" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C90" s="11" t="s">
+      <c r="B90" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" s="12" t="s">
         <v>312</v>
       </c>
-      <c r="D90" s="12" t="s">
+      <c r="D90" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E90" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F90" s="15">
+      <c r="E90" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F90" s="17">
         <f t="shared" ref="F90:G90" si="21">SUM(F91:F95)</f>
         <v>11</v>
       </c>
-      <c r="G90" s="15">
+      <c r="G90" s="17">
         <f t="shared" si="21"/>
         <v>7</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="12" t="s">
         <v>313</v>
       </c>
       <c r="I90" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K90" s="24"/>
       <c r="L90" s="24"/>
@@ -5508,131 +5508,131 @@
       <c r="X90" s="24"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="B91" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C91" s="16" t="s">
+      <c r="B91" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C91" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="D91" s="18" t="s">
+      <c r="D91" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E91" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" s="21">
+      <c r="E91" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F91" s="23">
         <v>2.0</v>
       </c>
       <c r="G91" s="30">
         <v>1.0</v>
       </c>
-      <c r="H91" s="16" t="s">
+      <c r="H91" s="20" t="s">
         <v>316</v>
       </c>
       <c r="I91" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J91" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J91" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="B92" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C92" s="16" t="s">
+      <c r="B92" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="D92" s="18" t="s">
+      <c r="D92" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E92" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F92" s="21">
+      <c r="E92" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F92" s="23">
         <v>3.0</v>
       </c>
       <c r="G92" s="30">
         <v>2.0</v>
       </c>
-      <c r="H92" s="16" t="s">
+      <c r="H92" s="20" t="s">
         <v>319</v>
       </c>
       <c r="I92" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J92" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J92" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="16" t="s">
+      <c r="A93" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="B93" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C93" s="16" t="s">
+      <c r="B93" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C93" s="20" t="s">
         <v>321</v>
       </c>
-      <c r="D93" s="18" t="s">
+      <c r="D93" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E93" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F93" s="21">
+      <c r="E93" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F93" s="23">
         <v>2.0</v>
       </c>
       <c r="G93" s="30">
         <v>1.0</v>
       </c>
-      <c r="H93" s="16" t="s">
+      <c r="H93" s="20" t="s">
         <v>322</v>
       </c>
       <c r="I93" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J93" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J93" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="16" t="s">
+      <c r="A94" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="B94" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C94" s="16" t="s">
+      <c r="B94" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C94" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="D94" s="18" t="s">
+      <c r="D94" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E94" s="20" t="s">
+      <c r="E94" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F94" s="21">
+      <c r="F94" s="23">
         <v>2.0</v>
       </c>
       <c r="G94" s="33">
         <v>1.0</v>
       </c>
-      <c r="H94" s="16" t="s">
+      <c r="H94" s="20" t="s">
         <v>325</v>
       </c>
       <c r="I94" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J94" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J94" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
@@ -5640,7 +5640,7 @@
         <v>326</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C95" s="31" t="s">
         <v>327</v>
@@ -5649,7 +5649,7 @@
         <v>50</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F95" s="30">
         <v>2.0</v>
@@ -5661,44 +5661,44 @@
         <v>328</v>
       </c>
       <c r="I95" s="32" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J95" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B96" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C96" s="11" t="s">
+      <c r="B96" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C96" s="12" t="s">
         <v>330</v>
       </c>
-      <c r="D96" s="12" t="s">
+      <c r="D96" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E96" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F96" s="15">
+      <c r="E96" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F96" s="17">
         <f t="shared" ref="F96:G96" si="22">SUM(F97:F101)</f>
         <v>8</v>
       </c>
-      <c r="G96" s="15">
+      <c r="G96" s="17">
         <f t="shared" si="22"/>
         <v>8</v>
       </c>
-      <c r="H96" s="11" t="s">
+      <c r="H96" s="12" t="s">
         <v>331</v>
       </c>
       <c r="I96" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="J96" s="11" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J96" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="24"/>
       <c r="L96" s="24"/>
@@ -5716,131 +5716,131 @@
       <c r="X96" s="24"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="B97" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C97" s="16" t="s">
+      <c r="B97" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C97" s="20" t="s">
         <v>333</v>
       </c>
-      <c r="D97" s="18" t="s">
+      <c r="D97" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E97" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" s="21">
+      <c r="E97" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F97" s="23">
         <v>3.0</v>
       </c>
       <c r="G97" s="30">
         <v>2.0</v>
       </c>
-      <c r="H97" s="16" t="s">
+      <c r="H97" s="20" t="s">
         <v>334</v>
       </c>
       <c r="I97" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J97" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J97" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="16" t="s">
+      <c r="A98" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="B98" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C98" s="16" t="s">
+      <c r="B98" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C98" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="D98" s="18" t="s">
+      <c r="D98" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E98" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F98" s="21">
+      <c r="E98" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F98" s="23">
         <v>2.0</v>
       </c>
       <c r="G98" s="30">
         <v>2.0</v>
       </c>
-      <c r="H98" s="16" t="s">
+      <c r="H98" s="20" t="s">
         <v>337</v>
       </c>
       <c r="I98" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J98" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J98" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="B99" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C99" s="16" t="s">
+      <c r="B99" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C99" s="20" t="s">
         <v>339</v>
       </c>
-      <c r="D99" s="18" t="s">
+      <c r="D99" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F99" s="21">
+      <c r="E99" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F99" s="23">
         <v>1.0</v>
       </c>
       <c r="G99" s="30">
         <v>1.0</v>
       </c>
-      <c r="H99" s="16" t="s">
+      <c r="H99" s="20" t="s">
         <v>340</v>
       </c>
       <c r="I99" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J99" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J99" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="16" t="s">
+      <c r="A100" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="B100" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C100" s="16" t="s">
+      <c r="B100" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C100" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="D100" s="18" t="s">
+      <c r="D100" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E100" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F100" s="21">
+      <c r="E100" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F100" s="23">
         <v>1.0</v>
       </c>
       <c r="G100" s="30">
         <v>1.0</v>
       </c>
-      <c r="H100" s="16" t="s">
+      <c r="H100" s="20" t="s">
         <v>343</v>
       </c>
       <c r="I100" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J100" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
+      </c>
+      <c r="J100" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
@@ -5848,7 +5848,7 @@
         <v>344</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C101" s="31" t="s">
         <v>345</v>
@@ -5857,7 +5857,7 @@
         <v>50</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F101" s="30">
         <v>1.0</v>
@@ -5869,43 +5869,43 @@
         <v>346</v>
       </c>
       <c r="I101" s="32" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="J101" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="B102" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C102" s="11" t="s">
+      <c r="B102" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C102" s="12" t="s">
         <v>348</v>
       </c>
-      <c r="D102" s="12" t="s">
+      <c r="D102" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E102" s="13" t="s">
-        <v>24</v>
+      <c r="E102" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F102" s="27">
         <v>12.0</v>
       </c>
-      <c r="G102" s="15">
+      <c r="G102" s="17">
         <f>SUM(G103:G106)</f>
         <v>0</v>
       </c>
-      <c r="H102" s="11" t="s">
+      <c r="H102" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="I102" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J102" s="11" t="s">
-        <v>25</v>
+      <c r="I102" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K102" s="24"/>
       <c r="L102" s="24"/>
@@ -5923,93 +5923,93 @@
       <c r="X102" s="24"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C103" s="20" t="s">
         <v>351</v>
       </c>
-      <c r="B103" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C103" s="16" t="s">
+      <c r="D103" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E103" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F103" s="23">
+        <v>2.0</v>
+      </c>
+      <c r="G103" s="23"/>
+      <c r="H103" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="D103" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E103" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F103" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="G103" s="21"/>
-      <c r="H103" s="16" t="s">
+      <c r="I103" s="22" t="s">
         <v>353</v>
       </c>
-      <c r="I103" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J103" s="16" t="s">
-        <v>25</v>
+      <c r="J103" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="16" t="s">
+      <c r="A104" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="B104" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C104" s="16" t="s">
+      <c r="B104" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C104" s="20" t="s">
         <v>355</v>
       </c>
-      <c r="D104" s="18" t="s">
+      <c r="D104" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E104" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F104" s="21">
+      <c r="E104" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F104" s="23">
         <v>3.0</v>
       </c>
-      <c r="G104" s="21"/>
-      <c r="H104" s="16" t="s">
+      <c r="G104" s="23"/>
+      <c r="H104" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="I104" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J104" s="16" t="s">
-        <v>25</v>
+      <c r="I104" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J104" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="16" t="s">
+      <c r="A105" s="20" t="s">
         <v>357</v>
       </c>
-      <c r="B105" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C105" s="16" t="s">
+      <c r="B105" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C105" s="20" t="s">
         <v>358</v>
       </c>
-      <c r="D105" s="18" t="s">
+      <c r="D105" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E105" s="20" t="s">
+      <c r="E105" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F105" s="21">
+      <c r="F105" s="23">
         <v>3.0</v>
       </c>
-      <c r="G105" s="21"/>
-      <c r="H105" s="16" t="s">
+      <c r="G105" s="23"/>
+      <c r="H105" s="31" t="s">
         <v>359</v>
       </c>
-      <c r="I105" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J105" s="16" t="s">
-        <v>25</v>
+      <c r="I105" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J105" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -6017,7 +6017,7 @@
         <v>360</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C106" s="31" t="s">
         <v>361</v>
@@ -6026,20 +6026,20 @@
         <v>99</v>
       </c>
       <c r="E106" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F106" s="30">
         <v>2.0</v>
       </c>
-      <c r="G106" s="21"/>
+      <c r="G106" s="23"/>
       <c r="H106" s="31" t="s">
         <v>362</v>
       </c>
       <c r="I106" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J106" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
@@ -6047,7 +6047,7 @@
         <v>363</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C107" s="31" t="s">
         <v>364</v>
@@ -6056,28 +6056,28 @@
         <v>99</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F107" s="30">
         <v>2.0</v>
       </c>
-      <c r="G107" s="21"/>
+      <c r="G107" s="23"/>
       <c r="H107" s="31" t="s">
         <v>365</v>
       </c>
       <c r="I107" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J107" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="11" t="s">
+      <c r="A108" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="B108" s="11" t="s">
-        <v>30</v>
+      <c r="B108" s="12" t="s">
+        <v>36</v>
       </c>
       <c r="C108" s="29" t="s">
         <v>367</v>
@@ -6085,25 +6085,25 @@
       <c r="D108" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="E108" s="13" t="s">
-        <v>24</v>
+      <c r="E108" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F108" s="26">
         <f t="shared" ref="F108:G108" si="23">SUM(F109)</f>
         <v>6</v>
       </c>
-      <c r="G108" s="15">
+      <c r="G108" s="17">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="H108" s="11" t="s">
+      <c r="H108" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="I108" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J108" s="11" t="s">
-        <v>25</v>
+      <c r="I108" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="J108" s="12" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
@@ -6111,7 +6111,7 @@
         <v>369</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C109" s="31" t="s">
         <v>370</v>
@@ -6120,20 +6120,20 @@
         <v>99</v>
       </c>
       <c r="E109" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F109" s="30">
         <v>6.0</v>
       </c>
-      <c r="G109" s="21"/>
+      <c r="G109" s="23"/>
       <c r="H109" s="31" t="s">
         <v>371</v>
       </c>
       <c r="I109" s="32" t="s">
-        <v>350</v>
+        <v>295</v>
       </c>
       <c r="J109" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
@@ -6141,7 +6141,7 @@
         <v>372</v>
       </c>
       <c r="B110" s="29" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C110" s="29" t="s">
         <v>373</v>
@@ -6150,7 +6150,7 @@
         <v>99</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F110" s="27">
         <v>5.0</v>
@@ -6162,10 +6162,10 @@
         <v>374</v>
       </c>
       <c r="I110" s="28" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="J110" s="29" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
@@ -6173,7 +6173,7 @@
         <v>375</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C111" s="31" t="s">
         <v>376</v>
@@ -6182,20 +6182,20 @@
         <v>99</v>
       </c>
       <c r="E111" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F111" s="30">
         <v>2.0</v>
       </c>
-      <c r="G111" s="21"/>
+      <c r="G111" s="23"/>
       <c r="H111" s="31" t="s">
         <v>377</v>
       </c>
       <c r="I111" s="32" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="J111" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
@@ -6203,7 +6203,7 @@
         <v>378</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C112" s="31" t="s">
         <v>379</v>
@@ -6212,20 +6212,20 @@
         <v>99</v>
       </c>
       <c r="E112" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F112" s="30">
         <v>2.0</v>
       </c>
-      <c r="G112" s="21"/>
+      <c r="G112" s="23"/>
       <c r="H112" s="31" t="s">
         <v>380</v>
       </c>
       <c r="I112" s="32" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="J112" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
@@ -6233,7 +6233,7 @@
         <v>381</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C113" s="31" t="s">
         <v>382</v>
@@ -6242,53 +6242,53 @@
         <v>99</v>
       </c>
       <c r="E113" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F113" s="30">
         <v>1.0</v>
       </c>
-      <c r="G113" s="21"/>
+      <c r="G113" s="23"/>
       <c r="H113" s="31" t="s">
         <v>383</v>
       </c>
       <c r="I113" s="32" t="s">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="J113" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
+      <c r="A114" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B114" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C114" s="11" t="s">
+      <c r="C114" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="D114" s="12" t="s">
+      <c r="D114" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E114" s="13" t="s">
-        <v>24</v>
+      <c r="E114" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F114" s="27">
         <v>70.0</v>
       </c>
-      <c r="G114" s="15">
+      <c r="G114" s="17">
         <f>G115+G123+G129+G134+G140</f>
         <v>0</v>
       </c>
-      <c r="H114" s="11" t="s">
+      <c r="H114" s="12" t="s">
         <v>386</v>
       </c>
-      <c r="I114" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J114" s="11" t="s">
-        <v>25</v>
+      <c r="I114" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J114" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K114" s="24"/>
       <c r="L114" s="24"/>
@@ -6306,20 +6306,20 @@
       <c r="X114" s="24"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="11" t="s">
+      <c r="A115" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="B115" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C115" s="11" t="s">
+      <c r="B115" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C115" s="12" t="s">
         <v>388</v>
       </c>
-      <c r="D115" s="12" t="s">
+      <c r="D115" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E115" s="13" t="s">
-        <v>24</v>
+      <c r="E115" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F115" s="27">
         <v>24.0</v>
@@ -6328,14 +6328,14 @@
         <f>SUM(G116:G121)</f>
         <v>0</v>
       </c>
-      <c r="H115" s="11" t="s">
+      <c r="H115" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="I115" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J115" s="11" t="s">
-        <v>25</v>
+      <c r="I115" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J115" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K115" s="24"/>
       <c r="L115" s="24"/>
@@ -6353,123 +6353,123 @@
       <c r="X115" s="24"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="16" t="s">
+      <c r="A116" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="B116" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C116" s="16" t="s">
+      <c r="B116" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D116" s="18" t="s">
+      <c r="D116" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E116" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F116" s="21">
+      <c r="E116" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F116" s="23">
         <v>3.0</v>
       </c>
-      <c r="G116" s="21"/>
-      <c r="H116" s="16" t="s">
+      <c r="G116" s="23"/>
+      <c r="H116" s="20" t="s">
         <v>392</v>
       </c>
-      <c r="I116" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J116" s="16" t="s">
-        <v>25</v>
+      <c r="I116" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J116" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="16" t="s">
+      <c r="A117" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="B117" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C117" s="16" t="s">
+      <c r="B117" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C117" s="20" t="s">
         <v>394</v>
       </c>
-      <c r="D117" s="18" t="s">
+      <c r="D117" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E117" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F117" s="21">
+      <c r="E117" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F117" s="23">
         <v>6.0</v>
       </c>
-      <c r="G117" s="21"/>
-      <c r="H117" s="16" t="s">
+      <c r="G117" s="23"/>
+      <c r="H117" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="I117" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J117" s="16" t="s">
-        <v>25</v>
+      <c r="I117" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J117" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="16" t="s">
+      <c r="A118" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="B118" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C118" s="16" t="s">
+      <c r="B118" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C118" s="20" t="s">
         <v>397</v>
       </c>
-      <c r="D118" s="18" t="s">
+      <c r="D118" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E118" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F118" s="21">
+      <c r="E118" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F118" s="23">
         <v>1.0</v>
       </c>
       <c r="G118" s="25"/>
-      <c r="H118" s="16" t="s">
+      <c r="H118" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="I118" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J118" s="16" t="s">
-        <v>25</v>
+      <c r="I118" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J118" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="16" t="s">
+      <c r="A119" s="20" t="s">
         <v>399</v>
       </c>
-      <c r="B119" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C119" s="16" t="s">
+      <c r="B119" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C119" s="20" t="s">
         <v>400</v>
       </c>
-      <c r="D119" s="18" t="s">
+      <c r="D119" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E119" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" s="21">
+      <c r="E119" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F119" s="23">
         <v>3.0</v>
       </c>
-      <c r="G119" s="21"/>
+      <c r="G119" s="23"/>
       <c r="H119" s="31" t="s">
         <v>401</v>
       </c>
-      <c r="I119" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J119" s="16" t="s">
-        <v>25</v>
+      <c r="I119" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J119" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -6477,7 +6477,7 @@
         <v>402</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C120" s="31" t="s">
         <v>403</v>
@@ -6486,20 +6486,20 @@
         <v>50</v>
       </c>
       <c r="E120" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F120" s="30">
         <v>5.0</v>
       </c>
-      <c r="G120" s="21"/>
+      <c r="G120" s="23"/>
       <c r="H120" s="31" t="s">
         <v>404</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J120" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
@@ -6507,7 +6507,7 @@
         <v>405</v>
       </c>
       <c r="B121" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C121" s="31" t="s">
         <v>406</v>
@@ -6521,15 +6521,15 @@
       <c r="F121" s="30">
         <v>3.0</v>
       </c>
-      <c r="G121" s="21"/>
+      <c r="G121" s="23"/>
       <c r="H121" s="31" t="s">
         <v>407</v>
       </c>
       <c r="I121" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J121" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
@@ -6537,7 +6537,7 @@
         <v>408</v>
       </c>
       <c r="B122" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C122" s="31" t="s">
         <v>409</v>
@@ -6546,36 +6546,36 @@
         <v>50</v>
       </c>
       <c r="E122" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F122" s="30">
         <v>3.0</v>
       </c>
-      <c r="G122" s="21"/>
+      <c r="G122" s="23"/>
       <c r="H122" s="31" t="s">
         <v>410</v>
       </c>
       <c r="I122" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J122" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="11" t="s">
+      <c r="A123" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="B123" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C123" s="11" t="s">
+      <c r="B123" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C123" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="D123" s="12" t="s">
+      <c r="D123" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E123" s="13" t="s">
+      <c r="E123" s="14" t="s">
         <v>110</v>
       </c>
       <c r="F123" s="27">
@@ -6585,14 +6585,14 @@
         <f>SUM(G124:G127)</f>
         <v>0</v>
       </c>
-      <c r="H123" s="11" t="s">
+      <c r="H123" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="I123" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J123" s="11" t="s">
-        <v>25</v>
+      <c r="I123" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J123" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K123" s="24"/>
       <c r="L123" s="24"/>
@@ -6610,93 +6610,93 @@
       <c r="X123" s="24"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="16" t="s">
+      <c r="A124" s="20" t="s">
         <v>414</v>
       </c>
-      <c r="B124" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C124" s="16" t="s">
+      <c r="B124" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C124" s="20" t="s">
         <v>415</v>
       </c>
-      <c r="D124" s="18" t="s">
+      <c r="D124" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E124" s="20" t="s">
+      <c r="E124" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F124" s="21">
+      <c r="F124" s="23">
         <v>2.0</v>
       </c>
-      <c r="G124" s="21"/>
-      <c r="H124" s="16" t="s">
+      <c r="G124" s="23"/>
+      <c r="H124" s="20" t="s">
         <v>416</v>
       </c>
-      <c r="I124" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J124" s="16" t="s">
-        <v>25</v>
+      <c r="I124" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J124" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="16" t="s">
+      <c r="A125" s="20" t="s">
         <v>417</v>
       </c>
-      <c r="B125" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C125" s="16" t="s">
+      <c r="B125" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="D125" s="18" t="s">
+      <c r="D125" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E125" s="20" t="s">
+      <c r="E125" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F125" s="21">
+      <c r="F125" s="23">
         <v>2.0</v>
       </c>
-      <c r="G125" s="21"/>
-      <c r="H125" s="16" t="s">
+      <c r="G125" s="23"/>
+      <c r="H125" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="I125" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J125" s="16" t="s">
-        <v>25</v>
+      <c r="I125" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J125" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="16" t="s">
+      <c r="A126" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="B126" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C126" s="16" t="s">
+      <c r="B126" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" s="20" t="s">
         <v>421</v>
       </c>
-      <c r="D126" s="18" t="s">
+      <c r="D126" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E126" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F126" s="21">
+      <c r="E126" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F126" s="23">
         <v>10.0</v>
       </c>
       <c r="G126" s="25"/>
-      <c r="H126" s="16" t="s">
+      <c r="H126" s="20" t="s">
         <v>422</v>
       </c>
-      <c r="I126" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J126" s="16" t="s">
-        <v>25</v>
+      <c r="I126" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J126" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
@@ -6704,7 +6704,7 @@
         <v>423</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C127" s="31" t="s">
         <v>424</v>
@@ -6723,10 +6723,10 @@
         <v>425</v>
       </c>
       <c r="I127" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J127" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -6734,7 +6734,7 @@
         <v>426</v>
       </c>
       <c r="B128" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C128" s="31" t="s">
         <v>427</v>
@@ -6753,44 +6753,44 @@
         <v>428</v>
       </c>
       <c r="I128" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J128" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="11" t="s">
+      <c r="A129" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="B129" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C129" s="11" t="s">
+      <c r="B129" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C129" s="12" t="s">
         <v>430</v>
       </c>
-      <c r="D129" s="12" t="s">
+      <c r="D129" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E129" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F129" s="15">
+      <c r="E129" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F129" s="17">
         <f t="shared" ref="F129:G129" si="24">SUM(F130:F133)</f>
         <v>12</v>
       </c>
-      <c r="G129" s="15">
+      <c r="G129" s="17">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="H129" s="11" t="s">
+      <c r="H129" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="I129" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J129" s="11" t="s">
-        <v>25</v>
+      <c r="I129" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J129" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K129" s="24"/>
       <c r="L129" s="24"/>
@@ -6808,93 +6808,93 @@
       <c r="X129" s="24"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="16" t="s">
+      <c r="A130" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="B130" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C130" s="16" t="s">
+      <c r="B130" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C130" s="20" t="s">
         <v>433</v>
       </c>
-      <c r="D130" s="18" t="s">
+      <c r="D130" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E130" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F130" s="21">
+      <c r="E130" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F130" s="23">
         <v>3.0</v>
       </c>
-      <c r="G130" s="21"/>
-      <c r="H130" s="16" t="s">
+      <c r="G130" s="23"/>
+      <c r="H130" s="20" t="s">
         <v>434</v>
       </c>
-      <c r="I130" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J130" s="16" t="s">
-        <v>25</v>
+      <c r="I130" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J130" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="16" t="s">
+      <c r="A131" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="B131" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C131" s="16" t="s">
+      <c r="B131" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C131" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="D131" s="18" t="s">
+      <c r="D131" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E131" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F131" s="21">
+      <c r="E131" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F131" s="23">
         <v>3.0</v>
       </c>
-      <c r="G131" s="21"/>
-      <c r="H131" s="16" t="s">
+      <c r="G131" s="23"/>
+      <c r="H131" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="I131" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J131" s="16" t="s">
-        <v>25</v>
+      <c r="I131" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J131" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="16" t="s">
+      <c r="A132" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B132" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C132" s="16" t="s">
+      <c r="B132" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C132" s="20" t="s">
         <v>439</v>
       </c>
-      <c r="D132" s="18" t="s">
+      <c r="D132" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E132" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F132" s="21">
+      <c r="E132" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F132" s="23">
         <v>3.0</v>
       </c>
-      <c r="G132" s="21"/>
-      <c r="H132" s="16" t="s">
+      <c r="G132" s="23"/>
+      <c r="H132" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="I132" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J132" s="16" t="s">
-        <v>25</v>
+      <c r="I132" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J132" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
@@ -6902,62 +6902,62 @@
         <v>441</v>
       </c>
       <c r="B133" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C133" s="31" t="s">
         <v>442</v>
       </c>
       <c r="D133" s="34" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E133" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F133" s="30">
         <v>3.0</v>
       </c>
-      <c r="G133" s="21"/>
+      <c r="G133" s="23"/>
       <c r="H133" s="31" t="s">
         <v>443</v>
       </c>
       <c r="I133" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J133" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="11" t="s">
+      <c r="A134" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="B134" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C134" s="11" t="s">
+      <c r="B134" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C134" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="D134" s="12" t="s">
+      <c r="D134" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E134" s="13" t="s">
+      <c r="E134" s="14" t="s">
         <v>110</v>
       </c>
       <c r="F134" s="27">
         <v>12.0</v>
       </c>
-      <c r="G134" s="15">
+      <c r="G134" s="17">
         <f>SUM(G135:G138)</f>
         <v>0</v>
       </c>
-      <c r="H134" s="11" t="s">
+      <c r="H134" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="I134" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J134" s="11" t="s">
-        <v>25</v>
+      <c r="I134" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J134" s="12" t="s">
+        <v>16</v>
       </c>
       <c r="K134" s="24"/>
       <c r="L134" s="24"/>
@@ -6975,123 +6975,123 @@
       <c r="X134" s="24"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="16" t="s">
+      <c r="A135" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="B135" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C135" s="16" t="s">
+      <c r="B135" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C135" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="D135" s="18" t="s">
+      <c r="D135" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E135" s="20" t="s">
+      <c r="E135" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F135" s="21">
+      <c r="F135" s="23">
         <v>3.0</v>
       </c>
-      <c r="G135" s="21"/>
-      <c r="H135" s="16" t="s">
+      <c r="G135" s="23"/>
+      <c r="H135" s="20" t="s">
         <v>449</v>
       </c>
-      <c r="I135" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J135" s="16" t="s">
-        <v>25</v>
+      <c r="I135" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J135" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="16" t="s">
+      <c r="A136" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="B136" s="16" t="s">
-        <v>37</v>
+      <c r="B136" s="20" t="s">
+        <v>41</v>
       </c>
       <c r="C136" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="D136" s="18" t="s">
+      <c r="D136" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E136" s="20" t="s">
+      <c r="E136" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F136" s="21">
+      <c r="F136" s="23">
         <v>3.0</v>
       </c>
-      <c r="G136" s="21"/>
-      <c r="H136" s="16" t="s">
+      <c r="G136" s="23"/>
+      <c r="H136" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="I136" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J136" s="16" t="s">
-        <v>25</v>
+      <c r="I136" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J136" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="16" t="s">
+      <c r="A137" s="20" t="s">
         <v>453</v>
       </c>
-      <c r="B137" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C137" s="16" t="s">
+      <c r="B137" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C137" s="20" t="s">
         <v>454</v>
       </c>
-      <c r="D137" s="18" t="s">
+      <c r="D137" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E137" s="20" t="s">
+      <c r="E137" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F137" s="21">
+      <c r="F137" s="23">
         <v>3.0</v>
       </c>
-      <c r="G137" s="21"/>
-      <c r="H137" s="16" t="s">
+      <c r="G137" s="23"/>
+      <c r="H137" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="I137" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J137" s="16" t="s">
-        <v>25</v>
+      <c r="I137" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J137" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="16" t="s">
+      <c r="A138" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="B138" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C138" s="16" t="s">
+      <c r="B138" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C138" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="D138" s="18" t="s">
+      <c r="D138" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E138" s="20" t="s">
+      <c r="E138" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F138" s="21">
+      <c r="F138" s="23">
         <v>2.0</v>
       </c>
       <c r="G138" s="25"/>
-      <c r="H138" s="16" t="s">
+      <c r="H138" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="I138" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J138" s="16" t="s">
-        <v>25</v>
+      <c r="I138" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J138" s="20" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -7099,7 +7099,7 @@
         <v>459</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C139" s="31" t="s">
         <v>460</v>
@@ -7118,44 +7118,44 @@
         <v>461</v>
       </c>
       <c r="I139" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J139" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="11" t="s">
+      <c r="A140" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="B140" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C140" s="11" t="s">
+      <c r="B140" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C140" s="12" t="s">
         <v>463</v>
       </c>
       <c r="D140" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="E140" s="13" t="s">
+      <c r="E140" s="14" t="s">
         <v>110</v>
       </c>
       <c r="F140" s="26">
         <f t="shared" ref="F140:G140" si="25">SUM(F141:F142)</f>
         <v>4</v>
       </c>
-      <c r="G140" s="15">
+      <c r="G140" s="17">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="H140" s="11" t="s">
+      <c r="H140" s="12" t="s">
         <v>464</v>
       </c>
       <c r="I140" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="J140" s="11" t="s">
-        <v>25</v>
+      <c r="J140" s="12" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
@@ -7163,7 +7163,7 @@
         <v>465</v>
       </c>
       <c r="B141" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C141" s="31" t="s">
         <v>466</v>
@@ -7185,7 +7185,7 @@
         <v>295</v>
       </c>
       <c r="J141" s="31" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
@@ -7193,7 +7193,7 @@
         <v>468</v>
       </c>
       <c r="B142" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C142" s="31" t="s">
         <v>469</v>
@@ -7212,27 +7212,27 @@
         <v>470</v>
       </c>
       <c r="I142" s="32" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J142" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
+      <c r="A143" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="B143" s="12" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="B143" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C143" s="11" t="s">
+      <c r="C143" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="D143" s="12" t="s">
+      <c r="D143" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E143" s="13" t="s">
-        <v>24</v>
+      <c r="E143" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F143" s="26">
         <f t="shared" ref="F143:G143" si="26">F144+F148+F152+F158</f>
@@ -7242,14 +7242,14 @@
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="H143" s="11" t="s">
+      <c r="H143" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="I143" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J143" s="11" t="s">
-        <v>33</v>
+      <c r="I143" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J143" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K143" s="24"/>
       <c r="L143" s="24"/>
@@ -7267,20 +7267,20 @@
       <c r="X143" s="24"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="11" t="s">
+      <c r="A144" s="12" t="s">
         <v>474</v>
       </c>
-      <c r="B144" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C144" s="11" t="s">
+      <c r="B144" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C144" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="D144" s="12" t="s">
+      <c r="D144" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="E144" s="13" t="s">
-        <v>24</v>
+      <c r="E144" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F144" s="26">
         <f t="shared" ref="F144:G144" si="27">SUM(F145:F147)</f>
@@ -7290,14 +7290,14 @@
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
-      <c r="H144" s="11" t="s">
+      <c r="H144" s="12" t="s">
         <v>476</v>
       </c>
-      <c r="I144" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J144" s="11" t="s">
-        <v>33</v>
+      <c r="I144" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J144" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K144" s="24"/>
       <c r="L144" s="24"/>
@@ -7315,127 +7315,127 @@
       <c r="X144" s="24"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="16" t="s">
+      <c r="A145" s="20" t="s">
         <v>477</v>
       </c>
-      <c r="B145" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C145" s="16" t="s">
+      <c r="B145" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C145" s="20" t="s">
         <v>478</v>
       </c>
-      <c r="D145" s="18" t="s">
+      <c r="D145" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E145" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F145" s="21">
+      <c r="E145" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F145" s="23">
         <v>10.0</v>
       </c>
-      <c r="G145" s="21"/>
-      <c r="H145" s="16" t="s">
+      <c r="G145" s="23"/>
+      <c r="H145" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="I145" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J145" s="16" t="s">
-        <v>33</v>
+      <c r="I145" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J145" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="16" t="s">
+      <c r="A146" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="B146" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C146" s="16" t="s">
+      <c r="B146" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" s="20" t="s">
         <v>481</v>
       </c>
-      <c r="D146" s="18" t="s">
+      <c r="D146" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E146" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F146" s="21">
+      <c r="E146" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F146" s="23">
         <v>10.0</v>
       </c>
-      <c r="G146" s="21"/>
-      <c r="H146" s="16" t="s">
+      <c r="G146" s="23"/>
+      <c r="H146" s="20" t="s">
         <v>479</v>
       </c>
-      <c r="I146" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J146" s="16" t="s">
-        <v>33</v>
+      <c r="I146" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J146" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="16" t="s">
+      <c r="A147" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="B147" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C147" s="16" t="s">
+      <c r="B147" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C147" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="D147" s="18" t="s">
+      <c r="D147" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E147" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F147" s="21">
+      <c r="E147" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F147" s="23">
         <v>5.0</v>
       </c>
-      <c r="G147" s="21"/>
-      <c r="H147" s="16" t="s">
+      <c r="G147" s="23"/>
+      <c r="H147" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="I147" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J147" s="16" t="s">
-        <v>33</v>
+      <c r="I147" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J147" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="11" t="s">
+      <c r="A148" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="B148" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C148" s="11" t="s">
+      <c r="B148" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C148" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="D148" s="12" t="s">
+      <c r="D148" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E148" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F148" s="15">
+      <c r="E148" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F148" s="17">
         <f t="shared" ref="F148:G148" si="28">SUM(F149:F151)</f>
         <v>12</v>
       </c>
-      <c r="G148" s="15">
+      <c r="G148" s="17">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H148" s="11" t="s">
+      <c r="H148" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="I148" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J148" s="11" t="s">
-        <v>33</v>
+      <c r="I148" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K148" s="24"/>
       <c r="L148" s="24"/>
@@ -7453,127 +7453,127 @@
       <c r="X148" s="24"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="16" t="s">
+      <c r="A149" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="B149" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C149" s="16" t="s">
+      <c r="B149" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C149" s="20" t="s">
         <v>489</v>
       </c>
-      <c r="D149" s="18" t="s">
+      <c r="D149" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E149" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F149" s="21">
+      <c r="E149" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F149" s="23">
         <v>4.0</v>
       </c>
-      <c r="G149" s="21"/>
-      <c r="H149" s="16" t="s">
+      <c r="G149" s="23"/>
+      <c r="H149" s="20" t="s">
         <v>490</v>
       </c>
-      <c r="I149" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J149" s="16" t="s">
-        <v>33</v>
+      <c r="I149" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J149" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="16" t="s">
+      <c r="A150" s="20" t="s">
         <v>491</v>
       </c>
-      <c r="B150" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C150" s="16" t="s">
+      <c r="B150" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C150" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="D150" s="18" t="s">
+      <c r="D150" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E150" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F150" s="21">
+      <c r="E150" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F150" s="23">
         <v>4.0</v>
       </c>
-      <c r="G150" s="21"/>
-      <c r="H150" s="16" t="s">
+      <c r="G150" s="23"/>
+      <c r="H150" s="20" t="s">
         <v>490</v>
       </c>
-      <c r="I150" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J150" s="16" t="s">
-        <v>33</v>
+      <c r="I150" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J150" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="16" t="s">
+      <c r="A151" s="20" t="s">
         <v>493</v>
       </c>
-      <c r="B151" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C151" s="16" t="s">
+      <c r="B151" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C151" s="20" t="s">
         <v>494</v>
       </c>
-      <c r="D151" s="18" t="s">
+      <c r="D151" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E151" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F151" s="21">
+      <c r="E151" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F151" s="23">
         <v>4.0</v>
       </c>
       <c r="G151" s="25"/>
-      <c r="H151" s="16" t="s">
+      <c r="H151" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="I151" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J151" s="16" t="s">
-        <v>33</v>
+      <c r="I151" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J151" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="11" t="s">
+      <c r="A152" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="B152" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C152" s="11" t="s">
+      <c r="B152" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C152" s="12" t="s">
         <v>497</v>
       </c>
-      <c r="D152" s="12" t="s">
+      <c r="D152" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E152" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F152" s="15">
+      <c r="E152" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F152" s="17">
         <f t="shared" ref="F152:G152" si="29">SUM(F153:F157)</f>
         <v>19</v>
       </c>
-      <c r="G152" s="15">
+      <c r="G152" s="17">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H152" s="11" t="s">
+      <c r="H152" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="I152" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J152" s="11" t="s">
-        <v>33</v>
+      <c r="I152" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J152" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K152" s="24"/>
       <c r="L152" s="24"/>
@@ -7591,170 +7591,170 @@
       <c r="X152" s="24"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="16" t="s">
+      <c r="A153" s="20" t="s">
         <v>499</v>
       </c>
-      <c r="B153" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C153" s="16" t="s">
+      <c r="B153" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C153" s="20" t="s">
         <v>500</v>
       </c>
-      <c r="D153" s="18" t="s">
+      <c r="D153" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E153" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F153" s="21">
+      <c r="E153" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F153" s="23">
         <v>4.0</v>
       </c>
-      <c r="G153" s="21"/>
-      <c r="H153" s="16" t="s">
+      <c r="G153" s="23"/>
+      <c r="H153" s="20" t="s">
         <v>501</v>
       </c>
-      <c r="I153" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J153" s="16" t="s">
-        <v>33</v>
+      <c r="I153" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J153" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="16" t="s">
+      <c r="A154" s="20" t="s">
         <v>502</v>
       </c>
-      <c r="B154" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C154" s="16" t="s">
+      <c r="B154" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C154" s="20" t="s">
         <v>503</v>
       </c>
-      <c r="D154" s="18" t="s">
+      <c r="D154" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E154" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F154" s="21">
+      <c r="E154" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F154" s="23">
         <v>4.0</v>
       </c>
-      <c r="G154" s="21"/>
-      <c r="H154" s="16" t="s">
+      <c r="G154" s="23"/>
+      <c r="H154" s="20" t="s">
         <v>504</v>
       </c>
-      <c r="I154" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J154" s="16" t="s">
-        <v>33</v>
+      <c r="I154" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J154" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="16" t="s">
+      <c r="A155" s="20" t="s">
         <v>505</v>
       </c>
-      <c r="B155" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C155" s="16" t="s">
+      <c r="B155" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C155" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="D155" s="18" t="s">
+      <c r="D155" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E155" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F155" s="21">
+      <c r="E155" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F155" s="23">
         <v>4.0</v>
       </c>
-      <c r="G155" s="21"/>
-      <c r="H155" s="16" t="s">
+      <c r="G155" s="23"/>
+      <c r="H155" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="I155" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J155" s="16" t="s">
-        <v>33</v>
+      <c r="I155" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J155" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="16" t="s">
+      <c r="A156" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="B156" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C156" s="16" t="s">
+      <c r="B156" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C156" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="D156" s="18" t="s">
+      <c r="D156" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E156" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F156" s="21">
+      <c r="E156" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F156" s="23">
         <v>4.0</v>
       </c>
       <c r="G156" s="25"/>
-      <c r="H156" s="16" t="s">
+      <c r="H156" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="I156" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J156" s="16" t="s">
-        <v>33</v>
+      <c r="I156" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J156" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="16" t="s">
+      <c r="A157" s="20" t="s">
         <v>511</v>
       </c>
-      <c r="B157" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C157" s="16" t="s">
+      <c r="B157" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C157" s="20" t="s">
         <v>512</v>
       </c>
-      <c r="D157" s="18" t="s">
+      <c r="D157" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E157" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F157" s="21">
+      <c r="E157" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F157" s="23">
         <v>3.0</v>
       </c>
-      <c r="G157" s="21"/>
-      <c r="H157" s="16" t="s">
+      <c r="G157" s="23"/>
+      <c r="H157" s="20" t="s">
         <v>513</v>
       </c>
-      <c r="I157" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J157" s="16" t="s">
-        <v>33</v>
+      <c r="I157" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J157" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="11" t="s">
+      <c r="A158" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="B158" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C158" s="11" t="s">
+      <c r="B158" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C158" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="D158" s="12" t="s">
+      <c r="D158" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="E158" s="13" t="s">
-        <v>24</v>
+      <c r="E158" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F158" s="26">
         <f t="shared" ref="F158:G158" si="30">SUM(F159:F160)</f>
@@ -7764,14 +7764,14 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H158" s="11" t="s">
+      <c r="H158" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="I158" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J158" s="11" t="s">
-        <v>33</v>
+      <c r="I158" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K158" s="24"/>
       <c r="L158" s="24"/>
@@ -7789,80 +7789,80 @@
       <c r="X158" s="24"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="16" t="s">
+      <c r="A159" s="20" t="s">
         <v>517</v>
       </c>
-      <c r="B159" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C159" s="16" t="s">
+      <c r="B159" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C159" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="D159" s="18" t="s">
+      <c r="D159" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E159" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F159" s="21">
+      <c r="E159" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F159" s="23">
         <v>3.0</v>
       </c>
       <c r="G159" s="25"/>
-      <c r="H159" s="16" t="s">
+      <c r="H159" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="I159" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J159" s="16" t="s">
-        <v>33</v>
+      <c r="I159" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J159" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="16" t="s">
+      <c r="A160" s="20" t="s">
         <v>520</v>
       </c>
-      <c r="B160" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C160" s="16" t="s">
+      <c r="B160" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C160" s="20" t="s">
         <v>521</v>
       </c>
-      <c r="D160" s="18" t="s">
+      <c r="D160" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E160" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F160" s="21">
+      <c r="E160" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F160" s="23">
         <v>3.0</v>
       </c>
-      <c r="G160" s="21"/>
-      <c r="H160" s="16" t="s">
+      <c r="G160" s="23"/>
+      <c r="H160" s="20" t="s">
         <v>522</v>
       </c>
-      <c r="I160" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J160" s="16" t="s">
-        <v>33</v>
+      <c r="I160" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J160" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="11" t="s">
+      <c r="A161" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="B161" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C161" s="11" t="s">
+      <c r="B161" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C161" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="D161" s="12" t="s">
+      <c r="D161" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="E161" s="13" t="s">
-        <v>24</v>
+      <c r="E161" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F161" s="26">
         <f t="shared" ref="F161:G161" si="31">F162+F166+F169+F172</f>
@@ -7872,14 +7872,14 @@
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H161" s="11" t="s">
+      <c r="H161" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="I161" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J161" s="11" t="s">
-        <v>33</v>
+      <c r="I161" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J161" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K161" s="24"/>
       <c r="L161" s="24"/>
@@ -7897,37 +7897,37 @@
       <c r="X161" s="24"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="11" t="s">
+      <c r="A162" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="B162" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C162" s="11" t="s">
+      <c r="B162" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C162" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="D162" s="12" t="s">
+      <c r="D162" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="E162" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F162" s="15">
+      <c r="E162" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F162" s="17">
         <f t="shared" ref="F162:G162" si="32">SUM(F163:F165)</f>
         <v>12</v>
       </c>
-      <c r="G162" s="15">
+      <c r="G162" s="17">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="H162" s="11" t="s">
+      <c r="H162" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="I162" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J162" s="11" t="s">
-        <v>33</v>
+      <c r="I162" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J162" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K162" s="24"/>
       <c r="L162" s="24"/>
@@ -7945,109 +7945,109 @@
       <c r="X162" s="24"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="16" t="s">
+      <c r="A163" s="20" t="s">
         <v>530</v>
       </c>
-      <c r="B163" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C163" s="16" t="s">
+      <c r="B163" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C163" s="20" t="s">
         <v>531</v>
       </c>
-      <c r="D163" s="18" t="s">
+      <c r="D163" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E163" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F163" s="21">
+      <c r="E163" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F163" s="23">
         <v>4.0</v>
       </c>
-      <c r="G163" s="21"/>
-      <c r="H163" s="16" t="s">
+      <c r="G163" s="23"/>
+      <c r="H163" s="20" t="s">
         <v>532</v>
       </c>
-      <c r="I163" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J163" s="16" t="s">
-        <v>33</v>
+      <c r="I163" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J163" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="16" t="s">
+      <c r="A164" s="20" t="s">
         <v>533</v>
       </c>
-      <c r="B164" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C164" s="16" t="s">
+      <c r="B164" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C164" s="20" t="s">
         <v>534</v>
       </c>
-      <c r="D164" s="18" t="s">
+      <c r="D164" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E164" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F164" s="21">
+      <c r="E164" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F164" s="23">
         <v>4.0</v>
       </c>
-      <c r="G164" s="21"/>
-      <c r="H164" s="16" t="s">
+      <c r="G164" s="23"/>
+      <c r="H164" s="20" t="s">
         <v>535</v>
       </c>
-      <c r="I164" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J164" s="16" t="s">
-        <v>33</v>
+      <c r="I164" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J164" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="16" t="s">
+      <c r="A165" s="20" t="s">
         <v>536</v>
       </c>
-      <c r="B165" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C165" s="16" t="s">
+      <c r="B165" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C165" s="20" t="s">
         <v>537</v>
       </c>
-      <c r="D165" s="18" t="s">
+      <c r="D165" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F165" s="21">
+      <c r="E165" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F165" s="23">
         <v>4.0</v>
       </c>
-      <c r="G165" s="21"/>
-      <c r="H165" s="16" t="s">
+      <c r="G165" s="23"/>
+      <c r="H165" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="I165" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J165" s="16" t="s">
-        <v>33</v>
+      <c r="I165" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J165" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="11" t="s">
+      <c r="A166" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="B166" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C166" s="11" t="s">
+      <c r="B166" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C166" s="12" t="s">
         <v>540</v>
       </c>
-      <c r="D166" s="12" t="s">
+      <c r="D166" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="E166" s="13" t="s">
+      <c r="E166" s="14" t="s">
         <v>55</v>
       </c>
       <c r="F166" s="26">
@@ -8058,14 +8058,14 @@
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="H166" s="11" t="s">
+      <c r="H166" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="I166" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J166" s="11" t="s">
-        <v>33</v>
+      <c r="I166" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J166" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K166" s="24"/>
       <c r="L166" s="24"/>
@@ -8083,82 +8083,82 @@
       <c r="X166" s="24"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="16" t="s">
+      <c r="A167" s="20" t="s">
         <v>542</v>
       </c>
-      <c r="B167" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C167" s="16" t="s">
+      <c r="B167" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C167" s="20" t="s">
         <v>543</v>
       </c>
-      <c r="D167" s="18" t="s">
+      <c r="D167" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E167" s="20" t="s">
+      <c r="E167" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F167" s="21">
+      <c r="F167" s="23">
         <v>5.0</v>
       </c>
       <c r="G167" s="38"/>
-      <c r="H167" s="16" t="s">
+      <c r="H167" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="I167" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J167" s="16" t="s">
-        <v>33</v>
+      <c r="I167" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J167" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="16" t="s">
+      <c r="A168" s="20" t="s">
         <v>545</v>
       </c>
-      <c r="B168" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C168" s="16" t="s">
+      <c r="B168" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C168" s="20" t="s">
         <v>546</v>
       </c>
-      <c r="D168" s="18" t="s">
+      <c r="D168" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E168" s="20" t="s">
+      <c r="E168" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F168" s="21">
+      <c r="F168" s="23">
         <v>3.0</v>
       </c>
       <c r="G168" s="38"/>
-      <c r="H168" s="16" t="s">
+      <c r="H168" s="20" t="s">
         <v>547</v>
       </c>
-      <c r="I168" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J168" s="16" t="s">
-        <v>33</v>
+      <c r="I168" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J168" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="16" t="s">
+      <c r="A169" s="20" t="s">
         <v>548</v>
       </c>
-      <c r="B169" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C169" s="16" t="s">
+      <c r="B169" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C169" s="20" t="s">
         <v>549</v>
       </c>
-      <c r="D169" s="18" t="s">
+      <c r="D169" s="21" t="s">
         <v>525</v>
       </c>
-      <c r="E169" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F169" s="21">
+      <c r="E169" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F169" s="23">
         <f t="shared" ref="F169:G169" si="34">SUM(F170:F171)</f>
         <v>8</v>
       </c>
@@ -8166,91 +8166,91 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="H169" s="16" t="s">
+      <c r="H169" s="20" t="s">
         <v>550</v>
       </c>
-      <c r="I169" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J169" s="16" t="s">
-        <v>33</v>
+      <c r="I169" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J169" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="16" t="s">
+      <c r="A170" s="20" t="s">
         <v>551</v>
       </c>
-      <c r="B170" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C170" s="16" t="s">
+      <c r="B170" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C170" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="D170" s="18" t="s">
+      <c r="D170" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E170" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F170" s="21">
+      <c r="E170" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F170" s="23">
         <v>4.0</v>
       </c>
       <c r="G170" s="38"/>
-      <c r="H170" s="16" t="s">
+      <c r="H170" s="20" t="s">
         <v>553</v>
       </c>
-      <c r="I170" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J170" s="16" t="s">
-        <v>33</v>
+      <c r="I170" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J170" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="16" t="s">
+      <c r="A171" s="20" t="s">
         <v>554</v>
       </c>
-      <c r="B171" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C171" s="16" t="s">
+      <c r="B171" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C171" s="20" t="s">
         <v>555</v>
       </c>
-      <c r="D171" s="18" t="s">
+      <c r="D171" s="21" t="s">
         <v>556</v>
       </c>
-      <c r="E171" s="20" t="s">
+      <c r="E171" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F171" s="21">
+      <c r="F171" s="23">
         <v>4.0</v>
       </c>
       <c r="G171" s="38"/>
-      <c r="H171" s="16" t="s">
+      <c r="H171" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="I171" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J171" s="16" t="s">
-        <v>33</v>
+      <c r="I171" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J171" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="11" t="s">
+      <c r="A172" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="B172" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C172" s="11" t="s">
+      <c r="B172" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C172" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="D172" s="12" t="s">
+      <c r="D172" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="E172" s="13" t="s">
-        <v>24</v>
+      <c r="E172" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="F172" s="26">
         <f t="shared" ref="F172:G172" si="35">SUM(F173:F176)</f>
@@ -8260,14 +8260,14 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="H172" s="11" t="s">
+      <c r="H172" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="I172" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="J172" s="11" t="s">
-        <v>33</v>
+      <c r="I172" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="J172" s="12" t="s">
+        <v>23</v>
       </c>
       <c r="K172" s="24"/>
       <c r="L172" s="24"/>
@@ -8285,123 +8285,123 @@
       <c r="X172" s="24"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="16" t="s">
+      <c r="A173" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="B173" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C173" s="16" t="s">
+      <c r="B173" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C173" s="20" t="s">
         <v>562</v>
       </c>
-      <c r="D173" s="18" t="s">
+      <c r="D173" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E173" s="20" t="s">
+      <c r="E173" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F173" s="21">
+      <c r="F173" s="23">
         <v>3.0</v>
       </c>
       <c r="G173" s="38"/>
-      <c r="H173" s="16" t="s">
+      <c r="H173" s="20" t="s">
         <v>563</v>
       </c>
-      <c r="I173" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J173" s="16" t="s">
-        <v>33</v>
+      <c r="I173" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J173" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="16" t="s">
+      <c r="A174" s="20" t="s">
         <v>564</v>
       </c>
-      <c r="B174" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C174" s="16" t="s">
+      <c r="B174" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C174" s="20" t="s">
         <v>565</v>
       </c>
-      <c r="D174" s="18" t="s">
+      <c r="D174" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E174" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F174" s="21">
+      <c r="E174" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F174" s="23">
         <v>4.0</v>
       </c>
       <c r="G174" s="38"/>
-      <c r="H174" s="16" t="s">
+      <c r="H174" s="20" t="s">
         <v>566</v>
       </c>
-      <c r="I174" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J174" s="16" t="s">
-        <v>33</v>
+      <c r="I174" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J174" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="16" t="s">
+      <c r="A175" s="20" t="s">
         <v>567</v>
       </c>
-      <c r="B175" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C175" s="16" t="s">
+      <c r="B175" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C175" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="D175" s="18" t="s">
+      <c r="D175" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E175" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F175" s="21">
+      <c r="E175" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F175" s="23">
         <v>5.0</v>
       </c>
       <c r="G175" s="38"/>
-      <c r="H175" s="16" t="s">
+      <c r="H175" s="20" t="s">
         <v>569</v>
       </c>
-      <c r="I175" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J175" s="16" t="s">
-        <v>33</v>
+      <c r="I175" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J175" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="16" t="s">
+      <c r="A176" s="20" t="s">
         <v>570</v>
       </c>
-      <c r="B176" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C176" s="16" t="s">
+      <c r="B176" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C176" s="20" t="s">
         <v>571</v>
       </c>
-      <c r="D176" s="18" t="s">
+      <c r="D176" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E176" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="F176" s="21">
+      <c r="E176" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="F176" s="23">
         <v>20.0</v>
       </c>
       <c r="G176" s="38"/>
-      <c r="H176" s="16" t="s">
+      <c r="H176" s="20" t="s">
         <v>572</v>
       </c>
-      <c r="I176" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J176" s="16" t="s">
-        <v>33</v>
+      <c r="I176" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="J176" s="20" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -11025,13 +11025,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4">
         <v>46297.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
@@ -11052,13 +11052,13 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="14">
+        <v>16</v>
+      </c>
+      <c r="B4" s="9">
         <v>46325.0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
@@ -11074,18 +11074,18 @@
       </c>
       <c r="G4" s="7">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A4,Backlog!I:I,"Realizado")</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4">
         <v>46360.0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D5" s="6">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
@@ -11105,45 +11105,45 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="22">
+      <c r="A8" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="18">
         <f>SUM(D2:D5)</f>
         <v>387</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="A9" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="18">
         <f>SUM(E2:E5)</f>
         <v>170</v>
       </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="19" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="7">
@@ -11152,12 +11152,12 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="19" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="7">
         <f>SUM(G2:G5)</f>
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/docs/Backlog Proyecto Titulo.xlsx
+++ b/docs/Backlog Proyecto Titulo.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="580">
   <si>
     <t>Etapa</t>
   </si>
@@ -71,22 +71,28 @@
     <t>EP-01</t>
   </si>
   <si>
+    <t>Épica</t>
+  </si>
+  <si>
+    <t>Etapa 1: Definición, investigación y análisis de requerimientos</t>
+  </si>
+  <si>
+    <t>OG, OE1, OE2, OE3, OE4</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
     <t>Etapa 2</t>
   </si>
   <si>
     <t>Diseño técnico, arquitectura, protocolo e implementación inicial</t>
   </si>
   <si>
-    <t>Épica</t>
-  </si>
-  <si>
-    <t>Etapa 1: Definición, investigación y análisis de requerimientos</t>
-  </si>
-  <si>
-    <t>OG, OE1, OE2, OE3, OE4</t>
-  </si>
-  <si>
-    <t>Alta</t>
+    <t>Problema, estado del arte, objetivos, requerimientos y alternativas definidos y respaldados.</t>
+  </si>
+  <si>
+    <t>Realizado</t>
   </si>
   <si>
     <t>Etapa 3</t>
@@ -95,12 +101,6 @@
     <t>Implementación observabilidad, pruebas piloto y validación preliminar</t>
   </si>
   <si>
-    <t>Problema, estado del arte, objetivos, requerimientos y alternativas definidos y respaldados.</t>
-  </si>
-  <si>
-    <t>Realizado</t>
-  </si>
-  <si>
     <t>HU-01</t>
   </si>
   <si>
@@ -128,33 +128,33 @@
     <t>Tarea</t>
   </si>
   <si>
+    <t>Indicador</t>
+  </si>
+  <si>
+    <t>Valor</t>
+  </si>
+  <si>
     <t>Investigar comparaciones de distribuciones ligeras de Kubernetes</t>
   </si>
   <si>
+    <t>Total de horas estimadas (tareas)</t>
+  </si>
+  <si>
     <t>OE1, OE2</t>
   </si>
   <si>
+    <t>Total de horas reales (tareas)</t>
+  </si>
+  <si>
     <t>Fichas bibliográficas sobre K3s, MicroK8s y métricas de CPU, memoria, throughput y latencia.</t>
   </si>
   <si>
-    <t>Indicador</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Total de horas estimadas (tareas)</t>
-  </si>
-  <si>
     <t>T-01.2</t>
   </si>
   <si>
     <t>Investigar mecanismos HA y almacenamiento de estado (etcd vs Dqlite)</t>
   </si>
   <si>
-    <t>Total de horas reales (tareas)</t>
-  </si>
-  <si>
     <t>Fichas sobre quórum, replicación, recuperación y diferencias arquitectónicas.</t>
   </si>
   <si>
@@ -899,417 +899,417 @@
     <t>Stack de observabilidad operativo y aplicación de referencia preparada.</t>
   </si>
   <si>
+    <t>HU-16</t>
+  </si>
+  <si>
+    <t>Implementación de medición energética</t>
+  </si>
+  <si>
+    <t>Scaphandre registra energía y potencia del host durante pruebas.</t>
+  </si>
+  <si>
+    <t>T-16.1</t>
+  </si>
+  <si>
+    <t>Instalar y configurar Scaphandre en el host físico</t>
+  </si>
+  <si>
+    <t>Scaphandre ejecuta y expone métricas energéticas. Fuente: evidencia_T-16.md.</t>
+  </si>
+  <si>
+    <t>T-16.2</t>
+  </si>
+  <si>
+    <t>Verificar disponibilidad de RAPL/powercap y dominios</t>
+  </si>
+  <si>
+    <t>Contadores accesibles y dominio energético documentado. Fuente: evidencia_T-16.md.</t>
+  </si>
+  <si>
+    <t>T-16.3</t>
+  </si>
+  <si>
+    <t>Configurar captura de energía y potencia durante una prueba</t>
+  </si>
+  <si>
+    <t>Datos de energía/potencia registrados para una ventana experimental, con lectura directa del contador en t_inicio y t_fin además de la consulta a Prometheus.</t>
+  </si>
+  <si>
+    <t>T-16.4</t>
+  </si>
+  <si>
+    <t>Validar Scaphandre contra lectura directa de los contadores</t>
+  </si>
+  <si>
+    <t>Consistencia comprobada durante una ventana común. Criterio: diferencia &lt; 2 % entre Scaphandre y el contador crudo.</t>
+  </si>
+  <si>
+    <t>HU-17</t>
+  </si>
+  <si>
+    <t>Implementación de monitoreo de recursos y almacenamiento temporal</t>
+  </si>
+  <si>
+    <t>CPU y RAM disponibles en Prometheus para ambos entornos.</t>
+  </si>
+  <si>
+    <t>T-17.1</t>
+  </si>
+  <si>
+    <t>Instalar Node Exporter en los nodos</t>
+  </si>
+  <si>
+    <t>Métricas de CPU y memoria expuestas en todos los nodos.</t>
+  </si>
+  <si>
+    <t>T-17.2</t>
+  </si>
+  <si>
+    <t>Instalar/configurar Prometheus</t>
+  </si>
+  <si>
+    <t>Prometheus recolecta correctamente Node Exporter.</t>
+  </si>
+  <si>
+    <t>T-17.3</t>
+  </si>
+  <si>
+    <t>Configurar etiquetas y separación de clúster/escenario</t>
+  </si>
+  <si>
+    <t>Series distinguibles por distribución, nodo y ejecución.</t>
+  </si>
+  <si>
+    <t>T-17.4</t>
+  </si>
+  <si>
+    <t>Validar continuidad y frecuencia de recolección</t>
+  </si>
+  <si>
+    <t>No existen interrupciones relevantes durante una prueba piloto.</t>
+  </si>
+  <si>
+    <t>T-17.5</t>
+  </si>
+  <si>
+    <t>Instalar kube-state-metrics y definir cómo Prometheus lo scrapea desde el host</t>
+  </si>
+  <si>
+    <t>kube-state-metrics operativo en ambos clústeres, scrapeado por Prometheus, con kube_node_status_condition disponible.</t>
+  </si>
+  <si>
+    <t>HU-18</t>
+  </si>
+  <si>
+    <t>Implementación de aplicación de referencia y pruebas de carga</t>
+  </si>
+  <si>
+    <t>Aplicación idéntica desplegada y accesible mediante el mecanismo definido.</t>
+  </si>
+  <si>
+    <t>T-18.1</t>
+  </si>
+  <si>
+    <t>Desplegar aplicación de referencia en K3s y MicroK8s</t>
+  </si>
+  <si>
+    <t>Aplicación responde correctamente en ambos clústeres.</t>
+  </si>
+  <si>
+    <t>T-18.2</t>
+  </si>
+  <si>
+    <t>Configurar acceso a la aplicación y endpoints de prueba</t>
+  </si>
+  <si>
+    <t>Endpoints equivalentes y comprobados.</t>
+  </si>
+  <si>
+    <t>T-18.3</t>
+  </si>
+  <si>
+    <t>Desarrollar scripts k6 para escenarios de carga</t>
+  </si>
+  <si>
+    <t>Scripts parametrizados para idle, carga media y carga alta.</t>
+  </si>
+  <si>
+    <t>T-18.4</t>
+  </si>
+  <si>
+    <t>Configurar exportación y organización de resultados k6</t>
+  </si>
+  <si>
+    <t>Resultados guardados por escenario y repetición.</t>
+  </si>
+  <si>
+    <t>T-18.5</t>
+  </si>
+  <si>
+    <t>Habilitar Service LoadBalancer con kube-vip (192.168.100.150) en ambas distribuciones</t>
+  </si>
+  <si>
+    <t>Service de la aplicación de referencia con IP .150 accesible desde el host en K3s y MicroK8s.</t>
+  </si>
+  <si>
+    <t>HU-19</t>
+  </si>
+  <si>
+    <t>Implementación de pruebas de resiliencia</t>
+  </si>
+  <si>
+    <t>Fallo controlado y recuperación medibles sin pérdida intencional de quórum.</t>
+  </si>
+  <si>
+    <t>T-19.1</t>
+  </si>
+  <si>
+    <t>Implementar procedimiento/script de fallo controlado de un nodo</t>
+  </si>
+  <si>
+    <t>Fallo reproducible sobre un único nodo.</t>
+  </si>
+  <si>
+    <t>T-19.2</t>
+  </si>
+  <si>
+    <t>Registrar inicio, detección y recuperación del fallo</t>
+  </si>
+  <si>
+    <t>Marcas temporales suficientes para calcular tiempos.</t>
+  </si>
+  <si>
+    <t>T-19.3</t>
+  </si>
+  <si>
+    <t>Integrar solicitudes afectadas con resultados k6</t>
+  </si>
+  <si>
+    <t>Cantidad de solicitudes afectadas asociada al intervalo de fallo. Si la tasa de carga es provisional (T-20.5 pendiente), las corridas se marcan como verificación y no como piloto.</t>
+  </si>
+  <si>
+    <t>T-19.4</t>
+  </si>
+  <si>
+    <t>Fijar ubicación del pod de NGINX durante el fallo y verificar parámetros de detección y tolerancia</t>
+  </si>
+  <si>
+    <t>Regla de ubicación implementada: al inyectar el fallo el pod no está en el nodo titular de la VIP (se mueve si coincide); valores efectivos de detección y tolerancia registrados por distribución y diferencias documentadas.</t>
+  </si>
+  <si>
+    <t>T-19.5</t>
+  </si>
+  <si>
+    <t>Revalidar la migración de la VIP con kube-vip v1.2.4</t>
+  </si>
+  <si>
+    <t>Migración de la VIP revalidada con kube-vip v1.2.4 en K3s y MicroK8s; titular de la VIP registrado en cada corrida, sin control del arranque.</t>
+  </si>
+  <si>
+    <t>HU-32</t>
+  </si>
+  <si>
+    <t>Orquestación de ejecuciones experimentales</t>
+  </si>
+  <si>
+    <t>Cada ejecución queda registrada con distribución, escenario, repetición y ventana temporal, y deja datos aptos para el análisis.</t>
+  </si>
+  <si>
+    <t>T-32.1</t>
+  </si>
+  <si>
+    <t>Implementar orquestador de ejecuciones con metadatos de ventana y ubicación</t>
+  </si>
+  <si>
+    <t>Script versionado que ejecuta una repetición completa y guarda metadatos, resultados de k6 y snapshot de Prometheus.</t>
+  </si>
+  <si>
+    <t>HU-34</t>
+  </si>
+  <si>
+    <t>Sincronización temporal con chrony entre el host y las VMs</t>
+  </si>
+  <si>
+    <t>Relojes del host y de las VMs sincronizados con chrony (host como fuente local), verificables en K3s y MicroK8s, como base de la alineación por marcas de tiempo (RO-07).</t>
+  </si>
+  <si>
+    <t>T-34.1</t>
+  </si>
+  <si>
+    <t>Implementar rol Ansible de chrony en el host (servidor NTP para 192.168.100.0/24)</t>
+  </si>
+  <si>
+    <t>chrony activo en el host y sirviendo a 192.168.100.0/24; rol idempotente (segunda corrida sin cambios).</t>
+  </si>
+  <si>
+    <t>T-34.2</t>
+  </si>
+  <si>
+    <t>Implementar rol Ansible de chrony en las VMs (cliente de 192.168.100.1 únicamente)</t>
+  </si>
+  <si>
+    <t>chrony activo en las VMs de K3s y MicroK8s con 192.168.100.1 como única fuente; rol idempotente y aplicable tras cada reconstrucción de las VMs.</t>
+  </si>
+  <si>
+    <t>T-34.3</t>
+  </si>
+  <si>
+    <t>Verificar sincronización con chronyc tracking y chronyc sources en K3s y MicroK8s</t>
+  </si>
+  <si>
+    <t>Salidas de chronyc tracking y chronyc sources registradas en el host y en las VMs de ambos clústeres, con desfase y fuente documentados.</t>
+  </si>
+  <si>
+    <t>EP-06</t>
+  </si>
+  <si>
+    <t>Etapa 3: Pruebas iniciales, mejoras y validación preliminar</t>
+  </si>
+  <si>
+    <t>Pruebas piloto ejecutadas, problemas corregidos y validación preliminar documentada.</t>
+  </si>
+  <si>
     <t>En progreso</t>
   </si>
   <si>
-    <t>HU-16</t>
-  </si>
-  <si>
-    <t>Implementación de medición energética</t>
-  </si>
-  <si>
-    <t>Scaphandre registra energía y potencia del host durante pruebas.</t>
-  </si>
-  <si>
-    <t>T-16.1</t>
-  </si>
-  <si>
-    <t>Instalar y configurar Scaphandre en el host físico</t>
-  </si>
-  <si>
-    <t>Scaphandre ejecuta y expone métricas energéticas. Fuente: evidencia_T-16.md.</t>
-  </si>
-  <si>
-    <t>T-16.2</t>
-  </si>
-  <si>
-    <t>Verificar disponibilidad de RAPL/powercap y dominios</t>
-  </si>
-  <si>
-    <t>Contadores accesibles y dominio energético documentado. Fuente: evidencia_T-16.md.</t>
-  </si>
-  <si>
-    <t>T-16.3</t>
-  </si>
-  <si>
-    <t>Configurar captura de energía y potencia durante una prueba</t>
-  </si>
-  <si>
-    <t>Datos de energía/potencia registrados para una ventana experimental, con lectura directa del contador en t_inicio y t_fin además de la consulta a Prometheus.</t>
-  </si>
-  <si>
-    <t>T-16.4</t>
-  </si>
-  <si>
-    <t>Validar Scaphandre contra lectura directa de los contadores</t>
-  </si>
-  <si>
-    <t>Consistencia comprobada durante una ventana común. Criterio: diferencia &lt; 2 % entre Scaphandre y el contador crudo.</t>
-  </si>
-  <si>
-    <t>HU-17</t>
-  </si>
-  <si>
-    <t>Implementación de monitoreo de recursos y almacenamiento temporal</t>
-  </si>
-  <si>
-    <t>CPU y RAM disponibles en Prometheus para ambos entornos.</t>
-  </si>
-  <si>
-    <t>T-17.1</t>
-  </si>
-  <si>
-    <t>Instalar Node Exporter en los nodos</t>
-  </si>
-  <si>
-    <t>Métricas de CPU y memoria expuestas en todos los nodos.</t>
-  </si>
-  <si>
-    <t>T-17.2</t>
-  </si>
-  <si>
-    <t>Instalar/configurar Prometheus</t>
-  </si>
-  <si>
-    <t>Prometheus recolecta correctamente Node Exporter.</t>
-  </si>
-  <si>
-    <t>T-17.3</t>
-  </si>
-  <si>
-    <t>Configurar etiquetas y separación de clúster/escenario</t>
-  </si>
-  <si>
-    <t>Series distinguibles por distribución, nodo y ejecución.</t>
-  </si>
-  <si>
-    <t>T-17.4</t>
-  </si>
-  <si>
-    <t>Validar continuidad y frecuencia de recolección</t>
-  </si>
-  <si>
-    <t>No existen interrupciones relevantes durante una prueba piloto.</t>
-  </si>
-  <si>
-    <t>T-17.5</t>
-  </si>
-  <si>
-    <t>Instalar kube-state-metrics y definir cómo Prometheus lo scrapea desde el host</t>
-  </si>
-  <si>
-    <t>kube-state-metrics operativo en ambos clústeres, scrapeado por Prometheus, con kube_node_status_condition disponible.</t>
-  </si>
-  <si>
-    <t>HU-18</t>
-  </si>
-  <si>
-    <t>Implementación de aplicación de referencia y pruebas de carga</t>
-  </si>
-  <si>
-    <t>Aplicación idéntica desplegada y accesible mediante el mecanismo definido.</t>
-  </si>
-  <si>
-    <t>T-18.1</t>
-  </si>
-  <si>
-    <t>Desplegar aplicación de referencia en K3s y MicroK8s</t>
-  </si>
-  <si>
-    <t>Aplicación responde correctamente en ambos clústeres.</t>
-  </si>
-  <si>
-    <t>T-18.2</t>
-  </si>
-  <si>
-    <t>Configurar acceso a la aplicación y endpoints de prueba</t>
-  </si>
-  <si>
-    <t>Endpoints equivalentes y comprobados.</t>
-  </si>
-  <si>
-    <t>T-18.3</t>
-  </si>
-  <si>
-    <t>Desarrollar scripts k6 para escenarios de carga</t>
-  </si>
-  <si>
-    <t>Scripts parametrizados para idle, carga media y carga alta.</t>
-  </si>
-  <si>
-    <t>T-18.4</t>
-  </si>
-  <si>
-    <t>Configurar exportación y organización de resultados k6</t>
-  </si>
-  <si>
-    <t>Resultados guardados por escenario y repetición.</t>
-  </si>
-  <si>
-    <t>T-18.5</t>
-  </si>
-  <si>
-    <t>Habilitar Service LoadBalancer con kube-vip (192.168.100.150) en ambas distribuciones</t>
-  </si>
-  <si>
-    <t>Service de la aplicación de referencia con IP .150 accesible desde el host en K3s y MicroK8s.</t>
-  </si>
-  <si>
-    <t>HU-19</t>
-  </si>
-  <si>
-    <t>Implementación de pruebas de resiliencia</t>
-  </si>
-  <si>
-    <t>Fallo controlado y recuperación medibles sin pérdida intencional de quórum.</t>
-  </si>
-  <si>
-    <t>T-19.1</t>
-  </si>
-  <si>
-    <t>Implementar procedimiento/script de fallo controlado de un nodo</t>
-  </si>
-  <si>
-    <t>Fallo reproducible sobre un único nodo.</t>
-  </si>
-  <si>
-    <t>T-19.2</t>
-  </si>
-  <si>
-    <t>Registrar inicio, detección y recuperación del fallo</t>
-  </si>
-  <si>
-    <t>Marcas temporales suficientes para calcular tiempos.</t>
-  </si>
-  <si>
-    <t>T-19.3</t>
-  </si>
-  <si>
-    <t>Integrar solicitudes afectadas con resultados k6</t>
-  </si>
-  <si>
-    <t>Cantidad de solicitudes afectadas asociada al intervalo de fallo. Si la tasa de carga es provisional (T-20.5 pendiente), las corridas se marcan como verificación y no como piloto.</t>
-  </si>
-  <si>
-    <t>T-19.4</t>
-  </si>
-  <si>
-    <t>Fijar ubicación del pod de NGINX durante el fallo y verificar parámetros de detección y tolerancia</t>
-  </si>
-  <si>
-    <t>Regla de ubicación implementada: al inyectar el fallo el pod no está en el nodo titular de la VIP (se mueve si coincide); valores efectivos de detección y tolerancia registrados por distribución y diferencias documentadas.</t>
-  </si>
-  <si>
-    <t>T-19.5</t>
-  </si>
-  <si>
-    <t>Revalidar la migración de la VIP con kube-vip v1.2.4</t>
-  </si>
-  <si>
-    <t>Migración de la VIP revalidada con kube-vip v1.2.4 en K3s y MicroK8s; titular de la VIP registrado en cada corrida, sin control del arranque.</t>
-  </si>
-  <si>
-    <t>HU-32</t>
-  </si>
-  <si>
-    <t>Orquestación de ejecuciones experimentales</t>
-  </si>
-  <si>
-    <t>Cada ejecución queda registrada con distribución, escenario, repetición y ventana temporal, y deja datos aptos para el análisis.</t>
-  </si>
-  <si>
-    <t>T-32.1</t>
-  </si>
-  <si>
-    <t>Implementar orquestador de ejecuciones con metadatos de ventana y ubicación</t>
-  </si>
-  <si>
-    <t>Script versionado que ejecuta una repetición completa y guarda metadatos, resultados de k6 y snapshot de Prometheus.</t>
-  </si>
-  <si>
-    <t>HU-34</t>
-  </si>
-  <si>
-    <t>Sincronización temporal con chrony entre el host y las VMs</t>
-  </si>
-  <si>
-    <t>Relojes del host y de las VMs sincronizados con chrony (host como fuente local), verificables en K3s y MicroK8s, como base de la alineación por marcas de tiempo (RO-07).</t>
-  </si>
-  <si>
-    <t>T-34.1</t>
-  </si>
-  <si>
-    <t>Implementar rol Ansible de chrony en el host (servidor NTP para 192.168.100.0/24)</t>
-  </si>
-  <si>
-    <t>chrony activo en el host y sirviendo a 192.168.100.0/24; rol idempotente (segunda corrida sin cambios).</t>
-  </si>
-  <si>
-    <t>T-34.2</t>
-  </si>
-  <si>
-    <t>Implementar rol Ansible de chrony en las VMs (cliente de 192.168.100.1 únicamente)</t>
-  </si>
-  <si>
-    <t>chrony activo en las VMs de K3s y MicroK8s con 192.168.100.1 como única fuente; rol idempotente y aplicable tras cada reconstrucción de las VMs.</t>
-  </si>
-  <si>
-    <t>T-34.3</t>
-  </si>
-  <si>
-    <t>Verificar sincronización con chronyc tracking y chronyc sources en K3s y MicroK8s</t>
-  </si>
-  <si>
-    <t>Salidas de chronyc tracking y chronyc sources registradas en el host y en las VMs de ambos clústeres, con desfase y fuente documentados.</t>
-  </si>
-  <si>
-    <t>EP-06</t>
-  </si>
-  <si>
-    <t>Etapa 3: Pruebas iniciales, mejoras y validación preliminar</t>
-  </si>
-  <si>
-    <t>Pruebas piloto ejecutadas, problemas corregidos y validación preliminar documentada.</t>
+    <t>HU-20</t>
+  </si>
+  <si>
+    <t>Ejecución de pruebas piloto</t>
+  </si>
+  <si>
+    <t>Datos piloto completos y útiles para detectar problemas de instrumentación.</t>
+  </si>
+  <si>
+    <t>T-20.1</t>
+  </si>
+  <si>
+    <t>Ejecutar escenario idle en K3s y MicroK8s</t>
+  </si>
+  <si>
+    <t>Una ejecución completa por distribución con datos de todas las fuentes.</t>
+  </si>
+  <si>
+    <t>T-20.2</t>
+  </si>
+  <si>
+    <t>Ejecutar escenarios de carga media y alta</t>
+  </si>
+  <si>
+    <t>Pruebas piloto realizadas y resultados preliminares disponibles.</t>
+  </si>
+  <si>
+    <t>T-20.3</t>
+  </si>
+  <si>
+    <t>Verificar sincronización entre Scaphandre, Prometheus y k6</t>
+  </si>
+  <si>
+    <t>Ventanas temporales coincidentes y trazables.</t>
+  </si>
+  <si>
+    <t>T-20.4</t>
+  </si>
+  <si>
+    <t>Detectar y corregir anomalías de recolección</t>
+  </si>
+  <si>
+    <t>Problemas de datos documentados y corregidos. Datos del piloto 1 congelados con un tag de git antes de aplicar las mejoras de HU-21.</t>
+  </si>
+  <si>
+    <t>T-20.5</t>
+  </si>
+  <si>
+    <t>Calibrar tasa de saturación y límite de CPU de NGINX, y decidir si hace falta un costo computacional determinístico</t>
+  </si>
+  <si>
+    <t>Tasas de carga media y alta fijadas con datos de Node Exporter, límite de CPU de NGINX confirmado y contingencia de costo computacional determinístico (SHA-256) aplicada y documentada.</t>
+  </si>
+  <si>
+    <t>T-20.6</t>
+  </si>
+  <si>
+    <t>Medir tiempo de despliegue (terraform destroy/apply) por distribución, sin carga</t>
+  </si>
+  <si>
+    <t>Mediciones puntuales de tiempo de construcción y destrucción por distribución, sin carga de k6. Los ciclos provienen de reconstrucciones de pilotos y calibraciones, no de ciclos dedicados de destroy/apply (desviación declarada).</t>
+  </si>
+  <si>
+    <t>T-20.7</t>
+  </si>
+  <si>
+    <t>Caracterizar reposo del host y fijar política de servicios</t>
+  </si>
+  <si>
+    <t>Reposo del host caracterizado sin sesión gráfica, en un único estado de medición (3 sesiones de 3 ventanas de 180 s); política de servicios definida como lista blanca de unidades permitidas, versionada en Ansible y verificada por el orquestador antes de cada corrida; política de fuentes externas de chrony y criterio de reloj convergido definidos; tratamiento de ufw y política de datos documentados; todo antes de T-20.1.</t>
+  </si>
+  <si>
+    <t>HU-21</t>
+  </si>
+  <si>
+    <t>Mejoras y optimización del entorno experimental</t>
+  </si>
+  <si>
+    <t>Configuración refinada sin alterar la equivalencia entre plataformas.</t>
+  </si>
+  <si>
+    <t>T-21.1</t>
+  </si>
+  <si>
+    <t>Ajustar frecuencia de muestreo y parámetros de recolección</t>
+  </si>
+  <si>
+    <t>Frecuencia estable y suficiente para las ventanas experimentales.</t>
+  </si>
+  <si>
+    <t>T-21.2</t>
+  </si>
+  <si>
+    <t>Refinar etiquetas, nombres de archivos y estructura de datos</t>
+  </si>
+  <si>
+    <t>Datos identificables y ordenados por distribución/escenario/repetición.</t>
+  </si>
+  <si>
+    <t>T-21.3</t>
+  </si>
+  <si>
+    <t>Repetir prueba piloto para verificar reproducibilidad</t>
+  </si>
+  <si>
+    <t>Precisión dentro de una sesión (sd ≤ 0,03 W), no reproducible entre sesiones, hallazgo abierto que resuelve T-24.4.</t>
+  </si>
+  <si>
+    <t>T-21.4</t>
+  </si>
+  <si>
+    <t>Revisar tamaño muestral con la varianza del piloto (potencia estadística)</t>
+  </si>
+  <si>
+    <t>Número de bloques (8 propuestos) y de repeticiones por celda confirmado o ajustado con la varianza entre episodios observada en el piloto y en el diagnóstico del desfase de ≈ 1 W; potencia justificada con simulación y supuestos explícitos.</t>
+  </si>
+  <si>
+    <t>T-21.5</t>
+  </si>
+  <si>
+    <t>Aislar CPU de servicios del host y de los hilos de QEMU</t>
+  </si>
+  <si>
+    <t>Aislamiento de CPU aplicado y documentado, o descartado con justificación; efecto sobre la variabilidad registrado. Los hilos del emulador y de E/S de QEMU no están fijados hoy (solo los de vCPU): se evalúa como candidato del diagnóstico del desfase de ≈ 1 W.</t>
+  </si>
+  <si>
+    <t>HU-22</t>
+  </si>
+  <si>
+    <t>Validación preliminar integral</t>
+  </si>
+  <si>
+    <t>Todos los componentes críticos validados antes de la campaña definitiva.</t>
   </si>
   <si>
     <t>Pendiente</t>
   </si>
   <si>
-    <t>HU-20</t>
-  </si>
-  <si>
-    <t>Ejecución de pruebas piloto</t>
-  </si>
-  <si>
-    <t>Datos piloto completos y útiles para detectar problemas de instrumentación.</t>
-  </si>
-  <si>
-    <t>T-20.1</t>
-  </si>
-  <si>
-    <t>Ejecutar escenario idle en K3s y MicroK8s</t>
-  </si>
-  <si>
-    <t>Una ejecución completa por distribución con datos de todas las fuentes.</t>
-  </si>
-  <si>
-    <t>T-20.2</t>
-  </si>
-  <si>
-    <t>Ejecutar escenarios de carga media y alta</t>
-  </si>
-  <si>
-    <t>Pruebas piloto realizadas y resultados preliminares disponibles.</t>
-  </si>
-  <si>
-    <t>T-20.3</t>
-  </si>
-  <si>
-    <t>Verificar sincronización entre Scaphandre, Prometheus y k6</t>
-  </si>
-  <si>
-    <t>Ventanas temporales coincidentes y trazables.</t>
-  </si>
-  <si>
-    <t>T-20.4</t>
-  </si>
-  <si>
-    <t>Detectar y corregir anomalías de recolección</t>
-  </si>
-  <si>
-    <t>Problemas de datos documentados y corregidos. Datos del piloto 1 congelados con un tag de git antes de aplicar las mejoras de HU-21.</t>
-  </si>
-  <si>
-    <t>T-20.5</t>
-  </si>
-  <si>
-    <t>Calibrar tasa de saturación y límite de CPU de NGINX, y decidir si hace falta un costo computacional determinístico</t>
-  </si>
-  <si>
-    <t>Tasas de carga media y alta fijadas con datos de Node Exporter, límite de CPU de NGINX confirmado y decisión sobre SHA256 documentada.</t>
-  </si>
-  <si>
-    <t>T-20.6</t>
-  </si>
-  <si>
-    <t>Medir tiempo de despliegue (terraform destroy/apply) por distribución, sin carga</t>
-  </si>
-  <si>
-    <t>Serie de tiempos de despliegue por distribución, cronometrada sin carga de k6.</t>
-  </si>
-  <si>
-    <t>T-20.7</t>
-  </si>
-  <si>
-    <t>Caracterizar reposo del host y fijar política de servicios</t>
-  </si>
-  <si>
-    <t>Consumo en reposo del host caracterizado con y sin sesión gráfica; política de servicios y de fuentes externas de chrony definida; criterio de reloj convergido antes de lanzar k6 y tratamiento de ufw documentados, antes de T-20.1.</t>
-  </si>
-  <si>
-    <t>HU-21</t>
-  </si>
-  <si>
-    <t>Mejoras y optimización del entorno experimental</t>
-  </si>
-  <si>
-    <t>Configuración refinada sin alterar la equivalencia entre plataformas.</t>
-  </si>
-  <si>
-    <t>T-21.1</t>
-  </si>
-  <si>
-    <t>Ajustar frecuencia de muestreo y parámetros de recolección</t>
-  </si>
-  <si>
-    <t>Frecuencia estable y suficiente para las ventanas experimentales.</t>
-  </si>
-  <si>
-    <t>T-21.2</t>
-  </si>
-  <si>
-    <t>Refinar etiquetas, nombres de archivos y estructura de datos</t>
-  </si>
-  <si>
-    <t>Datos identificables y ordenados por distribución/escenario/repetición.</t>
-  </si>
-  <si>
-    <t>T-21.3</t>
-  </si>
-  <si>
-    <t>Repetir prueba piloto para verificar reproducibilidad</t>
-  </si>
-  <si>
-    <t>Resultados comparables entre ejecuciones bajo la misma configuración.</t>
-  </si>
-  <si>
-    <t>T-21.4</t>
-  </si>
-  <si>
-    <t>Revisar tamaño muestral con la varianza del piloto (potencia estadística)</t>
-  </si>
-  <si>
-    <t>Número de repeticiones por combinación confirmado o ajustado según la variabilidad observada en el piloto.</t>
-  </si>
-  <si>
-    <t>T-21.5</t>
-  </si>
-  <si>
-    <t>Aislar CPU de servicios del host y de QEMU (opcional)</t>
-  </si>
-  <si>
-    <t>Aislamiento de CPU aplicado y documentado, o descartado con justificación; efecto sobre la variabilidad registrado.</t>
-  </si>
-  <si>
-    <t>HU-22</t>
-  </si>
-  <si>
-    <t>Validación preliminar integral</t>
-  </si>
-  <si>
-    <t>Todos los componentes críticos validados antes de la campaña definitiva.</t>
-  </si>
-  <si>
     <t>T-22.1</t>
   </si>
   <si>
@@ -1379,7 +1379,7 @@
     <t>Redacción: observabilidad, métricas y pipeline de datos</t>
   </si>
   <si>
-    <t>Scaphandre, Node Exporter, Prometheus y k6 descritos sin redundancia.</t>
+    <t>Scaphandre, Node Exporter, Prometheus y k6 descritos sin redundancia. Se declara que no hay medición propia del costo de la sesión gráfica ni del ahorro por detener servicios: la decisión de medir sin sesión gráfica se apoya en la Etapa 2 y en reducir fuentes de ruido.</t>
   </si>
   <si>
     <t>T-23.4</t>
@@ -1460,7 +1460,7 @@
     <t>Ejecutar campaña de carga en K3s</t>
   </si>
   <si>
-    <t>Todos los escenarios y repeticiones válidas registrados.</t>
+    <t>Todos los escenarios y repeticiones válidas de K3s registrados dentro de los bloques contrabalanceados definidos en el pre-registro (plan-campana-v1).</t>
   </si>
   <si>
     <t>T-24.2</t>
@@ -1469,6 +1469,9 @@
     <t>Ejecutar campaña de carga en MicroK8s</t>
   </si>
   <si>
+    <t>Todos los escenarios y repeticiones válidas de MicroK8s registrados dentro de los bloques contrabalanceados definidos en el pre-registro (plan-campana-v1).</t>
+  </si>
+  <si>
     <t>T-24.3</t>
   </si>
   <si>
@@ -1478,6 +1481,15 @@
     <t>Datos sincronizados y organizados por ejecución.</t>
   </si>
   <si>
+    <t>T-24.4</t>
+  </si>
+  <si>
+    <t>Cerrar pendientes técnicos previos a la campaña</t>
+  </si>
+  <si>
+    <t>Pilotos de energía repetidos con la aplicación definitiva (SHA-256, límite 2000m, tasas media 450 y alta 900 rps) en ambas distribuciones; K3s construido por el flujo completo de Ansible con la aplicación definitiva, sin ajustes manuales; orquestador registrando por ventana deltas de residencia de C-states, interrupciones, CPU por hilo de QEMU, KSM y halt polling; diagnóstico del desfase de ≈ 1 W (serie sin intervenir y ABAB sobre las covariables que se muevan, incluida la ubicación de los hilos de emulador y E/S de QEMU mediante emulatorpin), con límite de tiempo y causa identificada o declarada como no resuelta; desbordamiento del contador RAPL corregido en el análisis de Scaphandre; plan de campaña (secuencia de bloques con semilla, reglas de exclusión y plan de análisis) fijado en un commit etiquetado antes del primer bloque.</t>
+  </si>
+  <si>
     <t>HU-25</t>
   </si>
   <si>
@@ -1553,7 +1565,7 @@
     <t>Seleccionar y ejecutar pruebas estadísticas apropiadas</t>
   </si>
   <si>
-    <t>Pruebas definidas según diseño y supuestos, con nivel de significancia documentado.</t>
+    <t>Pruebas pareadas por bloque definidas según el pre-registro (Wilcoxon exacto, t pareada como complemento, Holm por familias de métricas), con supuestos y nivel de significancia documentados.</t>
   </si>
   <si>
     <t>T-26.5</t>
@@ -1854,20 +1866,20 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1884,8 +1896,14 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1893,17 +1911,11 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
@@ -2086,7 +2098,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J177" displayName="Backlog" name="Backlog" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:J178" displayName="Backlog" name="Backlog" id="1">
   <tableColumns count="10">
     <tableColumn name="ID" id="1"/>
     <tableColumn name="Tipo" id="2"/>
@@ -2314,34 +2326,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>0</v>
       </c>
     </row>
@@ -2350,16 +2362,16 @@
         <v>18</v>
       </c>
       <c r="B2" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F2" s="14">
         <f t="shared" ref="F2:G2" si="1">F3+F8+F12+F16+F22</f>
@@ -2370,10 +2382,10 @@
         <v>73</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>7</v>
@@ -2393,7 +2405,7 @@
         <v>32</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3" s="14">
         <f t="shared" ref="F3:G3" si="2">SUM(F4:F7)</f>
@@ -2407,137 +2419,137 @@
         <v>35</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="19">
+      <c r="B4" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="22">
         <v>6.0</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="22">
         <v>8.0</v>
       </c>
-      <c r="H4" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="16" t="s">
+      <c r="H4" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="19">
+      <c r="B5" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="22">
         <v>5.0</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="22">
         <v>5.0</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="16" t="s">
+      <c r="I5" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="19">
+      <c r="E6" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="22">
         <v>5.0</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="22">
         <v>4.0</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" s="16" t="s">
+      <c r="I6" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="16" t="s">
+      <c r="B7" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="22">
         <v>3.0</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="22">
         <v>3.0</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="16" t="s">
+      <c r="I7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="17" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2555,7 +2567,7 @@
         <v>59</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8" s="14">
         <f t="shared" ref="F8:G8" si="3">SUM(F9:F11)</f>
@@ -2569,7 +2581,7 @@
         <v>60</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>7</v>
@@ -2590,98 +2602,98 @@
       <c r="X8" s="24"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="19">
+      <c r="E9" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="22">
         <v>5.0</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="22">
         <v>5.0</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="16" t="s">
+      <c r="I9" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="19">
+      <c r="E10" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="22">
         <v>3.0</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="22">
         <v>3.0</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="16" t="s">
+      <c r="I10" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="19">
+      <c r="E11" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="22">
         <v>4.0</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="22">
         <v>4.0</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11" s="16" t="s">
+      <c r="I11" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="17" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2696,10 +2708,10 @@
         <v>72</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F12" s="14">
         <f t="shared" ref="F12:G12" si="4">SUM(F13:F15)</f>
@@ -2713,7 +2725,7 @@
         <v>73</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>7</v>
@@ -2734,98 +2746,98 @@
       <c r="X12" s="24"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="19">
+      <c r="D13" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="22">
         <v>4.0</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="22">
         <v>4.0</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="I13" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="16" t="s">
+      <c r="I13" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="19">
+      <c r="E14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="22">
         <v>3.0</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="22">
         <v>3.0</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J14" s="16" t="s">
+      <c r="I14" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="D15" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="22">
         <v>4.0</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="22">
         <v>4.0</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="16" t="s">
+      <c r="I15" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="17" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2843,7 +2855,7 @@
         <v>85</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" ref="F16:G16" si="5">SUM(F17:F21)</f>
@@ -2857,7 +2869,7 @@
         <v>86</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>7</v>
@@ -2878,162 +2890,162 @@
       <c r="X16" s="24"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="16" t="s">
+      <c r="B17" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="19">
+      <c r="E17" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="22">
         <v>3.0</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="22">
         <v>3.0</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="16" t="s">
+      <c r="I17" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J17" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E18" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="19">
+      <c r="E18" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="22">
         <v>3.0</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="22">
         <v>3.0</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="16" t="s">
+      <c r="I18" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J18" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="B19" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="19">
+      <c r="E19" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="22">
         <v>4.0</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="22">
         <v>3.0</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="16" t="s">
+      <c r="I19" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J19" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F20" s="19">
+      <c r="E20" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="22">
         <v>5.0</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="22">
         <v>4.0</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="16" t="s">
+      <c r="I20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="B21" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="19">
+      <c r="E21" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="22">
         <v>2.0</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="22">
         <v>2.0</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="I21" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="16" t="s">
+      <c r="I21" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J21" s="17" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3048,10 +3060,10 @@
         <v>106</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F22" s="14">
         <f t="shared" ref="F22:G22" si="6">SUM(F23:F27)</f>
@@ -3065,7 +3077,7 @@
         <v>107</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>7</v>
@@ -3086,162 +3098,162 @@
       <c r="X22" s="24"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="B23" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="22">
         <v>3.0</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="22">
         <v>3.0</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="16" t="s">
+      <c r="I23" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J23" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="B24" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="19">
+      <c r="E24" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="22">
         <v>3.0</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="22">
         <v>3.0</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="H24" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="I24" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24" s="16" t="s">
+      <c r="I24" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J24" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="B25" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="19">
+      <c r="E25" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="22">
         <v>3.0</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="22">
         <v>3.0</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="I25" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="16" t="s">
+      <c r="I25" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J25" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="B26" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="19">
+      <c r="E26" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="22">
         <v>3.0</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="22">
         <v>3.0</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="I26" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="16" t="s">
+      <c r="I26" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="17" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="B27" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="22">
         <v>3.0</v>
       </c>
-      <c r="G27" s="18">
+      <c r="G27" s="20">
         <v>3.0</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="I27" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="16" t="s">
+      <c r="I27" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J27" s="17" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3250,7 +3262,7 @@
         <v>124</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>125</v>
@@ -3259,7 +3271,7 @@
         <v>126</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F28" s="14">
         <f t="shared" ref="F28:G28" si="7">F29+F34+F40+F46</f>
@@ -3273,10 +3285,10 @@
         <v>127</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
@@ -3307,7 +3319,7 @@
         <v>89</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F29" s="14">
         <f t="shared" ref="F29:G29" si="8">SUM(F30:F33)</f>
@@ -3321,10 +3333,10 @@
         <v>130</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
@@ -3342,131 +3354,131 @@
       <c r="X29" s="24"/>
     </row>
     <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="B30" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="19">
+      <c r="E30" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="22">
         <v>2.0</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="22">
         <v>2.0</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="I30" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>19</v>
+      <c r="I30" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="B31" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="17" t="s">
+      <c r="D31" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="19">
+      <c r="E31" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" s="22">
         <v>3.0</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="22">
         <v>3.0</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="I31" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J31" s="16" t="s">
-        <v>19</v>
+      <c r="I31" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="B32" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="17" t="s">
+      <c r="D32" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="19">
+      <c r="E32" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="22">
         <v>3.0</v>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="22">
         <v>3.0</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="I32" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>19</v>
+      <c r="I32" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="16" t="s">
+      <c r="B33" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="D33" s="17" t="s">
+      <c r="D33" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="18" t="s">
+      <c r="E33" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="22">
         <v>2.0</v>
       </c>
       <c r="G33" s="25">
         <v>2.0</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="I33" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J33" s="16" t="s">
-        <v>19</v>
+      <c r="I33" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
@@ -3483,7 +3495,7 @@
         <v>50</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F34" s="26">
         <f t="shared" ref="F34:G34" si="9">SUM(F35:F39)</f>
@@ -3497,10 +3509,10 @@
         <v>145</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K34" s="24"/>
       <c r="L34" s="24"/>
@@ -3518,163 +3530,163 @@
       <c r="X34" s="24"/>
     </row>
     <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="B35" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="16" t="s">
+      <c r="B35" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="19">
+      <c r="E35" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" s="22">
         <v>3.0</v>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="22">
         <v>2.0</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="I35" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J35" s="16" t="s">
-        <v>19</v>
+      <c r="I35" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="16" t="s">
+      <c r="B36" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="19">
+      <c r="E36" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" s="22">
         <v>3.0</v>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="22">
         <v>2.0</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="I36" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J36" s="16" t="s">
-        <v>19</v>
+      <c r="I36" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="16" t="s">
+      <c r="B37" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F37" s="19">
+      <c r="E37" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="22">
         <v>3.0</v>
       </c>
-      <c r="G37" s="19">
+      <c r="G37" s="22">
         <v>2.0</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="17" t="s">
         <v>154</v>
       </c>
-      <c r="I37" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J37" s="16" t="s">
-        <v>19</v>
+      <c r="I37" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="17" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38" s="16" t="s">
+      <c r="B38" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F38" s="19">
+      <c r="E38" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" s="22">
         <v>3.0</v>
       </c>
-      <c r="G38" s="19">
+      <c r="G38" s="22">
         <v>2.0</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="H38" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="I38" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J38" s="16" t="s">
-        <v>19</v>
+      <c r="I38" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="16" t="s">
+      <c r="B39" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="19">
+      <c r="E39" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" s="22">
         <v>3.0</v>
       </c>
       <c r="G39" s="25">
         <v>2.0</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="I39" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J39" s="16" t="s">
-        <v>19</v>
+      <c r="I39" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
@@ -3691,7 +3703,7 @@
         <v>99</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F40" s="26">
         <f t="shared" ref="F40:G40" si="10">SUM(F41:F45)</f>
@@ -3705,10 +3717,10 @@
         <v>163</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K40" s="24"/>
       <c r="L40" s="24"/>
@@ -3726,163 +3738,163 @@
       <c r="X40" s="24"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="B41" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="16" t="s">
+      <c r="B41" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F41" s="19">
+      <c r="E41" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" s="22">
         <v>2.0</v>
       </c>
-      <c r="G41" s="19">
+      <c r="G41" s="22">
         <v>2.0</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="H41" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="I41" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J41" s="16" t="s">
-        <v>19</v>
+      <c r="I41" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="16" t="s">
+      <c r="A42" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="16" t="s">
+      <c r="B42" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C42" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="19">
+      <c r="E42" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" s="22">
         <v>2.0</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="22">
         <v>1.0</v>
       </c>
-      <c r="H42" s="16" t="s">
+      <c r="H42" s="17" t="s">
         <v>170</v>
       </c>
-      <c r="I42" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J42" s="16" t="s">
-        <v>19</v>
+      <c r="I42" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="16" t="s">
+      <c r="A43" s="17" t="s">
         <v>171</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C43" s="16" t="s">
+      <c r="B43" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E43" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F43" s="19">
+      <c r="E43" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" s="22">
         <v>2.0</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="22">
         <v>2.0</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="H43" s="17" t="s">
         <v>173</v>
       </c>
-      <c r="I43" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J43" s="16" t="s">
-        <v>19</v>
+      <c r="I43" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="16" t="s">
+      <c r="A44" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="B44" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="16" t="s">
+      <c r="B44" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E44" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F44" s="19">
+      <c r="E44" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" s="22">
         <v>2.0</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="22">
         <v>2.0</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="H44" s="17" t="s">
         <v>176</v>
       </c>
-      <c r="I44" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J44" s="16" t="s">
-        <v>19</v>
+      <c r="I44" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C45" s="16" t="s">
+      <c r="B45" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C45" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E45" s="18" t="s">
+      <c r="E45" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F45" s="19">
+      <c r="F45" s="22">
         <v>1.0</v>
       </c>
       <c r="G45" s="25">
         <v>1.0</v>
       </c>
-      <c r="H45" s="16" t="s">
+      <c r="H45" s="17" t="s">
         <v>179</v>
       </c>
-      <c r="I45" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J45" s="16" t="s">
-        <v>19</v>
+      <c r="I45" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
@@ -3913,10 +3925,10 @@
         <v>182</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K46" s="24"/>
       <c r="L46" s="24"/>
@@ -3934,99 +3946,99 @@
       <c r="X46" s="24"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C47" s="16" t="s">
+      <c r="B47" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="D47" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E47" s="18" t="s">
+      <c r="D47" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E47" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="22">
         <v>2.0</v>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="22">
         <v>2.0</v>
       </c>
-      <c r="H47" s="16" t="s">
+      <c r="H47" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="I47" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J47" s="16" t="s">
-        <v>19</v>
+      <c r="I47" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C48" s="16" t="s">
+      <c r="B48" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C48" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="D48" s="17" t="s">
+      <c r="D48" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="18" t="s">
+      <c r="E48" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="22">
         <v>1.0</v>
       </c>
-      <c r="G48" s="19">
+      <c r="G48" s="22">
         <v>1.0</v>
       </c>
-      <c r="H48" s="16" t="s">
+      <c r="H48" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="I48" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J48" s="16" t="s">
-        <v>19</v>
+      <c r="I48" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="16" t="s">
+      <c r="A49" s="17" t="s">
         <v>189</v>
       </c>
-      <c r="B49" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" s="16" t="s">
+      <c r="B49" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F49" s="19">
+      <c r="F49" s="22">
         <v>3.0</v>
       </c>
       <c r="G49" s="25">
         <v>2.0</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="H49" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="I49" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J49" s="16" t="s">
-        <v>19</v>
+      <c r="I49" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
@@ -4034,7 +4046,7 @@
         <v>193</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>194</v>
@@ -4043,7 +4055,7 @@
         <v>195</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F50" s="14">
         <f t="shared" ref="F50:G50" si="12">F51</f>
@@ -4057,10 +4069,10 @@
         <v>196</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K50" s="24"/>
       <c r="L50" s="24"/>
@@ -4091,7 +4103,7 @@
         <v>195</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F51" s="26">
         <f t="shared" ref="F51:G51" si="13">SUM(F52:F53)</f>
@@ -4105,10 +4117,10 @@
         <v>199</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K51" s="24"/>
       <c r="L51" s="24"/>
@@ -4126,67 +4138,67 @@
       <c r="X51" s="24"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="16" t="s">
+      <c r="A52" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="B52" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" s="16" t="s">
+      <c r="B52" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C52" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F52" s="19">
+      <c r="E52" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F52" s="22">
         <v>1.0</v>
       </c>
-      <c r="G52" s="19">
+      <c r="G52" s="22">
         <v>1.0</v>
       </c>
-      <c r="H52" s="16" t="s">
+      <c r="H52" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="I52" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J52" s="16" t="s">
-        <v>19</v>
+      <c r="I52" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J52" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="16" t="s">
+      <c r="A53" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="B53" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C53" s="16" t="s">
+      <c r="B53" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="D53" s="17" t="s">
+      <c r="D53" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="E53" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F53" s="19">
+      <c r="E53" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="22">
         <v>1.0</v>
       </c>
       <c r="G53" s="25">
         <v>1.0</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="I53" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J53" s="16" t="s">
-        <v>19</v>
+      <c r="I53" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J53" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -4194,7 +4206,7 @@
         <v>206</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>207</v>
@@ -4203,7 +4215,7 @@
         <v>89</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F54" s="14">
         <f t="shared" ref="F54:G54" si="14">F55+F61+F66+F71+F80</f>
@@ -4217,10 +4229,10 @@
         <v>208</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K54" s="24"/>
       <c r="L54" s="24"/>
@@ -4251,7 +4263,7 @@
         <v>89</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F55" s="26">
         <f t="shared" ref="F55:G55" si="15">SUM(F56:F60)</f>
@@ -4265,10 +4277,10 @@
         <v>211</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K55" s="24"/>
       <c r="L55" s="24"/>
@@ -4286,163 +4298,163 @@
       <c r="X55" s="24"/>
     </row>
     <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="B56" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C56" s="16" t="s">
+      <c r="B56" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C56" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E56" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F56" s="19">
+      <c r="E56" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F56" s="22">
         <v>1.0</v>
       </c>
-      <c r="G56" s="19">
+      <c r="G56" s="22">
         <v>1.0</v>
       </c>
-      <c r="H56" s="16" t="s">
+      <c r="H56" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="I56" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J56" s="16" t="s">
-        <v>19</v>
+      <c r="I56" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J56" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="16" t="s">
+      <c r="A57" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="B57" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C57" s="16" t="s">
+      <c r="B57" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="D57" s="17" t="s">
+      <c r="D57" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E57" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F57" s="19">
+      <c r="E57" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F57" s="22">
         <v>1.0</v>
       </c>
-      <c r="G57" s="19">
+      <c r="G57" s="22">
         <v>1.0</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H57" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="I57" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J57" s="16" t="s">
-        <v>19</v>
+      <c r="I57" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="16" t="s">
+      <c r="A58" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="B58" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C58" s="16" t="s">
+      <c r="B58" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="D58" s="17" t="s">
+      <c r="D58" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E58" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="19">
+      <c r="E58" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F58" s="22">
         <v>1.0</v>
       </c>
-      <c r="G58" s="19">
+      <c r="G58" s="22">
         <v>1.0</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="H58" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="I58" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J58" s="16" t="s">
-        <v>19</v>
+      <c r="I58" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J58" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="17" t="s">
         <v>221</v>
       </c>
-      <c r="B59" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C59" s="16" t="s">
+      <c r="B59" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="D59" s="17" t="s">
+      <c r="D59" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E59" s="18" t="s">
+      <c r="E59" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="19">
+      <c r="F59" s="22">
         <v>1.0</v>
       </c>
       <c r="G59" s="25">
         <v>1.0</v>
       </c>
-      <c r="H59" s="16" t="s">
+      <c r="H59" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="I59" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J59" s="16" t="s">
-        <v>19</v>
+      <c r="I59" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J59" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="16" t="s">
+      <c r="A60" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="B60" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="16" t="s">
+      <c r="B60" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C60" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="D60" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" s="19">
+      <c r="D60" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F60" s="22">
         <v>1.0</v>
       </c>
-      <c r="G60" s="19">
+      <c r="G60" s="22">
         <v>1.0</v>
       </c>
-      <c r="H60" s="16" t="s">
+      <c r="H60" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="I60" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J60" s="16" t="s">
-        <v>19</v>
+      <c r="I60" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
@@ -4459,7 +4471,7 @@
         <v>89</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F61" s="26">
         <f t="shared" ref="F61:G61" si="16">SUM(F62:F65)</f>
@@ -4473,10 +4485,10 @@
         <v>229</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K61" s="24"/>
       <c r="L61" s="24"/>
@@ -4494,131 +4506,131 @@
       <c r="X61" s="24"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="17" t="s">
         <v>230</v>
       </c>
-      <c r="B62" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C62" s="16" t="s">
+      <c r="B62" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C62" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="D62" s="17" t="s">
+      <c r="D62" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" s="19">
+      <c r="E62" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F62" s="22">
         <v>2.0</v>
       </c>
-      <c r="G62" s="19">
+      <c r="G62" s="22">
         <v>2.0</v>
       </c>
-      <c r="H62" s="16" t="s">
+      <c r="H62" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="I62" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J62" s="16" t="s">
-        <v>19</v>
+      <c r="I62" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J62" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="16" t="s">
+      <c r="A63" s="17" t="s">
         <v>233</v>
       </c>
-      <c r="B63" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C63" s="16" t="s">
+      <c r="B63" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C63" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="D63" s="17" t="s">
+      <c r="D63" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E63" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F63" s="19">
+      <c r="E63" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="22">
         <v>1.0</v>
       </c>
       <c r="G63" s="25">
         <v>1.0</v>
       </c>
-      <c r="H63" s="16" t="s">
+      <c r="H63" s="17" t="s">
         <v>235</v>
       </c>
-      <c r="I63" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J63" s="16" t="s">
-        <v>19</v>
+      <c r="I63" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J63" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C64" s="16" t="s">
+      <c r="B64" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C64" s="17" t="s">
         <v>237</v>
       </c>
-      <c r="D64" s="17" t="s">
+      <c r="D64" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F64" s="19">
+      <c r="E64" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="22">
         <v>2.0</v>
       </c>
-      <c r="G64" s="19">
+      <c r="G64" s="22">
         <v>2.0</v>
       </c>
-      <c r="H64" s="16" t="s">
+      <c r="H64" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="I64" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J64" s="16" t="s">
-        <v>19</v>
+      <c r="I64" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J64" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" s="16" t="s">
+      <c r="A65" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="B65" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65" s="16" t="s">
+      <c r="B65" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="D65" s="17" t="s">
+      <c r="D65" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E65" s="18" t="s">
+      <c r="E65" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F65" s="19">
+      <c r="F65" s="22">
         <v>2.0</v>
       </c>
-      <c r="G65" s="19">
+      <c r="G65" s="22">
         <v>2.0</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="H65" s="17" t="s">
         <v>241</v>
       </c>
-      <c r="I65" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J65" s="16" t="s">
-        <v>19</v>
+      <c r="I65" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
@@ -4635,7 +4647,7 @@
         <v>89</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F66" s="26">
         <f t="shared" ref="F66:G66" si="17">SUM(F67:F70)</f>
@@ -4649,10 +4661,10 @@
         <v>244</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K66" s="24"/>
       <c r="L66" s="24"/>
@@ -4670,131 +4682,131 @@
       <c r="X66" s="24"/>
     </row>
     <row r="67" ht="22.5" customHeight="1">
-      <c r="A67" s="16" t="s">
+      <c r="A67" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B67" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C67" s="16" t="s">
+      <c r="B67" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C67" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="D67" s="17" t="s">
+      <c r="D67" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E67" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" s="19">
+      <c r="E67" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F67" s="22">
         <v>2.0</v>
       </c>
       <c r="G67" s="25">
         <v>2.0</v>
       </c>
-      <c r="H67" s="16" t="s">
+      <c r="H67" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="I67" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J67" s="16" t="s">
-        <v>19</v>
+      <c r="I67" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" s="16" t="s">
+      <c r="B68" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C68" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="D68" s="17" t="s">
+      <c r="D68" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E68" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F68" s="19">
+      <c r="E68" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F68" s="22">
         <v>1.0</v>
       </c>
-      <c r="G68" s="19">
+      <c r="G68" s="22">
         <v>1.0</v>
       </c>
-      <c r="H68" s="16" t="s">
+      <c r="H68" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="I68" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J68" s="16" t="s">
-        <v>19</v>
+      <c r="I68" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J68" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="16" t="s">
+      <c r="A69" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C69" s="16" t="s">
+      <c r="B69" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C69" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E69" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F69" s="19">
+      <c r="E69" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" s="22">
         <v>1.0</v>
       </c>
-      <c r="G69" s="19">
+      <c r="G69" s="22">
         <v>1.0</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="H69" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="I69" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J69" s="16" t="s">
-        <v>19</v>
+      <c r="I69" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J69" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="16" t="s">
+      <c r="A70" s="17" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C70" s="16" t="s">
+      <c r="B70" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C70" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E70" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F70" s="19">
+      <c r="E70" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F70" s="22">
         <v>2.0</v>
       </c>
-      <c r="G70" s="19">
+      <c r="G70" s="22">
         <v>2.0</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="H70" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="I70" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J70" s="16" t="s">
-        <v>19</v>
+      <c r="I70" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J70" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -4811,7 +4823,7 @@
         <v>89</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F71" s="14">
         <f t="shared" ref="F71:G71" si="18">SUM(F72:F79)</f>
@@ -4825,10 +4837,10 @@
         <v>259</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
@@ -4846,259 +4858,259 @@
       <c r="X71" s="24"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="17" t="s">
         <v>260</v>
       </c>
-      <c r="B72" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C72" s="16" t="s">
+      <c r="B72" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F72" s="19">
+      <c r="E72" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F72" s="22">
         <v>2.0</v>
       </c>
-      <c r="G72" s="19">
+      <c r="G72" s="22">
         <v>2.0</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="H72" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="I72" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J72" s="16" t="s">
-        <v>19</v>
+      <c r="I72" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="17" t="s">
         <v>263</v>
       </c>
-      <c r="B73" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C73" s="16" t="s">
+      <c r="B73" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="17" t="s">
+      <c r="D73" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E73" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F73" s="19">
+      <c r="E73" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F73" s="22">
         <v>2.0</v>
       </c>
-      <c r="G73" s="19">
+      <c r="G73" s="22">
         <v>5.0</v>
       </c>
-      <c r="H73" s="16" t="s">
+      <c r="H73" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="I73" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J73" s="16" t="s">
-        <v>19</v>
+      <c r="I73" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J73" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="B74" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C74" s="16" t="s">
+      <c r="B74" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C74" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="D74" s="17" t="s">
+      <c r="D74" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E74" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F74" s="19">
+      <c r="E74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F74" s="22">
         <v>1.0</v>
       </c>
       <c r="G74" s="25">
         <v>1.0</v>
       </c>
-      <c r="H74" s="16" t="s">
+      <c r="H74" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="I74" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J74" s="16" t="s">
-        <v>19</v>
+      <c r="I74" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J74" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="17" t="s">
         <v>269</v>
       </c>
-      <c r="B75" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C75" s="16" t="s">
+      <c r="B75" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C75" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="D75" s="17" t="s">
+      <c r="D75" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E75" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F75" s="19">
+      <c r="E75" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F75" s="22">
         <v>1.0</v>
       </c>
       <c r="G75" s="25">
         <v>1.0</v>
       </c>
-      <c r="H75" s="16" t="s">
+      <c r="H75" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="I75" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J75" s="16" t="s">
-        <v>19</v>
+      <c r="I75" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J75" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="17" t="s">
         <v>271</v>
       </c>
-      <c r="B76" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C76" s="16" t="s">
+      <c r="B76" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" s="17" t="s">
         <v>272</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E76" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F76" s="19">
+      <c r="E76" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F76" s="22">
         <v>1.0</v>
       </c>
-      <c r="G76" s="19">
+      <c r="G76" s="22">
         <v>1.0</v>
       </c>
-      <c r="H76" s="16" t="s">
+      <c r="H76" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="I76" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J76" s="16" t="s">
-        <v>19</v>
+      <c r="I76" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J76" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="16" t="s">
+      <c r="A77" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C77" s="16" t="s">
+      <c r="B77" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C77" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="D77" s="17" t="s">
+      <c r="D77" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E77" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F77" s="19">
+      <c r="E77" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F77" s="22">
         <v>1.0</v>
       </c>
-      <c r="G77" s="19">
+      <c r="G77" s="22">
         <v>1.0</v>
       </c>
-      <c r="H77" s="16" t="s">
+      <c r="H77" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="I77" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J77" s="16" t="s">
-        <v>19</v>
+      <c r="I77" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J77" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="B78" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C78" s="16" t="s">
+      <c r="B78" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C78" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="D78" s="17" t="s">
+      <c r="D78" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E78" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F78" s="19">
+      <c r="E78" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F78" s="22">
         <v>1.0</v>
       </c>
-      <c r="G78" s="19">
+      <c r="G78" s="22">
         <v>1.0</v>
       </c>
-      <c r="H78" s="16" t="s">
+      <c r="H78" s="17" t="s">
         <v>268</v>
       </c>
-      <c r="I78" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J78" s="16" t="s">
-        <v>19</v>
+      <c r="I78" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="B79" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C79" s="16" t="s">
+      <c r="B79" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C79" s="17" t="s">
         <v>278</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E79" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F79" s="19">
+      <c r="E79" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="22">
         <v>1.0</v>
       </c>
-      <c r="G79" s="19">
+      <c r="G79" s="22">
         <v>2.0</v>
       </c>
-      <c r="H79" s="16" t="s">
+      <c r="H79" s="17" t="s">
         <v>279</v>
       </c>
-      <c r="I79" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J79" s="16" t="s">
-        <v>19</v>
+      <c r="I79" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J79" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
@@ -5115,7 +5127,7 @@
         <v>89</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F80" s="14">
         <f t="shared" ref="F80:G80" si="19">SUM(F81:F83)</f>
@@ -5129,10 +5141,10 @@
         <v>282</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K80" s="24"/>
       <c r="L80" s="24"/>
@@ -5150,99 +5162,99 @@
       <c r="X80" s="24"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="B81" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C81" s="16" t="s">
+      <c r="B81" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C81" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="D81" s="17" t="s">
+      <c r="D81" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E81" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F81" s="19">
+      <c r="E81" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F81" s="22">
         <v>2.0</v>
       </c>
-      <c r="G81" s="19">
+      <c r="G81" s="22">
         <v>8.0</v>
       </c>
-      <c r="H81" s="16" t="s">
+      <c r="H81" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="I81" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J81" s="16" t="s">
-        <v>19</v>
+      <c r="I81" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J81" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="B82" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C82" s="16" t="s">
+      <c r="B82" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C82" s="17" t="s">
         <v>287</v>
       </c>
-      <c r="D82" s="17" t="s">
+      <c r="D82" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E82" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F82" s="19">
+      <c r="E82" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" s="22">
         <v>1.0</v>
       </c>
-      <c r="G82" s="19">
+      <c r="G82" s="22">
         <v>1.0</v>
       </c>
-      <c r="H82" s="16" t="s">
+      <c r="H82" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="I82" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J82" s="16" t="s">
-        <v>19</v>
+      <c r="I82" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J82" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="B83" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C83" s="16" t="s">
+      <c r="B83" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C83" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="E83" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F83" s="19">
+      <c r="F83" s="22">
         <v>1.0</v>
       </c>
-      <c r="G83" s="19">
+      <c r="G83" s="22">
         <v>1.0</v>
       </c>
-      <c r="H83" s="16" t="s">
+      <c r="H83" s="17" t="s">
         <v>291</v>
       </c>
-      <c r="I83" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="J83" s="16" t="s">
-        <v>19</v>
+      <c r="I83" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83" s="17" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -5250,7 +5262,7 @@
         <v>292</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>293</v>
@@ -5259,23 +5271,23 @@
         <v>50</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F84" s="27">
         <v>47.0</v>
       </c>
       <c r="G84" s="26">
         <f>G85+G90+G96+G102+G108</f>
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H84" s="11" t="s">
         <v>294</v>
       </c>
       <c r="I84" s="28" t="s">
-        <v>295</v>
+        <v>26</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K84" s="24"/>
       <c r="L84" s="24"/>
@@ -5294,19 +5306,19 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D85" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F85" s="14">
         <f t="shared" ref="F85:G85" si="20">SUM(F86:F89)</f>
@@ -5317,13 +5329,13 @@
         <v>5</v>
       </c>
       <c r="H85" s="29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="I85" s="28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K85" s="24"/>
       <c r="L85" s="24"/>
@@ -5341,148 +5353,148 @@
       <c r="X85" s="24"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="16" t="s">
+      <c r="A86" s="17" t="s">
+        <v>298</v>
+      </c>
+      <c r="B86" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="B86" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C86" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E86" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="19">
+      <c r="E86" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F86" s="22">
         <v>1.0</v>
       </c>
       <c r="G86" s="30">
         <v>1.0</v>
       </c>
       <c r="H86" s="31" t="s">
+        <v>300</v>
+      </c>
+      <c r="I86" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J86" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="I86" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J86" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="16" t="s">
+      <c r="B87" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C87" s="17" t="s">
         <v>302</v>
       </c>
-      <c r="B87" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C87" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F87" s="19">
+      <c r="E87" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F87" s="22">
         <v>1.0</v>
       </c>
       <c r="G87" s="30">
         <v>1.0</v>
       </c>
       <c r="H87" s="31" t="s">
+        <v>303</v>
+      </c>
+      <c r="I87" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="I87" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J87" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="16" t="s">
+      <c r="B88" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="B88" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C88" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="D88" s="17" t="s">
+      <c r="D88" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E88" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F88" s="19">
+      <c r="E88" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F88" s="22">
         <v>2.0</v>
       </c>
       <c r="G88" s="30">
         <v>2.0</v>
       </c>
       <c r="H88" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="I88" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J88" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="I88" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J88" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="16" t="s">
+      <c r="B89" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C89" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="B89" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="D89" s="17" t="s">
+      <c r="D89" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E89" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F89" s="19">
+      <c r="E89" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F89" s="22">
         <v>1.0</v>
       </c>
       <c r="G89" s="30">
         <v>1.0</v>
       </c>
       <c r="H89" s="31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="I89" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J89" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J89" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="11" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F90" s="14">
         <f t="shared" ref="F90:G90" si="21">SUM(F91:F95)</f>
@@ -5493,13 +5505,13 @@
         <v>7</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I90" s="28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K90" s="24"/>
       <c r="L90" s="24"/>
@@ -5517,148 +5529,148 @@
       <c r="X90" s="24"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="B91" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C91" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="B91" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="D91" s="17" t="s">
+      <c r="D91" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E91" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" s="19">
+      <c r="E91" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F91" s="22">
         <v>2.0</v>
       </c>
       <c r="G91" s="30">
         <v>1.0</v>
       </c>
-      <c r="H91" s="16" t="s">
+      <c r="H91" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="I91" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J91" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="I91" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J91" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="16" t="s">
+      <c r="B92" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C92" s="17" t="s">
         <v>317</v>
       </c>
-      <c r="B92" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="D92" s="17" t="s">
+      <c r="D92" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E92" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F92" s="19">
+      <c r="E92" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F92" s="22">
         <v>3.0</v>
       </c>
       <c r="G92" s="30">
         <v>2.0</v>
       </c>
-      <c r="H92" s="16" t="s">
+      <c r="H92" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="I92" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J92" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="A93" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="I92" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J92" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="16" t="s">
+      <c r="B93" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C93" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="B93" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C93" s="16" t="s">
-        <v>321</v>
-      </c>
-      <c r="D93" s="17" t="s">
+      <c r="D93" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E93" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F93" s="19">
+      <c r="E93" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F93" s="22">
         <v>2.0</v>
       </c>
       <c r="G93" s="30">
         <v>1.0</v>
       </c>
-      <c r="H93" s="16" t="s">
+      <c r="H93" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="I93" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J93" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="A94" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="I93" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J93" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="16" t="s">
+      <c r="B94" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C94" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="B94" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C94" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="D94" s="17" t="s">
+      <c r="D94" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E94" s="18" t="s">
+      <c r="E94" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F94" s="19">
+      <c r="F94" s="22">
         <v>2.0</v>
       </c>
       <c r="G94" s="33">
         <v>1.0</v>
       </c>
-      <c r="H94" s="16" t="s">
-        <v>325</v>
+      <c r="H94" s="17" t="s">
+        <v>324</v>
       </c>
       <c r="I94" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J94" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J94" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="31" t="s">
+        <v>325</v>
+      </c>
+      <c r="B95" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C95" s="31" t="s">
         <v>326</v>
-      </c>
-      <c r="B95" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C95" s="31" t="s">
-        <v>327</v>
       </c>
       <c r="D95" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F95" s="30">
         <v>2.0</v>
@@ -5667,30 +5679,30 @@
         <v>2.0</v>
       </c>
       <c r="H95" s="31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I95" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J95" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="11" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D96" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F96" s="14">
         <f t="shared" ref="F96:G96" si="22">SUM(F97:F101)</f>
@@ -5701,13 +5713,13 @@
         <v>8</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I96" s="28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K96" s="24"/>
       <c r="L96" s="24"/>
@@ -5725,148 +5737,148 @@
       <c r="X96" s="24"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="16" t="s">
+      <c r="A97" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="B97" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C97" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="B97" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C97" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="D97" s="17" t="s">
+      <c r="D97" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E97" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" s="19">
+      <c r="E97" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F97" s="22">
         <v>3.0</v>
       </c>
       <c r="G97" s="30">
         <v>2.0</v>
       </c>
-      <c r="H97" s="16" t="s">
+      <c r="H97" s="17" t="s">
+        <v>333</v>
+      </c>
+      <c r="I97" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J97" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="I97" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J97" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="16" t="s">
+      <c r="B98" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C98" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="B98" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C98" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="D98" s="17" t="s">
+      <c r="D98" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E98" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F98" s="19">
+      <c r="E98" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F98" s="22">
         <v>2.0</v>
       </c>
       <c r="G98" s="30">
         <v>2.0</v>
       </c>
-      <c r="H98" s="16" t="s">
+      <c r="H98" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="I98" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J98" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="A99" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="I98" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J98" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="16" t="s">
+      <c r="B99" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C99" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="B99" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="D99" s="17" t="s">
+      <c r="D99" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F99" s="19">
+      <c r="E99" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F99" s="22">
         <v>1.0</v>
       </c>
       <c r="G99" s="30">
         <v>1.0</v>
       </c>
-      <c r="H99" s="16" t="s">
+      <c r="H99" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="I99" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J99" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="A100" s="17" t="s">
         <v>340</v>
       </c>
-      <c r="I99" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J99" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="16" t="s">
+      <c r="B100" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C100" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="B100" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C100" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E100" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F100" s="19">
+      <c r="E100" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F100" s="22">
         <v>1.0</v>
       </c>
       <c r="G100" s="30">
         <v>1.0</v>
       </c>
-      <c r="H100" s="16" t="s">
-        <v>343</v>
+      <c r="H100" s="17" t="s">
+        <v>342</v>
       </c>
       <c r="I100" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J100" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J100" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="B101" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C101" s="31" t="s">
         <v>344</v>
-      </c>
-      <c r="B101" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C101" s="31" t="s">
-        <v>345</v>
       </c>
       <c r="D101" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F101" s="30">
         <v>1.0</v>
@@ -5875,46 +5887,46 @@
         <v>2.0</v>
       </c>
       <c r="H101" s="31" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I101" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J101" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D102" s="12" t="s">
         <v>99</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F102" s="27">
         <v>12.0</v>
       </c>
       <c r="G102" s="14">
         <f>SUM(G103:G106)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I102" s="28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J102" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K102" s="24"/>
       <c r="L102" s="24"/>
@@ -5932,170 +5944,180 @@
       <c r="X102" s="24"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="16" t="s">
+      <c r="A103" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="B103" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C103" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="B103" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C103" s="16" t="s">
+      <c r="D103" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E103" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F103" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="G103" s="30">
+        <v>1.0</v>
+      </c>
+      <c r="H103" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="D103" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E103" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F103" s="19">
+      <c r="I103" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J103" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="A104" s="17" t="s">
+        <v>352</v>
+      </c>
+      <c r="B104" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>353</v>
+      </c>
+      <c r="D104" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E104" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F104" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="G104" s="30">
         <v>2.0</v>
       </c>
-      <c r="G103" s="19"/>
-      <c r="H103" s="16" t="s">
-        <v>352</v>
-      </c>
-      <c r="I103" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J103" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="16" t="s">
-        <v>353</v>
-      </c>
-      <c r="B104" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C104" s="16" t="s">
+      <c r="H104" s="17" t="s">
         <v>354</v>
       </c>
-      <c r="D104" s="17" t="s">
+      <c r="I104" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J104" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="A105" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="B105" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>356</v>
+      </c>
+      <c r="D105" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E104" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F104" s="19">
+      <c r="E105" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F105" s="22">
         <v>3.0</v>
       </c>
-      <c r="G104" s="19"/>
-      <c r="H104" s="16" t="s">
-        <v>355</v>
-      </c>
-      <c r="I104" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J104" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="B105" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C105" s="16" t="s">
+      <c r="G105" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="H105" s="31" t="s">
         <v>357</v>
       </c>
-      <c r="D105" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E105" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F105" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="G105" s="19"/>
-      <c r="H105" s="31" t="s">
-        <v>358</v>
-      </c>
       <c r="I105" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="J105" s="16" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="J105" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="B106" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C106" s="31" t="s">
         <v>359</v>
-      </c>
-      <c r="B106" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C106" s="31" t="s">
-        <v>360</v>
       </c>
       <c r="D106" s="34" t="s">
         <v>99</v>
       </c>
       <c r="E106" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F106" s="30">
         <v>2.0</v>
       </c>
-      <c r="G106" s="19"/>
+      <c r="G106" s="30">
+        <v>2.0</v>
+      </c>
       <c r="H106" s="31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I106" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J106" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="31" t="s">
+        <v>361</v>
+      </c>
+      <c r="B107" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C107" s="31" t="s">
         <v>362</v>
-      </c>
-      <c r="B107" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C107" s="31" t="s">
-        <v>363</v>
       </c>
       <c r="D107" s="34" t="s">
         <v>99</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F107" s="30">
         <v>2.0</v>
       </c>
-      <c r="G107" s="19"/>
+      <c r="G107" s="30">
+        <v>2.0</v>
+      </c>
       <c r="H107" s="31" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I107" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J107" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B108" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C108" s="29" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D108" s="35" t="s">
         <v>99</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F108" s="26">
         <f t="shared" ref="F108:G108" si="23">SUM(F109)</f>
@@ -6103,201 +6125,209 @@
       </c>
       <c r="G108" s="14">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H108" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I108" s="28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J108" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="31" t="s">
+        <v>367</v>
+      </c>
+      <c r="B109" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C109" s="31" t="s">
         <v>368</v>
-      </c>
-      <c r="B109" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C109" s="31" t="s">
-        <v>369</v>
       </c>
       <c r="D109" s="34" t="s">
         <v>99</v>
       </c>
       <c r="E109" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F109" s="30">
         <v>6.0</v>
       </c>
-      <c r="G109" s="19"/>
+      <c r="G109" s="30">
+        <v>4.0</v>
+      </c>
       <c r="H109" s="31" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I109" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J109" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="29" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B110" s="29" t="s">
         <v>30</v>
       </c>
       <c r="C110" s="29" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D110" s="36" t="s">
         <v>99</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F110" s="27">
         <v>5.0</v>
       </c>
       <c r="G110" s="37">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="H110" s="29" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I110" s="28" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J110" s="29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="B111" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C111" s="31" t="s">
         <v>374</v>
-      </c>
-      <c r="B111" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C111" s="31" t="s">
-        <v>375</v>
       </c>
       <c r="D111" s="34" t="s">
         <v>99</v>
       </c>
       <c r="E111" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F111" s="30">
         <v>2.0</v>
       </c>
-      <c r="G111" s="19"/>
+      <c r="G111" s="30">
+        <v>1.0</v>
+      </c>
       <c r="H111" s="31" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I111" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J111" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="31" t="s">
+        <v>376</v>
+      </c>
+      <c r="B112" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C112" s="31" t="s">
         <v>377</v>
-      </c>
-      <c r="B112" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C112" s="31" t="s">
-        <v>378</v>
       </c>
       <c r="D112" s="34" t="s">
         <v>99</v>
       </c>
       <c r="E112" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F112" s="30">
         <v>2.0</v>
       </c>
-      <c r="G112" s="19"/>
+      <c r="G112" s="30">
+        <v>1.0</v>
+      </c>
       <c r="H112" s="31" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I112" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J112" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="B113" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C113" s="31" t="s">
         <v>380</v>
-      </c>
-      <c r="B113" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C113" s="31" t="s">
-        <v>381</v>
       </c>
       <c r="D113" s="34" t="s">
         <v>99</v>
       </c>
       <c r="E113" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F113" s="30">
         <v>1.0</v>
       </c>
-      <c r="G113" s="19"/>
+      <c r="G113" s="30">
+        <v>1.0</v>
+      </c>
       <c r="H113" s="31" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I113" s="32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J113" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C114" s="11" t="s">
         <v>383</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>384</v>
       </c>
       <c r="D114" s="12" t="s">
         <v>99</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F114" s="27">
         <v>72.0</v>
       </c>
       <c r="G114" s="14">
         <f>G115+G123+G129+G134+G141</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H114" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="I114" s="28" t="s">
         <v>385</v>
       </c>
-      <c r="I114" s="13" t="s">
-        <v>386</v>
-      </c>
       <c r="J114" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K114" s="24"/>
       <c r="L114" s="24"/>
@@ -6316,35 +6346,35 @@
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C115" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>50</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F115" s="27">
         <v>24.0</v>
       </c>
       <c r="G115" s="26">
         <f>SUM(G116:G121)</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H115" s="11" t="s">
-        <v>389</v>
-      </c>
-      <c r="I115" s="13" t="s">
-        <v>386</v>
+        <v>388</v>
+      </c>
+      <c r="I115" s="28" t="s">
+        <v>26</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K115" s="24"/>
       <c r="L115" s="24"/>
@@ -6362,164 +6392,174 @@
       <c r="X115" s="24"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="16" t="s">
+      <c r="A116" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="B116" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C116" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="B116" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C116" s="16" t="s">
+      <c r="D116" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E116" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F116" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="G116" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="H116" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="D116" s="17" t="s">
+      <c r="I116" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J116" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
+      <c r="A117" s="17" t="s">
+        <v>392</v>
+      </c>
+      <c r="B117" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C117" s="17" t="s">
+        <v>393</v>
+      </c>
+      <c r="D117" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E116" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F116" s="19">
+      <c r="E117" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F117" s="22">
+        <v>6.0</v>
+      </c>
+      <c r="G117" s="30">
+        <v>8.0</v>
+      </c>
+      <c r="H117" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="I117" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J117" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
+      <c r="A118" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="B118" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="D118" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E118" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F118" s="22">
+        <v>1.0</v>
+      </c>
+      <c r="G118" s="33">
+        <v>1.0</v>
+      </c>
+      <c r="H118" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="I118" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J118" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
+      <c r="A119" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="B119" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="D119" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E119" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F119" s="22">
         <v>3.0</v>
       </c>
-      <c r="G116" s="19"/>
-      <c r="H116" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="I116" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J116" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="16" t="s">
-        <v>393</v>
-      </c>
-      <c r="B117" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C117" s="16" t="s">
-        <v>394</v>
-      </c>
-      <c r="D117" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E117" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F117" s="19">
-        <v>6.0</v>
-      </c>
-      <c r="G117" s="19"/>
-      <c r="H117" s="16" t="s">
-        <v>395</v>
-      </c>
-      <c r="I117" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J117" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="16" t="s">
-        <v>396</v>
-      </c>
-      <c r="B118" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C118" s="16" t="s">
-        <v>397</v>
-      </c>
-      <c r="D118" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E118" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F118" s="19">
-        <v>1.0</v>
-      </c>
-      <c r="G118" s="25"/>
-      <c r="H118" s="16" t="s">
-        <v>398</v>
-      </c>
-      <c r="I118" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J118" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="16" t="s">
-        <v>399</v>
-      </c>
-      <c r="B119" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C119" s="16" t="s">
+      <c r="G119" s="30">
+        <v>3.0</v>
+      </c>
+      <c r="H119" s="31" t="s">
         <v>400</v>
       </c>
-      <c r="D119" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E119" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="G119" s="19"/>
-      <c r="H119" s="31" t="s">
-        <v>401</v>
-      </c>
-      <c r="I119" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J119" s="16" t="s">
-        <v>25</v>
+      <c r="I119" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J119" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="31" t="s">
+        <v>401</v>
+      </c>
+      <c r="B120" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C120" s="31" t="s">
         <v>402</v>
-      </c>
-      <c r="B120" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C120" s="31" t="s">
-        <v>403</v>
       </c>
       <c r="D120" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E120" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F120" s="30">
         <v>5.0</v>
       </c>
-      <c r="G120" s="19"/>
+      <c r="G120" s="30">
+        <v>3.0</v>
+      </c>
       <c r="H120" s="31" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>386</v>
+        <v>26</v>
       </c>
       <c r="J120" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="31" t="s">
+        <v>404</v>
+      </c>
+      <c r="B121" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C121" s="31" t="s">
         <v>405</v>
-      </c>
-      <c r="B121" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C121" s="31" t="s">
-        <v>406</v>
       </c>
       <c r="D121" s="34" t="s">
         <v>99</v>
@@ -6530,56 +6570,60 @@
       <c r="F121" s="30">
         <v>3.0</v>
       </c>
-      <c r="G121" s="19"/>
+      <c r="G121" s="30">
+        <v>2.0</v>
+      </c>
       <c r="H121" s="31" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I121" s="32" t="s">
-        <v>386</v>
+        <v>26</v>
       </c>
       <c r="J121" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="B122" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C122" s="31" t="s">
         <v>408</v>
-      </c>
-      <c r="B122" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C122" s="31" t="s">
-        <v>409</v>
       </c>
       <c r="D122" s="34" t="s">
         <v>50</v>
       </c>
       <c r="E122" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F122" s="30">
         <v>3.0</v>
       </c>
-      <c r="G122" s="19"/>
+      <c r="G122" s="30">
+        <v>2.0</v>
+      </c>
       <c r="H122" s="31" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I122" s="32" t="s">
-        <v>386</v>
+        <v>26</v>
       </c>
       <c r="J122" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C123" s="11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D123" s="12" t="s">
         <v>99</v>
@@ -6595,13 +6639,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="11" t="s">
-        <v>413</v>
-      </c>
-      <c r="I123" s="13" t="s">
-        <v>386</v>
+        <v>412</v>
+      </c>
+      <c r="I123" s="28" t="s">
+        <v>385</v>
       </c>
       <c r="J123" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K123" s="24"/>
       <c r="L123" s="24"/>
@@ -6619,104 +6663,104 @@
       <c r="X123" s="24"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="16" t="s">
+      <c r="A124" s="17" t="s">
+        <v>413</v>
+      </c>
+      <c r="B124" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C124" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="B124" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C124" s="16" t="s">
+      <c r="D124" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E124" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="F124" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="G124" s="22"/>
+      <c r="H124" s="17" t="s">
         <v>415</v>
       </c>
-      <c r="D124" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E124" s="18" t="s">
+      <c r="I124" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J124" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
+      <c r="A125" s="17" t="s">
+        <v>416</v>
+      </c>
+      <c r="B125" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>417</v>
+      </c>
+      <c r="D125" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E125" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F124" s="19">
+      <c r="F125" s="22">
         <v>2.0</v>
       </c>
-      <c r="G124" s="19"/>
-      <c r="H124" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="I124" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J124" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="16" t="s">
-        <v>417</v>
-      </c>
-      <c r="B125" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C125" s="16" t="s">
+      <c r="G125" s="22"/>
+      <c r="H125" s="17" t="s">
         <v>418</v>
       </c>
-      <c r="D125" s="17" t="s">
+      <c r="I125" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J125" s="17" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
+      <c r="A126" s="17" t="s">
+        <v>419</v>
+      </c>
+      <c r="B126" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C126" s="17" t="s">
+        <v>420</v>
+      </c>
+      <c r="D126" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E125" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="F125" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="G125" s="19"/>
-      <c r="H125" s="16" t="s">
-        <v>419</v>
-      </c>
-      <c r="I125" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J125" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="16" t="s">
-        <v>420</v>
-      </c>
-      <c r="B126" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C126" s="16" t="s">
+      <c r="E126" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F126" s="22">
+        <v>10.0</v>
+      </c>
+      <c r="G126" s="25"/>
+      <c r="H126" s="31" t="s">
         <v>421</v>
       </c>
-      <c r="D126" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="E126" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F126" s="19">
-        <v>10.0</v>
-      </c>
-      <c r="G126" s="25"/>
-      <c r="H126" s="16" t="s">
-        <v>422</v>
-      </c>
-      <c r="I126" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J126" s="16" t="s">
-        <v>25</v>
+      <c r="I126" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="J126" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="B127" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C127" s="31" t="s">
         <v>423</v>
-      </c>
-      <c r="B127" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C127" s="31" t="s">
-        <v>424</v>
       </c>
       <c r="D127" s="34" t="s">
         <v>169</v>
@@ -6729,24 +6773,24 @@
       </c>
       <c r="G127" s="25"/>
       <c r="H127" s="31" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="I127" s="32" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J127" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="31" t="s">
+        <v>425</v>
+      </c>
+      <c r="B128" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C128" s="31" t="s">
         <v>426</v>
-      </c>
-      <c r="B128" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C128" s="31" t="s">
-        <v>427</v>
       </c>
       <c r="D128" s="34" t="s">
         <v>50</v>
@@ -6759,47 +6803,47 @@
       </c>
       <c r="G128" s="25"/>
       <c r="H128" s="31" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="I128" s="32" t="s">
-        <v>386</v>
+        <v>26</v>
       </c>
       <c r="J128" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="11" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>30</v>
       </c>
       <c r="C129" s="11" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D129" s="12" t="s">
         <v>126</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F129" s="14">
         <f t="shared" ref="F129:G129" si="24">SUM(F130:F133)</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G129" s="14">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="H129" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="I129" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="I129" s="13" t="s">
-        <v>386</v>
-      </c>
       <c r="J129" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K129" s="24"/>
       <c r="L129" s="24"/>
@@ -6817,93 +6861,93 @@
       <c r="X129" s="24"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="16" t="s">
+      <c r="A130" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="B130" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C130" s="16" t="s">
+      <c r="B130" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C130" s="17" t="s">
         <v>433</v>
       </c>
-      <c r="D130" s="17" t="s">
+      <c r="D130" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E130" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F130" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="G130" s="19"/>
-      <c r="H130" s="16" t="s">
+      <c r="E130" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F130" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="G130" s="22"/>
+      <c r="H130" s="17" t="s">
         <v>434</v>
       </c>
-      <c r="I130" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J130" s="16" t="s">
-        <v>25</v>
+      <c r="I130" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J130" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="16" t="s">
+      <c r="A131" s="17" t="s">
         <v>435</v>
       </c>
-      <c r="B131" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C131" s="16" t="s">
+      <c r="B131" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C131" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="D131" s="17" t="s">
+      <c r="D131" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E131" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F131" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="G131" s="19"/>
-      <c r="H131" s="16" t="s">
+      <c r="E131" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F131" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="G131" s="22"/>
+      <c r="H131" s="17" t="s">
         <v>437</v>
       </c>
-      <c r="I131" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J131" s="16" t="s">
-        <v>25</v>
+      <c r="I131" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J131" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="16" t="s">
+      <c r="A132" s="17" t="s">
         <v>438</v>
       </c>
-      <c r="B132" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C132" s="16" t="s">
+      <c r="B132" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C132" s="17" t="s">
         <v>439</v>
       </c>
-      <c r="D132" s="17" t="s">
+      <c r="D132" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E132" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F132" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="G132" s="19"/>
-      <c r="H132" s="16" t="s">
+      <c r="E132" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F132" s="30">
+        <v>2.0</v>
+      </c>
+      <c r="G132" s="22"/>
+      <c r="H132" s="17" t="s">
         <v>440</v>
       </c>
-      <c r="I132" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J132" s="16" t="s">
-        <v>25</v>
+      <c r="I132" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J132" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
@@ -6917,23 +6961,23 @@
         <v>442</v>
       </c>
       <c r="D133" s="34" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E133" s="32" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F133" s="30">
-        <v>3.0</v>
-      </c>
-      <c r="G133" s="19"/>
+        <v>2.0</v>
+      </c>
+      <c r="G133" s="22"/>
       <c r="H133" s="31" t="s">
         <v>443</v>
       </c>
       <c r="I133" s="32" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="J133" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
@@ -6963,10 +7007,10 @@
         <v>446</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K134" s="24"/>
       <c r="L134" s="24"/>
@@ -6984,123 +7028,123 @@
       <c r="X134" s="24"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="16" t="s">
+      <c r="A135" s="17" t="s">
         <v>447</v>
       </c>
-      <c r="B135" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C135" s="16" t="s">
+      <c r="B135" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C135" s="17" t="s">
         <v>448</v>
       </c>
-      <c r="D135" s="17" t="s">
+      <c r="D135" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E135" s="18" t="s">
+      <c r="E135" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F135" s="19">
+      <c r="F135" s="22">
         <v>3.0</v>
       </c>
-      <c r="G135" s="19"/>
-      <c r="H135" s="16" t="s">
+      <c r="G135" s="22"/>
+      <c r="H135" s="17" t="s">
         <v>449</v>
       </c>
-      <c r="I135" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J135" s="16" t="s">
-        <v>25</v>
+      <c r="I135" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J135" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="16" t="s">
+      <c r="A136" s="17" t="s">
         <v>450</v>
       </c>
-      <c r="B136" s="16" t="s">
+      <c r="B136" s="17" t="s">
         <v>37</v>
       </c>
       <c r="C136" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="D136" s="17" t="s">
+      <c r="D136" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E136" s="18" t="s">
+      <c r="E136" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F136" s="19">
+      <c r="F136" s="22">
         <v>3.0</v>
       </c>
-      <c r="G136" s="19"/>
-      <c r="H136" s="16" t="s">
+      <c r="G136" s="22"/>
+      <c r="H136" s="17" t="s">
         <v>452</v>
       </c>
-      <c r="I136" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J136" s="16" t="s">
-        <v>25</v>
+      <c r="I136" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J136" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="16" t="s">
+      <c r="A137" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="B137" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C137" s="16" t="s">
+      <c r="B137" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C137" s="17" t="s">
         <v>454</v>
       </c>
-      <c r="D137" s="17" t="s">
+      <c r="D137" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E137" s="18" t="s">
+      <c r="E137" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F137" s="19">
+      <c r="F137" s="22">
         <v>3.0</v>
       </c>
-      <c r="G137" s="19"/>
-      <c r="H137" s="16" t="s">
+      <c r="G137" s="22"/>
+      <c r="H137" s="31" t="s">
         <v>455</v>
       </c>
-      <c r="I137" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J137" s="16" t="s">
-        <v>25</v>
+      <c r="I137" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J137" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="16" t="s">
+      <c r="A138" s="17" t="s">
         <v>456</v>
       </c>
-      <c r="B138" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C138" s="16" t="s">
+      <c r="B138" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C138" s="17" t="s">
         <v>457</v>
       </c>
-      <c r="D138" s="17" t="s">
+      <c r="D138" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E138" s="18" t="s">
+      <c r="E138" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F138" s="19">
+      <c r="F138" s="22">
         <v>2.0</v>
       </c>
       <c r="G138" s="25"/>
-      <c r="H138" s="16" t="s">
+      <c r="H138" s="17" t="s">
         <v>458</v>
       </c>
-      <c r="I138" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J138" s="16" t="s">
-        <v>25</v>
+      <c r="I138" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J138" s="17" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -7127,10 +7171,10 @@
         <v>461</v>
       </c>
       <c r="I139" s="32" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="J139" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -7157,10 +7201,10 @@
         <v>464</v>
       </c>
       <c r="I140" s="32" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="J140" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
@@ -7191,10 +7235,10 @@
         <v>467</v>
       </c>
       <c r="I141" s="28" t="s">
-        <v>295</v>
+        <v>385</v>
       </c>
       <c r="J141" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
@@ -7221,10 +7265,10 @@
         <v>470</v>
       </c>
       <c r="I142" s="32" t="s">
-        <v>295</v>
+        <v>385</v>
       </c>
       <c r="J142" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
@@ -7251,10 +7295,10 @@
         <v>473</v>
       </c>
       <c r="I143" s="32" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="J143" s="31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
@@ -7262,7 +7306,7 @@
         <v>474</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>475</v>
@@ -7271,10 +7315,10 @@
         <v>99</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F144" s="26">
-        <f t="shared" ref="F144:G144" si="26">F145+F149+F153+F159</f>
+        <f t="shared" ref="F144:G144" si="26">F145+F150+F154+F160</f>
         <v>62</v>
       </c>
       <c r="G144" s="26">
@@ -7285,7 +7329,7 @@
         <v>476</v>
       </c>
       <c r="I144" s="13" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="J144" s="11" t="s">
         <v>33</v>
@@ -7319,7 +7363,7 @@
         <v>50</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F145" s="26">
         <f t="shared" ref="F145:G145" si="27">SUM(F146:F148)</f>
@@ -7333,7 +7377,7 @@
         <v>479</v>
       </c>
       <c r="I145" s="13" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="J145" s="11" t="s">
         <v>33</v>
@@ -7354,616 +7398,596 @@
       <c r="X145" s="24"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="16" t="s">
+      <c r="A146" s="17" t="s">
         <v>480</v>
       </c>
-      <c r="B146" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C146" s="16" t="s">
+      <c r="B146" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C146" s="17" t="s">
         <v>481</v>
       </c>
-      <c r="D146" s="17" t="s">
+      <c r="D146" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E146" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F146" s="19">
+      <c r="E146" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F146" s="22">
         <v>10.0</v>
       </c>
-      <c r="G146" s="19"/>
-      <c r="H146" s="16" t="s">
+      <c r="G146" s="22"/>
+      <c r="H146" s="31" t="s">
         <v>482</v>
       </c>
-      <c r="I146" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J146" s="16" t="s">
+      <c r="I146" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J146" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="16" t="s">
+      <c r="A147" s="17" t="s">
         <v>483</v>
       </c>
-      <c r="B147" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C147" s="16" t="s">
+      <c r="B147" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C147" s="17" t="s">
         <v>484</v>
       </c>
-      <c r="D147" s="17" t="s">
+      <c r="D147" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E147" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F147" s="19">
+      <c r="E147" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F147" s="22">
         <v>10.0</v>
       </c>
-      <c r="G147" s="19"/>
-      <c r="H147" s="16" t="s">
-        <v>482</v>
-      </c>
-      <c r="I147" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J147" s="16" t="s">
+      <c r="G147" s="22"/>
+      <c r="H147" s="31" t="s">
+        <v>485</v>
+      </c>
+      <c r="I147" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J147" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="16" t="s">
-        <v>485</v>
-      </c>
-      <c r="B148" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C148" s="16" t="s">
+      <c r="A148" s="17" t="s">
         <v>486</v>
       </c>
-      <c r="D148" s="17" t="s">
+      <c r="B148" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C148" s="17" t="s">
+        <v>487</v>
+      </c>
+      <c r="D148" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E148" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F148" s="19">
+      <c r="E148" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="22">
         <v>5.0</v>
       </c>
-      <c r="G148" s="19"/>
-      <c r="H148" s="16" t="s">
-        <v>487</v>
-      </c>
-      <c r="I148" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J148" s="16" t="s">
+      <c r="G148" s="22"/>
+      <c r="H148" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="I148" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J148" s="17" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="B149" s="11" t="s">
+      <c r="A149" s="31" t="s">
+        <v>489</v>
+      </c>
+      <c r="B149" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C149" s="31" t="s">
+        <v>490</v>
+      </c>
+      <c r="D149" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="E149" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F149" s="22"/>
+      <c r="G149" s="22"/>
+      <c r="H149" s="31" t="s">
+        <v>491</v>
+      </c>
+      <c r="I149" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="J149" s="31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
+      <c r="A150" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="B150" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C149" s="11" t="s">
-        <v>489</v>
-      </c>
-      <c r="D149" s="12" t="s">
+      <c r="C150" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="D150" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E149" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F149" s="14">
-        <f t="shared" ref="F149:G149" si="28">SUM(F150:F152)</f>
+      <c r="E150" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F150" s="14">
+        <f t="shared" ref="F150:G150" si="28">SUM(F151:F153)</f>
         <v>12</v>
       </c>
-      <c r="G149" s="14">
+      <c r="G150" s="14">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
-      <c r="H149" s="11" t="s">
-        <v>490</v>
-      </c>
-      <c r="I149" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="J149" s="11" t="s">
+      <c r="H150" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="I150" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J150" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K149" s="24"/>
-      <c r="L149" s="24"/>
-      <c r="M149" s="24"/>
-      <c r="N149" s="24"/>
-      <c r="O149" s="24"/>
-      <c r="P149" s="24"/>
-      <c r="Q149" s="24"/>
-      <c r="R149" s="24"/>
-      <c r="S149" s="24"/>
-      <c r="T149" s="24"/>
-      <c r="U149" s="24"/>
-      <c r="V149" s="24"/>
-      <c r="W149" s="24"/>
-      <c r="X149" s="24"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="16" t="s">
-        <v>491</v>
-      </c>
-      <c r="B150" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C150" s="16" t="s">
-        <v>492</v>
-      </c>
-      <c r="D150" s="17" t="s">
+      <c r="K150" s="24"/>
+      <c r="L150" s="24"/>
+      <c r="M150" s="24"/>
+      <c r="N150" s="24"/>
+      <c r="O150" s="24"/>
+      <c r="P150" s="24"/>
+      <c r="Q150" s="24"/>
+      <c r="R150" s="24"/>
+      <c r="S150" s="24"/>
+      <c r="T150" s="24"/>
+      <c r="U150" s="24"/>
+      <c r="V150" s="24"/>
+      <c r="W150" s="24"/>
+      <c r="X150" s="24"/>
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
+      <c r="A151" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="B151" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C151" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="D151" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E150" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F150" s="19">
+      <c r="E151" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F151" s="22">
         <v>4.0</v>
       </c>
-      <c r="G150" s="19"/>
-      <c r="H150" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="I150" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J150" s="16" t="s">
+      <c r="G151" s="22"/>
+      <c r="H151" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="I151" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J151" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="16" t="s">
-        <v>494</v>
-      </c>
-      <c r="B151" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C151" s="16" t="s">
-        <v>495</v>
-      </c>
-      <c r="D151" s="17" t="s">
+    <row r="152" ht="15.75" customHeight="1">
+      <c r="A152" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="B152" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C152" s="17" t="s">
+        <v>499</v>
+      </c>
+      <c r="D152" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E151" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F151" s="19">
+      <c r="E152" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" s="22">
         <v>4.0</v>
       </c>
-      <c r="G151" s="19"/>
-      <c r="H151" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="I151" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J151" s="16" t="s">
+      <c r="G152" s="22"/>
+      <c r="H152" s="17" t="s">
+        <v>497</v>
+      </c>
+      <c r="I152" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J152" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="16" t="s">
-        <v>496</v>
-      </c>
-      <c r="B152" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C152" s="16" t="s">
-        <v>497</v>
-      </c>
-      <c r="D152" s="17" t="s">
+    <row r="153" ht="15.75" customHeight="1">
+      <c r="A153" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="B153" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C153" s="17" t="s">
+        <v>501</v>
+      </c>
+      <c r="D153" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E152" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F152" s="19">
+      <c r="E153" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F153" s="22">
         <v>4.0</v>
       </c>
-      <c r="G152" s="25"/>
-      <c r="H152" s="16" t="s">
-        <v>498</v>
-      </c>
-      <c r="I152" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J152" s="16" t="s">
+      <c r="G153" s="25"/>
+      <c r="H153" s="17" t="s">
+        <v>502</v>
+      </c>
+      <c r="I153" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J153" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="11" t="s">
-        <v>499</v>
-      </c>
-      <c r="B153" s="11" t="s">
+    <row r="154" ht="15.75" customHeight="1">
+      <c r="A154" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="B154" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C153" s="11" t="s">
-        <v>500</v>
-      </c>
-      <c r="D153" s="12" t="s">
+      <c r="C154" s="11" t="s">
+        <v>504</v>
+      </c>
+      <c r="D154" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E153" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F153" s="14">
-        <f t="shared" ref="F153:G153" si="29">SUM(F154:F158)</f>
+      <c r="E154" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F154" s="14">
+        <f t="shared" ref="F154:G154" si="29">SUM(F155:F159)</f>
         <v>19</v>
       </c>
-      <c r="G153" s="14">
+      <c r="G154" s="14">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="H153" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="I153" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="J153" s="11" t="s">
+      <c r="H154" s="11" t="s">
+        <v>505</v>
+      </c>
+      <c r="I154" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J154" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K153" s="24"/>
-      <c r="L153" s="24"/>
-      <c r="M153" s="24"/>
-      <c r="N153" s="24"/>
-      <c r="O153" s="24"/>
-      <c r="P153" s="24"/>
-      <c r="Q153" s="24"/>
-      <c r="R153" s="24"/>
-      <c r="S153" s="24"/>
-      <c r="T153" s="24"/>
-      <c r="U153" s="24"/>
-      <c r="V153" s="24"/>
-      <c r="W153" s="24"/>
-      <c r="X153" s="24"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="16" t="s">
-        <v>502</v>
-      </c>
-      <c r="B154" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C154" s="16" t="s">
-        <v>503</v>
-      </c>
-      <c r="D154" s="17" t="s">
+      <c r="K154" s="24"/>
+      <c r="L154" s="24"/>
+      <c r="M154" s="24"/>
+      <c r="N154" s="24"/>
+      <c r="O154" s="24"/>
+      <c r="P154" s="24"/>
+      <c r="Q154" s="24"/>
+      <c r="R154" s="24"/>
+      <c r="S154" s="24"/>
+      <c r="T154" s="24"/>
+      <c r="U154" s="24"/>
+      <c r="V154" s="24"/>
+      <c r="W154" s="24"/>
+      <c r="X154" s="24"/>
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
+      <c r="A155" s="17" t="s">
+        <v>506</v>
+      </c>
+      <c r="B155" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C155" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="D155" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E154" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F154" s="19">
+      <c r="E155" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F155" s="22">
         <v>4.0</v>
       </c>
-      <c r="G154" s="19"/>
-      <c r="H154" s="16" t="s">
-        <v>504</v>
-      </c>
-      <c r="I154" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J154" s="16" t="s">
+      <c r="G155" s="22"/>
+      <c r="H155" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="I155" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J155" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="16" t="s">
-        <v>505</v>
-      </c>
-      <c r="B155" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C155" s="16" t="s">
-        <v>506</v>
-      </c>
-      <c r="D155" s="17" t="s">
+    <row r="156" ht="15.75" customHeight="1">
+      <c r="A156" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="B156" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C156" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="D156" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E155" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F155" s="19">
+      <c r="E156" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F156" s="22">
         <v>4.0</v>
       </c>
-      <c r="G155" s="19"/>
-      <c r="H155" s="16" t="s">
-        <v>507</v>
-      </c>
-      <c r="I155" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J155" s="16" t="s">
+      <c r="G156" s="22"/>
+      <c r="H156" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="I156" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J156" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="B156" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C156" s="16" t="s">
-        <v>509</v>
-      </c>
-      <c r="D156" s="17" t="s">
+    <row r="157" ht="15.75" customHeight="1">
+      <c r="A157" s="17" t="s">
+        <v>512</v>
+      </c>
+      <c r="B157" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C157" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="D157" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E156" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F156" s="19">
+      <c r="E157" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F157" s="22">
         <v>4.0</v>
       </c>
-      <c r="G156" s="19"/>
-      <c r="H156" s="16" t="s">
-        <v>510</v>
-      </c>
-      <c r="I156" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J156" s="16" t="s">
+      <c r="G157" s="22"/>
+      <c r="H157" s="17" t="s">
+        <v>514</v>
+      </c>
+      <c r="I157" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J157" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="16" t="s">
-        <v>511</v>
-      </c>
-      <c r="B157" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C157" s="16" t="s">
-        <v>512</v>
-      </c>
-      <c r="D157" s="17" t="s">
+    <row r="158" ht="15.75" customHeight="1">
+      <c r="A158" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="B158" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C158" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="D158" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E157" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F157" s="19">
+      <c r="E158" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F158" s="22">
         <v>4.0</v>
       </c>
-      <c r="G157" s="25"/>
-      <c r="H157" s="16" t="s">
-        <v>513</v>
-      </c>
-      <c r="I157" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J157" s="16" t="s">
+      <c r="G158" s="25"/>
+      <c r="H158" s="31" t="s">
+        <v>517</v>
+      </c>
+      <c r="I158" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J158" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="16" t="s">
-        <v>514</v>
-      </c>
-      <c r="B158" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C158" s="16" t="s">
-        <v>515</v>
-      </c>
-      <c r="D158" s="17" t="s">
+    <row r="159" ht="15.75" customHeight="1">
+      <c r="A159" s="17" t="s">
+        <v>518</v>
+      </c>
+      <c r="B159" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C159" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="D159" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E158" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F158" s="19">
+      <c r="E159" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F159" s="22">
         <v>3.0</v>
       </c>
-      <c r="G158" s="19"/>
-      <c r="H158" s="16" t="s">
-        <v>516</v>
-      </c>
-      <c r="I158" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J158" s="16" t="s">
+      <c r="G159" s="22"/>
+      <c r="H159" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="I159" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J159" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="B159" s="11" t="s">
+    <row r="160" ht="15.75" customHeight="1">
+      <c r="A160" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="B160" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C159" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="D159" s="12" t="s">
+      <c r="C160" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="D160" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E159" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F159" s="26">
-        <f t="shared" ref="F159:G159" si="30">SUM(F160:F161)</f>
+      <c r="E160" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F160" s="26">
+        <f t="shared" ref="F160:G160" si="30">SUM(F161:F162)</f>
         <v>6</v>
       </c>
-      <c r="G159" s="26">
+      <c r="G160" s="26">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="H159" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="I159" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="J159" s="11" t="s">
+      <c r="H160" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="I160" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J160" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K159" s="24"/>
-      <c r="L159" s="24"/>
-      <c r="M159" s="24"/>
-      <c r="N159" s="24"/>
-      <c r="O159" s="24"/>
-      <c r="P159" s="24"/>
-      <c r="Q159" s="24"/>
-      <c r="R159" s="24"/>
-      <c r="S159" s="24"/>
-      <c r="T159" s="24"/>
-      <c r="U159" s="24"/>
-      <c r="V159" s="24"/>
-      <c r="W159" s="24"/>
-      <c r="X159" s="24"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="16" t="s">
-        <v>520</v>
-      </c>
-      <c r="B160" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C160" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="D160" s="17" t="s">
+      <c r="K160" s="24"/>
+      <c r="L160" s="24"/>
+      <c r="M160" s="24"/>
+      <c r="N160" s="24"/>
+      <c r="O160" s="24"/>
+      <c r="P160" s="24"/>
+      <c r="Q160" s="24"/>
+      <c r="R160" s="24"/>
+      <c r="S160" s="24"/>
+      <c r="T160" s="24"/>
+      <c r="U160" s="24"/>
+      <c r="V160" s="24"/>
+      <c r="W160" s="24"/>
+      <c r="X160" s="24"/>
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
+      <c r="A161" s="17" t="s">
+        <v>524</v>
+      </c>
+      <c r="B161" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C161" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="D161" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="E160" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F160" s="19">
+      <c r="E161" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F161" s="22">
         <v>3.0</v>
       </c>
-      <c r="G160" s="25"/>
-      <c r="H160" s="16" t="s">
-        <v>522</v>
-      </c>
-      <c r="I160" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J160" s="16" t="s">
+      <c r="G161" s="25"/>
+      <c r="H161" s="17" t="s">
+        <v>526</v>
+      </c>
+      <c r="I161" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J161" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="16" t="s">
-        <v>523</v>
-      </c>
-      <c r="B161" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C161" s="16" t="s">
-        <v>524</v>
-      </c>
-      <c r="D161" s="17" t="s">
+    <row r="162" ht="15.75" customHeight="1">
+      <c r="A162" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C162" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="D162" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E161" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F161" s="19">
+      <c r="E162" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F162" s="22">
         <v>3.0</v>
       </c>
-      <c r="G161" s="19"/>
-      <c r="H161" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="I161" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J161" s="16" t="s">
+      <c r="G162" s="22"/>
+      <c r="H162" s="17" t="s">
+        <v>529</v>
+      </c>
+      <c r="I162" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J162" s="17" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="B162" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C162" s="11" t="s">
-        <v>527</v>
-      </c>
-      <c r="D162" s="12" t="s">
-        <v>528</v>
-      </c>
-      <c r="E162" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F162" s="26">
-        <f t="shared" ref="F162:G162" si="31">F163+F167+F170+F173</f>
-        <v>60</v>
-      </c>
-      <c r="G162" s="26">
-        <f t="shared" si="31"/>
-        <v>0</v>
-      </c>
-      <c r="H162" s="11" t="s">
-        <v>529</v>
-      </c>
-      <c r="I162" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="J162" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="K162" s="24"/>
-      <c r="L162" s="24"/>
-      <c r="M162" s="24"/>
-      <c r="N162" s="24"/>
-      <c r="O162" s="24"/>
-      <c r="P162" s="24"/>
-      <c r="Q162" s="24"/>
-      <c r="R162" s="24"/>
-      <c r="S162" s="24"/>
-      <c r="T162" s="24"/>
-      <c r="U162" s="24"/>
-      <c r="V162" s="24"/>
-      <c r="W162" s="24"/>
-      <c r="X162" s="24"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="11" t="s">
         <v>530</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>531</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>99</v>
+        <v>532</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F163" s="14">
-        <f t="shared" ref="F163:G163" si="32">SUM(F164:F166)</f>
-        <v>12</v>
-      </c>
-      <c r="G163" s="14">
-        <f t="shared" si="32"/>
+        <v>22</v>
+      </c>
+      <c r="F163" s="26">
+        <f t="shared" ref="F163:G163" si="31">F164+F168+F171+F174</f>
+        <v>60</v>
+      </c>
+      <c r="G163" s="26">
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="H163" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="I163" s="13" t="s">
-        <v>386</v>
+        <v>431</v>
       </c>
       <c r="J163" s="11" t="s">
         <v>33</v>
@@ -7984,473 +8008,518 @@
       <c r="X163" s="24"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="B164" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C164" s="16" t="s">
+      <c r="A164" s="11" t="s">
         <v>534</v>
       </c>
-      <c r="D164" s="17" t="s">
+      <c r="B164" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>535</v>
+      </c>
+      <c r="D164" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E164" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F164" s="19">
+      <c r="E164" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F164" s="14">
+        <f t="shared" ref="F164:G164" si="32">SUM(F165:F167)</f>
+        <v>12</v>
+      </c>
+      <c r="G164" s="14">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="H164" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="I164" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J164" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K164" s="24"/>
+      <c r="L164" s="24"/>
+      <c r="M164" s="24"/>
+      <c r="N164" s="24"/>
+      <c r="O164" s="24"/>
+      <c r="P164" s="24"/>
+      <c r="Q164" s="24"/>
+      <c r="R164" s="24"/>
+      <c r="S164" s="24"/>
+      <c r="T164" s="24"/>
+      <c r="U164" s="24"/>
+      <c r="V164" s="24"/>
+      <c r="W164" s="24"/>
+      <c r="X164" s="24"/>
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
+      <c r="A165" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="B165" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C165" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="D165" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E165" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F165" s="22">
         <v>4.0</v>
       </c>
-      <c r="G164" s="19"/>
-      <c r="H164" s="16" t="s">
-        <v>535</v>
-      </c>
-      <c r="I164" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J164" s="16" t="s">
+      <c r="G165" s="22"/>
+      <c r="H165" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="I165" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J165" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="16" t="s">
-        <v>536</v>
-      </c>
-      <c r="B165" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C165" s="16" t="s">
-        <v>537</v>
-      </c>
-      <c r="D165" s="17" t="s">
+    <row r="166" ht="15.75" customHeight="1">
+      <c r="A166" s="17" t="s">
+        <v>540</v>
+      </c>
+      <c r="B166" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C166" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="D166" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F165" s="19">
+      <c r="E166" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F166" s="22">
         <v>4.0</v>
       </c>
-      <c r="G165" s="19"/>
-      <c r="H165" s="16" t="s">
-        <v>538</v>
-      </c>
-      <c r="I165" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J165" s="16" t="s">
+      <c r="G166" s="22"/>
+      <c r="H166" s="17" t="s">
+        <v>542</v>
+      </c>
+      <c r="I166" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J166" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="16" t="s">
-        <v>539</v>
-      </c>
-      <c r="B166" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C166" s="16" t="s">
-        <v>540</v>
-      </c>
-      <c r="D166" s="17" t="s">
+    <row r="167" ht="15.75" customHeight="1">
+      <c r="A167" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="B167" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C167" s="17" t="s">
+        <v>544</v>
+      </c>
+      <c r="D167" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E166" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F166" s="19">
+      <c r="E167" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F167" s="22">
         <v>4.0</v>
       </c>
-      <c r="G166" s="19"/>
-      <c r="H166" s="16" t="s">
-        <v>541</v>
-      </c>
-      <c r="I166" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J166" s="16" t="s">
+      <c r="G167" s="22"/>
+      <c r="H167" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="I167" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J167" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="11" t="s">
-        <v>542</v>
-      </c>
-      <c r="B167" s="11" t="s">
+    <row r="168" ht="15.75" customHeight="1">
+      <c r="A168" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="B168" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C167" s="11" t="s">
-        <v>543</v>
-      </c>
-      <c r="D167" s="12" t="s">
+      <c r="C168" s="11" t="s">
+        <v>547</v>
+      </c>
+      <c r="D168" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="E167" s="13" t="s">
+      <c r="E168" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F167" s="26">
-        <f t="shared" ref="F167:G167" si="33">SUM(F168:F169)</f>
+      <c r="F168" s="26">
+        <f t="shared" ref="F168:G168" si="33">SUM(F169:F170)</f>
         <v>8</v>
       </c>
-      <c r="G167" s="26">
+      <c r="G168" s="26">
         <f t="shared" si="33"/>
         <v>0</v>
       </c>
-      <c r="H167" s="11" t="s">
-        <v>544</v>
-      </c>
-      <c r="I167" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="J167" s="11" t="s">
+      <c r="H168" s="11" t="s">
+        <v>548</v>
+      </c>
+      <c r="I168" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J168" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K167" s="24"/>
-      <c r="L167" s="24"/>
-      <c r="M167" s="24"/>
-      <c r="N167" s="24"/>
-      <c r="O167" s="24"/>
-      <c r="P167" s="24"/>
-      <c r="Q167" s="24"/>
-      <c r="R167" s="24"/>
-      <c r="S167" s="24"/>
-      <c r="T167" s="24"/>
-      <c r="U167" s="24"/>
-      <c r="V167" s="24"/>
-      <c r="W167" s="24"/>
-      <c r="X167" s="24"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="16" t="s">
-        <v>545</v>
-      </c>
-      <c r="B168" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C168" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="D168" s="17" t="s">
+      <c r="K168" s="24"/>
+      <c r="L168" s="24"/>
+      <c r="M168" s="24"/>
+      <c r="N168" s="24"/>
+      <c r="O168" s="24"/>
+      <c r="P168" s="24"/>
+      <c r="Q168" s="24"/>
+      <c r="R168" s="24"/>
+      <c r="S168" s="24"/>
+      <c r="T168" s="24"/>
+      <c r="U168" s="24"/>
+      <c r="V168" s="24"/>
+      <c r="W168" s="24"/>
+      <c r="X168" s="24"/>
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
+      <c r="A169" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="B169" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C169" s="17" t="s">
+        <v>550</v>
+      </c>
+      <c r="D169" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E168" s="18" t="s">
+      <c r="E169" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F168" s="19">
+      <c r="F169" s="22">
         <v>5.0</v>
       </c>
-      <c r="G168" s="38"/>
-      <c r="H168" s="16" t="s">
-        <v>547</v>
-      </c>
-      <c r="I168" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J168" s="16" t="s">
+      <c r="G169" s="38"/>
+      <c r="H169" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="I169" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J169" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="16" t="s">
-        <v>548</v>
-      </c>
-      <c r="B169" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C169" s="16" t="s">
-        <v>549</v>
-      </c>
-      <c r="D169" s="17" t="s">
+    <row r="170" ht="15.75" customHeight="1">
+      <c r="A170" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B170" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C170" s="17" t="s">
+        <v>553</v>
+      </c>
+      <c r="D170" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E169" s="18" t="s">
+      <c r="E170" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F169" s="19">
+      <c r="F170" s="22">
         <v>3.0</v>
       </c>
-      <c r="G169" s="38"/>
-      <c r="H169" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="I169" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J169" s="16" t="s">
+      <c r="G170" s="38"/>
+      <c r="H170" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="I170" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J170" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="16" t="s">
-        <v>551</v>
-      </c>
-      <c r="B170" s="16" t="s">
+    <row r="171" ht="15.75" customHeight="1">
+      <c r="A171" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="B171" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="C170" s="16" t="s">
-        <v>552</v>
-      </c>
-      <c r="D170" s="17" t="s">
-        <v>528</v>
-      </c>
-      <c r="E170" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F170" s="19">
-        <f t="shared" ref="F170:G170" si="34">SUM(F171:F172)</f>
+      <c r="C171" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="D171" s="19" t="s">
+        <v>532</v>
+      </c>
+      <c r="E171" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F171" s="22">
+        <f t="shared" ref="F171:G171" si="34">SUM(F172:F173)</f>
         <v>8</v>
       </c>
-      <c r="G170" s="38">
+      <c r="G171" s="38">
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="H170" s="16" t="s">
-        <v>553</v>
-      </c>
-      <c r="I170" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J170" s="16" t="s">
+      <c r="H171" s="17" t="s">
+        <v>557</v>
+      </c>
+      <c r="I171" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J171" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="16" t="s">
-        <v>554</v>
-      </c>
-      <c r="B171" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C171" s="16" t="s">
-        <v>555</v>
-      </c>
-      <c r="D171" s="17" t="s">
+    <row r="172" ht="15.75" customHeight="1">
+      <c r="A172" s="17" t="s">
+        <v>558</v>
+      </c>
+      <c r="B172" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C172" s="17" t="s">
+        <v>559</v>
+      </c>
+      <c r="D172" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="E171" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F171" s="19">
+      <c r="E172" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F172" s="22">
         <v>4.0</v>
       </c>
-      <c r="G171" s="38"/>
-      <c r="H171" s="16" t="s">
-        <v>556</v>
-      </c>
-      <c r="I171" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J171" s="16" t="s">
+      <c r="G172" s="38"/>
+      <c r="H172" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="I172" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J172" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="16" t="s">
-        <v>557</v>
-      </c>
-      <c r="B172" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C172" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="D172" s="17" t="s">
-        <v>559</v>
-      </c>
-      <c r="E172" s="18" t="s">
+    <row r="173" ht="15.75" customHeight="1">
+      <c r="A173" s="17" t="s">
+        <v>561</v>
+      </c>
+      <c r="B173" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C173" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="D173" s="19" t="s">
+        <v>563</v>
+      </c>
+      <c r="E173" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F172" s="19">
+      <c r="F173" s="22">
         <v>4.0</v>
       </c>
-      <c r="G172" s="38"/>
-      <c r="H172" s="16" t="s">
-        <v>560</v>
-      </c>
-      <c r="I172" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J172" s="16" t="s">
+      <c r="G173" s="38"/>
+      <c r="H173" s="17" t="s">
+        <v>564</v>
+      </c>
+      <c r="I173" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J173" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="11" t="s">
-        <v>561</v>
-      </c>
-      <c r="B173" s="11" t="s">
+    <row r="174" ht="15.75" customHeight="1">
+      <c r="A174" s="11" t="s">
+        <v>565</v>
+      </c>
+      <c r="B174" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C173" s="11" t="s">
-        <v>562</v>
-      </c>
-      <c r="D173" s="12" t="s">
+      <c r="C174" s="11" t="s">
+        <v>566</v>
+      </c>
+      <c r="D174" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E173" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F173" s="26">
-        <f t="shared" ref="F173:G173" si="35">SUM(F174:F177)</f>
+      <c r="E174" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F174" s="26">
+        <f t="shared" ref="F174:G174" si="35">SUM(F175:F178)</f>
         <v>32</v>
       </c>
-      <c r="G173" s="39">
+      <c r="G174" s="39">
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="H173" s="11" t="s">
-        <v>563</v>
-      </c>
-      <c r="I173" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="J173" s="11" t="s">
+      <c r="H174" s="11" t="s">
+        <v>567</v>
+      </c>
+      <c r="I174" s="13" t="s">
+        <v>431</v>
+      </c>
+      <c r="J174" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="K173" s="24"/>
-      <c r="L173" s="24"/>
-      <c r="M173" s="24"/>
-      <c r="N173" s="24"/>
-      <c r="O173" s="24"/>
-      <c r="P173" s="24"/>
-      <c r="Q173" s="24"/>
-      <c r="R173" s="24"/>
-      <c r="S173" s="24"/>
-      <c r="T173" s="24"/>
-      <c r="U173" s="24"/>
-      <c r="V173" s="24"/>
-      <c r="W173" s="24"/>
-      <c r="X173" s="24"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="16" t="s">
-        <v>564</v>
-      </c>
-      <c r="B174" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C174" s="16" t="s">
-        <v>565</v>
-      </c>
-      <c r="D174" s="17" t="s">
+      <c r="K174" s="24"/>
+      <c r="L174" s="24"/>
+      <c r="M174" s="24"/>
+      <c r="N174" s="24"/>
+      <c r="O174" s="24"/>
+      <c r="P174" s="24"/>
+      <c r="Q174" s="24"/>
+      <c r="R174" s="24"/>
+      <c r="S174" s="24"/>
+      <c r="T174" s="24"/>
+      <c r="U174" s="24"/>
+      <c r="V174" s="24"/>
+      <c r="W174" s="24"/>
+      <c r="X174" s="24"/>
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
+      <c r="A175" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="B175" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C175" s="17" t="s">
+        <v>569</v>
+      </c>
+      <c r="D175" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E174" s="18" t="s">
+      <c r="E175" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="F174" s="19">
+      <c r="F175" s="22">
         <v>3.0</v>
       </c>
-      <c r="G174" s="38"/>
-      <c r="H174" s="16" t="s">
-        <v>566</v>
-      </c>
-      <c r="I174" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J174" s="16" t="s">
+      <c r="G175" s="38"/>
+      <c r="H175" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="I175" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J175" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="16" t="s">
-        <v>567</v>
-      </c>
-      <c r="B175" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C175" s="16" t="s">
-        <v>568</v>
-      </c>
-      <c r="D175" s="17" t="s">
+    <row r="176" ht="15.75" customHeight="1">
+      <c r="A176" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="B176" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C176" s="17" t="s">
+        <v>572</v>
+      </c>
+      <c r="D176" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E175" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F175" s="19">
+      <c r="E176" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F176" s="22">
         <v>4.0</v>
       </c>
-      <c r="G175" s="38"/>
-      <c r="H175" s="16" t="s">
-        <v>569</v>
-      </c>
-      <c r="I175" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J175" s="16" t="s">
+      <c r="G176" s="38"/>
+      <c r="H176" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="I176" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J176" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="16" t="s">
-        <v>570</v>
-      </c>
-      <c r="B176" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C176" s="16" t="s">
-        <v>571</v>
-      </c>
-      <c r="D176" s="17" t="s">
+    <row r="177" ht="15.75" customHeight="1">
+      <c r="A177" s="17" t="s">
+        <v>574</v>
+      </c>
+      <c r="B177" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C177" s="17" t="s">
+        <v>575</v>
+      </c>
+      <c r="D177" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E176" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F176" s="19">
+      <c r="E177" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F177" s="22">
         <v>5.0</v>
       </c>
-      <c r="G176" s="38"/>
-      <c r="H176" s="16" t="s">
-        <v>572</v>
-      </c>
-      <c r="I176" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J176" s="16" t="s">
+      <c r="G177" s="38"/>
+      <c r="H177" s="17" t="s">
+        <v>576</v>
+      </c>
+      <c r="I177" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J177" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="B177" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="C177" s="16" t="s">
-        <v>574</v>
-      </c>
-      <c r="D177" s="17" t="s">
+    <row r="178" ht="15.75" customHeight="1">
+      <c r="A178" s="17" t="s">
+        <v>577</v>
+      </c>
+      <c r="B178" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C178" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="D178" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E177" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F177" s="19">
+      <c r="E178" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F178" s="22">
         <v>20.0</v>
       </c>
-      <c r="G177" s="38"/>
-      <c r="H177" s="16" t="s">
-        <v>575</v>
-      </c>
-      <c r="I177" s="18" t="s">
-        <v>386</v>
-      </c>
-      <c r="J177" s="16" t="s">
+      <c r="G178" s="38"/>
+      <c r="H178" s="17" t="s">
+        <v>579</v>
+      </c>
+      <c r="I178" s="20" t="s">
+        <v>431</v>
+      </c>
+      <c r="J178" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="I178" s="40"/>
-    </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="C179" s="41"/>
       <c r="I179" s="40"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
+      <c r="C180" s="41"/>
       <c r="I180" s="40"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
@@ -10940,7 +11009,9 @@
     <row r="1009" ht="15.75" customHeight="1">
       <c r="I1009" s="40"/>
     </row>
-    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1">
+      <c r="I1010" s="40"/>
+    </row>
     <row r="1011" ht="15.75" customHeight="1"/>
     <row r="1012" ht="15.75" customHeight="1"/>
     <row r="1013" ht="15.75" customHeight="1"/>
@@ -10952,33 +11023,34 @@
     <row r="1019" ht="15.75" customHeight="1"/>
     <row r="1020" ht="15.75" customHeight="1"/>
     <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="I2:I1009">
+  <conditionalFormatting sqref="I2:I1010">
     <cfRule type="cellIs" dxfId="5" priority="1" stopIfTrue="1" operator="equal">
       <formula>"Realizado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I1009">
+  <conditionalFormatting sqref="I2:I1010">
     <cfRule type="cellIs" dxfId="6" priority="2" stopIfTrue="1" operator="equal">
       <formula>"En progreso"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I1009">
+  <conditionalFormatting sqref="I2:I1010">
     <cfRule type="cellIs" dxfId="7" priority="3" stopIfTrue="1" operator="equal">
       <formula>"Pendiente"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I1009">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I1010">
       <formula1>"Pendiente,En progreso,Realizado"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="B2:B67">
       <formula1>"Épica,Historia,Tarea"</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F177">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:F178">
       <formula1>AND(ISNUMBER(F2),(NOT(OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D")))))</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" sqref="D2:D177">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" sqref="D2:D178">
       <formula1>"OE1,OE2,OE3,OG,OE4,OE2, OE3,OE1, OE2, OE3,OG, OE1, OE2, OE3,OG, OE1, OE2, OE3, OE4,OE1, OE2,OG, OE1, OE2, OE4,OG, OE2, OE3, OE4,OE1, OE2, OE3, OE4,OG, OE3, OE4,OG, OE3, OE4,OG, OE3"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="E2:E67">
@@ -11045,75 +11117,75 @@
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="7">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>74</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="10">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>73</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="10">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>20</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="10">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A2,Backlog!I:I,"Realizado")</f>
         <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3" s="4">
         <v>46297.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D3" s="3">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>74</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="10">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>77</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="10">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>43</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="10">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A3,Backlog!I:I,"Realizado")</f>
         <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="15">
         <v>46325.0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
-        <v>119</v>
-      </c>
-      <c r="E4" s="8">
+        <v>115</v>
+      </c>
+      <c r="E4" s="10">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
-        <v>20</v>
-      </c>
-      <c r="F4" s="8">
+        <v>57</v>
+      </c>
+      <c r="F4" s="10">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
         <v>47</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="10">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A4,Backlog!I:I,"Realizado")</f>
-        <v>23</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -11126,77 +11198,77 @@
       <c r="C5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="7">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
         <v>122</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="10">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="10">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
-        <v>24</v>
-      </c>
-      <c r="G5" s="8">
+        <v>25</v>
+      </c>
+      <c r="G5" s="10">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A5,Backlog!I:I,"Realizado")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="s">
+      <c r="B8" s="21">
+        <f>SUM(D2:D5)</f>
+        <v>385</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="22">
-        <f>SUM(D2:D5)</f>
-        <v>389</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="22">
+      <c r="B9" s="21">
         <f>SUM(E2:E5)</f>
-        <v>170</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
+        <v>207</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
     </row>
     <row r="10">
       <c r="A10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="10">
         <f>SUM(F2:F5)</f>
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="10">
         <f>SUM(G2:G5)</f>
-        <v>86</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/docs/Backlog Proyecto Titulo.xlsx
+++ b/docs/Backlog Proyecto Titulo.xlsx
@@ -68,6 +68,12 @@
     <t>Estado</t>
   </si>
   <si>
+    <t>Etapa 2</t>
+  </si>
+  <si>
+    <t>Diseño técnico, arquitectura, protocolo e implementación inicial</t>
+  </si>
+  <si>
     <t>EP-01</t>
   </si>
   <si>
@@ -83,10 +89,10 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>Etapa 2</t>
-  </si>
-  <si>
-    <t>Diseño técnico, arquitectura, protocolo e implementación inicial</t>
+    <t>Etapa 3</t>
+  </si>
+  <si>
+    <t>Implementación observabilidad, pruebas piloto y validación preliminar</t>
   </si>
   <si>
     <t>Problema, estado del arte, objetivos, requerimientos y alternativas definidos y respaldados.</t>
@@ -95,10 +101,10 @@
     <t>Realizado</t>
   </si>
   <si>
-    <t>Etapa 3</t>
-  </si>
-  <si>
-    <t>Implementación observabilidad, pruebas piloto y validación preliminar</t>
+    <t>Etapa 4</t>
+  </si>
+  <si>
+    <t>Campaña definitiva, análisis, informe final y defensa</t>
   </si>
   <si>
     <t>HU-01</t>
@@ -113,39 +119,33 @@
     <t>OG, OE1, OE2, OE4</t>
   </si>
   <si>
-    <t>Etapa 4</t>
-  </si>
-  <si>
-    <t>Campaña definitiva, análisis, informe final y defensa</t>
+    <t>Indicador</t>
+  </si>
+  <si>
+    <t>Valor</t>
   </si>
   <si>
     <t>Conjunto de fuentes académicas y técnicas organizado en BibTeX y utilizado en el informe.</t>
   </si>
   <si>
+    <t>Total de horas estimadas (tareas)</t>
+  </si>
+  <si>
+    <t>Total de horas reales (tareas)</t>
+  </si>
+  <si>
     <t>T-01.1</t>
   </si>
   <si>
     <t>Tarea</t>
   </si>
   <si>
-    <t>Indicador</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
     <t>Investigar comparaciones de distribuciones ligeras de Kubernetes</t>
   </si>
   <si>
-    <t>Total de horas estimadas (tareas)</t>
-  </si>
-  <si>
     <t>OE1, OE2</t>
   </si>
   <si>
-    <t>Total de horas reales (tareas)</t>
-  </si>
-  <si>
     <t>Fichas bibliográficas sobre K3s, MicroK8s y métricas de CPU, memoria, throughput y latencia.</t>
   </si>
   <si>
@@ -1286,7 +1286,7 @@
     <t>Revisar tamaño muestral con la varianza del piloto (potencia estadística)</t>
   </si>
   <si>
-    <t>Número de bloques (8 propuestos) y de repeticiones por celda confirmado o ajustado con la varianza entre episodios observada en el piloto y en el diagnóstico del desfase de ≈ 1 W; potencia justificada con simulación y supuestos explícitos.</t>
+    <t>8 bloques y 2 repeticiones por celda propuestos según la variabilidad observada en el piloto; potencia condicionada a σ_u (limitación declarada); fijación definitiva en el pre-registro (T-24.4).</t>
   </si>
   <si>
     <t>T-21.5</t>
@@ -1487,7 +1487,7 @@
     <t>Cerrar pendientes técnicos previos a la campaña</t>
   </si>
   <si>
-    <t>Pilotos de energía repetidos con la aplicación definitiva (SHA-256, límite 2000m, tasas media 450 y alta 900 rps) en ambas distribuciones; K3s construido por el flujo completo de Ansible con la aplicación definitiva, sin ajustes manuales; orquestador registrando por ventana deltas de residencia de C-states, interrupciones, CPU por hilo de QEMU, KSM y halt polling; diagnóstico del desfase de ≈ 1 W (serie sin intervenir y ABAB sobre las covariables que se muevan, incluida la ubicación de los hilos de emulador y E/S de QEMU mediante emulatorpin), con límite de tiempo y causa identificada o declarada como no resuelta; desbordamiento del contador RAPL corregido en el análisis de Scaphandre; plan de campaña (secuencia de bloques con semilla, reglas de exclusión y plan de análisis) fijado en un commit etiquetado antes del primer bloque.</t>
+    <t>Pilotos de energía repetidos con la aplicación definitiva (SHA-256, límite 2000m, tasas media 450 y alta 900 rps) en ambas distribuciones; K3s construido por el flujo completo de Ansible con la aplicación definitiva, sin ajustes manuales; orquestador registrando por ventana deltas de residencia de C-states, interrupciones, CPU por hilo de QEMU, KSM y halt polling; diagnóstico del desfase de ≈ 1 W (serie sin intervenir y ABAB sobre las covariables que se muevan, incluida la ubicación de los hilos de emulador y E/S de QEMU mediante emulatorpin), con límite de tiempo y causa identificada o declarada como no resuelta; desbordamiento del contador RAPL corregido en el análisis de Scaphandre; pre-registro fijado antes del primer bloque: etiqueta plan-campana-v1, número de bloques y repeticiones, secuencia con semilla, reglas de exclusión y plan de análisis (Wilcoxon exacto por bloque, t pareada complementaria, Hodges-Lehmann, Holm por familias, modelo mixto como sensibilidad).</t>
   </si>
   <si>
     <t>HU-25</t>
@@ -1866,20 +1866,20 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1890,20 +1890,26 @@
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1911,14 +1917,8 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -2326,66 +2326,66 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="14">
+        <v>24</v>
+      </c>
+      <c r="F2" s="15">
         <f t="shared" ref="F2:G2" si="1">F3+F8+F12+F16+F22</f>
         <v>74</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="15">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>7</v>
@@ -2393,163 +2393,163 @@
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="14">
+        <v>24</v>
+      </c>
+      <c r="F3" s="15">
         <f t="shared" ref="F3:G3" si="2">SUM(F4:F7)</f>
         <v>19</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="15">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J3" s="11" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="17" t="s">
+      <c r="A4" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="B4" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="22">
+      <c r="D4" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="23">
         <v>6.0</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="23">
         <v>8.0</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="H4" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="17" t="s">
+      <c r="I4" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="17" t="s">
+      <c r="B5" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="22">
+      <c r="D5" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="23">
         <v>5.0</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="23">
         <v>5.0</v>
       </c>
-      <c r="H5" s="17" t="s">
+      <c r="H5" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="17" t="s">
+      <c r="I5" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="22">
+      <c r="E6" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="23">
         <v>5.0</v>
       </c>
-      <c r="G6" s="22">
+      <c r="G6" s="23">
         <v>4.0</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="I6" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="17" t="s">
+      <c r="I6" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <v>3.0</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <v>3.0</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="I7" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="17" t="s">
+      <c r="I7" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7" s="20" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
         <v>57</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>58</v>
@@ -2567,13 +2567,13 @@
         <v>59</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="14">
+        <v>24</v>
+      </c>
+      <c r="F8" s="15">
         <f t="shared" ref="F8:G8" si="3">SUM(F9:F11)</f>
         <v>12</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>60</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J8" s="11" t="s">
         <v>7</v>
@@ -2602,98 +2602,98 @@
       <c r="X8" s="24"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
-      <c r="A9" s="17" t="s">
+      <c r="A9" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="17" t="s">
+      <c r="B9" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="22">
+      <c r="E9" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="23">
         <v>5.0</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="23">
         <v>5.0</v>
       </c>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J9" s="17" t="s">
+      <c r="I9" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="22">
+      <c r="E10" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="23">
         <v>3.0</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="23">
         <v>3.0</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="17" t="s">
+      <c r="I10" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="17" t="s">
+      <c r="B11" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="22">
+      <c r="E11" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="23">
         <v>4.0</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <v>4.0</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" s="17" t="s">
+      <c r="I11" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J11" s="20" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2702,22 +2702,22 @@
         <v>71</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>72</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="14">
+        <v>24</v>
+      </c>
+      <c r="F12" s="15">
         <f t="shared" ref="F12:G12" si="4">SUM(F13:F15)</f>
         <v>11</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="15">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
@@ -2725,7 +2725,7 @@
         <v>73</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>7</v>
@@ -2746,98 +2746,98 @@
       <c r="X12" s="24"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="17" t="s">
+      <c r="B13" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="22">
+      <c r="D13" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="23">
         <v>4.0</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="23">
         <v>4.0</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="I13" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J13" s="17" t="s">
+      <c r="I13" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="17" t="s">
+      <c r="B14" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="22">
+      <c r="E14" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="23">
         <v>3.0</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <v>3.0</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="I14" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="17" t="s">
+      <c r="I14" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="17" t="s">
+      <c r="B15" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="22">
+      <c r="D15" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="23">
         <v>4.0</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <v>4.0</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="I15" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="17" t="s">
+      <c r="I15" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="20" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2846,7 +2846,7 @@
         <v>83</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C16" s="11" t="s">
         <v>84</v>
@@ -2855,13 +2855,13 @@
         <v>85</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="14">
+        <v>24</v>
+      </c>
+      <c r="F16" s="15">
         <f t="shared" ref="F16:G16" si="5">SUM(F17:F21)</f>
         <v>17</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <f t="shared" si="5"/>
         <v>15</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>86</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J16" s="11" t="s">
         <v>7</v>
@@ -2890,162 +2890,162 @@
       <c r="X16" s="24"/>
     </row>
     <row r="17" ht="22.5" customHeight="1">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C17" s="17" t="s">
+      <c r="B17" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E17" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="22">
+      <c r="E17" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="23">
         <v>3.0</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <v>3.0</v>
       </c>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="I17" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J17" s="17" t="s">
+      <c r="I17" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="17" t="s">
+      <c r="B18" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E18" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F18" s="22">
+      <c r="E18" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="23">
         <v>3.0</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="23">
         <v>3.0</v>
       </c>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="I18" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J18" s="17" t="s">
+      <c r="I18" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J18" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C19" s="17" t="s">
+      <c r="B19" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="22">
+      <c r="E19" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="23">
         <v>4.0</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="23">
         <v>3.0</v>
       </c>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="I19" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J19" s="17" t="s">
+      <c r="I19" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="17" t="s">
+      <c r="B20" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E20" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="22">
+      <c r="E20" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="23">
         <v>5.0</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="23">
         <v>4.0</v>
       </c>
-      <c r="H20" s="17" t="s">
+      <c r="H20" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="I20" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J20" s="17" t="s">
+      <c r="I20" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="17" t="s">
+      <c r="B21" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="22">
+      <c r="E21" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="23">
         <v>2.0</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="23">
         <v>2.0</v>
       </c>
-      <c r="H21" s="17" t="s">
+      <c r="H21" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="I21" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J21" s="17" t="s">
+      <c r="I21" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="20" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3054,22 +3054,22 @@
         <v>105</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>106</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F22" s="14">
+        <v>24</v>
+      </c>
+      <c r="F22" s="15">
         <f t="shared" ref="F22:G22" si="6">SUM(F23:F27)</f>
         <v>15</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <f t="shared" si="6"/>
         <v>15</v>
       </c>
@@ -3077,7 +3077,7 @@
         <v>107</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J22" s="11" t="s">
         <v>7</v>
@@ -3098,162 +3098,162 @@
       <c r="X22" s="24"/>
     </row>
     <row r="23" ht="22.5" customHeight="1">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="17" t="s">
+      <c r="B23" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F23" s="22">
+      <c r="F23" s="23">
         <v>3.0</v>
       </c>
-      <c r="G23" s="22">
+      <c r="G23" s="23">
         <v>3.0</v>
       </c>
-      <c r="H23" s="17" t="s">
+      <c r="H23" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="I23" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="17" t="s">
+      <c r="I23" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="17" t="s">
+      <c r="B24" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="D24" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E24" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F24" s="22">
+      <c r="E24" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="23">
         <v>3.0</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="23">
         <v>3.0</v>
       </c>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="I24" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="17" t="s">
+      <c r="I24" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="20" t="s">
         <v>115</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="17" t="s">
+      <c r="B25" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E25" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="22">
+      <c r="E25" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="23">
         <v>3.0</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="23">
         <v>3.0</v>
       </c>
-      <c r="H25" s="17" t="s">
+      <c r="H25" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="I25" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" s="17" t="s">
+      <c r="I25" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B26" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="17" t="s">
+      <c r="B26" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="D26" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="22">
+      <c r="E26" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="23">
         <v>3.0</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="23">
         <v>3.0</v>
       </c>
-      <c r="H26" s="17" t="s">
+      <c r="H26" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="I26" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J26" s="17" t="s">
+      <c r="I26" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="B27" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="17" t="s">
+      <c r="B27" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="D27" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="23">
         <v>3.0</v>
       </c>
-      <c r="G27" s="20">
+      <c r="G27" s="22">
         <v>3.0</v>
       </c>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="I27" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J27" s="17" t="s">
+      <c r="I27" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" s="20" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3262,7 +3262,7 @@
         <v>124</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>125</v>
@@ -3271,13 +3271,13 @@
         <v>126</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="14">
+        <v>24</v>
+      </c>
+      <c r="F28" s="15">
         <f t="shared" ref="F28:G28" si="7">F29+F34+F40+F46</f>
         <v>40</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="15">
         <f t="shared" si="7"/>
         <v>33</v>
       </c>
@@ -3285,10 +3285,10 @@
         <v>127</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
@@ -3310,7 +3310,7 @@
         <v>128</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>129</v>
@@ -3319,13 +3319,13 @@
         <v>89</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="14">
+        <v>24</v>
+      </c>
+      <c r="F29" s="15">
         <f t="shared" ref="F29:G29" si="8">SUM(F30:F33)</f>
         <v>10</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <f t="shared" si="8"/>
         <v>10</v>
       </c>
@@ -3333,10 +3333,10 @@
         <v>130</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
@@ -3354,131 +3354,131 @@
       <c r="X29" s="24"/>
     </row>
     <row r="30" ht="22.5" customHeight="1">
-      <c r="A30" s="17" t="s">
+      <c r="A30" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C30" s="17" t="s">
+      <c r="B30" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E30" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="22">
+      <c r="E30" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="23">
         <v>2.0</v>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="23">
         <v>2.0</v>
       </c>
-      <c r="H30" s="17" t="s">
+      <c r="H30" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="I30" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J30" s="17" t="s">
-        <v>23</v>
+      <c r="I30" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
-      <c r="A31" s="17" t="s">
+      <c r="A31" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="17" t="s">
+      <c r="B31" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E31" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F31" s="22">
+      <c r="E31" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="23">
         <v>3.0</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="23">
         <v>3.0</v>
       </c>
-      <c r="H31" s="17" t="s">
+      <c r="H31" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="I31" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J31" s="17" t="s">
-        <v>23</v>
+      <c r="I31" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
-      <c r="A32" s="17" t="s">
+      <c r="A32" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C32" s="17" t="s">
+      <c r="B32" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E32" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F32" s="22">
+      <c r="E32" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="23">
         <v>3.0</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="23">
         <v>3.0</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="I32" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>23</v>
+      <c r="I32" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
-      <c r="A33" s="17" t="s">
+      <c r="A33" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="B33" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="17" t="s">
+      <c r="B33" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="23">
         <v>2.0</v>
       </c>
       <c r="G33" s="25">
         <v>2.0</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="H33" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="I33" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>23</v>
+      <c r="I33" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J33" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
@@ -3486,7 +3486,7 @@
         <v>143</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C34" s="11" t="s">
         <v>144</v>
@@ -3495,7 +3495,7 @@
         <v>50</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F34" s="26">
         <f t="shared" ref="F34:G34" si="9">SUM(F35:F39)</f>
@@ -3509,10 +3509,10 @@
         <v>145</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K34" s="24"/>
       <c r="L34" s="24"/>
@@ -3530,163 +3530,163 @@
       <c r="X34" s="24"/>
     </row>
     <row r="35" ht="22.5" customHeight="1">
-      <c r="A35" s="17" t="s">
+      <c r="A35" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="B35" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C35" s="17" t="s">
+      <c r="B35" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" s="20" t="s">
         <v>147</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F35" s="22">
+      <c r="E35" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="23">
         <v>3.0</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="23">
         <v>2.0</v>
       </c>
-      <c r="H35" s="17" t="s">
+      <c r="H35" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="I35" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J35" s="17" t="s">
-        <v>23</v>
+      <c r="I35" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B36" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="17" t="s">
+      <c r="B36" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E36" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="22">
+      <c r="E36" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="23">
         <v>3.0</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="23">
         <v>2.0</v>
       </c>
-      <c r="H36" s="17" t="s">
+      <c r="H36" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="I36" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J36" s="17" t="s">
-        <v>23</v>
+      <c r="I36" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J36" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="B37" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="17" t="s">
+      <c r="B37" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="19" t="s">
+      <c r="D37" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E37" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F37" s="22">
+      <c r="E37" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="23">
         <v>3.0</v>
       </c>
-      <c r="G37" s="22">
+      <c r="G37" s="23">
         <v>2.0</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="H37" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="I37" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J37" s="17" t="s">
-        <v>23</v>
+      <c r="I37" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C38" s="17" t="s">
+      <c r="B38" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="D38" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E38" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F38" s="22">
+      <c r="E38" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F38" s="23">
         <v>3.0</v>
       </c>
-      <c r="G38" s="22">
+      <c r="G38" s="23">
         <v>2.0</v>
       </c>
-      <c r="H38" s="17" t="s">
+      <c r="H38" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="I38" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J38" s="17" t="s">
-        <v>23</v>
+      <c r="I38" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
-      <c r="A39" s="17" t="s">
+      <c r="A39" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="B39" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C39" s="17" t="s">
+      <c r="B39" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E39" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F39" s="22">
+      <c r="E39" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F39" s="23">
         <v>3.0</v>
       </c>
       <c r="G39" s="25">
         <v>2.0</v>
       </c>
-      <c r="H39" s="17" t="s">
+      <c r="H39" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="I39" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" s="17" t="s">
-        <v>23</v>
+      <c r="I39" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
@@ -3694,7 +3694,7 @@
         <v>161</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>162</v>
@@ -3703,7 +3703,7 @@
         <v>99</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F40" s="26">
         <f t="shared" ref="F40:G40" si="10">SUM(F41:F45)</f>
@@ -3717,10 +3717,10 @@
         <v>163</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K40" s="24"/>
       <c r="L40" s="24"/>
@@ -3738,163 +3738,163 @@
       <c r="X40" s="24"/>
     </row>
     <row r="41" ht="22.5" customHeight="1">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="B41" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C41" s="17" t="s">
+      <c r="B41" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="D41" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E41" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="22">
+      <c r="E41" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="23">
         <v>2.0</v>
       </c>
-      <c r="G41" s="22">
+      <c r="G41" s="23">
         <v>2.0</v>
       </c>
-      <c r="H41" s="17" t="s">
+      <c r="H41" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="I41" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J41" s="17" t="s">
-        <v>23</v>
+      <c r="I41" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B42" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C42" s="17" t="s">
+      <c r="B42" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="22">
+      <c r="E42" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="23">
         <v>2.0</v>
       </c>
-      <c r="G42" s="22">
+      <c r="G42" s="23">
         <v>1.0</v>
       </c>
-      <c r="H42" s="17" t="s">
+      <c r="H42" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="I42" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J42" s="17" t="s">
-        <v>23</v>
+      <c r="I42" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J42" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
-      <c r="A43" s="17" t="s">
+      <c r="A43" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="B43" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C43" s="17" t="s">
+      <c r="B43" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E43" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F43" s="22">
+      <c r="E43" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="23">
         <v>2.0</v>
       </c>
-      <c r="G43" s="22">
+      <c r="G43" s="23">
         <v>2.0</v>
       </c>
-      <c r="H43" s="17" t="s">
+      <c r="H43" s="20" t="s">
         <v>173</v>
       </c>
-      <c r="I43" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J43" s="17" t="s">
-        <v>23</v>
+      <c r="I43" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
-      <c r="A44" s="17" t="s">
+      <c r="A44" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="B44" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="17" t="s">
+      <c r="B44" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E44" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="22">
+      <c r="E44" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F44" s="23">
         <v>2.0</v>
       </c>
-      <c r="G44" s="22">
+      <c r="G44" s="23">
         <v>2.0</v>
       </c>
-      <c r="H44" s="17" t="s">
+      <c r="H44" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="I44" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J44" s="17" t="s">
-        <v>23</v>
+      <c r="I44" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J44" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
-      <c r="A45" s="17" t="s">
+      <c r="A45" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B45" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C45" s="17" t="s">
+      <c r="B45" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F45" s="22">
+      <c r="F45" s="23">
         <v>1.0</v>
       </c>
       <c r="G45" s="25">
         <v>1.0</v>
       </c>
-      <c r="H45" s="17" t="s">
+      <c r="H45" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="I45" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J45" s="17" t="s">
-        <v>23</v>
+      <c r="I45" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J45" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
@@ -3902,7 +3902,7 @@
         <v>180</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>181</v>
@@ -3925,10 +3925,10 @@
         <v>182</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K46" s="24"/>
       <c r="L46" s="24"/>
@@ -3946,99 +3946,99 @@
       <c r="X46" s="24"/>
     </row>
     <row r="47" ht="22.5" customHeight="1">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="B47" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C47" s="17" t="s">
+      <c r="B47" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="D47" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E47" s="20" t="s">
+      <c r="D47" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E47" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F47" s="22">
+      <c r="F47" s="23">
         <v>2.0</v>
       </c>
-      <c r="G47" s="22">
+      <c r="G47" s="23">
         <v>2.0</v>
       </c>
-      <c r="H47" s="17" t="s">
+      <c r="H47" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="I47" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J47" s="17" t="s">
-        <v>23</v>
+      <c r="I47" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
-      <c r="A48" s="17" t="s">
+      <c r="A48" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C48" s="17" t="s">
+      <c r="B48" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F48" s="22">
+      <c r="F48" s="23">
         <v>1.0</v>
       </c>
-      <c r="G48" s="22">
+      <c r="G48" s="23">
         <v>1.0</v>
       </c>
-      <c r="H48" s="17" t="s">
+      <c r="H48" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="I48" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J48" s="17" t="s">
-        <v>23</v>
+      <c r="I48" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J48" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
-      <c r="A49" s="17" t="s">
+      <c r="A49" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="B49" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C49" s="17" t="s">
+      <c r="B49" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F49" s="22">
+      <c r="F49" s="23">
         <v>3.0</v>
       </c>
       <c r="G49" s="25">
         <v>2.0</v>
       </c>
-      <c r="H49" s="17" t="s">
+      <c r="H49" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="I49" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J49" s="17" t="s">
-        <v>23</v>
+      <c r="I49" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J49" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
@@ -4046,7 +4046,7 @@
         <v>193</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>194</v>
@@ -4055,13 +4055,13 @@
         <v>195</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="14">
+        <v>24</v>
+      </c>
+      <c r="F50" s="15">
         <f t="shared" ref="F50:G50" si="12">F51</f>
         <v>2</v>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="15">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
@@ -4069,10 +4069,10 @@
         <v>196</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K50" s="24"/>
       <c r="L50" s="24"/>
@@ -4094,7 +4094,7 @@
         <v>197</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>198</v>
@@ -4103,7 +4103,7 @@
         <v>195</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F51" s="26">
         <f t="shared" ref="F51:G51" si="13">SUM(F52:F53)</f>
@@ -4117,10 +4117,10 @@
         <v>199</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K51" s="24"/>
       <c r="L51" s="24"/>
@@ -4138,67 +4138,67 @@
       <c r="X51" s="24"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
-      <c r="A52" s="17" t="s">
+      <c r="A52" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="B52" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C52" s="17" t="s">
+      <c r="B52" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="D52" s="19" t="s">
+      <c r="D52" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F52" s="22">
+      <c r="E52" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="23">
         <v>1.0</v>
       </c>
-      <c r="G52" s="22">
+      <c r="G52" s="23">
         <v>1.0</v>
       </c>
-      <c r="H52" s="17" t="s">
+      <c r="H52" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="I52" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J52" s="17" t="s">
-        <v>23</v>
+      <c r="I52" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J52" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="B53" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C53" s="17" t="s">
+      <c r="B53" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D53" s="19" t="s">
+      <c r="D53" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E53" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F53" s="22">
+      <c r="E53" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" s="23">
         <v>1.0</v>
       </c>
       <c r="G53" s="25">
         <v>1.0</v>
       </c>
-      <c r="H53" s="17" t="s">
+      <c r="H53" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="I53" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J53" s="17" t="s">
-        <v>23</v>
+      <c r="I53" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J53" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
@@ -4206,7 +4206,7 @@
         <v>206</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>207</v>
@@ -4215,13 +4215,13 @@
         <v>89</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F54" s="14">
+        <v>24</v>
+      </c>
+      <c r="F54" s="15">
         <f t="shared" ref="F54:G54" si="14">F55+F61+F66+F71+F80</f>
         <v>32</v>
       </c>
-      <c r="G54" s="14">
+      <c r="G54" s="15">
         <f t="shared" si="14"/>
         <v>42</v>
       </c>
@@ -4229,10 +4229,10 @@
         <v>208</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K54" s="24"/>
       <c r="L54" s="24"/>
@@ -4254,7 +4254,7 @@
         <v>209</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C55" s="11" t="s">
         <v>210</v>
@@ -4263,7 +4263,7 @@
         <v>89</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F55" s="26">
         <f t="shared" ref="F55:G55" si="15">SUM(F56:F60)</f>
@@ -4277,10 +4277,10 @@
         <v>211</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K55" s="24"/>
       <c r="L55" s="24"/>
@@ -4298,163 +4298,163 @@
       <c r="X55" s="24"/>
     </row>
     <row r="56" ht="22.5" customHeight="1">
-      <c r="A56" s="17" t="s">
+      <c r="A56" s="20" t="s">
         <v>212</v>
       </c>
-      <c r="B56" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C56" s="17" t="s">
+      <c r="B56" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="D56" s="19" t="s">
+      <c r="D56" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E56" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F56" s="22">
+      <c r="E56" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="23">
         <v>1.0</v>
       </c>
-      <c r="G56" s="22">
+      <c r="G56" s="23">
         <v>1.0</v>
       </c>
-      <c r="H56" s="17" t="s">
+      <c r="H56" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="I56" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J56" s="17" t="s">
-        <v>23</v>
+      <c r="I56" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J56" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
-      <c r="A57" s="17" t="s">
+      <c r="A57" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="B57" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C57" s="17" t="s">
+      <c r="B57" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="D57" s="19" t="s">
+      <c r="D57" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E57" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F57" s="22">
+      <c r="E57" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F57" s="23">
         <v>1.0</v>
       </c>
-      <c r="G57" s="22">
+      <c r="G57" s="23">
         <v>1.0</v>
       </c>
-      <c r="H57" s="17" t="s">
+      <c r="H57" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="I57" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J57" s="17" t="s">
-        <v>23</v>
+      <c r="I57" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J57" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="20" t="s">
         <v>218</v>
       </c>
-      <c r="B58" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C58" s="17" t="s">
+      <c r="B58" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="20" t="s">
         <v>219</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="D58" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E58" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F58" s="22">
+      <c r="E58" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" s="23">
         <v>1.0</v>
       </c>
-      <c r="G58" s="22">
+      <c r="G58" s="23">
         <v>1.0</v>
       </c>
-      <c r="H58" s="17" t="s">
+      <c r="H58" s="20" t="s">
         <v>220</v>
       </c>
-      <c r="I58" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J58" s="17" t="s">
-        <v>23</v>
+      <c r="I58" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J58" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="20" t="s">
         <v>221</v>
       </c>
-      <c r="B59" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C59" s="17" t="s">
+      <c r="B59" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="D59" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F59" s="22">
+      <c r="F59" s="23">
         <v>1.0</v>
       </c>
       <c r="G59" s="25">
         <v>1.0</v>
       </c>
-      <c r="H59" s="17" t="s">
+      <c r="H59" s="20" t="s">
         <v>223</v>
       </c>
-      <c r="I59" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J59" s="17" t="s">
-        <v>23</v>
+      <c r="I59" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J59" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="B60" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C60" s="17" t="s">
+      <c r="B60" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="D60" s="19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F60" s="22">
+      <c r="D60" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F60" s="23">
         <v>1.0</v>
       </c>
-      <c r="G60" s="22">
+      <c r="G60" s="23">
         <v>1.0</v>
       </c>
-      <c r="H60" s="17" t="s">
+      <c r="H60" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="I60" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J60" s="17" t="s">
-        <v>23</v>
+      <c r="I60" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J60" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
@@ -4462,7 +4462,7 @@
         <v>227</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>228</v>
@@ -4471,7 +4471,7 @@
         <v>89</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F61" s="26">
         <f t="shared" ref="F61:G61" si="16">SUM(F62:F65)</f>
@@ -4485,10 +4485,10 @@
         <v>229</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K61" s="24"/>
       <c r="L61" s="24"/>
@@ -4506,131 +4506,131 @@
       <c r="X61" s="24"/>
     </row>
     <row r="62" ht="22.5" customHeight="1">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="B62" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C62" s="17" t="s">
+      <c r="B62" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D62" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F62" s="22">
+      <c r="E62" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="23">
         <v>2.0</v>
       </c>
-      <c r="G62" s="22">
+      <c r="G62" s="23">
         <v>2.0</v>
       </c>
-      <c r="H62" s="17" t="s">
+      <c r="H62" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="I62" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J62" s="17" t="s">
-        <v>23</v>
+      <c r="I62" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J62" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
-      <c r="A63" s="17" t="s">
+      <c r="A63" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="B63" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C63" s="17" t="s">
+      <c r="B63" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" s="20" t="s">
         <v>234</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E63" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F63" s="22">
+      <c r="E63" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" s="23">
         <v>1.0</v>
       </c>
       <c r="G63" s="25">
         <v>1.0</v>
       </c>
-      <c r="H63" s="17" t="s">
+      <c r="H63" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="I63" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J63" s="17" t="s">
-        <v>23</v>
+      <c r="I63" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J63" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
-      <c r="A64" s="17" t="s">
+      <c r="A64" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="B64" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C64" s="17" t="s">
+      <c r="B64" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E64" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F64" s="22">
+      <c r="E64" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" s="23">
         <v>2.0</v>
       </c>
-      <c r="G64" s="22">
+      <c r="G64" s="23">
         <v>2.0</v>
       </c>
-      <c r="H64" s="17" t="s">
+      <c r="H64" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="I64" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J64" s="17" t="s">
-        <v>23</v>
+      <c r="I64" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
-      <c r="A65" s="17" t="s">
+      <c r="A65" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B65" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65" s="17" t="s">
+      <c r="B65" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="20" t="s">
         <v>240</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="D65" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F65" s="22">
+      <c r="F65" s="23">
         <v>2.0</v>
       </c>
-      <c r="G65" s="22">
+      <c r="G65" s="23">
         <v>2.0</v>
       </c>
-      <c r="H65" s="17" t="s">
+      <c r="H65" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="I65" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" s="17" t="s">
-        <v>23</v>
+      <c r="I65" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J65" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
@@ -4638,7 +4638,7 @@
         <v>242</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>243</v>
@@ -4647,7 +4647,7 @@
         <v>89</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F66" s="26">
         <f t="shared" ref="F66:G66" si="17">SUM(F67:F70)</f>
@@ -4661,10 +4661,10 @@
         <v>244</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K66" s="24"/>
       <c r="L66" s="24"/>
@@ -4682,131 +4682,131 @@
       <c r="X66" s="24"/>
     </row>
     <row r="67" ht="22.5" customHeight="1">
-      <c r="A67" s="17" t="s">
+      <c r="A67" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="B67" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C67" s="17" t="s">
+      <c r="B67" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="D67" s="19" t="s">
+      <c r="D67" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E67" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F67" s="22">
+      <c r="E67" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="23">
         <v>2.0</v>
       </c>
       <c r="G67" s="25">
         <v>2.0</v>
       </c>
-      <c r="H67" s="17" t="s">
+      <c r="H67" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="I67" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" s="17" t="s">
-        <v>23</v>
+      <c r="I67" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J67" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="17" t="s">
+      <c r="A68" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="B68" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C68" s="17" t="s">
+      <c r="B68" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="D68" s="19" t="s">
+      <c r="D68" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E68" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F68" s="22">
+      <c r="E68" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F68" s="23">
         <v>1.0</v>
       </c>
-      <c r="G68" s="22">
+      <c r="G68" s="23">
         <v>1.0</v>
       </c>
-      <c r="H68" s="17" t="s">
+      <c r="H68" s="20" t="s">
         <v>250</v>
       </c>
-      <c r="I68" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J68" s="17" t="s">
-        <v>23</v>
+      <c r="I68" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J68" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="17" t="s">
+      <c r="A69" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="B69" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C69" s="17" t="s">
+      <c r="B69" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="D69" s="19" t="s">
+      <c r="D69" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E69" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F69" s="22">
+      <c r="E69" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F69" s="23">
         <v>1.0</v>
       </c>
-      <c r="G69" s="22">
+      <c r="G69" s="23">
         <v>1.0</v>
       </c>
-      <c r="H69" s="17" t="s">
+      <c r="H69" s="20" t="s">
         <v>253</v>
       </c>
-      <c r="I69" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J69" s="17" t="s">
-        <v>23</v>
+      <c r="I69" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J69" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="17" t="s">
+      <c r="A70" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="B70" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C70" s="17" t="s">
+      <c r="B70" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="D70" s="19" t="s">
+      <c r="D70" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E70" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F70" s="22">
+      <c r="E70" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F70" s="23">
         <v>2.0</v>
       </c>
-      <c r="G70" s="22">
+      <c r="G70" s="23">
         <v>2.0</v>
       </c>
-      <c r="H70" s="17" t="s">
+      <c r="H70" s="20" t="s">
         <v>256</v>
       </c>
-      <c r="I70" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J70" s="17" t="s">
-        <v>23</v>
+      <c r="I70" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J70" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
@@ -4814,7 +4814,7 @@
         <v>257</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>258</v>
@@ -4823,13 +4823,13 @@
         <v>89</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F71" s="14">
+        <v>24</v>
+      </c>
+      <c r="F71" s="15">
         <f t="shared" ref="F71:G71" si="18">SUM(F72:F79)</f>
         <v>10</v>
       </c>
-      <c r="G71" s="14">
+      <c r="G71" s="15">
         <f t="shared" si="18"/>
         <v>14</v>
       </c>
@@ -4837,10 +4837,10 @@
         <v>259</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
@@ -4858,259 +4858,259 @@
       <c r="X71" s="24"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="17" t="s">
+      <c r="A72" s="20" t="s">
         <v>260</v>
       </c>
-      <c r="B72" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C72" s="17" t="s">
+      <c r="B72" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="D72" s="19" t="s">
+      <c r="D72" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F72" s="22">
+      <c r="E72" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F72" s="23">
         <v>2.0</v>
       </c>
-      <c r="G72" s="22">
+      <c r="G72" s="23">
         <v>2.0</v>
       </c>
-      <c r="H72" s="17" t="s">
+      <c r="H72" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="I72" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J72" s="17" t="s">
-        <v>23</v>
+      <c r="I72" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J72" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
-      <c r="A73" s="17" t="s">
+      <c r="A73" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="B73" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C73" s="17" t="s">
+      <c r="B73" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C73" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="D73" s="19" t="s">
+      <c r="D73" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E73" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F73" s="22">
+      <c r="E73" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="23">
         <v>2.0</v>
       </c>
-      <c r="G73" s="22">
+      <c r="G73" s="23">
         <v>5.0</v>
       </c>
-      <c r="H73" s="17" t="s">
+      <c r="H73" s="20" t="s">
         <v>265</v>
       </c>
-      <c r="I73" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J73" s="17" t="s">
-        <v>23</v>
+      <c r="I73" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J73" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="B74" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C74" s="17" t="s">
+      <c r="B74" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" s="20" t="s">
         <v>267</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D74" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E74" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F74" s="22">
+      <c r="E74" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F74" s="23">
         <v>1.0</v>
       </c>
       <c r="G74" s="25">
         <v>1.0</v>
       </c>
-      <c r="H74" s="17" t="s">
+      <c r="H74" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I74" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J74" s="17" t="s">
-        <v>23</v>
+      <c r="I74" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J74" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="B75" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C75" s="17" t="s">
+      <c r="B75" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="D75" s="19" t="s">
+      <c r="D75" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E75" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F75" s="22">
+      <c r="E75" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="23">
         <v>1.0</v>
       </c>
       <c r="G75" s="25">
         <v>1.0</v>
       </c>
-      <c r="H75" s="17" t="s">
+      <c r="H75" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I75" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J75" s="17" t="s">
-        <v>23</v>
+      <c r="I75" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J75" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="B76" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C76" s="17" t="s">
+      <c r="B76" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C76" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D76" s="19" t="s">
+      <c r="D76" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E76" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F76" s="22">
+      <c r="E76" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="23">
         <v>1.0</v>
       </c>
-      <c r="G76" s="22">
+      <c r="G76" s="23">
         <v>1.0</v>
       </c>
-      <c r="H76" s="17" t="s">
+      <c r="H76" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I76" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J76" s="17" t="s">
-        <v>23</v>
+      <c r="I76" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J76" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="17" t="s">
+      <c r="A77" s="20" t="s">
         <v>273</v>
       </c>
-      <c r="B77" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C77" s="17" t="s">
+      <c r="B77" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C77" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="D77" s="19" t="s">
+      <c r="D77" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E77" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F77" s="22">
+      <c r="E77" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="23">
         <v>1.0</v>
       </c>
-      <c r="G77" s="22">
+      <c r="G77" s="23">
         <v>1.0</v>
       </c>
-      <c r="H77" s="17" t="s">
+      <c r="H77" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I77" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J77" s="17" t="s">
-        <v>23</v>
+      <c r="I77" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J77" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="17" t="s">
+      <c r="A78" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="B78" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C78" s="17" t="s">
+      <c r="B78" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C78" s="20" t="s">
         <v>276</v>
       </c>
-      <c r="D78" s="19" t="s">
+      <c r="D78" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E78" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F78" s="22">
+      <c r="E78" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F78" s="23">
         <v>1.0</v>
       </c>
-      <c r="G78" s="22">
+      <c r="G78" s="23">
         <v>1.0</v>
       </c>
-      <c r="H78" s="17" t="s">
+      <c r="H78" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="I78" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J78" s="17" t="s">
-        <v>23</v>
+      <c r="I78" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J78" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="17" t="s">
+      <c r="A79" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="B79" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C79" s="17" t="s">
+      <c r="B79" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="D79" s="19" t="s">
+      <c r="D79" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E79" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F79" s="22">
+      <c r="E79" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="23">
         <v>1.0</v>
       </c>
-      <c r="G79" s="22">
+      <c r="G79" s="23">
         <v>2.0</v>
       </c>
-      <c r="H79" s="17" t="s">
+      <c r="H79" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="I79" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J79" s="17" t="s">
-        <v>23</v>
+      <c r="I79" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J79" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
@@ -5118,7 +5118,7 @@
         <v>280</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>281</v>
@@ -5127,13 +5127,13 @@
         <v>89</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F80" s="14">
+        <v>24</v>
+      </c>
+      <c r="F80" s="15">
         <f t="shared" ref="F80:G80" si="19">SUM(F81:F83)</f>
         <v>4</v>
       </c>
-      <c r="G80" s="14">
+      <c r="G80" s="15">
         <f t="shared" si="19"/>
         <v>10</v>
       </c>
@@ -5141,10 +5141,10 @@
         <v>282</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J80" s="11" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K80" s="24"/>
       <c r="L80" s="24"/>
@@ -5162,99 +5162,99 @@
       <c r="X80" s="24"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="17" t="s">
+      <c r="A81" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="B81" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C81" s="17" t="s">
+      <c r="B81" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C81" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="D81" s="19" t="s">
+      <c r="D81" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E81" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F81" s="22">
+      <c r="E81" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F81" s="23">
         <v>2.0</v>
       </c>
-      <c r="G81" s="22">
+      <c r="G81" s="23">
         <v>8.0</v>
       </c>
-      <c r="H81" s="17" t="s">
+      <c r="H81" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="I81" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J81" s="17" t="s">
-        <v>23</v>
+      <c r="I81" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J81" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="17" t="s">
+      <c r="A82" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="B82" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C82" s="17" t="s">
+      <c r="B82" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C82" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="D82" s="19" t="s">
+      <c r="D82" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E82" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F82" s="22">
+      <c r="E82" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F82" s="23">
         <v>1.0</v>
       </c>
-      <c r="G82" s="22">
+      <c r="G82" s="23">
         <v>1.0</v>
       </c>
-      <c r="H82" s="17" t="s">
+      <c r="H82" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="I82" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J82" s="17" t="s">
-        <v>23</v>
+      <c r="I82" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J82" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="17" t="s">
+      <c r="A83" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="B83" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C83" s="17" t="s">
+      <c r="B83" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C83" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="D83" s="19" t="s">
+      <c r="D83" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E83" s="20" t="s">
+      <c r="E83" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F83" s="22">
+      <c r="F83" s="23">
         <v>1.0</v>
       </c>
-      <c r="G83" s="22">
+      <c r="G83" s="23">
         <v>1.0</v>
       </c>
-      <c r="H83" s="17" t="s">
+      <c r="H83" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="I83" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="J83" s="17" t="s">
-        <v>23</v>
+      <c r="I83" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="J83" s="20" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
@@ -5262,7 +5262,7 @@
         <v>292</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>293</v>
@@ -5271,7 +5271,7 @@
         <v>50</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F84" s="27">
         <v>47.0</v>
@@ -5284,10 +5284,10 @@
         <v>294</v>
       </c>
       <c r="I84" s="28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J84" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K84" s="24"/>
       <c r="L84" s="24"/>
@@ -5309,7 +5309,7 @@
         <v>295</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C85" s="11" t="s">
         <v>296</v>
@@ -5318,13 +5318,13 @@
         <v>50</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F85" s="14">
+        <v>24</v>
+      </c>
+      <c r="F85" s="15">
         <f t="shared" ref="F85:G85" si="20">SUM(F86:F89)</f>
         <v>5</v>
       </c>
-      <c r="G85" s="14">
+      <c r="G85" s="15">
         <f t="shared" si="20"/>
         <v>5</v>
       </c>
@@ -5332,10 +5332,10 @@
         <v>297</v>
       </c>
       <c r="I85" s="28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J85" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K85" s="24"/>
       <c r="L85" s="24"/>
@@ -5353,22 +5353,22 @@
       <c r="X85" s="24"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="17" t="s">
+      <c r="A86" s="20" t="s">
         <v>298</v>
       </c>
-      <c r="B86" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C86" s="17" t="s">
+      <c r="B86" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C86" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="D86" s="19" t="s">
+      <c r="D86" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E86" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F86" s="22">
+      <c r="E86" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" s="23">
         <v>1.0</v>
       </c>
       <c r="G86" s="30">
@@ -5378,29 +5378,29 @@
         <v>300</v>
       </c>
       <c r="I86" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J86" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J86" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="17" t="s">
+      <c r="A87" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="B87" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C87" s="17" t="s">
+      <c r="B87" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C87" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="D87" s="19" t="s">
+      <c r="D87" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E87" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F87" s="22">
+      <c r="E87" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" s="23">
         <v>1.0</v>
       </c>
       <c r="G87" s="30">
@@ -5410,29 +5410,29 @@
         <v>303</v>
       </c>
       <c r="I87" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J87" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J87" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="17" t="s">
+      <c r="A88" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="B88" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C88" s="17" t="s">
+      <c r="B88" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C88" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="D88" s="19" t="s">
+      <c r="D88" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E88" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F88" s="22">
+      <c r="E88" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="23">
         <v>2.0</v>
       </c>
       <c r="G88" s="30">
@@ -5442,29 +5442,29 @@
         <v>306</v>
       </c>
       <c r="I88" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J88" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J88" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="17" t="s">
+      <c r="A89" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="B89" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C89" s="17" t="s">
+      <c r="B89" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C89" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="D89" s="19" t="s">
+      <c r="D89" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E89" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F89" s="22">
+      <c r="E89" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F89" s="23">
         <v>1.0</v>
       </c>
       <c r="G89" s="30">
@@ -5474,10 +5474,10 @@
         <v>309</v>
       </c>
       <c r="I89" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J89" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J89" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1">
@@ -5485,7 +5485,7 @@
         <v>310</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C90" s="11" t="s">
         <v>311</v>
@@ -5494,13 +5494,13 @@
         <v>50</v>
       </c>
       <c r="E90" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F90" s="14">
+        <v>24</v>
+      </c>
+      <c r="F90" s="15">
         <f t="shared" ref="F90:G90" si="21">SUM(F91:F95)</f>
         <v>11</v>
       </c>
-      <c r="G90" s="14">
+      <c r="G90" s="15">
         <f t="shared" si="21"/>
         <v>7</v>
       </c>
@@ -5508,10 +5508,10 @@
         <v>312</v>
       </c>
       <c r="I90" s="28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J90" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K90" s="24"/>
       <c r="L90" s="24"/>
@@ -5529,131 +5529,131 @@
       <c r="X90" s="24"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="17" t="s">
+      <c r="A91" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="B91" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C91" s="17" t="s">
+      <c r="B91" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C91" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="D91" s="19" t="s">
+      <c r="D91" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E91" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F91" s="22">
+      <c r="E91" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="23">
         <v>2.0</v>
       </c>
       <c r="G91" s="30">
         <v>1.0</v>
       </c>
-      <c r="H91" s="17" t="s">
+      <c r="H91" s="20" t="s">
         <v>315</v>
       </c>
       <c r="I91" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J91" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J91" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="17" t="s">
+      <c r="A92" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="B92" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C92" s="17" t="s">
+      <c r="B92" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="D92" s="19" t="s">
+      <c r="D92" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E92" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F92" s="22">
+      <c r="E92" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="23">
         <v>3.0</v>
       </c>
       <c r="G92" s="30">
         <v>2.0</v>
       </c>
-      <c r="H92" s="17" t="s">
+      <c r="H92" s="20" t="s">
         <v>318</v>
       </c>
       <c r="I92" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J92" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J92" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="17" t="s">
+      <c r="A93" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="B93" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C93" s="17" t="s">
+      <c r="B93" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C93" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="D93" s="19" t="s">
+      <c r="D93" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E93" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F93" s="22">
+      <c r="E93" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="23">
         <v>2.0</v>
       </c>
       <c r="G93" s="30">
         <v>1.0</v>
       </c>
-      <c r="H93" s="17" t="s">
+      <c r="H93" s="20" t="s">
         <v>321</v>
       </c>
       <c r="I93" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J93" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J93" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="17" t="s">
+      <c r="A94" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="B94" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C94" s="17" t="s">
+      <c r="B94" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C94" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="D94" s="19" t="s">
+      <c r="D94" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E94" s="20" t="s">
+      <c r="E94" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F94" s="22">
+      <c r="F94" s="23">
         <v>2.0</v>
       </c>
       <c r="G94" s="33">
         <v>1.0</v>
       </c>
-      <c r="H94" s="17" t="s">
+      <c r="H94" s="20" t="s">
         <v>324</v>
       </c>
       <c r="I94" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J94" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J94" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
@@ -5661,7 +5661,7 @@
         <v>325</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C95" s="31" t="s">
         <v>326</v>
@@ -5670,7 +5670,7 @@
         <v>50</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F95" s="30">
         <v>2.0</v>
@@ -5682,10 +5682,10 @@
         <v>327</v>
       </c>
       <c r="I95" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J95" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
@@ -5693,7 +5693,7 @@
         <v>328</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C96" s="11" t="s">
         <v>329</v>
@@ -5702,13 +5702,13 @@
         <v>50</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F96" s="14">
+        <v>24</v>
+      </c>
+      <c r="F96" s="15">
         <f t="shared" ref="F96:G96" si="22">SUM(F97:F101)</f>
         <v>8</v>
       </c>
-      <c r="G96" s="14">
+      <c r="G96" s="15">
         <f t="shared" si="22"/>
         <v>8</v>
       </c>
@@ -5716,10 +5716,10 @@
         <v>330</v>
       </c>
       <c r="I96" s="28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J96" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K96" s="24"/>
       <c r="L96" s="24"/>
@@ -5737,131 +5737,131 @@
       <c r="X96" s="24"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="17" t="s">
+      <c r="A97" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="B97" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C97" s="17" t="s">
+      <c r="B97" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C97" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="D97" s="19" t="s">
+      <c r="D97" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E97" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F97" s="22">
+      <c r="E97" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="23">
         <v>3.0</v>
       </c>
       <c r="G97" s="30">
         <v>2.0</v>
       </c>
-      <c r="H97" s="17" t="s">
+      <c r="H97" s="20" t="s">
         <v>333</v>
       </c>
       <c r="I97" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J97" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J97" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="17" t="s">
+      <c r="A98" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="B98" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C98" s="17" t="s">
+      <c r="B98" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C98" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="D98" s="19" t="s">
+      <c r="D98" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E98" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F98" s="22">
+      <c r="E98" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" s="23">
         <v>2.0</v>
       </c>
       <c r="G98" s="30">
         <v>2.0</v>
       </c>
-      <c r="H98" s="17" t="s">
+      <c r="H98" s="20" t="s">
         <v>336</v>
       </c>
       <c r="I98" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J98" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J98" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="17" t="s">
+      <c r="A99" s="20" t="s">
         <v>337</v>
       </c>
-      <c r="B99" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C99" s="17" t="s">
+      <c r="B99" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C99" s="20" t="s">
         <v>338</v>
       </c>
-      <c r="D99" s="19" t="s">
+      <c r="D99" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E99" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F99" s="22">
+      <c r="E99" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="23">
         <v>1.0</v>
       </c>
       <c r="G99" s="30">
         <v>1.0</v>
       </c>
-      <c r="H99" s="17" t="s">
+      <c r="H99" s="20" t="s">
         <v>339</v>
       </c>
       <c r="I99" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J99" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J99" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="17" t="s">
+      <c r="A100" s="20" t="s">
         <v>340</v>
       </c>
-      <c r="B100" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C100" s="17" t="s">
+      <c r="B100" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C100" s="20" t="s">
         <v>341</v>
       </c>
-      <c r="D100" s="19" t="s">
+      <c r="D100" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E100" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F100" s="22">
+      <c r="E100" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="23">
         <v>1.0</v>
       </c>
       <c r="G100" s="30">
         <v>1.0</v>
       </c>
-      <c r="H100" s="17" t="s">
+      <c r="H100" s="20" t="s">
         <v>342</v>
       </c>
       <c r="I100" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J100" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J100" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
@@ -5869,7 +5869,7 @@
         <v>343</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C101" s="31" t="s">
         <v>344</v>
@@ -5878,7 +5878,7 @@
         <v>50</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F101" s="30">
         <v>1.0</v>
@@ -5890,10 +5890,10 @@
         <v>345</v>
       </c>
       <c r="I101" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J101" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
@@ -5901,7 +5901,7 @@
         <v>346</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C102" s="11" t="s">
         <v>347</v>
@@ -5910,12 +5910,12 @@
         <v>99</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F102" s="27">
         <v>12.0</v>
       </c>
-      <c r="G102" s="14">
+      <c r="G102" s="15">
         <f>SUM(G103:G106)</f>
         <v>7</v>
       </c>
@@ -5923,10 +5923,10 @@
         <v>348</v>
       </c>
       <c r="I102" s="28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J102" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K102" s="24"/>
       <c r="L102" s="24"/>
@@ -5944,86 +5944,86 @@
       <c r="X102" s="24"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="17" t="s">
+      <c r="A103" s="20" t="s">
         <v>349</v>
       </c>
-      <c r="B103" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C103" s="17" t="s">
+      <c r="B103" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C103" s="20" t="s">
         <v>350</v>
       </c>
-      <c r="D103" s="19" t="s">
+      <c r="D103" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E103" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F103" s="22">
+      <c r="E103" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" s="23">
         <v>2.0</v>
       </c>
       <c r="G103" s="30">
         <v>1.0</v>
       </c>
-      <c r="H103" s="17" t="s">
+      <c r="H103" s="20" t="s">
         <v>351</v>
       </c>
       <c r="I103" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J103" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J103" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="17" t="s">
+      <c r="A104" s="20" t="s">
         <v>352</v>
       </c>
-      <c r="B104" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C104" s="17" t="s">
+      <c r="B104" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C104" s="20" t="s">
         <v>353</v>
       </c>
-      <c r="D104" s="19" t="s">
+      <c r="D104" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E104" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F104" s="22">
+      <c r="E104" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F104" s="23">
         <v>3.0</v>
       </c>
       <c r="G104" s="30">
         <v>2.0</v>
       </c>
-      <c r="H104" s="17" t="s">
+      <c r="H104" s="20" t="s">
         <v>354</v>
       </c>
       <c r="I104" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J104" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J104" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="17" t="s">
+      <c r="A105" s="20" t="s">
         <v>355</v>
       </c>
-      <c r="B105" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C105" s="17" t="s">
+      <c r="B105" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C105" s="20" t="s">
         <v>356</v>
       </c>
-      <c r="D105" s="19" t="s">
+      <c r="D105" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E105" s="20" t="s">
+      <c r="E105" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F105" s="22">
+      <c r="F105" s="23">
         <v>3.0</v>
       </c>
       <c r="G105" s="30">
@@ -6033,10 +6033,10 @@
         <v>357</v>
       </c>
       <c r="I105" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J105" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J105" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
@@ -6044,7 +6044,7 @@
         <v>358</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C106" s="31" t="s">
         <v>359</v>
@@ -6053,7 +6053,7 @@
         <v>99</v>
       </c>
       <c r="E106" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F106" s="30">
         <v>2.0</v>
@@ -6065,10 +6065,10 @@
         <v>360</v>
       </c>
       <c r="I106" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J106" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
@@ -6076,7 +6076,7 @@
         <v>361</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C107" s="31" t="s">
         <v>362</v>
@@ -6085,7 +6085,7 @@
         <v>99</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F107" s="30">
         <v>2.0</v>
@@ -6097,10 +6097,10 @@
         <v>363</v>
       </c>
       <c r="I107" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J107" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
@@ -6108,7 +6108,7 @@
         <v>364</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C108" s="29" t="s">
         <v>365</v>
@@ -6117,13 +6117,13 @@
         <v>99</v>
       </c>
       <c r="E108" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F108" s="26">
         <f t="shared" ref="F108:G108" si="23">SUM(F109)</f>
         <v>6</v>
       </c>
-      <c r="G108" s="14">
+      <c r="G108" s="15">
         <f t="shared" si="23"/>
         <v>4</v>
       </c>
@@ -6131,10 +6131,10 @@
         <v>366</v>
       </c>
       <c r="I108" s="28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J108" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
@@ -6142,7 +6142,7 @@
         <v>367</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C109" s="31" t="s">
         <v>368</v>
@@ -6151,7 +6151,7 @@
         <v>99</v>
       </c>
       <c r="E109" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F109" s="30">
         <v>6.0</v>
@@ -6163,10 +6163,10 @@
         <v>369</v>
       </c>
       <c r="I109" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J109" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
@@ -6174,7 +6174,7 @@
         <v>370</v>
       </c>
       <c r="B110" s="29" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C110" s="29" t="s">
         <v>371</v>
@@ -6183,7 +6183,7 @@
         <v>99</v>
       </c>
       <c r="E110" s="28" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F110" s="27">
         <v>5.0</v>
@@ -6195,10 +6195,10 @@
         <v>372</v>
       </c>
       <c r="I110" s="28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J110" s="29" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
@@ -6206,7 +6206,7 @@
         <v>373</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C111" s="31" t="s">
         <v>374</v>
@@ -6215,7 +6215,7 @@
         <v>99</v>
       </c>
       <c r="E111" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F111" s="30">
         <v>2.0</v>
@@ -6227,10 +6227,10 @@
         <v>375</v>
       </c>
       <c r="I111" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J111" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
@@ -6238,7 +6238,7 @@
         <v>376</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C112" s="31" t="s">
         <v>377</v>
@@ -6247,7 +6247,7 @@
         <v>99</v>
       </c>
       <c r="E112" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F112" s="30">
         <v>2.0</v>
@@ -6259,10 +6259,10 @@
         <v>378</v>
       </c>
       <c r="I112" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J112" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
@@ -6270,7 +6270,7 @@
         <v>379</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C113" s="31" t="s">
         <v>380</v>
@@ -6279,7 +6279,7 @@
         <v>99</v>
       </c>
       <c r="E113" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F113" s="30">
         <v>1.0</v>
@@ -6291,10 +6291,10 @@
         <v>381</v>
       </c>
       <c r="I113" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J113" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
@@ -6302,7 +6302,7 @@
         <v>382</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C114" s="11" t="s">
         <v>383</v>
@@ -6311,14 +6311,14 @@
         <v>99</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F114" s="27">
         <v>72.0</v>
       </c>
-      <c r="G114" s="14">
+      <c r="G114" s="15">
         <f>G115+G123+G129+G134+G141</f>
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="H114" s="11" t="s">
         <v>384</v>
@@ -6327,7 +6327,7 @@
         <v>385</v>
       </c>
       <c r="J114" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K114" s="24"/>
       <c r="L114" s="24"/>
@@ -6349,7 +6349,7 @@
         <v>386</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C115" s="11" t="s">
         <v>387</v>
@@ -6358,7 +6358,7 @@
         <v>50</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F115" s="27">
         <v>24.0</v>
@@ -6371,10 +6371,10 @@
         <v>388</v>
       </c>
       <c r="I115" s="28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J115" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K115" s="24"/>
       <c r="L115" s="24"/>
@@ -6392,118 +6392,118 @@
       <c r="X115" s="24"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="17" t="s">
+      <c r="A116" s="20" t="s">
         <v>389</v>
       </c>
-      <c r="B116" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C116" s="17" t="s">
+      <c r="B116" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="D116" s="19" t="s">
+      <c r="D116" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E116" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F116" s="22">
+      <c r="E116" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F116" s="23">
         <v>3.0</v>
       </c>
       <c r="G116" s="30">
         <v>2.0</v>
       </c>
-      <c r="H116" s="17" t="s">
+      <c r="H116" s="20" t="s">
         <v>391</v>
       </c>
       <c r="I116" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J116" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J116" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="17" t="s">
+      <c r="A117" s="20" t="s">
         <v>392</v>
       </c>
-      <c r="B117" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C117" s="17" t="s">
+      <c r="B117" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C117" s="20" t="s">
         <v>393</v>
       </c>
-      <c r="D117" s="19" t="s">
+      <c r="D117" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E117" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F117" s="22">
+      <c r="E117" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F117" s="23">
         <v>6.0</v>
       </c>
       <c r="G117" s="30">
         <v>8.0</v>
       </c>
-      <c r="H117" s="17" t="s">
+      <c r="H117" s="20" t="s">
         <v>394</v>
       </c>
       <c r="I117" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J117" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J117" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="17" t="s">
+      <c r="A118" s="20" t="s">
         <v>395</v>
       </c>
-      <c r="B118" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C118" s="17" t="s">
+      <c r="B118" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C118" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="D118" s="19" t="s">
+      <c r="D118" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E118" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F118" s="22">
+      <c r="E118" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F118" s="23">
         <v>1.0</v>
       </c>
       <c r="G118" s="33">
         <v>1.0</v>
       </c>
-      <c r="H118" s="17" t="s">
+      <c r="H118" s="20" t="s">
         <v>397</v>
       </c>
       <c r="I118" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J118" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J118" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="17" t="s">
+      <c r="A119" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="B119" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C119" s="17" t="s">
+      <c r="B119" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C119" s="20" t="s">
         <v>399</v>
       </c>
-      <c r="D119" s="19" t="s">
+      <c r="D119" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E119" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F119" s="22">
+      <c r="E119" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F119" s="23">
         <v>3.0</v>
       </c>
       <c r="G119" s="30">
@@ -6513,10 +6513,10 @@
         <v>400</v>
       </c>
       <c r="I119" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J119" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J119" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="120" ht="15.75" customHeight="1">
@@ -6524,7 +6524,7 @@
         <v>401</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C120" s="31" t="s">
         <v>402</v>
@@ -6533,7 +6533,7 @@
         <v>50</v>
       </c>
       <c r="E120" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F120" s="30">
         <v>5.0</v>
@@ -6545,10 +6545,10 @@
         <v>403</v>
       </c>
       <c r="I120" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J120" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="121" ht="15.75" customHeight="1">
@@ -6556,7 +6556,7 @@
         <v>404</v>
       </c>
       <c r="B121" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C121" s="31" t="s">
         <v>405</v>
@@ -6577,10 +6577,10 @@
         <v>406</v>
       </c>
       <c r="I121" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J121" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="122" ht="15.75" customHeight="1">
@@ -6588,7 +6588,7 @@
         <v>407</v>
       </c>
       <c r="B122" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C122" s="31" t="s">
         <v>408</v>
@@ -6597,7 +6597,7 @@
         <v>50</v>
       </c>
       <c r="E122" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F122" s="30">
         <v>3.0</v>
@@ -6609,10 +6609,10 @@
         <v>409</v>
       </c>
       <c r="I122" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J122" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123" ht="15.75" customHeight="1">
@@ -6620,7 +6620,7 @@
         <v>410</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C123" s="11" t="s">
         <v>411</v>
@@ -6636,16 +6636,16 @@
       </c>
       <c r="G123" s="26">
         <f>SUM(G124:G127)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H123" s="11" t="s">
         <v>412</v>
       </c>
       <c r="I123" s="28" t="s">
-        <v>385</v>
+        <v>28</v>
       </c>
       <c r="J123" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K123" s="24"/>
       <c r="L123" s="24"/>
@@ -6663,93 +6663,99 @@
       <c r="X123" s="24"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="17" t="s">
+      <c r="A124" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="B124" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C124" s="17" t="s">
+      <c r="B124" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C124" s="20" t="s">
         <v>414</v>
       </c>
-      <c r="D124" s="19" t="s">
+      <c r="D124" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E124" s="20" t="s">
+      <c r="E124" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F124" s="22">
+      <c r="F124" s="23">
         <v>2.0</v>
       </c>
-      <c r="G124" s="22"/>
-      <c r="H124" s="17" t="s">
+      <c r="G124" s="30">
+        <v>1.0</v>
+      </c>
+      <c r="H124" s="20" t="s">
         <v>415</v>
       </c>
       <c r="I124" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J124" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J124" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="17" t="s">
+      <c r="A125" s="20" t="s">
         <v>416</v>
       </c>
-      <c r="B125" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C125" s="17" t="s">
+      <c r="B125" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" s="20" t="s">
         <v>417</v>
       </c>
-      <c r="D125" s="19" t="s">
+      <c r="D125" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E125" s="20" t="s">
+      <c r="E125" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F125" s="22">
+      <c r="F125" s="23">
         <v>2.0</v>
       </c>
-      <c r="G125" s="22"/>
-      <c r="H125" s="17" t="s">
+      <c r="G125" s="30">
+        <v>1.0</v>
+      </c>
+      <c r="H125" s="20" t="s">
         <v>418</v>
       </c>
       <c r="I125" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J125" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J125" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="17" t="s">
+      <c r="A126" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="B126" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C126" s="17" t="s">
+      <c r="B126" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C126" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="D126" s="19" t="s">
+      <c r="D126" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E126" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F126" s="22">
+      <c r="E126" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F126" s="23">
         <v>10.0</v>
       </c>
-      <c r="G126" s="25"/>
+      <c r="G126" s="33">
+        <v>6.0</v>
+      </c>
       <c r="H126" s="31" t="s">
         <v>421</v>
       </c>
       <c r="I126" s="32" t="s">
-        <v>26</v>
-      </c>
-      <c r="J126" s="17" t="s">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="J126" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="127" ht="15.75" customHeight="1">
@@ -6757,7 +6763,7 @@
         <v>422</v>
       </c>
       <c r="B127" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C127" s="31" t="s">
         <v>423</v>
@@ -6771,15 +6777,17 @@
       <c r="F127" s="30">
         <v>2.0</v>
       </c>
-      <c r="G127" s="25"/>
+      <c r="G127" s="33">
+        <v>1.0</v>
+      </c>
       <c r="H127" s="31" t="s">
         <v>424</v>
       </c>
       <c r="I127" s="32" t="s">
-        <v>385</v>
+        <v>28</v>
       </c>
       <c r="J127" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="128" ht="15.75" customHeight="1">
@@ -6787,7 +6795,7 @@
         <v>425</v>
       </c>
       <c r="B128" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C128" s="31" t="s">
         <v>426</v>
@@ -6801,15 +6809,17 @@
       <c r="F128" s="30">
         <v>2.0</v>
       </c>
-      <c r="G128" s="25"/>
+      <c r="G128" s="33">
+        <v>1.0</v>
+      </c>
       <c r="H128" s="31" t="s">
         <v>427</v>
       </c>
       <c r="I128" s="32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J128" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" ht="15.75" customHeight="1">
@@ -6817,7 +6827,7 @@
         <v>428</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C129" s="11" t="s">
         <v>429</v>
@@ -6826,13 +6836,13 @@
         <v>126</v>
       </c>
       <c r="E129" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F129" s="14">
+        <v>24</v>
+      </c>
+      <c r="F129" s="15">
         <f t="shared" ref="F129:G129" si="24">SUM(F130:F133)</f>
         <v>8</v>
       </c>
-      <c r="G129" s="14">
+      <c r="G129" s="15">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
@@ -6843,7 +6853,7 @@
         <v>431</v>
       </c>
       <c r="J129" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K129" s="24"/>
       <c r="L129" s="24"/>
@@ -6861,93 +6871,93 @@
       <c r="X129" s="24"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="17" t="s">
+      <c r="A130" s="20" t="s">
         <v>432</v>
       </c>
-      <c r="B130" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C130" s="17" t="s">
+      <c r="B130" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C130" s="20" t="s">
         <v>433</v>
       </c>
-      <c r="D130" s="19" t="s">
+      <c r="D130" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E130" s="20" t="s">
-        <v>22</v>
+      <c r="E130" s="22" t="s">
+        <v>24</v>
       </c>
       <c r="F130" s="30">
         <v>2.0</v>
       </c>
-      <c r="G130" s="22"/>
-      <c r="H130" s="17" t="s">
+      <c r="G130" s="23"/>
+      <c r="H130" s="20" t="s">
         <v>434</v>
       </c>
-      <c r="I130" s="20" t="s">
+      <c r="I130" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J130" s="17" t="s">
-        <v>27</v>
+      <c r="J130" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="17" t="s">
+      <c r="A131" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="B131" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C131" s="17" t="s">
+      <c r="B131" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C131" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="D131" s="19" t="s">
+      <c r="D131" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E131" s="20" t="s">
-        <v>22</v>
+      <c r="E131" s="22" t="s">
+        <v>24</v>
       </c>
       <c r="F131" s="30">
         <v>2.0</v>
       </c>
-      <c r="G131" s="22"/>
-      <c r="H131" s="17" t="s">
+      <c r="G131" s="23"/>
+      <c r="H131" s="20" t="s">
         <v>437</v>
       </c>
-      <c r="I131" s="20" t="s">
+      <c r="I131" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J131" s="17" t="s">
-        <v>27</v>
+      <c r="J131" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="17" t="s">
+      <c r="A132" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B132" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C132" s="17" t="s">
+      <c r="B132" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C132" s="20" t="s">
         <v>439</v>
       </c>
-      <c r="D132" s="19" t="s">
+      <c r="D132" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E132" s="20" t="s">
-        <v>22</v>
+      <c r="E132" s="22" t="s">
+        <v>24</v>
       </c>
       <c r="F132" s="30">
         <v>2.0</v>
       </c>
-      <c r="G132" s="22"/>
-      <c r="H132" s="17" t="s">
+      <c r="G132" s="23"/>
+      <c r="H132" s="20" t="s">
         <v>440</v>
       </c>
-      <c r="I132" s="20" t="s">
+      <c r="I132" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J132" s="17" t="s">
-        <v>27</v>
+      <c r="J132" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="133" ht="15.75" customHeight="1">
@@ -6955,21 +6965,21 @@
         <v>441</v>
       </c>
       <c r="B133" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C133" s="31" t="s">
         <v>442</v>
       </c>
       <c r="D133" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E133" s="32" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F133" s="30">
         <v>2.0</v>
       </c>
-      <c r="G133" s="22"/>
+      <c r="G133" s="23"/>
       <c r="H133" s="31" t="s">
         <v>443</v>
       </c>
@@ -6977,7 +6987,7 @@
         <v>431</v>
       </c>
       <c r="J133" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" ht="15.75" customHeight="1">
@@ -6985,7 +6995,7 @@
         <v>444</v>
       </c>
       <c r="B134" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C134" s="11" t="s">
         <v>445</v>
@@ -6999,7 +7009,7 @@
       <c r="F134" s="27">
         <v>14.0</v>
       </c>
-      <c r="G134" s="14">
+      <c r="G134" s="15">
         <f>SUM(G135:G138)</f>
         <v>0</v>
       </c>
@@ -7010,7 +7020,7 @@
         <v>431</v>
       </c>
       <c r="J134" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K134" s="24"/>
       <c r="L134" s="24"/>
@@ -7028,123 +7038,123 @@
       <c r="X134" s="24"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="17" t="s">
+      <c r="A135" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="B135" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C135" s="17" t="s">
+      <c r="B135" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C135" s="20" t="s">
         <v>448</v>
       </c>
-      <c r="D135" s="19" t="s">
+      <c r="D135" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E135" s="20" t="s">
+      <c r="E135" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F135" s="22">
+      <c r="F135" s="23">
         <v>3.0</v>
       </c>
-      <c r="G135" s="22"/>
-      <c r="H135" s="17" t="s">
+      <c r="G135" s="23"/>
+      <c r="H135" s="20" t="s">
         <v>449</v>
       </c>
-      <c r="I135" s="20" t="s">
+      <c r="I135" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J135" s="17" t="s">
-        <v>27</v>
+      <c r="J135" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="17" t="s">
+      <c r="A136" s="20" t="s">
         <v>450</v>
       </c>
-      <c r="B136" s="17" t="s">
-        <v>37</v>
+      <c r="B136" s="20" t="s">
+        <v>41</v>
       </c>
       <c r="C136" s="31" t="s">
         <v>451</v>
       </c>
-      <c r="D136" s="19" t="s">
+      <c r="D136" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="E136" s="20" t="s">
+      <c r="E136" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F136" s="22">
+      <c r="F136" s="23">
         <v>3.0</v>
       </c>
-      <c r="G136" s="22"/>
-      <c r="H136" s="17" t="s">
+      <c r="G136" s="23"/>
+      <c r="H136" s="20" t="s">
         <v>452</v>
       </c>
-      <c r="I136" s="20" t="s">
+      <c r="I136" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J136" s="17" t="s">
-        <v>27</v>
+      <c r="J136" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="17" t="s">
+      <c r="A137" s="20" t="s">
         <v>453</v>
       </c>
-      <c r="B137" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C137" s="17" t="s">
+      <c r="B137" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C137" s="20" t="s">
         <v>454</v>
       </c>
-      <c r="D137" s="19" t="s">
+      <c r="D137" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E137" s="20" t="s">
+      <c r="E137" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F137" s="22">
+      <c r="F137" s="23">
         <v>3.0</v>
       </c>
-      <c r="G137" s="22"/>
+      <c r="G137" s="23"/>
       <c r="H137" s="31" t="s">
         <v>455</v>
       </c>
-      <c r="I137" s="20" t="s">
+      <c r="I137" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J137" s="17" t="s">
-        <v>27</v>
+      <c r="J137" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="17" t="s">
+      <c r="A138" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="B138" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C138" s="17" t="s">
+      <c r="B138" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C138" s="20" t="s">
         <v>457</v>
       </c>
-      <c r="D138" s="19" t="s">
+      <c r="D138" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E138" s="20" t="s">
+      <c r="E138" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F138" s="22">
+      <c r="F138" s="23">
         <v>2.0</v>
       </c>
       <c r="G138" s="25"/>
-      <c r="H138" s="17" t="s">
+      <c r="H138" s="20" t="s">
         <v>458</v>
       </c>
-      <c r="I138" s="20" t="s">
+      <c r="I138" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J138" s="17" t="s">
-        <v>27</v>
+      <c r="J138" s="20" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="139" ht="15.75" customHeight="1">
@@ -7152,7 +7162,7 @@
         <v>459</v>
       </c>
       <c r="B139" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C139" s="31" t="s">
         <v>460</v>
@@ -7174,7 +7184,7 @@
         <v>431</v>
       </c>
       <c r="J139" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" ht="15.75" customHeight="1">
@@ -7182,7 +7192,7 @@
         <v>462</v>
       </c>
       <c r="B140" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C140" s="31" t="s">
         <v>463</v>
@@ -7204,7 +7214,7 @@
         <v>431</v>
       </c>
       <c r="J140" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="141" ht="15.75" customHeight="1">
@@ -7212,7 +7222,7 @@
         <v>465</v>
       </c>
       <c r="B141" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C141" s="11" t="s">
         <v>466</v>
@@ -7227,7 +7237,7 @@
         <f t="shared" ref="F141:G141" si="25">SUM(F142:F143)</f>
         <v>4</v>
       </c>
-      <c r="G141" s="14">
+      <c r="G141" s="15">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
@@ -7238,7 +7248,7 @@
         <v>385</v>
       </c>
       <c r="J141" s="11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="142" ht="15.75" customHeight="1">
@@ -7246,7 +7256,7 @@
         <v>468</v>
       </c>
       <c r="B142" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C142" s="31" t="s">
         <v>469</v>
@@ -7268,7 +7278,7 @@
         <v>385</v>
       </c>
       <c r="J142" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="143" ht="15.75" customHeight="1">
@@ -7276,7 +7286,7 @@
         <v>471</v>
       </c>
       <c r="B143" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C143" s="31" t="s">
         <v>472</v>
@@ -7298,7 +7308,7 @@
         <v>431</v>
       </c>
       <c r="J143" s="31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" ht="15.75" customHeight="1">
@@ -7306,7 +7316,7 @@
         <v>474</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C144" s="11" t="s">
         <v>475</v>
@@ -7315,7 +7325,7 @@
         <v>99</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F144" s="26">
         <f t="shared" ref="F144:G144" si="26">F145+F150+F154+F160</f>
@@ -7332,7 +7342,7 @@
         <v>431</v>
       </c>
       <c r="J144" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K144" s="24"/>
       <c r="L144" s="24"/>
@@ -7354,7 +7364,7 @@
         <v>477</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C145" s="11" t="s">
         <v>478</v>
@@ -7363,7 +7373,7 @@
         <v>50</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F145" s="26">
         <f t="shared" ref="F145:G145" si="27">SUM(F146:F148)</f>
@@ -7380,7 +7390,7 @@
         <v>431</v>
       </c>
       <c r="J145" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K145" s="24"/>
       <c r="L145" s="24"/>
@@ -7398,93 +7408,93 @@
       <c r="X145" s="24"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="17" t="s">
+      <c r="A146" s="20" t="s">
         <v>480</v>
       </c>
-      <c r="B146" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C146" s="17" t="s">
+      <c r="B146" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C146" s="20" t="s">
         <v>481</v>
       </c>
-      <c r="D146" s="19" t="s">
+      <c r="D146" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E146" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F146" s="22">
+      <c r="E146" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F146" s="23">
         <v>10.0</v>
       </c>
-      <c r="G146" s="22"/>
+      <c r="G146" s="23"/>
       <c r="H146" s="31" t="s">
         <v>482</v>
       </c>
-      <c r="I146" s="20" t="s">
+      <c r="I146" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J146" s="17" t="s">
-        <v>33</v>
+      <c r="J146" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="17" t="s">
+      <c r="A147" s="20" t="s">
         <v>483</v>
       </c>
-      <c r="B147" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C147" s="17" t="s">
+      <c r="B147" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C147" s="20" t="s">
         <v>484</v>
       </c>
-      <c r="D147" s="19" t="s">
+      <c r="D147" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E147" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F147" s="22">
+      <c r="E147" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F147" s="23">
         <v>10.0</v>
       </c>
-      <c r="G147" s="22"/>
+      <c r="G147" s="23"/>
       <c r="H147" s="31" t="s">
         <v>485</v>
       </c>
-      <c r="I147" s="20" t="s">
+      <c r="I147" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J147" s="17" t="s">
-        <v>33</v>
+      <c r="J147" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="17" t="s">
+      <c r="A148" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="B148" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C148" s="17" t="s">
+      <c r="B148" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C148" s="20" t="s">
         <v>487</v>
       </c>
-      <c r="D148" s="19" t="s">
+      <c r="D148" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E148" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F148" s="22">
+      <c r="E148" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F148" s="23">
         <v>5.0</v>
       </c>
-      <c r="G148" s="22"/>
-      <c r="H148" s="17" t="s">
+      <c r="G148" s="23"/>
+      <c r="H148" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="I148" s="20" t="s">
+      <c r="I148" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J148" s="17" t="s">
-        <v>33</v>
+      <c r="J148" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1">
@@ -7492,7 +7502,7 @@
         <v>489</v>
       </c>
       <c r="B149" s="31" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C149" s="31" t="s">
         <v>490</v>
@@ -7501,10 +7511,10 @@
         <v>99</v>
       </c>
       <c r="E149" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="F149" s="22"/>
-      <c r="G149" s="22"/>
+        <v>24</v>
+      </c>
+      <c r="F149" s="23"/>
+      <c r="G149" s="23"/>
       <c r="H149" s="31" t="s">
         <v>491</v>
       </c>
@@ -7512,7 +7522,7 @@
         <v>431</v>
       </c>
       <c r="J149" s="31" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1">
@@ -7520,7 +7530,7 @@
         <v>492</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C150" s="11" t="s">
         <v>493</v>
@@ -7529,13 +7539,13 @@
         <v>99</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F150" s="14">
+        <v>24</v>
+      </c>
+      <c r="F150" s="15">
         <f t="shared" ref="F150:G150" si="28">SUM(F151:F153)</f>
         <v>12</v>
       </c>
-      <c r="G150" s="14">
+      <c r="G150" s="15">
         <f t="shared" si="28"/>
         <v>0</v>
       </c>
@@ -7546,7 +7556,7 @@
         <v>431</v>
       </c>
       <c r="J150" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K150" s="24"/>
       <c r="L150" s="24"/>
@@ -7564,93 +7574,93 @@
       <c r="X150" s="24"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="17" t="s">
+      <c r="A151" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="B151" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C151" s="17" t="s">
+      <c r="B151" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C151" s="20" t="s">
         <v>496</v>
       </c>
-      <c r="D151" s="19" t="s">
+      <c r="D151" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E151" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F151" s="22">
+      <c r="E151" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F151" s="23">
         <v>4.0</v>
       </c>
-      <c r="G151" s="22"/>
-      <c r="H151" s="17" t="s">
+      <c r="G151" s="23"/>
+      <c r="H151" s="20" t="s">
         <v>497</v>
       </c>
-      <c r="I151" s="20" t="s">
+      <c r="I151" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J151" s="17" t="s">
-        <v>33</v>
+      <c r="J151" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="17" t="s">
+      <c r="A152" s="20" t="s">
         <v>498</v>
       </c>
-      <c r="B152" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C152" s="17" t="s">
+      <c r="B152" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C152" s="20" t="s">
         <v>499</v>
       </c>
-      <c r="D152" s="19" t="s">
+      <c r="D152" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E152" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F152" s="22">
+      <c r="E152" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F152" s="23">
         <v>4.0</v>
       </c>
-      <c r="G152" s="22"/>
-      <c r="H152" s="17" t="s">
+      <c r="G152" s="23"/>
+      <c r="H152" s="20" t="s">
         <v>497</v>
       </c>
-      <c r="I152" s="20" t="s">
+      <c r="I152" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J152" s="17" t="s">
-        <v>33</v>
+      <c r="J152" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="17" t="s">
+      <c r="A153" s="20" t="s">
         <v>500</v>
       </c>
-      <c r="B153" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C153" s="17" t="s">
+      <c r="B153" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C153" s="20" t="s">
         <v>501</v>
       </c>
-      <c r="D153" s="19" t="s">
+      <c r="D153" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E153" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F153" s="22">
+      <c r="E153" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F153" s="23">
         <v>4.0</v>
       </c>
       <c r="G153" s="25"/>
-      <c r="H153" s="17" t="s">
+      <c r="H153" s="20" t="s">
         <v>502</v>
       </c>
-      <c r="I153" s="20" t="s">
+      <c r="I153" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J153" s="17" t="s">
-        <v>33</v>
+      <c r="J153" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="154" ht="15.75" customHeight="1">
@@ -7658,7 +7668,7 @@
         <v>503</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C154" s="11" t="s">
         <v>504</v>
@@ -7667,13 +7677,13 @@
         <v>99</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F154" s="14">
+        <v>24</v>
+      </c>
+      <c r="F154" s="15">
         <f t="shared" ref="F154:G154" si="29">SUM(F155:F159)</f>
         <v>19</v>
       </c>
-      <c r="G154" s="14">
+      <c r="G154" s="15">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
@@ -7684,7 +7694,7 @@
         <v>431</v>
       </c>
       <c r="J154" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K154" s="24"/>
       <c r="L154" s="24"/>
@@ -7702,153 +7712,153 @@
       <c r="X154" s="24"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="17" t="s">
+      <c r="A155" s="20" t="s">
         <v>506</v>
       </c>
-      <c r="B155" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C155" s="17" t="s">
+      <c r="B155" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C155" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="D155" s="19" t="s">
+      <c r="D155" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E155" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F155" s="22">
+      <c r="E155" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F155" s="23">
         <v>4.0</v>
       </c>
-      <c r="G155" s="22"/>
-      <c r="H155" s="17" t="s">
+      <c r="G155" s="23"/>
+      <c r="H155" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="I155" s="20" t="s">
+      <c r="I155" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J155" s="17" t="s">
-        <v>33</v>
+      <c r="J155" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="17" t="s">
+      <c r="A156" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="B156" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C156" s="17" t="s">
+      <c r="B156" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C156" s="20" t="s">
         <v>510</v>
       </c>
-      <c r="D156" s="19" t="s">
+      <c r="D156" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E156" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F156" s="22">
+      <c r="E156" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F156" s="23">
         <v>4.0</v>
       </c>
-      <c r="G156" s="22"/>
-      <c r="H156" s="17" t="s">
+      <c r="G156" s="23"/>
+      <c r="H156" s="20" t="s">
         <v>511</v>
       </c>
-      <c r="I156" s="20" t="s">
+      <c r="I156" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J156" s="17" t="s">
-        <v>33</v>
+      <c r="J156" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="17" t="s">
+      <c r="A157" s="20" t="s">
         <v>512</v>
       </c>
-      <c r="B157" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C157" s="17" t="s">
+      <c r="B157" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C157" s="20" t="s">
         <v>513</v>
       </c>
-      <c r="D157" s="19" t="s">
+      <c r="D157" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E157" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F157" s="22">
+      <c r="E157" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F157" s="23">
         <v>4.0</v>
       </c>
-      <c r="G157" s="22"/>
-      <c r="H157" s="17" t="s">
+      <c r="G157" s="23"/>
+      <c r="H157" s="20" t="s">
         <v>514</v>
       </c>
-      <c r="I157" s="20" t="s">
+      <c r="I157" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J157" s="17" t="s">
-        <v>33</v>
+      <c r="J157" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="17" t="s">
+      <c r="A158" s="20" t="s">
         <v>515</v>
       </c>
-      <c r="B158" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C158" s="17" t="s">
+      <c r="B158" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C158" s="20" t="s">
         <v>516</v>
       </c>
-      <c r="D158" s="19" t="s">
+      <c r="D158" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E158" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F158" s="22">
+      <c r="E158" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F158" s="23">
         <v>4.0</v>
       </c>
       <c r="G158" s="25"/>
       <c r="H158" s="31" t="s">
         <v>517</v>
       </c>
-      <c r="I158" s="20" t="s">
+      <c r="I158" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J158" s="17" t="s">
-        <v>33</v>
+      <c r="J158" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="17" t="s">
+      <c r="A159" s="20" t="s">
         <v>518</v>
       </c>
-      <c r="B159" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C159" s="17" t="s">
+      <c r="B159" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C159" s="20" t="s">
         <v>519</v>
       </c>
-      <c r="D159" s="19" t="s">
+      <c r="D159" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E159" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F159" s="22">
+      <c r="E159" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F159" s="23">
         <v>3.0</v>
       </c>
-      <c r="G159" s="22"/>
-      <c r="H159" s="17" t="s">
+      <c r="G159" s="23"/>
+      <c r="H159" s="20" t="s">
         <v>520</v>
       </c>
-      <c r="I159" s="20" t="s">
+      <c r="I159" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J159" s="17" t="s">
-        <v>33</v>
+      <c r="J159" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="160" ht="15.75" customHeight="1">
@@ -7856,7 +7866,7 @@
         <v>521</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C160" s="11" t="s">
         <v>522</v>
@@ -7865,7 +7875,7 @@
         <v>126</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F160" s="26">
         <f t="shared" ref="F160:G160" si="30">SUM(F161:F162)</f>
@@ -7882,7 +7892,7 @@
         <v>431</v>
       </c>
       <c r="J160" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K160" s="24"/>
       <c r="L160" s="24"/>
@@ -7900,63 +7910,63 @@
       <c r="X160" s="24"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="17" t="s">
+      <c r="A161" s="20" t="s">
         <v>524</v>
       </c>
-      <c r="B161" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C161" s="17" t="s">
+      <c r="B161" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C161" s="20" t="s">
         <v>525</v>
       </c>
-      <c r="D161" s="19" t="s">
+      <c r="D161" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E161" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F161" s="22">
+      <c r="E161" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F161" s="23">
         <v>3.0</v>
       </c>
       <c r="G161" s="25"/>
-      <c r="H161" s="17" t="s">
+      <c r="H161" s="20" t="s">
         <v>526</v>
       </c>
-      <c r="I161" s="20" t="s">
+      <c r="I161" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J161" s="17" t="s">
-        <v>33</v>
+      <c r="J161" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="17" t="s">
+      <c r="A162" s="20" t="s">
         <v>527</v>
       </c>
-      <c r="B162" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C162" s="17" t="s">
+      <c r="B162" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C162" s="20" t="s">
         <v>528</v>
       </c>
-      <c r="D162" s="19" t="s">
+      <c r="D162" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E162" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F162" s="22">
+      <c r="E162" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F162" s="23">
         <v>3.0</v>
       </c>
-      <c r="G162" s="22"/>
-      <c r="H162" s="17" t="s">
+      <c r="G162" s="23"/>
+      <c r="H162" s="20" t="s">
         <v>529</v>
       </c>
-      <c r="I162" s="20" t="s">
+      <c r="I162" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J162" s="17" t="s">
-        <v>33</v>
+      <c r="J162" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="163" ht="15.75" customHeight="1">
@@ -7964,7 +7974,7 @@
         <v>530</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C163" s="11" t="s">
         <v>531</v>
@@ -7973,7 +7983,7 @@
         <v>532</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F163" s="26">
         <f t="shared" ref="F163:G163" si="31">F164+F168+F171+F174</f>
@@ -7990,7 +8000,7 @@
         <v>431</v>
       </c>
       <c r="J163" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K163" s="24"/>
       <c r="L163" s="24"/>
@@ -8012,7 +8022,7 @@
         <v>534</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C164" s="11" t="s">
         <v>535</v>
@@ -8021,13 +8031,13 @@
         <v>99</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="F164" s="14">
+        <v>24</v>
+      </c>
+      <c r="F164" s="15">
         <f t="shared" ref="F164:G164" si="32">SUM(F165:F167)</f>
         <v>12</v>
       </c>
-      <c r="G164" s="14">
+      <c r="G164" s="15">
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
@@ -8038,7 +8048,7 @@
         <v>431</v>
       </c>
       <c r="J164" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K164" s="24"/>
       <c r="L164" s="24"/>
@@ -8056,93 +8066,93 @@
       <c r="X164" s="24"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="17" t="s">
+      <c r="A165" s="20" t="s">
         <v>537</v>
       </c>
-      <c r="B165" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C165" s="17" t="s">
+      <c r="B165" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C165" s="20" t="s">
         <v>538</v>
       </c>
-      <c r="D165" s="19" t="s">
+      <c r="D165" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E165" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F165" s="22">
+      <c r="E165" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F165" s="23">
         <v>4.0</v>
       </c>
-      <c r="G165" s="22"/>
-      <c r="H165" s="17" t="s">
+      <c r="G165" s="23"/>
+      <c r="H165" s="20" t="s">
         <v>539</v>
       </c>
-      <c r="I165" s="20" t="s">
+      <c r="I165" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J165" s="17" t="s">
-        <v>33</v>
+      <c r="J165" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="17" t="s">
+      <c r="A166" s="20" t="s">
         <v>540</v>
       </c>
-      <c r="B166" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C166" s="17" t="s">
+      <c r="B166" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C166" s="20" t="s">
         <v>541</v>
       </c>
-      <c r="D166" s="19" t="s">
+      <c r="D166" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E166" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F166" s="22">
+      <c r="E166" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F166" s="23">
         <v>4.0</v>
       </c>
-      <c r="G166" s="22"/>
-      <c r="H166" s="17" t="s">
+      <c r="G166" s="23"/>
+      <c r="H166" s="20" t="s">
         <v>542</v>
       </c>
-      <c r="I166" s="20" t="s">
+      <c r="I166" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J166" s="17" t="s">
-        <v>33</v>
+      <c r="J166" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="17" t="s">
+      <c r="A167" s="20" t="s">
         <v>543</v>
       </c>
-      <c r="B167" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C167" s="17" t="s">
+      <c r="B167" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C167" s="20" t="s">
         <v>544</v>
       </c>
-      <c r="D167" s="19" t="s">
+      <c r="D167" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="E167" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F167" s="22">
+      <c r="E167" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F167" s="23">
         <v>4.0</v>
       </c>
-      <c r="G167" s="22"/>
-      <c r="H167" s="17" t="s">
+      <c r="G167" s="23"/>
+      <c r="H167" s="20" t="s">
         <v>545</v>
       </c>
-      <c r="I167" s="20" t="s">
+      <c r="I167" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J167" s="17" t="s">
-        <v>33</v>
+      <c r="J167" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
@@ -8150,7 +8160,7 @@
         <v>546</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C168" s="11" t="s">
         <v>547</v>
@@ -8176,7 +8186,7 @@
         <v>431</v>
       </c>
       <c r="J168" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K168" s="24"/>
       <c r="L168" s="24"/>
@@ -8194,82 +8204,82 @@
       <c r="X168" s="24"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="17" t="s">
+      <c r="A169" s="20" t="s">
         <v>549</v>
       </c>
-      <c r="B169" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C169" s="17" t="s">
+      <c r="B169" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C169" s="20" t="s">
         <v>550</v>
       </c>
-      <c r="D169" s="19" t="s">
+      <c r="D169" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E169" s="20" t="s">
+      <c r="E169" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F169" s="22">
+      <c r="F169" s="23">
         <v>5.0</v>
       </c>
       <c r="G169" s="38"/>
-      <c r="H169" s="17" t="s">
+      <c r="H169" s="20" t="s">
         <v>551</v>
       </c>
-      <c r="I169" s="20" t="s">
+      <c r="I169" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J169" s="17" t="s">
-        <v>33</v>
+      <c r="J169" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="17" t="s">
+      <c r="A170" s="20" t="s">
         <v>552</v>
       </c>
-      <c r="B170" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C170" s="17" t="s">
+      <c r="B170" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C170" s="20" t="s">
         <v>553</v>
       </c>
-      <c r="D170" s="19" t="s">
+      <c r="D170" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="E170" s="20" t="s">
+      <c r="E170" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F170" s="22">
+      <c r="F170" s="23">
         <v>3.0</v>
       </c>
       <c r="G170" s="38"/>
-      <c r="H170" s="17" t="s">
+      <c r="H170" s="20" t="s">
         <v>554</v>
       </c>
-      <c r="I170" s="20" t="s">
+      <c r="I170" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J170" s="17" t="s">
-        <v>33</v>
+      <c r="J170" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="17" t="s">
+      <c r="A171" s="20" t="s">
         <v>555</v>
       </c>
-      <c r="B171" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C171" s="17" t="s">
+      <c r="B171" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C171" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="D171" s="19" t="s">
+      <c r="D171" s="21" t="s">
         <v>532</v>
       </c>
-      <c r="E171" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F171" s="22">
+      <c r="E171" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F171" s="23">
         <f t="shared" ref="F171:G171" si="34">SUM(F172:F173)</f>
         <v>8</v>
       </c>
@@ -8277,74 +8287,74 @@
         <f t="shared" si="34"/>
         <v>0</v>
       </c>
-      <c r="H171" s="17" t="s">
+      <c r="H171" s="20" t="s">
         <v>557</v>
       </c>
-      <c r="I171" s="20" t="s">
+      <c r="I171" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J171" s="17" t="s">
-        <v>33</v>
+      <c r="J171" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="17" t="s">
+      <c r="A172" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="B172" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C172" s="17" t="s">
+      <c r="B172" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C172" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="D172" s="19" t="s">
+      <c r="D172" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="E172" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F172" s="22">
+      <c r="E172" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F172" s="23">
         <v>4.0</v>
       </c>
       <c r="G172" s="38"/>
-      <c r="H172" s="17" t="s">
+      <c r="H172" s="20" t="s">
         <v>560</v>
       </c>
-      <c r="I172" s="20" t="s">
+      <c r="I172" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J172" s="17" t="s">
-        <v>33</v>
+      <c r="J172" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="17" t="s">
+      <c r="A173" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="B173" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C173" s="17" t="s">
+      <c r="B173" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C173" s="20" t="s">
         <v>562</v>
       </c>
-      <c r="D173" s="19" t="s">
+      <c r="D173" s="21" t="s">
         <v>563</v>
       </c>
-      <c r="E173" s="20" t="s">
+      <c r="E173" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F173" s="22">
+      <c r="F173" s="23">
         <v>4.0</v>
       </c>
       <c r="G173" s="38"/>
-      <c r="H173" s="17" t="s">
+      <c r="H173" s="20" t="s">
         <v>564</v>
       </c>
-      <c r="I173" s="20" t="s">
+      <c r="I173" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J173" s="17" t="s">
-        <v>33</v>
+      <c r="J173" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
@@ -8352,7 +8362,7 @@
         <v>565</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C174" s="11" t="s">
         <v>566</v>
@@ -8361,7 +8371,7 @@
         <v>59</v>
       </c>
       <c r="E174" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F174" s="26">
         <f t="shared" ref="F174:G174" si="35">SUM(F175:F178)</f>
@@ -8378,7 +8388,7 @@
         <v>431</v>
       </c>
       <c r="J174" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K174" s="24"/>
       <c r="L174" s="24"/>
@@ -8396,123 +8406,123 @@
       <c r="X174" s="24"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="17" t="s">
+      <c r="A175" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="B175" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C175" s="17" t="s">
+      <c r="B175" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C175" s="20" t="s">
         <v>569</v>
       </c>
-      <c r="D175" s="19" t="s">
+      <c r="D175" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E175" s="20" t="s">
+      <c r="E175" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="F175" s="22">
+      <c r="F175" s="23">
         <v>3.0</v>
       </c>
       <c r="G175" s="38"/>
-      <c r="H175" s="17" t="s">
+      <c r="H175" s="20" t="s">
         <v>570</v>
       </c>
-      <c r="I175" s="20" t="s">
+      <c r="I175" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J175" s="17" t="s">
-        <v>33</v>
+      <c r="J175" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="17" t="s">
+      <c r="A176" s="20" t="s">
         <v>571</v>
       </c>
-      <c r="B176" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C176" s="17" t="s">
+      <c r="B176" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C176" s="20" t="s">
         <v>572</v>
       </c>
-      <c r="D176" s="19" t="s">
+      <c r="D176" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E176" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F176" s="22">
+      <c r="E176" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F176" s="23">
         <v>4.0</v>
       </c>
       <c r="G176" s="38"/>
-      <c r="H176" s="17" t="s">
+      <c r="H176" s="20" t="s">
         <v>573</v>
       </c>
-      <c r="I176" s="20" t="s">
+      <c r="I176" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J176" s="17" t="s">
-        <v>33</v>
+      <c r="J176" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="17" t="s">
+      <c r="A177" s="20" t="s">
         <v>574</v>
       </c>
-      <c r="B177" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C177" s="17" t="s">
+      <c r="B177" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C177" s="20" t="s">
         <v>575</v>
       </c>
-      <c r="D177" s="19" t="s">
+      <c r="D177" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E177" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F177" s="22">
+      <c r="E177" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F177" s="23">
         <v>5.0</v>
       </c>
       <c r="G177" s="38"/>
-      <c r="H177" s="17" t="s">
+      <c r="H177" s="20" t="s">
         <v>576</v>
       </c>
-      <c r="I177" s="20" t="s">
+      <c r="I177" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J177" s="17" t="s">
-        <v>33</v>
+      <c r="J177" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="17" t="s">
+      <c r="A178" s="20" t="s">
         <v>577</v>
       </c>
-      <c r="B178" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="C178" s="17" t="s">
+      <c r="B178" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C178" s="20" t="s">
         <v>578</v>
       </c>
-      <c r="D178" s="19" t="s">
+      <c r="D178" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E178" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="F178" s="22">
+      <c r="E178" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F178" s="23">
         <v>20.0</v>
       </c>
       <c r="G178" s="38"/>
-      <c r="H178" s="17" t="s">
+      <c r="H178" s="20" t="s">
         <v>579</v>
       </c>
-      <c r="I178" s="20" t="s">
+      <c r="I178" s="22" t="s">
         <v>431</v>
       </c>
-      <c r="J178" s="17" t="s">
-        <v>33</v>
+      <c r="J178" s="20" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -11117,100 +11127,100 @@
       <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>74</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="8">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>73</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="8">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A2)</f>
         <v>20</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="8">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A2,Backlog!I:I,"Realizado")</f>
         <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4">
         <v>46297.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D3" s="3">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>74</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="8">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>77</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="8">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A3)</f>
         <v>43</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A3,Backlog!I:I,"Realizado")</f>
         <v>43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="15">
+        <v>25</v>
+      </c>
+      <c r="B4" s="14">
         <v>46325.0</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
         <v>115</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
-        <v>57</v>
-      </c>
-      <c r="F4" s="10">
+        <v>67</v>
+      </c>
+      <c r="F4" s="8">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A4)</f>
         <v>47</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A4,Backlog!I:I,"Realizado")</f>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B5" s="4">
         <v>46360.0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="7">
+        <v>30</v>
+      </c>
+      <c r="D5" s="6">
         <f>SUMIFS(Backlog!F:F,Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
         <v>122</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <f>SUMIFS(Backlog!G:G,Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="8">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A5)</f>
         <v>25</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <f>COUNTIFS(Backlog!B:B,"Tarea",Backlog!J:J,A5,Backlog!I:I,"Realizado")</f>
         <v>0</v>
       </c>
@@ -11223,19 +11233,19 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="21">
+      <c r="A8" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="18">
         <f>SUM(D2:D5)</f>
         <v>385</v>
       </c>
@@ -11243,32 +11253,32 @@
       <c r="D8" s="16"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B9" s="21">
+      <c r="A9" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="18">
         <f>SUM(E2:E5)</f>
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="8">
         <f>SUM(F2:F5)</f>
         <v>135</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="8">
         <f>SUM(G2:G5)</f>
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
